--- a/youzi/湖州劳动路/index.xlsx
+++ b/youzi/湖州劳动路/index.xlsx
@@ -45,6 +45,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -75,36 +93,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD02F3E"/>
         <bgColor/>
       </patternFill>
@@ -117,6 +105,66 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -177,18 +225,600 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEB8D96"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4553"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8BCF9B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8BCF9B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -207,91 +837,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CFD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -303,79 +945,1555 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4CB564"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8336"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA6DAB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -387,37 +2505,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -429,73 +2523,211 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF83CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77782"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -507,25 +2739,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -537,49 +2775,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -627,163 +2913,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BCF9B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4553"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AFB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -795,1675 +3027,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEC929B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BCF9B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8336"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CFD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4CB564"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA6DAB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
+        <fgColor rgb="FFB62431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2475,583 +3051,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF83CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77782"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AFB5"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8474,7 +8474,7 @@
       <c r="C2" t="str">
         <v>002105</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="5" t="str">
         <v>净卖: -286.93万</v>
       </c>
       <c r="E2">
@@ -8489,40 +8489,40 @@
       <c r="H2">
         <v>3.63</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>6.13</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="11">
         <v>16.75</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="2">
         <v>28.37</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="3">
         <v>41.25</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="6">
         <v>55.38</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="7">
         <v>46.12</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="12">
         <v>46.75</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="9">
         <v>33.13</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="13">
         <v>34.87</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="1">
         <v>21.38</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="8">
         <v>11.62</v>
       </c>
-      <c r="T2" s="11">
+      <c r="T2" s="4">
         <v>-21</v>
       </c>
     </row>
@@ -8536,7 +8536,7 @@
       <c r="C3" t="str">
         <v>002760</v>
       </c>
-      <c r="D3" s="24" t="str">
+      <c r="D3" s="15" t="str">
         <v>净买: 1264.22万</v>
       </c>
       <c r="E3">
@@ -8551,40 +8551,40 @@
       <c r="H3">
         <v>3.43</v>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="25">
         <v>6.36</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="14">
         <v>2.8</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="26">
         <v>-6.84</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="22">
         <v>-13.76</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="16">
         <v>-13.72</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="17">
         <v>-14.84</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="23">
         <v>-15.92</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="18">
         <v>-16.68</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="19">
         <v>-19.6</v>
       </c>
-      <c r="R3" s="16">
+      <c r="R3" s="24">
         <v>-22.72</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="20">
         <v>-23.88</v>
       </c>
-      <c r="T3" s="23">
+      <c r="T3" s="21">
         <v>-12.4</v>
       </c>
     </row>
@@ -8598,7 +8598,7 @@
       <c r="C4" t="str">
         <v>002760</v>
       </c>
-      <c r="D4" s="28" t="str">
+      <c r="D4" s="32" t="str">
         <v>净卖: -1488.32万</v>
       </c>
       <c r="E4">
@@ -8613,40 +8613,40 @@
       <c r="H4">
         <v>4.59</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="37">
         <v>-7.59</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="28">
         <v>-16.25</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="38">
         <v>-22.47</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="35">
         <v>-22.44</v>
       </c>
-      <c r="M4" s="37">
+      <c r="M4" s="36">
         <v>-23.44</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="39">
         <v>-24.42</v>
       </c>
       <c r="O4" s="33">
         <v>-25.1</v>
       </c>
-      <c r="P4" s="38">
+      <c r="P4" s="29">
         <v>-27.72</v>
       </c>
-      <c r="Q4" s="31">
+      <c r="Q4" s="30">
         <v>-30.53</v>
       </c>
-      <c r="R4" s="39">
+      <c r="R4" s="27">
         <v>-31.57</v>
       </c>
       <c r="S4" s="34">
         <v>-31.07</v>
       </c>
-      <c r="T4" s="27">
+      <c r="T4" s="31">
         <v>-21.25</v>
       </c>
     </row>
@@ -8660,7 +8660,7 @@
       <c r="C5" t="str">
         <v>603958</v>
       </c>
-      <c r="D5" s="44" t="str">
+      <c r="D5" s="50" t="str">
         <v>净买: 2814.34万</v>
       </c>
       <c r="E5">
@@ -8675,40 +8675,40 @@
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5" s="48">
+      <c r="I5" s="51">
         <v>-3.71</v>
       </c>
-      <c r="J5" s="51">
+      <c r="J5" s="52">
         <v>-13.32</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="46">
         <v>-18.35</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="40">
         <v>-15.42</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="42">
         <v>-11.81</v>
       </c>
-      <c r="N5" s="40">
+      <c r="N5" s="47">
         <v>-11.27</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="48">
         <v>-11.13</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="41">
         <v>-13.08</v>
       </c>
-      <c r="Q5" s="42">
+      <c r="Q5" s="45">
         <v>-16.15</v>
       </c>
-      <c r="R5" s="47">
+      <c r="R5" s="43">
         <v>-17.72</v>
       </c>
-      <c r="S5" s="43">
+      <c r="S5" s="44">
         <v>-18.79</v>
       </c>
-      <c r="T5" s="50">
+      <c r="T5" s="49">
         <v>24.11</v>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
       <c r="C6" t="str">
         <v>603958</v>
       </c>
-      <c r="D6" s="65" t="str">
+      <c r="D6" s="53" t="str">
         <v>净卖: -2283.55万</v>
       </c>
       <c r="E6">
@@ -8737,37 +8737,37 @@
       <c r="H6">
         <v>-6.13</v>
       </c>
-      <c r="I6" s="61">
+      <c r="I6" s="62">
         <v>-4.1</v>
       </c>
-      <c r="J6" s="62">
+      <c r="J6" s="63">
         <v>-9.67</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="54">
         <v>-6.43</v>
       </c>
-      <c r="L6" s="63">
+      <c r="L6" s="55">
         <v>-2.43</v>
       </c>
-      <c r="M6" s="57">
+      <c r="M6" s="56">
         <v>-1.84</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="57">
         <v>-1.67</v>
       </c>
-      <c r="O6" s="55">
+      <c r="O6" s="64">
         <v>-3.83</v>
       </c>
-      <c r="P6" s="64">
+      <c r="P6" s="58">
         <v>-7.24</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="59">
         <v>-8.96</v>
       </c>
-      <c r="R6" s="56">
+      <c r="R6" s="65">
         <v>-10.15</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="61">
         <v>-9.99</v>
       </c>
       <c r="T6" s="60">
@@ -8784,7 +8784,7 @@
       <c r="C7" t="str">
         <v>002645</v>
       </c>
-      <c r="D7" s="78" t="str">
+      <c r="D7" s="75" t="str">
         <v>净买: 1223.21万</v>
       </c>
       <c r="E7">
@@ -8799,40 +8799,40 @@
       <c r="H7">
         <v>1.72</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="71">
         <v>8.14</v>
       </c>
-      <c r="J7" s="72">
+      <c r="J7" s="68">
         <v>5.31</v>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="78">
         <v>9.04</v>
       </c>
-      <c r="L7" s="73">
+      <c r="L7" s="72">
         <v>4.75</v>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="76">
         <v>3.5</v>
       </c>
-      <c r="N7" s="74">
+      <c r="N7" s="73">
         <v>-6.89</v>
       </c>
-      <c r="O7" s="68">
+      <c r="O7" s="66">
         <v>-5.42</v>
       </c>
-      <c r="P7" s="75">
+      <c r="P7" s="67">
         <v>-7.12</v>
       </c>
-      <c r="Q7" s="71">
+      <c r="Q7" s="69">
         <v>-7.23</v>
       </c>
-      <c r="R7" s="76">
+      <c r="R7" s="77">
         <v>-10.73</v>
       </c>
-      <c r="S7" s="69">
+      <c r="S7" s="74">
         <v>-9.94</v>
       </c>
-      <c r="T7" s="77">
+      <c r="T7" s="70">
         <v>152.09</v>
       </c>
     </row>
@@ -8846,7 +8846,7 @@
       <c r="C8" t="str">
         <v>600537</v>
       </c>
-      <c r="D8" s="83" t="str">
+      <c r="D8" s="80" t="str">
         <v>净买: 358.47万</v>
       </c>
       <c r="E8">
@@ -8861,40 +8861,40 @@
       <c r="H8">
         <v>5.03</v>
       </c>
-      <c r="I8" s="84">
+      <c r="I8" s="87">
         <v>4.79</v>
       </c>
-      <c r="J8" s="85">
+      <c r="J8" s="88">
         <v>8.98</v>
       </c>
-      <c r="K8" s="86">
+      <c r="K8" s="90">
         <v>-1.8</v>
       </c>
-      <c r="L8" s="88">
+      <c r="L8" s="84">
         <v>8.08</v>
       </c>
-      <c r="M8" s="87">
+      <c r="M8" s="81">
         <v>18.86</v>
       </c>
-      <c r="N8" s="79">
+      <c r="N8" s="82">
         <v>19.76</v>
       </c>
-      <c r="O8" s="80">
+      <c r="O8" s="85">
         <v>19.16</v>
       </c>
-      <c r="P8" s="81">
+      <c r="P8" s="83">
         <v>15.57</v>
       </c>
-      <c r="Q8" s="89">
+      <c r="Q8" s="91">
         <v>8.38</v>
       </c>
-      <c r="R8" s="90">
+      <c r="R8" s="86">
         <v>4.49</v>
       </c>
-      <c r="S8" s="91">
+      <c r="S8" s="89">
         <v>14.97</v>
       </c>
-      <c r="T8" s="82">
+      <c r="T8" s="79">
         <v>20.36</v>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
       <c r="C9" t="str">
         <v>603122</v>
       </c>
-      <c r="D9" s="97" t="str">
+      <c r="D9" s="98" t="str">
         <v>净卖: -557.16万</v>
       </c>
       <c r="E9">
@@ -8926,37 +8926,37 @@
       <c r="I9" s="103">
         <v>2.8</v>
       </c>
-      <c r="J9" s="98">
+      <c r="J9" s="99">
         <v>13.09</v>
       </c>
-      <c r="K9" s="94">
+      <c r="K9" s="104">
         <v>24.4</v>
       </c>
-      <c r="L9" s="95">
+      <c r="L9" s="101">
         <v>36.85</v>
       </c>
-      <c r="M9" s="99">
+      <c r="M9" s="95">
         <v>50.57</v>
       </c>
-      <c r="N9" s="104">
+      <c r="N9" s="96">
         <v>65.69</v>
       </c>
-      <c r="O9" s="100">
+      <c r="O9" s="97">
         <v>82.21</v>
       </c>
-      <c r="P9" s="101">
+      <c r="P9" s="100">
         <v>100.38</v>
       </c>
-      <c r="Q9" s="102">
+      <c r="Q9" s="92">
         <v>110.93</v>
       </c>
-      <c r="R9" s="96">
+      <c r="R9" s="102">
         <v>132.02</v>
       </c>
-      <c r="S9" s="92">
+      <c r="S9" s="93">
         <v>155.27</v>
       </c>
-      <c r="T9" s="93">
+      <c r="T9" s="94">
         <v>105.34</v>
       </c>
     </row>
@@ -8970,7 +8970,7 @@
       <c r="C10" t="str">
         <v>002682</v>
       </c>
-      <c r="D10" s="105" t="str">
+      <c r="D10" s="117" t="str">
         <v>净买: 749.97万</v>
       </c>
       <c r="E10">
@@ -8985,40 +8985,40 @@
       <c r="H10">
         <v>10.02</v>
       </c>
-      <c r="I10" s="109">
+      <c r="I10" s="105">
         <v>0</v>
       </c>
-      <c r="J10" s="112">
+      <c r="J10" s="109">
         <v>10.03</v>
       </c>
       <c r="K10" s="106">
         <v>20.99</v>
       </c>
-      <c r="L10" s="113">
+      <c r="L10" s="110">
         <v>8.95</v>
       </c>
-      <c r="M10" s="110">
+      <c r="M10" s="107">
         <v>-2.01</v>
       </c>
-      <c r="N10" s="115">
+      <c r="N10" s="114">
         <v>-11.73</v>
       </c>
-      <c r="O10" s="111">
+      <c r="O10" s="108">
         <v>-16.05</v>
       </c>
-      <c r="P10" s="116">
+      <c r="P10" s="115">
         <v>-13.73</v>
       </c>
-      <c r="Q10" s="114">
+      <c r="Q10" s="111">
         <v>-17.59</v>
       </c>
-      <c r="R10" s="107">
+      <c r="R10" s="116">
         <v>-17.28</v>
       </c>
-      <c r="S10" s="117">
+      <c r="S10" s="112">
         <v>-14.04</v>
       </c>
-      <c r="T10" s="108">
+      <c r="T10" s="113">
         <v>-8.33</v>
       </c>
     </row>
@@ -9032,7 +9032,7 @@
       <c r="C11" t="str">
         <v>600227</v>
       </c>
-      <c r="D11" s="125" t="str">
+      <c r="D11" s="130" t="str">
         <v>净买: 484.48万</v>
       </c>
       <c r="E11">
@@ -9047,40 +9047,40 @@
       <c r="H11">
         <v>1.56</v>
       </c>
-      <c r="I11" s="126">
+      <c r="I11" s="118">
         <v>8.43</v>
       </c>
-      <c r="J11" s="118">
+      <c r="J11" s="122">
         <v>13.79</v>
       </c>
       <c r="K11" s="119">
         <v>9.2</v>
       </c>
-      <c r="L11" s="122">
+      <c r="L11" s="120">
         <v>7.28</v>
       </c>
-      <c r="M11" s="127">
+      <c r="M11" s="123">
         <v>2.68</v>
       </c>
-      <c r="N11" s="123">
+      <c r="N11" s="121">
         <v>4.6</v>
       </c>
-      <c r="O11" s="120">
+      <c r="O11" s="126">
         <v>0.77</v>
       </c>
-      <c r="P11" s="124">
+      <c r="P11" s="127">
         <v>-4.6</v>
       </c>
       <c r="Q11" s="128">
         <v>-2.68</v>
       </c>
-      <c r="R11" s="129">
+      <c r="R11" s="124">
         <v>-4.6</v>
       </c>
-      <c r="S11" s="121">
+      <c r="S11" s="125">
         <v>-2.68</v>
       </c>
-      <c r="T11" s="130">
+      <c r="T11" s="129">
         <v>32.57</v>
       </c>
     </row>
@@ -9112,34 +9112,34 @@
       <c r="I12" s="134">
         <v>-1.95</v>
       </c>
-      <c r="J12" s="141">
+      <c r="J12" s="135">
         <v>-3.78</v>
       </c>
-      <c r="K12" s="135">
+      <c r="K12" s="136">
         <v>-11.08</v>
       </c>
-      <c r="L12" s="136">
+      <c r="L12" s="137">
         <v>-18.92</v>
       </c>
-      <c r="M12" s="137">
+      <c r="M12" s="138">
         <v>-18.16</v>
       </c>
-      <c r="N12" s="140">
+      <c r="N12" s="131">
         <v>-18.54</v>
       </c>
-      <c r="O12" s="143">
+      <c r="O12" s="139">
         <v>-17.08</v>
       </c>
-      <c r="P12" s="131">
+      <c r="P12" s="141">
         <v>-17.95</v>
       </c>
-      <c r="Q12" s="142">
+      <c r="Q12" s="140">
         <v>-14.43</v>
       </c>
-      <c r="R12" s="138">
+      <c r="R12" s="142">
         <v>-20</v>
       </c>
-      <c r="S12" s="139">
+      <c r="S12" s="143">
         <v>-18.32</v>
       </c>
       <c r="T12" s="132">
@@ -9156,7 +9156,7 @@
       <c r="C13" t="str">
         <v>600493</v>
       </c>
-      <c r="D13" s="146" t="str">
+      <c r="D13" s="151" t="str">
         <v>净买: 999.07万</v>
       </c>
       <c r="E13">
@@ -9174,37 +9174,37 @@
       <c r="I13" s="147">
         <v>8.05</v>
       </c>
-      <c r="J13" s="148">
+      <c r="J13" s="152">
         <v>-0.65</v>
       </c>
-      <c r="K13" s="155">
+      <c r="K13" s="154">
         <v>3.12</v>
       </c>
-      <c r="L13" s="156">
+      <c r="L13" s="155">
         <v>-4.16</v>
       </c>
-      <c r="M13" s="149">
+      <c r="M13" s="156">
         <v>-8.05</v>
       </c>
-      <c r="N13" s="150">
+      <c r="N13" s="144">
         <v>1.17</v>
       </c>
-      <c r="O13" s="151">
+      <c r="O13" s="148">
         <v>-1.3</v>
       </c>
-      <c r="P13" s="152">
+      <c r="P13" s="149">
         <v>-2.47</v>
       </c>
-      <c r="Q13" s="144">
+      <c r="Q13" s="150">
         <v>1.56</v>
       </c>
-      <c r="R13" s="153">
+      <c r="R13" s="145">
         <v>3.77</v>
       </c>
-      <c r="S13" s="145">
+      <c r="S13" s="146">
         <v>4.03</v>
       </c>
-      <c r="T13" s="154">
+      <c r="T13" s="153">
         <v>-3.12</v>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
       <c r="C14" t="str">
         <v>001330</v>
       </c>
-      <c r="D14" s="169" t="str">
+      <c r="D14" s="167" t="str">
         <v>净卖: -4990.62万</v>
       </c>
       <c r="E14">
@@ -9233,40 +9233,40 @@
       <c r="H14">
         <v>1.65</v>
       </c>
-      <c r="I14" s="157">
+      <c r="I14" s="161">
         <v>8.18</v>
       </c>
-      <c r="J14" s="163">
+      <c r="J14" s="164">
         <v>-2.59</v>
       </c>
-      <c r="K14" s="167">
+      <c r="K14" s="162">
         <v>-12.32</v>
       </c>
-      <c r="L14" s="158">
+      <c r="L14" s="168">
         <v>-20.34</v>
       </c>
-      <c r="M14" s="159">
+      <c r="M14" s="169">
         <v>-12.4</v>
       </c>
-      <c r="N14" s="165">
+      <c r="N14" s="163">
         <v>-18.4</v>
       </c>
       <c r="O14" s="160">
         <v>-26.58</v>
       </c>
-      <c r="P14" s="161">
+      <c r="P14" s="157">
         <v>-33.95</v>
       </c>
-      <c r="Q14" s="168">
+      <c r="Q14" s="158">
         <v>-32.82</v>
       </c>
-      <c r="R14" s="166">
+      <c r="R14" s="165">
         <v>-35.66</v>
       </c>
-      <c r="S14" s="164">
+      <c r="S14" s="166">
         <v>-34.76</v>
       </c>
-      <c r="T14" s="162">
+      <c r="T14" s="159">
         <v>-33.31</v>
       </c>
     </row>
@@ -9280,7 +9280,7 @@
       <c r="C15" t="str">
         <v>600865</v>
       </c>
-      <c r="D15" s="179" t="str">
+      <c r="D15" s="172" t="str">
         <v>净买: 4692.22万</v>
       </c>
       <c r="E15">
@@ -9295,40 +9295,40 @@
       <c r="H15">
         <v>10.02</v>
       </c>
-      <c r="I15" s="180">
+      <c r="I15" s="177">
         <v>0</v>
       </c>
-      <c r="J15" s="171">
+      <c r="J15" s="170">
         <v>10.01</v>
       </c>
-      <c r="K15" s="181">
+      <c r="K15" s="173">
         <v>21</v>
       </c>
-      <c r="L15" s="182">
+      <c r="L15" s="174">
         <v>25.24</v>
       </c>
-      <c r="M15" s="178">
+      <c r="M15" s="175">
         <v>32.13</v>
       </c>
-      <c r="N15" s="170">
+      <c r="N15" s="176">
         <v>27.75</v>
       </c>
-      <c r="O15" s="175">
+      <c r="O15" s="178">
         <v>37.2</v>
       </c>
-      <c r="P15" s="172">
+      <c r="P15" s="182">
         <v>50.9</v>
       </c>
-      <c r="Q15" s="176">
+      <c r="Q15" s="179">
         <v>48.33</v>
       </c>
-      <c r="R15" s="173">
+      <c r="R15" s="180">
         <v>33.52</v>
       </c>
-      <c r="S15" s="174">
+      <c r="S15" s="171">
         <v>20.17</v>
       </c>
-      <c r="T15" s="177">
+      <c r="T15" s="181">
         <v>-20.38</v>
       </c>
     </row>
@@ -9357,40 +9357,40 @@
       <c r="H16">
         <v>10.01</v>
       </c>
-      <c r="I16" s="193">
+      <c r="I16" s="186">
         <v>0</v>
       </c>
-      <c r="J16" s="194">
+      <c r="J16" s="187">
         <v>9.99</v>
       </c>
-      <c r="K16" s="186">
+      <c r="K16" s="188">
         <v>13.84</v>
       </c>
-      <c r="L16" s="187">
+      <c r="L16" s="184">
         <v>20.1</v>
       </c>
-      <c r="M16" s="192">
+      <c r="M16" s="193">
         <v>16.12</v>
       </c>
-      <c r="N16" s="195">
+      <c r="N16" s="189">
         <v>24.72</v>
       </c>
       <c r="O16" s="190">
         <v>37.17</v>
       </c>
-      <c r="P16" s="188">
+      <c r="P16" s="191">
         <v>34.83</v>
       </c>
-      <c r="Q16" s="183">
+      <c r="Q16" s="192">
         <v>21.37</v>
       </c>
-      <c r="R16" s="184">
+      <c r="R16" s="194">
         <v>9.23</v>
       </c>
-      <c r="S16" s="189">
+      <c r="S16" s="195">
         <v>3.67</v>
       </c>
-      <c r="T16" s="191">
+      <c r="T16" s="183">
         <v>-27.62</v>
       </c>
     </row>
@@ -9404,7 +9404,7 @@
       <c r="C17" t="str">
         <v>600693</v>
       </c>
-      <c r="D17" s="205" t="str">
+      <c r="D17" s="197" t="str">
         <v>净买: 4205.60万</v>
       </c>
       <c r="E17">
@@ -9419,19 +9419,19 @@
       <c r="H17">
         <v>2.51</v>
       </c>
-      <c r="I17" s="200">
+      <c r="I17" s="201">
         <v>0.41</v>
       </c>
-      <c r="J17" s="202">
+      <c r="J17" s="198">
         <v>-0.58</v>
       </c>
-      <c r="K17" s="197">
+      <c r="K17" s="199">
         <v>9.33</v>
       </c>
-      <c r="L17" s="206">
+      <c r="L17" s="203">
         <v>13.77</v>
       </c>
-      <c r="M17" s="207">
+      <c r="M17" s="204">
         <v>25.15</v>
       </c>
       <c r="N17" s="208">
@@ -9440,19 +9440,19 @@
       <c r="O17" s="196">
         <v>27.65</v>
       </c>
-      <c r="P17" s="198">
+      <c r="P17" s="202">
         <v>15.52</v>
       </c>
-      <c r="Q17" s="199">
+      <c r="Q17" s="205">
         <v>3.97</v>
       </c>
-      <c r="R17" s="203">
+      <c r="R17" s="206">
         <v>3.97</v>
       </c>
-      <c r="S17" s="201">
+      <c r="S17" s="207">
         <v>7.29</v>
       </c>
-      <c r="T17" s="204">
+      <c r="T17" s="200">
         <v>-30.51</v>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       <c r="C18" t="str">
         <v>603023</v>
       </c>
-      <c r="D18" s="221" t="str">
+      <c r="D18" s="212" t="str">
         <v>净买: 2053.34万</v>
       </c>
       <c r="E18">
@@ -9481,40 +9481,40 @@
       <c r="H18">
         <v>-0.38</v>
       </c>
-      <c r="I18" s="211">
+      <c r="I18" s="215">
         <v>10.48</v>
       </c>
-      <c r="J18" s="216">
+      <c r="J18" s="213">
         <v>13.9</v>
       </c>
-      <c r="K18" s="209">
+      <c r="K18" s="216">
         <v>10.1</v>
       </c>
-      <c r="L18" s="212">
+      <c r="L18" s="214">
         <v>5.14</v>
       </c>
-      <c r="M18" s="217">
+      <c r="M18" s="220">
         <v>4.95</v>
       </c>
-      <c r="N18" s="218">
+      <c r="N18" s="221">
         <v>6.29</v>
       </c>
-      <c r="O18" s="210">
+      <c r="O18" s="217">
         <v>0.57</v>
       </c>
-      <c r="P18" s="219">
+      <c r="P18" s="218">
         <v>1.9</v>
       </c>
-      <c r="Q18" s="220">
+      <c r="Q18" s="219">
         <v>-4.19</v>
       </c>
-      <c r="R18" s="213">
+      <c r="R18" s="209">
         <v>-2.48</v>
       </c>
-      <c r="S18" s="214">
+      <c r="S18" s="210">
         <v>7.24</v>
       </c>
-      <c r="T18" s="215">
+      <c r="T18" s="211">
         <v>-14.86</v>
       </c>
     </row>
@@ -9528,7 +9528,7 @@
       <c r="C19" t="str">
         <v>601566</v>
       </c>
-      <c r="D19" s="229" t="str">
+      <c r="D19" s="226" t="str">
         <v>净卖: -2383.06万</v>
       </c>
       <c r="E19">
@@ -9543,40 +9543,40 @@
       <c r="H19">
         <v>3.63</v>
       </c>
-      <c r="I19" s="233">
+      <c r="I19" s="231">
         <v>6.13</v>
       </c>
-      <c r="J19" s="230">
+      <c r="J19" s="227">
         <v>2.75</v>
       </c>
-      <c r="K19" s="231">
+      <c r="K19" s="233">
         <v>-4.06</v>
       </c>
-      <c r="L19" s="222">
+      <c r="L19" s="228">
         <v>-3.37</v>
       </c>
-      <c r="M19" s="223">
+      <c r="M19" s="224">
         <v>-6.81</v>
       </c>
-      <c r="N19" s="226">
+      <c r="N19" s="234">
         <v>-7.5</v>
       </c>
-      <c r="O19" s="232">
+      <c r="O19" s="229">
         <v>-12.5</v>
       </c>
-      <c r="P19" s="224">
+      <c r="P19" s="222">
         <v>-13.88</v>
       </c>
-      <c r="Q19" s="234">
+      <c r="Q19" s="230">
         <v>-18.06</v>
       </c>
       <c r="R19" s="225">
         <v>-17.94</v>
       </c>
-      <c r="S19" s="227">
+      <c r="S19" s="232">
         <v>-16.56</v>
       </c>
-      <c r="T19" s="228">
+      <c r="T19" s="223">
         <v>-33.25</v>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       <c r="C20" t="str">
         <v>600865</v>
       </c>
-      <c r="D20" s="235" t="str">
+      <c r="D20" s="247" t="str">
         <v>净卖: -5744.79万</v>
       </c>
       <c r="E20">
@@ -9605,37 +9605,37 @@
       <c r="H20">
         <v>-5.17</v>
       </c>
-      <c r="I20" s="242">
+      <c r="I20" s="245">
         <v>9.15</v>
       </c>
-      <c r="J20" s="247">
+      <c r="J20" s="243">
         <v>15.15</v>
       </c>
-      <c r="K20" s="236">
+      <c r="K20" s="235">
         <v>11.33</v>
       </c>
-      <c r="L20" s="238">
+      <c r="L20" s="236">
         <v>19.58</v>
       </c>
-      <c r="M20" s="239">
+      <c r="M20" s="237">
         <v>31.52</v>
       </c>
-      <c r="N20" s="240">
+      <c r="N20" s="244">
         <v>29.27</v>
       </c>
-      <c r="O20" s="243">
+      <c r="O20" s="241">
         <v>16.36</v>
       </c>
-      <c r="P20" s="244">
+      <c r="P20" s="238">
         <v>4.73</v>
       </c>
-      <c r="Q20" s="237">
+      <c r="Q20" s="239">
         <v>-0.61</v>
       </c>
-      <c r="R20" s="245">
+      <c r="R20" s="242">
         <v>0.12</v>
       </c>
-      <c r="S20" s="241">
+      <c r="S20" s="240">
         <v>0.12</v>
       </c>
       <c r="T20" s="246">
@@ -9652,7 +9652,7 @@
       <c r="C21" t="str">
         <v>001317</v>
       </c>
-      <c r="D21" s="250" t="str">
+      <c r="D21" s="258" t="str">
         <v>净卖: -1614.69万</v>
       </c>
       <c r="E21">
@@ -9667,40 +9667,40 @@
       <c r="H21">
         <v>-0.39</v>
       </c>
-      <c r="I21" s="258">
+      <c r="I21" s="249">
         <v>3.7</v>
       </c>
-      <c r="J21" s="251">
+      <c r="J21" s="250">
         <v>-1.32</v>
       </c>
       <c r="K21" s="255">
         <v>-4.71</v>
       </c>
-      <c r="L21" s="259">
+      <c r="L21" s="251">
         <v>-6.34</v>
       </c>
-      <c r="M21" s="260">
+      <c r="M21" s="252">
         <v>-4.27</v>
       </c>
-      <c r="N21" s="248">
+      <c r="N21" s="256">
         <v>-2.18</v>
       </c>
-      <c r="O21" s="256">
+      <c r="O21" s="253">
         <v>0.05</v>
       </c>
-      <c r="P21" s="253">
+      <c r="P21" s="260">
         <v>-1.59</v>
       </c>
-      <c r="Q21" s="249">
+      <c r="Q21" s="254">
         <v>-4.68</v>
       </c>
-      <c r="R21" s="252">
+      <c r="R21" s="257">
         <v>-5.25</v>
       </c>
-      <c r="S21" s="254">
+      <c r="S21" s="259">
         <v>-4.79</v>
       </c>
-      <c r="T21" s="257">
+      <c r="T21" s="248">
         <v>-10.84</v>
       </c>
     </row>
@@ -9714,7 +9714,7 @@
       <c r="C22" t="str">
         <v>002792</v>
       </c>
-      <c r="D22" s="267" t="str">
+      <c r="D22" s="264" t="str">
         <v>净买: 6812.35万</v>
       </c>
       <c r="E22">
@@ -9729,40 +9729,40 @@
       <c r="H22">
         <v>4.23</v>
       </c>
-      <c r="I22" s="268">
+      <c r="I22" s="265">
         <v>5.52</v>
       </c>
-      <c r="J22" s="263">
+      <c r="J22" s="273">
         <v>-2.54</v>
       </c>
-      <c r="K22" s="269">
+      <c r="K22" s="266">
         <v>3.61</v>
       </c>
-      <c r="L22" s="261">
+      <c r="L22" s="271">
         <v>13.97</v>
       </c>
-      <c r="M22" s="270">
+      <c r="M22" s="269">
         <v>25.37</v>
       </c>
-      <c r="N22" s="262">
+      <c r="N22" s="267">
         <v>26.81</v>
       </c>
-      <c r="O22" s="271">
+      <c r="O22" s="268">
         <v>18.51</v>
       </c>
       <c r="P22" s="272">
         <v>27.46</v>
       </c>
-      <c r="Q22" s="273">
+      <c r="Q22" s="261">
         <v>36.75</v>
       </c>
-      <c r="R22" s="265">
+      <c r="R22" s="262">
         <v>41.37</v>
       </c>
-      <c r="S22" s="266">
+      <c r="S22" s="263">
         <v>55.52</v>
       </c>
-      <c r="T22" s="264">
+      <c r="T22" s="270">
         <v>52.3</v>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       <c r="C23" t="str">
         <v>603023</v>
       </c>
-      <c r="D23" s="277" t="str">
+      <c r="D23" s="281" t="str">
         <v>净卖: -1105.11万</v>
       </c>
       <c r="E23">
@@ -9791,28 +9791,28 @@
       <c r="H23">
         <v>4.14</v>
       </c>
-      <c r="I23" s="281">
+      <c r="I23" s="285">
         <v>-0.99</v>
       </c>
-      <c r="J23" s="278">
+      <c r="J23" s="276">
         <v>-4.3</v>
       </c>
-      <c r="K23" s="279">
+      <c r="K23" s="277">
         <v>-8.61</v>
       </c>
-      <c r="L23" s="285">
+      <c r="L23" s="286">
         <v>-8.77</v>
       </c>
-      <c r="M23" s="286">
+      <c r="M23" s="274">
         <v>-7.62</v>
       </c>
       <c r="N23" s="282">
         <v>-12.58</v>
       </c>
-      <c r="O23" s="274">
+      <c r="O23" s="278">
         <v>-11.42</v>
       </c>
-      <c r="P23" s="276">
+      <c r="P23" s="279">
         <v>-16.72</v>
       </c>
       <c r="Q23" s="275">
@@ -9838,7 +9838,7 @@
       <c r="C24" t="str">
         <v>600343</v>
       </c>
-      <c r="D24" s="298" t="str">
+      <c r="D24" s="292" t="str">
         <v>净买: 1.33亿</v>
       </c>
       <c r="E24">
@@ -9853,40 +9853,40 @@
       <c r="H24">
         <v>-1.32</v>
       </c>
-      <c r="I24" s="291">
+      <c r="I24" s="288">
         <v>11.47</v>
       </c>
-      <c r="J24" s="292">
+      <c r="J24" s="293">
         <v>15.39</v>
       </c>
-      <c r="K24" s="296">
+      <c r="K24" s="294">
         <v>21.07</v>
       </c>
-      <c r="L24" s="293">
+      <c r="L24" s="295">
         <v>25.17</v>
       </c>
-      <c r="M24" s="288">
+      <c r="M24" s="289">
         <v>30</v>
       </c>
-      <c r="N24" s="294">
+      <c r="N24" s="296">
         <v>30.59</v>
       </c>
       <c r="O24" s="299">
         <v>21.84</v>
       </c>
-      <c r="P24" s="289">
+      <c r="P24" s="297">
         <v>20.93</v>
       </c>
-      <c r="Q24" s="297">
+      <c r="Q24" s="290">
         <v>20.8</v>
       </c>
-      <c r="R24" s="295">
+      <c r="R24" s="298">
         <v>26.21</v>
       </c>
-      <c r="S24" s="287">
+      <c r="S24" s="291">
         <v>23.73</v>
       </c>
-      <c r="T24" s="290">
+      <c r="T24" s="287">
         <v>-4.88</v>
       </c>
     </row>
@@ -9900,7 +9900,7 @@
       <c r="C25" t="str">
         <v>600693</v>
       </c>
-      <c r="D25" s="306" t="str">
+      <c r="D25" s="300" t="str">
         <v>净卖: -8573.84万</v>
       </c>
       <c r="E25">
@@ -9915,40 +9915,40 @@
       <c r="H25">
         <v>0</v>
       </c>
-      <c r="I25" s="302">
+      <c r="I25" s="303">
         <v>-2.52</v>
       </c>
-      <c r="J25" s="312">
+      <c r="J25" s="308">
         <v>2</v>
       </c>
-      <c r="K25" s="307">
+      <c r="K25" s="301">
         <v>-7.69</v>
       </c>
-      <c r="L25" s="308">
+      <c r="L25" s="309">
         <v>-16.92</v>
       </c>
-      <c r="M25" s="300">
+      <c r="M25" s="302">
         <v>-16.92</v>
       </c>
-      <c r="N25" s="303">
+      <c r="N25" s="311">
         <v>-14.27</v>
       </c>
       <c r="O25" s="304">
         <v>-16.64</v>
       </c>
-      <c r="P25" s="309">
+      <c r="P25" s="305">
         <v>-16.6</v>
       </c>
-      <c r="Q25" s="310">
+      <c r="Q25" s="312">
         <v>-11.79</v>
       </c>
-      <c r="R25" s="311">
+      <c r="R25" s="310">
         <v>-8.67</v>
       </c>
-      <c r="S25" s="305">
+      <c r="S25" s="306">
         <v>-2.05</v>
       </c>
-      <c r="T25" s="301">
+      <c r="T25" s="307">
         <v>-44.48</v>
       </c>
     </row>
@@ -9962,7 +9962,7 @@
       <c r="C26" t="str">
         <v>603686</v>
       </c>
-      <c r="D26" s="317" t="str">
+      <c r="D26" s="320" t="str">
         <v>净买: 6401.27万</v>
       </c>
       <c r="E26">
@@ -9977,40 +9977,40 @@
       <c r="H26">
         <v>-1.39</v>
       </c>
-      <c r="I26" s="313">
+      <c r="I26" s="324">
         <v>11.56</v>
       </c>
-      <c r="J26" s="318">
+      <c r="J26" s="317">
         <v>12.1</v>
       </c>
-      <c r="K26" s="323">
+      <c r="K26" s="325">
         <v>23.31</v>
       </c>
-      <c r="L26" s="324">
+      <c r="L26" s="313">
         <v>15.93</v>
       </c>
-      <c r="M26" s="314">
+      <c r="M26" s="323">
         <v>12.77</v>
       </c>
-      <c r="N26" s="315">
+      <c r="N26" s="314">
         <v>13.16</v>
       </c>
-      <c r="O26" s="325">
+      <c r="O26" s="318">
         <v>10.86</v>
       </c>
-      <c r="P26" s="321">
+      <c r="P26" s="319">
         <v>9.14</v>
       </c>
-      <c r="Q26" s="316">
+      <c r="Q26" s="315">
         <v>9.84</v>
       </c>
-      <c r="R26" s="322">
+      <c r="R26" s="321">
         <v>10.82</v>
       </c>
-      <c r="S26" s="319">
+      <c r="S26" s="322">
         <v>-0.23</v>
       </c>
-      <c r="T26" s="320">
+      <c r="T26" s="316">
         <v>-26.28</v>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       <c r="C27" t="str">
         <v>603686</v>
       </c>
-      <c r="D27" s="337" t="str">
+      <c r="D27" s="330" t="str">
         <v>净卖: -6520.61万</v>
       </c>
       <c r="E27">
@@ -10039,40 +10039,40 @@
       <c r="H27">
         <v>5.01</v>
       </c>
-      <c r="I27" s="338">
+      <c r="I27" s="326">
         <v>-4.3</v>
       </c>
-      <c r="J27" s="329">
+      <c r="J27" s="336">
         <v>5.27</v>
       </c>
-      <c r="K27" s="332">
+      <c r="K27" s="331">
         <v>-1.03</v>
       </c>
-      <c r="L27" s="326">
+      <c r="L27" s="337">
         <v>-3.73</v>
       </c>
-      <c r="M27" s="333">
+      <c r="M27" s="332">
         <v>-3.4</v>
       </c>
-      <c r="N27" s="327">
+      <c r="N27" s="333">
         <v>-5.37</v>
       </c>
-      <c r="O27" s="334">
+      <c r="O27" s="328">
         <v>-6.83</v>
       </c>
-      <c r="P27" s="336">
+      <c r="P27" s="329">
         <v>-6.23</v>
       </c>
-      <c r="Q27" s="335">
+      <c r="Q27" s="334">
         <v>-5.4</v>
       </c>
-      <c r="R27" s="330">
+      <c r="R27" s="335">
         <v>-14.83</v>
       </c>
-      <c r="S27" s="331">
+      <c r="S27" s="338">
         <v>-14.37</v>
       </c>
-      <c r="T27" s="328">
+      <c r="T27" s="327">
         <v>-37.07</v>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       <c r="C28" t="str">
         <v>002361</v>
       </c>
-      <c r="D28" s="344" t="str">
+      <c r="D28" s="347" t="str">
         <v>净卖: -5584.65万</v>
       </c>
       <c r="E28">
@@ -10101,40 +10101,40 @@
       <c r="H28">
         <v>-3.59</v>
       </c>
-      <c r="I28" s="345">
+      <c r="I28" s="348">
         <v>-6.66</v>
       </c>
-      <c r="J28" s="350">
+      <c r="J28" s="343">
         <v>2.65</v>
       </c>
-      <c r="K28" s="351">
+      <c r="K28" s="349">
         <v>-1.93</v>
       </c>
-      <c r="L28" s="340">
+      <c r="L28" s="345">
         <v>3.51</v>
       </c>
-      <c r="M28" s="346">
+      <c r="M28" s="341">
         <v>3.15</v>
       </c>
-      <c r="N28" s="347">
+      <c r="N28" s="342">
         <v>13.46</v>
       </c>
-      <c r="O28" s="348">
+      <c r="O28" s="350">
         <v>11.67</v>
       </c>
-      <c r="P28" s="349">
+      <c r="P28" s="344">
         <v>20.26</v>
       </c>
-      <c r="Q28" s="339">
+      <c r="Q28" s="351">
         <v>17.97</v>
       </c>
-      <c r="R28" s="341">
+      <c r="R28" s="339">
         <v>29.71</v>
       </c>
-      <c r="S28" s="342">
+      <c r="S28" s="340">
         <v>16.75</v>
       </c>
-      <c r="T28" s="343">
+      <c r="T28" s="346">
         <v>34.22</v>
       </c>
     </row>
@@ -10148,7 +10148,7 @@
       <c r="C29" t="str">
         <v>001231</v>
       </c>
-      <c r="D29" s="363" t="str">
+      <c r="D29" s="360" t="str">
         <v>净卖: -943.73万</v>
       </c>
       <c r="E29">
@@ -10163,40 +10163,40 @@
       <c r="H29">
         <v>-10.01</v>
       </c>
-      <c r="I29" s="356">
+      <c r="I29" s="364">
         <v>0</v>
       </c>
       <c r="J29" s="353">
         <v>-1.36</v>
       </c>
-      <c r="K29" s="364">
+      <c r="K29" s="354">
         <v>-7.18</v>
       </c>
-      <c r="L29" s="360">
+      <c r="L29" s="357">
         <v>-8.91</v>
       </c>
-      <c r="M29" s="354">
+      <c r="M29" s="358">
         <v>-9.1</v>
       </c>
-      <c r="N29" s="352">
+      <c r="N29" s="355">
         <v>-9.98</v>
       </c>
-      <c r="O29" s="355">
+      <c r="O29" s="356">
         <v>-8.84</v>
       </c>
-      <c r="P29" s="357">
+      <c r="P29" s="352">
         <v>-10.31</v>
       </c>
-      <c r="Q29" s="358">
+      <c r="Q29" s="361">
         <v>-7.96</v>
       </c>
-      <c r="R29" s="361">
+      <c r="R29" s="362">
         <v>-8.8</v>
       </c>
-      <c r="S29" s="362">
+      <c r="S29" s="359">
         <v>-9.28</v>
       </c>
-      <c r="T29" s="359">
+      <c r="T29" s="363">
         <v>-8.18</v>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       <c r="C30" t="str">
         <v>002788</v>
       </c>
-      <c r="D30" s="368" t="str">
+      <c r="D30" s="367" t="str">
         <v>净买: 3825.22万</v>
       </c>
       <c r="E30">
@@ -10228,37 +10228,37 @@
       <c r="I30" s="369">
         <v>3.95</v>
       </c>
-      <c r="J30" s="376">
+      <c r="J30" s="370">
         <v>14.35</v>
       </c>
-      <c r="K30" s="372">
+      <c r="K30" s="373">
         <v>11.56</v>
       </c>
-      <c r="L30" s="373">
+      <c r="L30" s="371">
         <v>13.48</v>
       </c>
-      <c r="M30" s="377">
+      <c r="M30" s="374">
         <v>9.23</v>
       </c>
-      <c r="N30" s="365">
+      <c r="N30" s="372">
         <v>1.08</v>
       </c>
-      <c r="O30" s="374">
+      <c r="O30" s="377">
         <v>-9.03</v>
       </c>
-      <c r="P30" s="370">
+      <c r="P30" s="375">
         <v>-18.14</v>
       </c>
-      <c r="Q30" s="375">
+      <c r="Q30" s="365">
         <v>-26.33</v>
       </c>
-      <c r="R30" s="367">
+      <c r="R30" s="366">
         <v>-30.78</v>
       </c>
-      <c r="S30" s="366">
+      <c r="S30" s="368">
         <v>-32.45</v>
       </c>
-      <c r="T30" s="371">
+      <c r="T30" s="376">
         <v>-37.23</v>
       </c>
     </row>
@@ -10272,7 +10272,7 @@
       <c r="C31" t="str">
         <v>002788</v>
       </c>
-      <c r="D31" s="389" t="str">
+      <c r="D31" s="385" t="str">
         <v>净卖: -24.07万</v>
       </c>
       <c r="E31">
@@ -10287,40 +10287,40 @@
       <c r="H31">
         <v>-0.04</v>
       </c>
-      <c r="I31" s="390">
+      <c r="I31" s="382">
         <v>10.05</v>
       </c>
-      <c r="J31" s="378">
+      <c r="J31" s="390">
         <v>7.37</v>
       </c>
-      <c r="K31" s="380">
+      <c r="K31" s="383">
         <v>9.21</v>
       </c>
-      <c r="L31" s="381">
+      <c r="L31" s="386">
         <v>5.12</v>
       </c>
-      <c r="M31" s="388">
+      <c r="M31" s="378">
         <v>-2.72</v>
       </c>
-      <c r="N31" s="382">
+      <c r="N31" s="379">
         <v>-12.45</v>
       </c>
-      <c r="O31" s="383">
+      <c r="O31" s="387">
         <v>-21.22</v>
       </c>
-      <c r="P31" s="379">
+      <c r="P31" s="388">
         <v>-29.1</v>
       </c>
       <c r="Q31" s="384">
         <v>-33.39</v>
       </c>
-      <c r="R31" s="385">
+      <c r="R31" s="380">
         <v>-34.99</v>
       </c>
-      <c r="S31" s="386">
+      <c r="S31" s="381">
         <v>-32.95</v>
       </c>
-      <c r="T31" s="387">
+      <c r="T31" s="389">
         <v>-39.59</v>
       </c>
     </row>
@@ -10334,7 +10334,7 @@
       <c r="C32" t="str">
         <v>600151</v>
       </c>
-      <c r="D32" s="401" t="str">
+      <c r="D32" s="397" t="str">
         <v>净买: 7884.07万</v>
       </c>
       <c r="E32">
@@ -10349,37 +10349,37 @@
       <c r="H32">
         <v>3.26</v>
       </c>
-      <c r="I32" s="392">
+      <c r="I32" s="398">
         <v>-11.53</v>
       </c>
-      <c r="J32" s="397">
+      <c r="J32" s="402">
         <v>-20.23</v>
       </c>
-      <c r="K32" s="402">
+      <c r="K32" s="392">
         <v>-21.06</v>
       </c>
-      <c r="L32" s="398">
+      <c r="L32" s="393">
         <v>-24.22</v>
       </c>
-      <c r="M32" s="393">
+      <c r="M32" s="396">
         <v>-21.69</v>
       </c>
       <c r="N32" s="399">
         <v>-16.73</v>
       </c>
-      <c r="O32" s="394">
+      <c r="O32" s="403">
         <v>-25.05</v>
       </c>
-      <c r="P32" s="395">
+      <c r="P32" s="394">
         <v>-25.88</v>
       </c>
-      <c r="Q32" s="396">
+      <c r="Q32" s="400">
         <v>-27.43</v>
       </c>
-      <c r="R32" s="400">
+      <c r="R32" s="395">
         <v>-26.65</v>
       </c>
-      <c r="S32" s="403">
+      <c r="S32" s="401">
         <v>-26.61</v>
       </c>
       <c r="T32" s="391">
@@ -10396,7 +10396,7 @@
       <c r="C33" t="str">
         <v>600916</v>
       </c>
-      <c r="D33" s="412" t="str">
+      <c r="D33" s="414" t="str">
         <v>净卖: -1428.23万</v>
       </c>
       <c r="E33">
@@ -10411,40 +10411,40 @@
       <c r="H33">
         <v>10.04</v>
       </c>
-      <c r="I33" s="408">
+      <c r="I33" s="415">
         <v>0</v>
       </c>
-      <c r="J33" s="413">
+      <c r="J33" s="416">
         <v>10.02</v>
       </c>
-      <c r="K33" s="409">
+      <c r="K33" s="404">
         <v>19.64</v>
       </c>
-      <c r="L33" s="414">
+      <c r="L33" s="409">
         <v>7.66</v>
       </c>
-      <c r="M33" s="406">
+      <c r="M33" s="405">
         <v>5.87</v>
       </c>
       <c r="N33" s="410">
         <v>-0.81</v>
       </c>
-      <c r="O33" s="404">
+      <c r="O33" s="411">
         <v>-8.96</v>
       </c>
-      <c r="P33" s="415">
+      <c r="P33" s="406">
         <v>-6.93</v>
       </c>
-      <c r="Q33" s="405">
+      <c r="Q33" s="407">
         <v>-5.79</v>
       </c>
-      <c r="R33" s="416">
+      <c r="R33" s="412">
         <v>-8.96</v>
       </c>
-      <c r="S33" s="411">
+      <c r="S33" s="408">
         <v>-9.54</v>
       </c>
-      <c r="T33" s="407">
+      <c r="T33" s="413">
         <v>-25.84</v>
       </c>
     </row>
@@ -10458,7 +10458,7 @@
       <c r="C34" t="str">
         <v>600969</v>
       </c>
-      <c r="D34" s="422" t="str">
+      <c r="D34" s="424" t="str">
         <v>净卖: -723.23万</v>
       </c>
       <c r="E34">
@@ -10473,40 +10473,40 @@
       <c r="H34">
         <v>0</v>
       </c>
-      <c r="I34" s="429">
+      <c r="I34" s="419">
         <v>-9.99</v>
       </c>
-      <c r="J34" s="417">
+      <c r="J34" s="428">
         <v>-9.99</v>
       </c>
-      <c r="K34" s="423">
+      <c r="K34" s="420">
         <v>-18.98</v>
       </c>
-      <c r="L34" s="424">
+      <c r="L34" s="425">
         <v>-21.07</v>
       </c>
-      <c r="M34" s="418">
+      <c r="M34" s="422">
         <v>-21.98</v>
       </c>
-      <c r="N34" s="419">
+      <c r="N34" s="429">
         <v>-18.98</v>
       </c>
-      <c r="O34" s="420">
+      <c r="O34" s="426">
         <v>-16.9</v>
       </c>
-      <c r="P34" s="425">
+      <c r="P34" s="427">
         <v>-16.82</v>
       </c>
-      <c r="Q34" s="426">
+      <c r="Q34" s="423">
         <v>-14.32</v>
       </c>
-      <c r="R34" s="427">
+      <c r="R34" s="417">
         <v>-13.66</v>
       </c>
-      <c r="S34" s="421">
+      <c r="S34" s="418">
         <v>-15.99</v>
       </c>
-      <c r="T34" s="428">
+      <c r="T34" s="421">
         <v>-18.07</v>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       <c r="C35" t="str">
         <v>002040</v>
       </c>
-      <c r="D35" s="432" t="str">
+      <c r="D35" s="437" t="str">
         <v>净卖: -895.74万</v>
       </c>
       <c r="E35">
@@ -10535,37 +10535,37 @@
       <c r="H35">
         <v>-7.37</v>
       </c>
-      <c r="I35" s="435">
+      <c r="I35" s="438">
         <v>-2.87</v>
       </c>
-      <c r="J35" s="436">
+      <c r="J35" s="430">
         <v>-8.52</v>
       </c>
-      <c r="K35" s="437">
+      <c r="K35" s="432">
         <v>-8.36</v>
       </c>
-      <c r="L35" s="438">
+      <c r="L35" s="433">
         <v>-10.49</v>
       </c>
-      <c r="M35" s="433">
+      <c r="M35" s="439">
         <v>-8.44</v>
       </c>
-      <c r="N35" s="439">
+      <c r="N35" s="435">
         <v>-9.02</v>
       </c>
       <c r="O35" s="440">
         <v>-9.51</v>
       </c>
-      <c r="P35" s="441">
+      <c r="P35" s="434">
         <v>-12.05</v>
       </c>
-      <c r="Q35" s="442">
+      <c r="Q35" s="441">
         <v>-8.28</v>
       </c>
-      <c r="R35" s="434">
+      <c r="R35" s="442">
         <v>-10.33</v>
       </c>
-      <c r="S35" s="430">
+      <c r="S35" s="436">
         <v>-11.07</v>
       </c>
       <c r="T35" s="431">
@@ -10582,7 +10582,7 @@
       <c r="C36" t="str">
         <v>603017</v>
       </c>
-      <c r="D36" s="454" t="str">
+      <c r="D36" s="450" t="str">
         <v>净买: 694.09万</v>
       </c>
       <c r="E36">
@@ -10600,34 +10600,34 @@
       <c r="I36" s="455">
         <v>7.84</v>
       </c>
-      <c r="J36" s="443">
+      <c r="J36" s="445">
         <v>7.04</v>
       </c>
-      <c r="K36" s="444">
+      <c r="K36" s="451">
         <v>6.48</v>
       </c>
-      <c r="L36" s="452">
+      <c r="L36" s="443">
         <v>5.04</v>
       </c>
-      <c r="M36" s="448">
+      <c r="M36" s="444">
         <v>7.28</v>
       </c>
-      <c r="N36" s="449">
+      <c r="N36" s="446">
         <v>5.44</v>
       </c>
-      <c r="O36" s="450">
+      <c r="O36" s="452">
         <v>10.72</v>
       </c>
-      <c r="P36" s="445">
+      <c r="P36" s="453">
         <v>10.32</v>
       </c>
-      <c r="Q36" s="446">
+      <c r="Q36" s="448">
         <v>7.92</v>
       </c>
-      <c r="R36" s="451">
+      <c r="R36" s="449">
         <v>1.28</v>
       </c>
-      <c r="S36" s="453">
+      <c r="S36" s="454">
         <v>11.44</v>
       </c>
       <c r="T36" s="447">
@@ -10644,7 +10644,7 @@
       <c r="C37" t="str">
         <v>600495</v>
       </c>
-      <c r="D37" s="467" t="str">
+      <c r="D37" s="456" t="str">
         <v>净买: 998.97万</v>
       </c>
       <c r="E37">
@@ -10659,40 +10659,40 @@
       <c r="H37">
         <v>0</v>
       </c>
-      <c r="I37" s="468">
+      <c r="I37" s="463">
         <v>10.04</v>
       </c>
-      <c r="J37" s="463">
+      <c r="J37" s="457">
         <v>11.16</v>
       </c>
-      <c r="K37" s="456">
+      <c r="K37" s="465">
         <v>12.28</v>
       </c>
-      <c r="L37" s="464">
+      <c r="L37" s="466">
         <v>2.23</v>
       </c>
-      <c r="M37" s="459">
+      <c r="M37" s="458">
         <v>0.67</v>
       </c>
-      <c r="N37" s="457">
+      <c r="N37" s="459">
         <v>4.46</v>
       </c>
-      <c r="O37" s="458">
+      <c r="O37" s="467">
         <v>0.67</v>
       </c>
-      <c r="P37" s="465">
+      <c r="P37" s="461">
         <v>0.45</v>
       </c>
       <c r="Q37" s="460">
         <v>-1.34</v>
       </c>
-      <c r="R37" s="461">
+      <c r="R37" s="468">
         <v>-1.34</v>
       </c>
       <c r="S37" s="462">
         <v>-2.01</v>
       </c>
-      <c r="T37" s="466">
+      <c r="T37" s="464">
         <v>-2.46</v>
       </c>
     </row>
@@ -10706,7 +10706,7 @@
       <c r="C38" t="str">
         <v>600488</v>
       </c>
-      <c r="D38" s="473" t="str">
+      <c r="D38" s="478" t="str">
         <v>净卖: -1388.23万</v>
       </c>
       <c r="E38">
@@ -10721,40 +10721,40 @@
       <c r="H38">
         <v>9.92</v>
       </c>
-      <c r="I38" s="470">
+      <c r="I38" s="472">
         <v>0</v>
       </c>
-      <c r="J38" s="471">
+      <c r="J38" s="469">
         <v>10.07</v>
       </c>
-      <c r="K38" s="476">
+      <c r="K38" s="473">
         <v>21.01</v>
       </c>
-      <c r="L38" s="480">
+      <c r="L38" s="474">
         <v>33.16</v>
       </c>
-      <c r="M38" s="481">
+      <c r="M38" s="475">
         <v>27.78</v>
       </c>
-      <c r="N38" s="469">
+      <c r="N38" s="476">
         <v>22.92</v>
       </c>
-      <c r="O38" s="477">
+      <c r="O38" s="479">
         <v>11.46</v>
       </c>
-      <c r="P38" s="478">
+      <c r="P38" s="470">
         <v>2.6</v>
       </c>
-      <c r="Q38" s="474">
+      <c r="Q38" s="480">
         <v>7.99</v>
       </c>
-      <c r="R38" s="472">
+      <c r="R38" s="477">
         <v>18.75</v>
       </c>
-      <c r="S38" s="475">
+      <c r="S38" s="471">
         <v>9.2</v>
       </c>
-      <c r="T38" s="479">
+      <c r="T38" s="481">
         <v>5.21</v>
       </c>
     </row>
@@ -10817,40 +10817,40 @@
       <c r="F40" t="str"/>
       <c r="G40" t="str"/>
       <c r="H40" t="str"/>
-      <c r="I40" s="492">
+      <c r="I40" s="493">
         <v>54.05</v>
       </c>
       <c r="J40" s="489">
         <v>62.16</v>
       </c>
-      <c r="K40" s="484">
+      <c r="K40" s="490">
         <v>54.05</v>
       </c>
-      <c r="L40" s="493">
+      <c r="L40" s="491">
         <v>56.76</v>
       </c>
-      <c r="M40" s="485">
+      <c r="M40" s="483">
         <v>51.35</v>
       </c>
-      <c r="N40" s="486">
+      <c r="N40" s="484">
         <v>48.65</v>
       </c>
       <c r="O40" s="482">
         <v>45.95</v>
       </c>
-      <c r="P40" s="487">
+      <c r="P40" s="485">
         <v>40.54</v>
       </c>
-      <c r="Q40" s="488">
+      <c r="Q40" s="487">
         <v>35.14</v>
       </c>
-      <c r="R40" s="483">
+      <c r="R40" s="492">
         <v>37.84</v>
       </c>
-      <c r="S40" s="490">
+      <c r="S40" s="486">
         <v>37.84</v>
       </c>
-      <c r="T40" s="491">
+      <c r="T40" s="488">
         <v>27.03</v>
       </c>
     </row>
@@ -10865,28 +10865,28 @@
       <c r="F41" t="str"/>
       <c r="G41" t="str"/>
       <c r="H41" t="str"/>
-      <c r="I41" s="494">
+      <c r="I41" s="502">
         <v>2.35</v>
       </c>
-      <c r="J41" s="495">
+      <c r="J41" s="498">
         <v>3.37</v>
       </c>
-      <c r="K41" s="496">
+      <c r="K41" s="499">
         <v>3.41</v>
       </c>
-      <c r="L41" s="497">
+      <c r="L41" s="494">
         <v>3.11</v>
       </c>
-      <c r="M41" s="502">
+      <c r="M41" s="500">
         <v>4.56</v>
       </c>
-      <c r="N41" s="498">
+      <c r="N41" s="503">
         <v>3.99</v>
       </c>
-      <c r="O41" s="499">
+      <c r="O41" s="497">
         <v>2.28</v>
       </c>
-      <c r="P41" s="503">
+      <c r="P41" s="495">
         <v>0.79</v>
       </c>
       <c r="Q41" s="504">
@@ -10895,7 +10895,7 @@
       <c r="R41" s="505">
         <v>-0.68</v>
       </c>
-      <c r="S41" s="500">
+      <c r="S41" s="496">
         <v>-0.22</v>
       </c>
       <c r="T41" s="501">

--- a/youzi/湖州劳动路/index.xlsx
+++ b/youzi/湖州劳动路/index.xlsx
@@ -39,25 +39,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFD02F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -87,7 +111,1267 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4553"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8BCF9B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8BCF9B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8336"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF78C88A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4CB564"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CFD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -99,25 +1383,217 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,61 +1605,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -195,19 +1701,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF208838"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -231,97 +1725,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -339,7 +1779,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2DA949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA6DAB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -357,31 +1899,565 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
+        <fgColor rgb="FF92D2A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8136"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -393,79 +2469,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -483,31 +2529,271 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF83CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77782"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95D3A3"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -525,79 +2811,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -627,115 +2919,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -747,1735 +3015,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4553"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BCF9B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BCF9B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CFD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4CB564"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8336"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA6DAB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AFB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E1BF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2487,511 +3045,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF83CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77782"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
+        <fgColor rgb="FFB62431"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3003,67 +3057,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1AFB5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E1BF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8474,7 +8474,7 @@
       <c r="C2" t="str">
         <v>002105</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="9" t="str">
         <v>净卖: -286.93万</v>
       </c>
       <c r="E2">
@@ -8489,40 +8489,40 @@
       <c r="H2">
         <v>3.63</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="1">
         <v>6.13</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="8">
         <v>16.75</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="10">
         <v>28.37</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="2">
         <v>41.25</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="3">
         <v>55.38</v>
       </c>
-      <c r="N2" s="7">
+      <c r="N2" s="4">
         <v>46.12</v>
       </c>
-      <c r="O2" s="12">
+      <c r="O2" s="5">
         <v>46.75</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="11">
         <v>33.13</v>
       </c>
-      <c r="Q2" s="13">
+      <c r="Q2" s="6">
         <v>34.87</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="12">
         <v>21.38</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="7">
         <v>11.62</v>
       </c>
-      <c r="T2" s="4">
+      <c r="T2" s="13">
         <v>-21</v>
       </c>
     </row>
@@ -8536,7 +8536,7 @@
       <c r="C3" t="str">
         <v>002760</v>
       </c>
-      <c r="D3" s="15" t="str">
+      <c r="D3" s="21" t="str">
         <v>净买: 1264.22万</v>
       </c>
       <c r="E3">
@@ -8551,40 +8551,40 @@
       <c r="H3">
         <v>3.43</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="22">
         <v>6.36</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="19">
         <v>2.8</v>
       </c>
       <c r="K3" s="26">
         <v>-6.84</v>
       </c>
-      <c r="L3" s="22">
+      <c r="L3" s="15">
         <v>-13.76</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="23">
         <v>-13.72</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="16">
         <v>-14.84</v>
       </c>
-      <c r="O3" s="23">
+      <c r="O3" s="24">
         <v>-15.92</v>
       </c>
-      <c r="P3" s="18">
+      <c r="P3" s="17">
         <v>-16.68</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="25">
         <v>-19.6</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="14">
         <v>-22.72</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="18">
         <v>-23.88</v>
       </c>
-      <c r="T3" s="21">
+      <c r="T3" s="20">
         <v>-12.4</v>
       </c>
     </row>
@@ -8613,37 +8613,37 @@
       <c r="H4">
         <v>4.59</v>
       </c>
-      <c r="I4" s="37">
+      <c r="I4" s="28">
         <v>-7.59</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="29">
         <v>-16.25</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="33">
         <v>-22.47</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="34">
         <v>-22.44</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="35">
         <v>-23.44</v>
       </c>
       <c r="N4" s="39">
         <v>-24.42</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="36">
         <v>-25.1</v>
       </c>
-      <c r="P4" s="29">
+      <c r="P4" s="37">
         <v>-27.72</v>
       </c>
-      <c r="Q4" s="30">
+      <c r="Q4" s="38">
         <v>-30.53</v>
       </c>
       <c r="R4" s="27">
         <v>-31.57</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="30">
         <v>-31.07</v>
       </c>
       <c r="T4" s="31">
@@ -8660,7 +8660,7 @@
       <c r="C5" t="str">
         <v>603958</v>
       </c>
-      <c r="D5" s="50" t="str">
+      <c r="D5" s="41" t="str">
         <v>净买: 2814.34万</v>
       </c>
       <c r="E5">
@@ -8675,40 +8675,40 @@
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="50">
         <v>-3.71</v>
       </c>
-      <c r="J5" s="52">
+      <c r="J5" s="48">
         <v>-13.32</v>
       </c>
-      <c r="K5" s="46">
+      <c r="K5" s="51">
         <v>-18.35</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="49">
         <v>-15.42</v>
       </c>
-      <c r="M5" s="42">
+      <c r="M5" s="46">
         <v>-11.81</v>
       </c>
-      <c r="N5" s="47">
+      <c r="N5" s="42">
         <v>-11.27</v>
       </c>
-      <c r="O5" s="48">
+      <c r="O5" s="52">
         <v>-11.13</v>
       </c>
-      <c r="P5" s="41">
+      <c r="P5" s="43">
         <v>-13.08</v>
       </c>
-      <c r="Q5" s="45">
+      <c r="Q5" s="44">
         <v>-16.15</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="40">
         <v>-17.72</v>
       </c>
-      <c r="S5" s="44">
+      <c r="S5" s="45">
         <v>-18.79</v>
       </c>
-      <c r="T5" s="49">
+      <c r="T5" s="47">
         <v>24.11</v>
       </c>
     </row>
@@ -8722,7 +8722,7 @@
       <c r="C6" t="str">
         <v>603958</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="58" t="str">
         <v>净卖: -2283.55万</v>
       </c>
       <c r="E6">
@@ -8737,40 +8737,40 @@
       <c r="H6">
         <v>-6.13</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="55">
         <v>-4.1</v>
       </c>
-      <c r="J6" s="63">
+      <c r="J6" s="64">
         <v>-9.67</v>
       </c>
-      <c r="K6" s="54">
+      <c r="K6" s="65">
         <v>-6.43</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="59">
         <v>-2.43</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="53">
         <v>-1.84</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="56">
         <v>-1.67</v>
       </c>
-      <c r="O6" s="64">
+      <c r="O6" s="60">
         <v>-3.83</v>
       </c>
-      <c r="P6" s="58">
+      <c r="P6" s="61">
         <v>-7.24</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="62">
         <v>-8.96</v>
       </c>
-      <c r="R6" s="65">
+      <c r="R6" s="54">
         <v>-10.15</v>
       </c>
-      <c r="S6" s="61">
+      <c r="S6" s="63">
         <v>-9.99</v>
       </c>
-      <c r="T6" s="60">
+      <c r="T6" s="57">
         <v>37.31</v>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       <c r="C7" t="str">
         <v>002645</v>
       </c>
-      <c r="D7" s="75" t="str">
+      <c r="D7" s="76" t="str">
         <v>净买: 1223.21万</v>
       </c>
       <c r="E7">
@@ -8799,40 +8799,40 @@
       <c r="H7">
         <v>1.72</v>
       </c>
-      <c r="I7" s="71">
+      <c r="I7" s="70">
         <v>8.14</v>
       </c>
-      <c r="J7" s="68">
+      <c r="J7" s="77">
         <v>5.31</v>
       </c>
-      <c r="K7" s="78">
+      <c r="K7" s="73">
         <v>9.04</v>
       </c>
-      <c r="L7" s="72">
+      <c r="L7" s="74">
         <v>4.75</v>
       </c>
-      <c r="M7" s="76">
+      <c r="M7" s="78">
         <v>3.5</v>
       </c>
-      <c r="N7" s="73">
+      <c r="N7" s="66">
         <v>-6.89</v>
       </c>
-      <c r="O7" s="66">
+      <c r="O7" s="71">
         <v>-5.42</v>
       </c>
-      <c r="P7" s="67">
+      <c r="P7" s="75">
         <v>-7.12</v>
       </c>
-      <c r="Q7" s="69">
+      <c r="Q7" s="68">
         <v>-7.23</v>
       </c>
-      <c r="R7" s="77">
+      <c r="R7" s="67">
         <v>-10.73</v>
       </c>
-      <c r="S7" s="74">
+      <c r="S7" s="72">
         <v>-9.94</v>
       </c>
-      <c r="T7" s="70">
+      <c r="T7" s="69">
         <v>152.09</v>
       </c>
     </row>
@@ -8846,7 +8846,7 @@
       <c r="C8" t="str">
         <v>600537</v>
       </c>
-      <c r="D8" s="80" t="str">
+      <c r="D8" s="82" t="str">
         <v>净买: 358.47万</v>
       </c>
       <c r="E8">
@@ -8861,40 +8861,40 @@
       <c r="H8">
         <v>5.03</v>
       </c>
-      <c r="I8" s="87">
+      <c r="I8" s="85">
         <v>4.79</v>
       </c>
-      <c r="J8" s="88">
+      <c r="J8" s="86">
         <v>8.98</v>
       </c>
-      <c r="K8" s="90">
+      <c r="K8" s="83">
         <v>-1.8</v>
       </c>
-      <c r="L8" s="84">
+      <c r="L8" s="87">
         <v>8.08</v>
       </c>
-      <c r="M8" s="81">
+      <c r="M8" s="91">
         <v>18.86</v>
       </c>
-      <c r="N8" s="82">
+      <c r="N8" s="79">
         <v>19.76</v>
       </c>
-      <c r="O8" s="85">
+      <c r="O8" s="80">
         <v>19.16</v>
       </c>
-      <c r="P8" s="83">
+      <c r="P8" s="84">
         <v>15.57</v>
       </c>
-      <c r="Q8" s="91">
+      <c r="Q8" s="88">
         <v>8.38</v>
       </c>
-      <c r="R8" s="86">
+      <c r="R8" s="89">
         <v>4.49</v>
       </c>
-      <c r="S8" s="89">
+      <c r="S8" s="81">
         <v>14.97</v>
       </c>
-      <c r="T8" s="79">
+      <c r="T8" s="90">
         <v>20.36</v>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
       <c r="C9" t="str">
         <v>603122</v>
       </c>
-      <c r="D9" s="98" t="str">
+      <c r="D9" s="93" t="str">
         <v>净卖: -557.16万</v>
       </c>
       <c r="E9">
@@ -8923,40 +8923,40 @@
       <c r="H9">
         <v>7.07</v>
       </c>
-      <c r="I9" s="103">
+      <c r="I9" s="102">
         <v>2.8</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="96">
         <v>13.09</v>
       </c>
-      <c r="K9" s="104">
+      <c r="K9" s="103">
         <v>24.4</v>
       </c>
-      <c r="L9" s="101">
+      <c r="L9" s="97">
         <v>36.85</v>
       </c>
-      <c r="M9" s="95">
+      <c r="M9" s="94">
         <v>50.57</v>
       </c>
-      <c r="N9" s="96">
+      <c r="N9" s="95">
         <v>65.69</v>
       </c>
-      <c r="O9" s="97">
+      <c r="O9" s="98">
         <v>82.21</v>
       </c>
-      <c r="P9" s="100">
+      <c r="P9" s="99">
         <v>100.38</v>
       </c>
-      <c r="Q9" s="92">
+      <c r="Q9" s="104">
         <v>110.93</v>
       </c>
-      <c r="R9" s="102">
+      <c r="R9" s="92">
         <v>132.02</v>
       </c>
-      <c r="S9" s="93">
+      <c r="S9" s="100">
         <v>155.27</v>
       </c>
-      <c r="T9" s="94">
+      <c r="T9" s="101">
         <v>105.34</v>
       </c>
     </row>
@@ -8970,7 +8970,7 @@
       <c r="C10" t="str">
         <v>002682</v>
       </c>
-      <c r="D10" s="117" t="str">
+      <c r="D10" s="105" t="str">
         <v>净买: 749.97万</v>
       </c>
       <c r="E10">
@@ -8985,40 +8985,40 @@
       <c r="H10">
         <v>10.02</v>
       </c>
-      <c r="I10" s="105">
+      <c r="I10" s="106">
         <v>0</v>
       </c>
-      <c r="J10" s="109">
+      <c r="J10" s="107">
         <v>10.03</v>
       </c>
-      <c r="K10" s="106">
+      <c r="K10" s="108">
         <v>20.99</v>
       </c>
-      <c r="L10" s="110">
+      <c r="L10" s="115">
         <v>8.95</v>
       </c>
-      <c r="M10" s="107">
+      <c r="M10" s="116">
         <v>-2.01</v>
       </c>
-      <c r="N10" s="114">
+      <c r="N10" s="109">
         <v>-11.73</v>
       </c>
-      <c r="O10" s="108">
+      <c r="O10" s="111">
         <v>-16.05</v>
       </c>
-      <c r="P10" s="115">
+      <c r="P10" s="112">
         <v>-13.73</v>
       </c>
-      <c r="Q10" s="111">
+      <c r="Q10" s="117">
         <v>-17.59</v>
       </c>
-      <c r="R10" s="116">
+      <c r="R10" s="110">
         <v>-17.28</v>
       </c>
-      <c r="S10" s="112">
+      <c r="S10" s="113">
         <v>-14.04</v>
       </c>
-      <c r="T10" s="113">
+      <c r="T10" s="114">
         <v>-8.33</v>
       </c>
     </row>
@@ -9032,7 +9032,7 @@
       <c r="C11" t="str">
         <v>600227</v>
       </c>
-      <c r="D11" s="130" t="str">
+      <c r="D11" s="126" t="str">
         <v>净买: 484.48万</v>
       </c>
       <c r="E11">
@@ -9047,40 +9047,40 @@
       <c r="H11">
         <v>1.56</v>
       </c>
-      <c r="I11" s="118">
+      <c r="I11" s="120">
         <v>8.43</v>
       </c>
-      <c r="J11" s="122">
+      <c r="J11" s="127">
         <v>13.79</v>
       </c>
-      <c r="K11" s="119">
+      <c r="K11" s="123">
         <v>9.2</v>
       </c>
-      <c r="L11" s="120">
+      <c r="L11" s="118">
         <v>7.28</v>
       </c>
-      <c r="M11" s="123">
+      <c r="M11" s="128">
         <v>2.68</v>
       </c>
-      <c r="N11" s="121">
+      <c r="N11" s="119">
         <v>4.6</v>
       </c>
-      <c r="O11" s="126">
+      <c r="O11" s="121">
         <v>0.77</v>
       </c>
-      <c r="P11" s="127">
+      <c r="P11" s="124">
         <v>-4.6</v>
       </c>
-      <c r="Q11" s="128">
+      <c r="Q11" s="125">
         <v>-2.68</v>
       </c>
-      <c r="R11" s="124">
+      <c r="R11" s="129">
         <v>-4.6</v>
       </c>
-      <c r="S11" s="125">
+      <c r="S11" s="130">
         <v>-2.68</v>
       </c>
-      <c r="T11" s="129">
+      <c r="T11" s="122">
         <v>32.57</v>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       <c r="C12" t="str">
         <v>603386</v>
       </c>
-      <c r="D12" s="133" t="str">
+      <c r="D12" s="142" t="str">
         <v>净卖: -4389.34万</v>
       </c>
       <c r="E12">
@@ -9109,40 +9109,40 @@
       <c r="H12">
         <v>-8.19</v>
       </c>
-      <c r="I12" s="134">
+      <c r="I12" s="143">
         <v>-1.95</v>
       </c>
-      <c r="J12" s="135">
+      <c r="J12" s="140">
         <v>-3.78</v>
       </c>
-      <c r="K12" s="136">
+      <c r="K12" s="131">
         <v>-11.08</v>
       </c>
-      <c r="L12" s="137">
+      <c r="L12" s="132">
         <v>-18.92</v>
       </c>
-      <c r="M12" s="138">
+      <c r="M12" s="133">
         <v>-18.16</v>
       </c>
-      <c r="N12" s="131">
+      <c r="N12" s="141">
         <v>-18.54</v>
       </c>
-      <c r="O12" s="139">
+      <c r="O12" s="136">
         <v>-17.08</v>
       </c>
-      <c r="P12" s="141">
+      <c r="P12" s="137">
         <v>-17.95</v>
       </c>
-      <c r="Q12" s="140">
+      <c r="Q12" s="134">
         <v>-14.43</v>
       </c>
-      <c r="R12" s="142">
+      <c r="R12" s="135">
         <v>-20</v>
       </c>
-      <c r="S12" s="143">
+      <c r="S12" s="138">
         <v>-18.32</v>
       </c>
-      <c r="T12" s="132">
+      <c r="T12" s="139">
         <v>-22.43</v>
       </c>
     </row>
@@ -9156,7 +9156,7 @@
       <c r="C13" t="str">
         <v>600493</v>
       </c>
-      <c r="D13" s="151" t="str">
+      <c r="D13" s="154" t="str">
         <v>净买: 999.07万</v>
       </c>
       <c r="E13">
@@ -9171,40 +9171,40 @@
       <c r="H13">
         <v>1.85</v>
       </c>
-      <c r="I13" s="147">
+      <c r="I13" s="144">
         <v>8.05</v>
       </c>
-      <c r="J13" s="152">
+      <c r="J13" s="150">
         <v>-0.65</v>
       </c>
-      <c r="K13" s="154">
+      <c r="K13" s="145">
         <v>3.12</v>
       </c>
       <c r="L13" s="155">
         <v>-4.16</v>
       </c>
-      <c r="M13" s="156">
+      <c r="M13" s="146">
         <v>-8.05</v>
       </c>
-      <c r="N13" s="144">
+      <c r="N13" s="156">
         <v>1.17</v>
       </c>
-      <c r="O13" s="148">
+      <c r="O13" s="147">
         <v>-1.3</v>
       </c>
-      <c r="P13" s="149">
+      <c r="P13" s="148">
         <v>-2.47</v>
       </c>
-      <c r="Q13" s="150">
+      <c r="Q13" s="153">
         <v>1.56</v>
       </c>
-      <c r="R13" s="145">
+      <c r="R13" s="151">
         <v>3.77</v>
       </c>
-      <c r="S13" s="146">
+      <c r="S13" s="149">
         <v>4.03</v>
       </c>
-      <c r="T13" s="153">
+      <c r="T13" s="152">
         <v>-3.12</v>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
       <c r="C14" t="str">
         <v>001330</v>
       </c>
-      <c r="D14" s="167" t="str">
+      <c r="D14" s="168" t="str">
         <v>净卖: -4990.62万</v>
       </c>
       <c r="E14">
@@ -9233,40 +9233,40 @@
       <c r="H14">
         <v>1.65</v>
       </c>
-      <c r="I14" s="161">
+      <c r="I14" s="169">
         <v>8.18</v>
       </c>
-      <c r="J14" s="164">
+      <c r="J14" s="165">
         <v>-2.59</v>
       </c>
-      <c r="K14" s="162">
+      <c r="K14" s="157">
         <v>-12.32</v>
       </c>
-      <c r="L14" s="168">
+      <c r="L14" s="166">
         <v>-20.34</v>
       </c>
-      <c r="M14" s="169">
+      <c r="M14" s="158">
         <v>-12.4</v>
       </c>
       <c r="N14" s="163">
         <v>-18.4</v>
       </c>
-      <c r="O14" s="160">
+      <c r="O14" s="159">
         <v>-26.58</v>
       </c>
-      <c r="P14" s="157">
+      <c r="P14" s="167">
         <v>-33.95</v>
       </c>
-      <c r="Q14" s="158">
+      <c r="Q14" s="160">
         <v>-32.82</v>
       </c>
-      <c r="R14" s="165">
+      <c r="R14" s="161">
         <v>-35.66</v>
       </c>
-      <c r="S14" s="166">
+      <c r="S14" s="162">
         <v>-34.76</v>
       </c>
-      <c r="T14" s="159">
+      <c r="T14" s="164">
         <v>-33.31</v>
       </c>
     </row>
@@ -9280,7 +9280,7 @@
       <c r="C15" t="str">
         <v>600865</v>
       </c>
-      <c r="D15" s="172" t="str">
+      <c r="D15" s="174" t="str">
         <v>净买: 4692.22万</v>
       </c>
       <c r="E15">
@@ -9295,40 +9295,40 @@
       <c r="H15">
         <v>10.02</v>
       </c>
-      <c r="I15" s="177">
+      <c r="I15" s="175">
         <v>0</v>
       </c>
-      <c r="J15" s="170">
+      <c r="J15" s="181">
         <v>10.01</v>
       </c>
-      <c r="K15" s="173">
+      <c r="K15" s="182">
         <v>21</v>
       </c>
-      <c r="L15" s="174">
+      <c r="L15" s="177">
         <v>25.24</v>
       </c>
-      <c r="M15" s="175">
+      <c r="M15" s="170">
         <v>32.13</v>
       </c>
-      <c r="N15" s="176">
+      <c r="N15" s="178">
         <v>27.75</v>
       </c>
-      <c r="O15" s="178">
+      <c r="O15" s="172">
         <v>37.2</v>
       </c>
-      <c r="P15" s="182">
+      <c r="P15" s="171">
         <v>50.9</v>
       </c>
       <c r="Q15" s="179">
         <v>48.33</v>
       </c>
-      <c r="R15" s="180">
+      <c r="R15" s="176">
         <v>33.52</v>
       </c>
-      <c r="S15" s="171">
+      <c r="S15" s="180">
         <v>20.17</v>
       </c>
-      <c r="T15" s="181">
+      <c r="T15" s="173">
         <v>-20.38</v>
       </c>
     </row>
@@ -9342,7 +9342,7 @@
       <c r="C16" t="str">
         <v>600865</v>
       </c>
-      <c r="D16" s="185" t="str">
+      <c r="D16" s="186" t="str">
         <v>净卖: -5679.38万</v>
       </c>
       <c r="E16">
@@ -9357,16 +9357,16 @@
       <c r="H16">
         <v>10.01</v>
       </c>
-      <c r="I16" s="186">
+      <c r="I16" s="187">
         <v>0</v>
       </c>
-      <c r="J16" s="187">
+      <c r="J16" s="183">
         <v>9.99</v>
       </c>
-      <c r="K16" s="188">
+      <c r="K16" s="192">
         <v>13.84</v>
       </c>
-      <c r="L16" s="184">
+      <c r="L16" s="188">
         <v>20.1</v>
       </c>
       <c r="M16" s="193">
@@ -9375,13 +9375,13 @@
       <c r="N16" s="189">
         <v>24.72</v>
       </c>
-      <c r="O16" s="190">
+      <c r="O16" s="184">
         <v>37.17</v>
       </c>
-      <c r="P16" s="191">
+      <c r="P16" s="190">
         <v>34.83</v>
       </c>
-      <c r="Q16" s="192">
+      <c r="Q16" s="185">
         <v>21.37</v>
       </c>
       <c r="R16" s="194">
@@ -9390,7 +9390,7 @@
       <c r="S16" s="195">
         <v>3.67</v>
       </c>
-      <c r="T16" s="183">
+      <c r="T16" s="191">
         <v>-27.62</v>
       </c>
     </row>
@@ -9404,7 +9404,7 @@
       <c r="C17" t="str">
         <v>600693</v>
       </c>
-      <c r="D17" s="197" t="str">
+      <c r="D17" s="199" t="str">
         <v>净买: 4205.60万</v>
       </c>
       <c r="E17">
@@ -9419,40 +9419,40 @@
       <c r="H17">
         <v>2.51</v>
       </c>
-      <c r="I17" s="201">
+      <c r="I17" s="200">
         <v>0.41</v>
       </c>
-      <c r="J17" s="198">
+      <c r="J17" s="196">
         <v>-0.58</v>
       </c>
-      <c r="K17" s="199">
+      <c r="K17" s="197">
         <v>9.33</v>
       </c>
-      <c r="L17" s="203">
+      <c r="L17" s="201">
         <v>13.77</v>
       </c>
-      <c r="M17" s="204">
+      <c r="M17" s="205">
         <v>25.15</v>
       </c>
-      <c r="N17" s="208">
+      <c r="N17" s="206">
         <v>22</v>
       </c>
-      <c r="O17" s="196">
+      <c r="O17" s="202">
         <v>27.65</v>
       </c>
-      <c r="P17" s="202">
+      <c r="P17" s="203">
         <v>15.52</v>
       </c>
-      <c r="Q17" s="205">
+      <c r="Q17" s="204">
         <v>3.97</v>
       </c>
-      <c r="R17" s="206">
+      <c r="R17" s="198">
         <v>3.97</v>
       </c>
       <c r="S17" s="207">
         <v>7.29</v>
       </c>
-      <c r="T17" s="200">
+      <c r="T17" s="208">
         <v>-30.51</v>
       </c>
     </row>
@@ -9466,7 +9466,7 @@
       <c r="C18" t="str">
         <v>603023</v>
       </c>
-      <c r="D18" s="212" t="str">
+      <c r="D18" s="211" t="str">
         <v>净买: 2053.34万</v>
       </c>
       <c r="E18">
@@ -9481,40 +9481,40 @@
       <c r="H18">
         <v>-0.38</v>
       </c>
-      <c r="I18" s="215">
+      <c r="I18" s="218">
         <v>10.48</v>
       </c>
-      <c r="J18" s="213">
+      <c r="J18" s="210">
         <v>13.9</v>
       </c>
-      <c r="K18" s="216">
+      <c r="K18" s="212">
         <v>10.1</v>
       </c>
-      <c r="L18" s="214">
+      <c r="L18" s="219">
         <v>5.14</v>
       </c>
-      <c r="M18" s="220">
+      <c r="M18" s="213">
         <v>4.95</v>
       </c>
-      <c r="N18" s="221">
+      <c r="N18" s="214">
         <v>6.29</v>
       </c>
-      <c r="O18" s="217">
+      <c r="O18" s="221">
         <v>0.57</v>
       </c>
-      <c r="P18" s="218">
+      <c r="P18" s="215">
         <v>1.9</v>
       </c>
-      <c r="Q18" s="219">
+      <c r="Q18" s="216">
         <v>-4.19</v>
       </c>
-      <c r="R18" s="209">
+      <c r="R18" s="217">
         <v>-2.48</v>
       </c>
-      <c r="S18" s="210">
+      <c r="S18" s="209">
         <v>7.24</v>
       </c>
-      <c r="T18" s="211">
+      <c r="T18" s="220">
         <v>-14.86</v>
       </c>
     </row>
@@ -9528,7 +9528,7 @@
       <c r="C19" t="str">
         <v>601566</v>
       </c>
-      <c r="D19" s="226" t="str">
+      <c r="D19" s="228" t="str">
         <v>净卖: -2383.06万</v>
       </c>
       <c r="E19">
@@ -9543,40 +9543,40 @@
       <c r="H19">
         <v>3.63</v>
       </c>
-      <c r="I19" s="231">
+      <c r="I19" s="224">
         <v>6.13</v>
       </c>
-      <c r="J19" s="227">
+      <c r="J19" s="225">
         <v>2.75</v>
       </c>
-      <c r="K19" s="233">
+      <c r="K19" s="229">
         <v>-4.06</v>
       </c>
-      <c r="L19" s="228">
+      <c r="L19" s="230">
         <v>-3.37</v>
       </c>
-      <c r="M19" s="224">
+      <c r="M19" s="222">
         <v>-6.81</v>
       </c>
       <c r="N19" s="234">
         <v>-7.5</v>
       </c>
-      <c r="O19" s="229">
+      <c r="O19" s="226">
         <v>-12.5</v>
       </c>
-      <c r="P19" s="222">
+      <c r="P19" s="227">
         <v>-13.88</v>
       </c>
-      <c r="Q19" s="230">
+      <c r="Q19" s="231">
         <v>-18.06</v>
       </c>
-      <c r="R19" s="225">
+      <c r="R19" s="223">
         <v>-17.94</v>
       </c>
       <c r="S19" s="232">
         <v>-16.56</v>
       </c>
-      <c r="T19" s="223">
+      <c r="T19" s="233">
         <v>-33.25</v>
       </c>
     </row>
@@ -9590,7 +9590,7 @@
       <c r="C20" t="str">
         <v>600865</v>
       </c>
-      <c r="D20" s="247" t="str">
+      <c r="D20" s="244" t="str">
         <v>净卖: -5744.79万</v>
       </c>
       <c r="E20">
@@ -9605,40 +9605,40 @@
       <c r="H20">
         <v>-5.17</v>
       </c>
-      <c r="I20" s="245">
+      <c r="I20" s="247">
         <v>9.15</v>
       </c>
-      <c r="J20" s="243">
+      <c r="J20" s="236">
         <v>15.15</v>
       </c>
-      <c r="K20" s="235">
+      <c r="K20" s="245">
         <v>11.33</v>
       </c>
-      <c r="L20" s="236">
+      <c r="L20" s="241">
         <v>19.58</v>
       </c>
       <c r="M20" s="237">
         <v>31.52</v>
       </c>
-      <c r="N20" s="244">
+      <c r="N20" s="235">
         <v>29.27</v>
       </c>
-      <c r="O20" s="241">
+      <c r="O20" s="238">
         <v>16.36</v>
       </c>
-      <c r="P20" s="238">
+      <c r="P20" s="242">
         <v>4.73</v>
       </c>
       <c r="Q20" s="239">
         <v>-0.61</v>
       </c>
-      <c r="R20" s="242">
+      <c r="R20" s="240">
         <v>0.12</v>
       </c>
-      <c r="S20" s="240">
+      <c r="S20" s="246">
         <v>0.12</v>
       </c>
-      <c r="T20" s="246">
+      <c r="T20" s="243">
         <v>-30.61</v>
       </c>
     </row>
@@ -9652,7 +9652,7 @@
       <c r="C21" t="str">
         <v>001317</v>
       </c>
-      <c r="D21" s="258" t="str">
+      <c r="D21" s="248" t="str">
         <v>净卖: -1614.69万</v>
       </c>
       <c r="E21">
@@ -9667,40 +9667,40 @@
       <c r="H21">
         <v>-0.39</v>
       </c>
-      <c r="I21" s="249">
+      <c r="I21" s="260">
         <v>3.7</v>
       </c>
-      <c r="J21" s="250">
+      <c r="J21" s="252">
         <v>-1.32</v>
       </c>
-      <c r="K21" s="255">
+      <c r="K21" s="249">
         <v>-4.71</v>
       </c>
-      <c r="L21" s="251">
+      <c r="L21" s="253">
         <v>-6.34</v>
       </c>
-      <c r="M21" s="252">
+      <c r="M21" s="257">
         <v>-4.27</v>
       </c>
-      <c r="N21" s="256">
+      <c r="N21" s="254">
         <v>-2.18</v>
       </c>
-      <c r="O21" s="253">
+      <c r="O21" s="250">
         <v>0.05</v>
       </c>
-      <c r="P21" s="260">
+      <c r="P21" s="258">
         <v>-1.59</v>
       </c>
-      <c r="Q21" s="254">
+      <c r="Q21" s="251">
         <v>-4.68</v>
       </c>
-      <c r="R21" s="257">
+      <c r="R21" s="255">
         <v>-5.25</v>
       </c>
-      <c r="S21" s="259">
+      <c r="S21" s="256">
         <v>-4.79</v>
       </c>
-      <c r="T21" s="248">
+      <c r="T21" s="259">
         <v>-10.84</v>
       </c>
     </row>
@@ -9714,7 +9714,7 @@
       <c r="C22" t="str">
         <v>002792</v>
       </c>
-      <c r="D22" s="264" t="str">
+      <c r="D22" s="261" t="str">
         <v>净买: 6812.35万</v>
       </c>
       <c r="E22">
@@ -9729,40 +9729,40 @@
       <c r="H22">
         <v>4.23</v>
       </c>
-      <c r="I22" s="265">
+      <c r="I22" s="262">
         <v>5.52</v>
       </c>
-      <c r="J22" s="273">
+      <c r="J22" s="263">
         <v>-2.54</v>
       </c>
-      <c r="K22" s="266">
+      <c r="K22" s="268">
         <v>3.61</v>
       </c>
       <c r="L22" s="271">
         <v>13.97</v>
       </c>
-      <c r="M22" s="269">
+      <c r="M22" s="264">
         <v>25.37</v>
       </c>
-      <c r="N22" s="267">
+      <c r="N22" s="269">
         <v>26.81</v>
       </c>
-      <c r="O22" s="268">
+      <c r="O22" s="272">
         <v>18.51</v>
       </c>
-      <c r="P22" s="272">
+      <c r="P22" s="273">
         <v>27.46</v>
       </c>
-      <c r="Q22" s="261">
+      <c r="Q22" s="270">
         <v>36.75</v>
       </c>
-      <c r="R22" s="262">
+      <c r="R22" s="265">
         <v>41.37</v>
       </c>
-      <c r="S22" s="263">
+      <c r="S22" s="266">
         <v>55.52</v>
       </c>
-      <c r="T22" s="270">
+      <c r="T22" s="267">
         <v>52.3</v>
       </c>
     </row>
@@ -9791,34 +9791,34 @@
       <c r="H23">
         <v>4.14</v>
       </c>
-      <c r="I23" s="285">
+      <c r="I23" s="282">
         <v>-0.99</v>
       </c>
-      <c r="J23" s="276">
+      <c r="J23" s="274">
         <v>-4.3</v>
       </c>
-      <c r="K23" s="277">
+      <c r="K23" s="275">
         <v>-8.61</v>
       </c>
-      <c r="L23" s="286">
+      <c r="L23" s="283">
         <v>-8.77</v>
       </c>
-      <c r="M23" s="274">
+      <c r="M23" s="278">
         <v>-7.62</v>
       </c>
-      <c r="N23" s="282">
+      <c r="N23" s="276">
         <v>-12.58</v>
       </c>
-      <c r="O23" s="278">
+      <c r="O23" s="279">
         <v>-11.42</v>
       </c>
-      <c r="P23" s="279">
+      <c r="P23" s="285">
         <v>-16.72</v>
       </c>
-      <c r="Q23" s="275">
+      <c r="Q23" s="286">
         <v>-15.23</v>
       </c>
-      <c r="R23" s="283">
+      <c r="R23" s="277">
         <v>-6.79</v>
       </c>
       <c r="S23" s="284">
@@ -9838,7 +9838,7 @@
       <c r="C24" t="str">
         <v>600343</v>
       </c>
-      <c r="D24" s="292" t="str">
+      <c r="D24" s="290" t="str">
         <v>净买: 1.33亿</v>
       </c>
       <c r="E24">
@@ -9853,40 +9853,40 @@
       <c r="H24">
         <v>-1.32</v>
       </c>
-      <c r="I24" s="288">
+      <c r="I24" s="299">
         <v>11.47</v>
       </c>
-      <c r="J24" s="293">
+      <c r="J24" s="291">
         <v>15.39</v>
       </c>
-      <c r="K24" s="294">
+      <c r="K24" s="292">
         <v>21.07</v>
       </c>
-      <c r="L24" s="295">
+      <c r="L24" s="293">
         <v>25.17</v>
       </c>
-      <c r="M24" s="289">
+      <c r="M24" s="297">
         <v>30</v>
       </c>
-      <c r="N24" s="296">
+      <c r="N24" s="294">
         <v>30.59</v>
       </c>
-      <c r="O24" s="299">
+      <c r="O24" s="287">
         <v>21.84</v>
       </c>
-      <c r="P24" s="297">
+      <c r="P24" s="288">
         <v>20.93</v>
       </c>
-      <c r="Q24" s="290">
+      <c r="Q24" s="295">
         <v>20.8</v>
       </c>
-      <c r="R24" s="298">
+      <c r="R24" s="296">
         <v>26.21</v>
       </c>
-      <c r="S24" s="291">
+      <c r="S24" s="289">
         <v>23.73</v>
       </c>
-      <c r="T24" s="287">
+      <c r="T24" s="298">
         <v>-4.88</v>
       </c>
     </row>
@@ -9900,7 +9900,7 @@
       <c r="C25" t="str">
         <v>600693</v>
       </c>
-      <c r="D25" s="300" t="str">
+      <c r="D25" s="310" t="str">
         <v>净卖: -8573.84万</v>
       </c>
       <c r="E25">
@@ -9915,40 +9915,40 @@
       <c r="H25">
         <v>0</v>
       </c>
-      <c r="I25" s="303">
+      <c r="I25" s="311">
         <v>-2.52</v>
       </c>
-      <c r="J25" s="308">
+      <c r="J25" s="312">
         <v>2</v>
       </c>
-      <c r="K25" s="301">
+      <c r="K25" s="306">
         <v>-7.69</v>
       </c>
-      <c r="L25" s="309">
+      <c r="L25" s="307">
         <v>-16.92</v>
       </c>
-      <c r="M25" s="302">
+      <c r="M25" s="300">
         <v>-16.92</v>
       </c>
-      <c r="N25" s="311">
+      <c r="N25" s="308">
         <v>-14.27</v>
       </c>
-      <c r="O25" s="304">
+      <c r="O25" s="309">
         <v>-16.64</v>
       </c>
-      <c r="P25" s="305">
+      <c r="P25" s="301">
         <v>-16.6</v>
       </c>
-      <c r="Q25" s="312">
+      <c r="Q25" s="302">
         <v>-11.79</v>
       </c>
-      <c r="R25" s="310">
+      <c r="R25" s="303">
         <v>-8.67</v>
       </c>
-      <c r="S25" s="306">
+      <c r="S25" s="304">
         <v>-2.05</v>
       </c>
-      <c r="T25" s="307">
+      <c r="T25" s="305">
         <v>-44.48</v>
       </c>
     </row>
@@ -9962,7 +9962,7 @@
       <c r="C26" t="str">
         <v>603686</v>
       </c>
-      <c r="D26" s="320" t="str">
+      <c r="D26" s="323" t="str">
         <v>净买: 6401.27万</v>
       </c>
       <c r="E26">
@@ -9980,7 +9980,7 @@
       <c r="I26" s="324">
         <v>11.56</v>
       </c>
-      <c r="J26" s="317">
+      <c r="J26" s="320">
         <v>12.1</v>
       </c>
       <c r="K26" s="325">
@@ -9989,28 +9989,28 @@
       <c r="L26" s="313">
         <v>15.93</v>
       </c>
-      <c r="M26" s="323">
+      <c r="M26" s="317">
         <v>12.77</v>
       </c>
-      <c r="N26" s="314">
+      <c r="N26" s="318">
         <v>13.16</v>
       </c>
-      <c r="O26" s="318">
+      <c r="O26" s="316">
         <v>10.86</v>
       </c>
-      <c r="P26" s="319">
+      <c r="P26" s="321">
         <v>9.14</v>
       </c>
-      <c r="Q26" s="315">
+      <c r="Q26" s="314">
         <v>9.84</v>
       </c>
-      <c r="R26" s="321">
+      <c r="R26" s="322">
         <v>10.82</v>
       </c>
-      <c r="S26" s="322">
+      <c r="S26" s="319">
         <v>-0.23</v>
       </c>
-      <c r="T26" s="316">
+      <c r="T26" s="315">
         <v>-26.28</v>
       </c>
     </row>
@@ -10024,7 +10024,7 @@
       <c r="C27" t="str">
         <v>603686</v>
       </c>
-      <c r="D27" s="330" t="str">
+      <c r="D27" s="332" t="str">
         <v>净卖: -6520.61万</v>
       </c>
       <c r="E27">
@@ -10042,37 +10042,37 @@
       <c r="I27" s="326">
         <v>-4.3</v>
       </c>
-      <c r="J27" s="336">
+      <c r="J27" s="333">
         <v>5.27</v>
       </c>
-      <c r="K27" s="331">
+      <c r="K27" s="328">
         <v>-1.03</v>
       </c>
-      <c r="L27" s="337">
+      <c r="L27" s="334">
         <v>-3.73</v>
       </c>
-      <c r="M27" s="332">
+      <c r="M27" s="335">
         <v>-3.4</v>
       </c>
-      <c r="N27" s="333">
+      <c r="N27" s="329">
         <v>-5.37</v>
       </c>
-      <c r="O27" s="328">
+      <c r="O27" s="336">
         <v>-6.83</v>
       </c>
-      <c r="P27" s="329">
+      <c r="P27" s="327">
         <v>-6.23</v>
       </c>
-      <c r="Q27" s="334">
+      <c r="Q27" s="337">
         <v>-5.4</v>
       </c>
-      <c r="R27" s="335">
+      <c r="R27" s="330">
         <v>-14.83</v>
       </c>
       <c r="S27" s="338">
         <v>-14.37</v>
       </c>
-      <c r="T27" s="327">
+      <c r="T27" s="331">
         <v>-37.07</v>
       </c>
     </row>
@@ -10086,7 +10086,7 @@
       <c r="C28" t="str">
         <v>002361</v>
       </c>
-      <c r="D28" s="347" t="str">
+      <c r="D28" s="351" t="str">
         <v>净卖: -5584.65万</v>
       </c>
       <c r="E28">
@@ -10101,40 +10101,40 @@
       <c r="H28">
         <v>-3.59</v>
       </c>
-      <c r="I28" s="348">
+      <c r="I28" s="344">
         <v>-6.66</v>
       </c>
-      <c r="J28" s="343">
+      <c r="J28" s="347">
         <v>2.65</v>
       </c>
-      <c r="K28" s="349">
+      <c r="K28" s="345">
         <v>-1.93</v>
       </c>
-      <c r="L28" s="345">
+      <c r="L28" s="346">
         <v>3.51</v>
       </c>
-      <c r="M28" s="341">
+      <c r="M28" s="339">
         <v>3.15</v>
       </c>
-      <c r="N28" s="342">
+      <c r="N28" s="348">
         <v>13.46</v>
       </c>
-      <c r="O28" s="350">
+      <c r="O28" s="349">
         <v>11.67</v>
       </c>
-      <c r="P28" s="344">
+      <c r="P28" s="342">
         <v>20.26</v>
       </c>
-      <c r="Q28" s="351">
+      <c r="Q28" s="343">
         <v>17.97</v>
       </c>
-      <c r="R28" s="339">
+      <c r="R28" s="340">
         <v>29.71</v>
       </c>
-      <c r="S28" s="340">
+      <c r="S28" s="341">
         <v>16.75</v>
       </c>
-      <c r="T28" s="346">
+      <c r="T28" s="350">
         <v>34.22</v>
       </c>
     </row>
@@ -10148,7 +10148,7 @@
       <c r="C29" t="str">
         <v>001231</v>
       </c>
-      <c r="D29" s="360" t="str">
+      <c r="D29" s="356" t="str">
         <v>净卖: -943.73万</v>
       </c>
       <c r="E29">
@@ -10163,40 +10163,40 @@
       <c r="H29">
         <v>-10.01</v>
       </c>
-      <c r="I29" s="364">
+      <c r="I29" s="357">
         <v>0</v>
       </c>
-      <c r="J29" s="353">
+      <c r="J29" s="359">
         <v>-1.36</v>
       </c>
-      <c r="K29" s="354">
+      <c r="K29" s="363">
         <v>-7.18</v>
       </c>
-      <c r="L29" s="357">
+      <c r="L29" s="353">
         <v>-8.91</v>
       </c>
-      <c r="M29" s="358">
+      <c r="M29" s="364">
         <v>-9.1</v>
       </c>
-      <c r="N29" s="355">
+      <c r="N29" s="360">
         <v>-9.98</v>
       </c>
-      <c r="O29" s="356">
+      <c r="O29" s="358">
         <v>-8.84</v>
       </c>
-      <c r="P29" s="352">
+      <c r="P29" s="361">
         <v>-10.31</v>
       </c>
-      <c r="Q29" s="361">
+      <c r="Q29" s="354">
         <v>-7.96</v>
       </c>
       <c r="R29" s="362">
         <v>-8.8</v>
       </c>
-      <c r="S29" s="359">
+      <c r="S29" s="355">
         <v>-9.28</v>
       </c>
-      <c r="T29" s="363">
+      <c r="T29" s="352">
         <v>-8.18</v>
       </c>
     </row>
@@ -10210,7 +10210,7 @@
       <c r="C30" t="str">
         <v>002788</v>
       </c>
-      <c r="D30" s="367" t="str">
+      <c r="D30" s="372" t="str">
         <v>净买: 3825.22万</v>
       </c>
       <c r="E30">
@@ -10225,40 +10225,40 @@
       <c r="H30">
         <v>5.81</v>
       </c>
-      <c r="I30" s="369">
+      <c r="I30" s="373">
         <v>3.95</v>
       </c>
-      <c r="J30" s="370">
+      <c r="J30" s="374">
         <v>14.35</v>
       </c>
-      <c r="K30" s="373">
+      <c r="K30" s="369">
         <v>11.56</v>
       </c>
-      <c r="L30" s="371">
+      <c r="L30" s="366">
         <v>13.48</v>
       </c>
-      <c r="M30" s="374">
+      <c r="M30" s="367">
         <v>9.23</v>
       </c>
-      <c r="N30" s="372">
+      <c r="N30" s="375">
         <v>1.08</v>
       </c>
-      <c r="O30" s="377">
+      <c r="O30" s="376">
         <v>-9.03</v>
       </c>
-      <c r="P30" s="375">
+      <c r="P30" s="377">
         <v>-18.14</v>
       </c>
-      <c r="Q30" s="365">
+      <c r="Q30" s="370">
         <v>-26.33</v>
       </c>
-      <c r="R30" s="366">
+      <c r="R30" s="365">
         <v>-30.78</v>
       </c>
-      <c r="S30" s="368">
+      <c r="S30" s="371">
         <v>-32.45</v>
       </c>
-      <c r="T30" s="376">
+      <c r="T30" s="368">
         <v>-37.23</v>
       </c>
     </row>
@@ -10272,7 +10272,7 @@
       <c r="C31" t="str">
         <v>002788</v>
       </c>
-      <c r="D31" s="385" t="str">
+      <c r="D31" s="384" t="str">
         <v>净卖: -24.07万</v>
       </c>
       <c r="E31">
@@ -10287,40 +10287,40 @@
       <c r="H31">
         <v>-0.04</v>
       </c>
-      <c r="I31" s="382">
+      <c r="I31" s="388">
         <v>10.05</v>
       </c>
-      <c r="J31" s="390">
+      <c r="J31" s="385">
         <v>7.37</v>
       </c>
-      <c r="K31" s="383">
+      <c r="K31" s="386">
         <v>9.21</v>
       </c>
-      <c r="L31" s="386">
+      <c r="L31" s="380">
         <v>5.12</v>
       </c>
-      <c r="M31" s="378">
+      <c r="M31" s="381">
         <v>-2.72</v>
       </c>
-      <c r="N31" s="379">
+      <c r="N31" s="390">
         <v>-12.45</v>
       </c>
-      <c r="O31" s="387">
+      <c r="O31" s="389">
         <v>-21.22</v>
       </c>
-      <c r="P31" s="388">
+      <c r="P31" s="382">
         <v>-29.1</v>
       </c>
-      <c r="Q31" s="384">
+      <c r="Q31" s="378">
         <v>-33.39</v>
       </c>
-      <c r="R31" s="380">
+      <c r="R31" s="379">
         <v>-34.99</v>
       </c>
-      <c r="S31" s="381">
+      <c r="S31" s="387">
         <v>-32.95</v>
       </c>
-      <c r="T31" s="389">
+      <c r="T31" s="383">
         <v>-39.59</v>
       </c>
     </row>
@@ -10334,7 +10334,7 @@
       <c r="C32" t="str">
         <v>600151</v>
       </c>
-      <c r="D32" s="397" t="str">
+      <c r="D32" s="398" t="str">
         <v>净买: 7884.07万</v>
       </c>
       <c r="E32">
@@ -10349,40 +10349,40 @@
       <c r="H32">
         <v>3.26</v>
       </c>
-      <c r="I32" s="398">
+      <c r="I32" s="399">
         <v>-11.53</v>
       </c>
-      <c r="J32" s="402">
+      <c r="J32" s="400">
         <v>-20.23</v>
       </c>
       <c r="K32" s="392">
         <v>-21.06</v>
       </c>
-      <c r="L32" s="393">
+      <c r="L32" s="401">
         <v>-24.22</v>
       </c>
-      <c r="M32" s="396">
+      <c r="M32" s="393">
         <v>-21.69</v>
       </c>
-      <c r="N32" s="399">
+      <c r="N32" s="397">
         <v>-16.73</v>
       </c>
-      <c r="O32" s="403">
+      <c r="O32" s="402">
         <v>-25.05</v>
       </c>
-      <c r="P32" s="394">
+      <c r="P32" s="403">
         <v>-25.88</v>
       </c>
-      <c r="Q32" s="400">
+      <c r="Q32" s="394">
         <v>-27.43</v>
       </c>
-      <c r="R32" s="395">
+      <c r="R32" s="391">
         <v>-26.65</v>
       </c>
-      <c r="S32" s="401">
+      <c r="S32" s="395">
         <v>-26.61</v>
       </c>
-      <c r="T32" s="391">
+      <c r="T32" s="396">
         <v>-28.89</v>
       </c>
     </row>
@@ -10396,7 +10396,7 @@
       <c r="C33" t="str">
         <v>600916</v>
       </c>
-      <c r="D33" s="414" t="str">
+      <c r="D33" s="416" t="str">
         <v>净卖: -1428.23万</v>
       </c>
       <c r="E33">
@@ -10411,40 +10411,40 @@
       <c r="H33">
         <v>10.04</v>
       </c>
-      <c r="I33" s="415">
+      <c r="I33" s="409">
         <v>0</v>
       </c>
-      <c r="J33" s="416">
+      <c r="J33" s="410">
         <v>10.02</v>
       </c>
-      <c r="K33" s="404">
+      <c r="K33" s="411">
         <v>19.64</v>
       </c>
-      <c r="L33" s="409">
+      <c r="L33" s="412">
         <v>7.66</v>
       </c>
-      <c r="M33" s="405">
+      <c r="M33" s="413">
         <v>5.87</v>
       </c>
-      <c r="N33" s="410">
+      <c r="N33" s="404">
         <v>-0.81</v>
       </c>
-      <c r="O33" s="411">
+      <c r="O33" s="405">
         <v>-8.96</v>
       </c>
-      <c r="P33" s="406">
+      <c r="P33" s="414">
         <v>-6.93</v>
       </c>
-      <c r="Q33" s="407">
+      <c r="Q33" s="406">
         <v>-5.79</v>
       </c>
-      <c r="R33" s="412">
+      <c r="R33" s="407">
         <v>-8.96</v>
       </c>
       <c r="S33" s="408">
         <v>-9.54</v>
       </c>
-      <c r="T33" s="413">
+      <c r="T33" s="415">
         <v>-25.84</v>
       </c>
     </row>
@@ -10458,7 +10458,7 @@
       <c r="C34" t="str">
         <v>600969</v>
       </c>
-      <c r="D34" s="424" t="str">
+      <c r="D34" s="427" t="str">
         <v>净卖: -723.23万</v>
       </c>
       <c r="E34">
@@ -10473,40 +10473,40 @@
       <c r="H34">
         <v>0</v>
       </c>
-      <c r="I34" s="419">
+      <c r="I34" s="421">
         <v>-9.99</v>
       </c>
       <c r="J34" s="428">
         <v>-9.99</v>
       </c>
-      <c r="K34" s="420">
+      <c r="K34" s="422">
         <v>-18.98</v>
       </c>
-      <c r="L34" s="425">
+      <c r="L34" s="424">
         <v>-21.07</v>
       </c>
-      <c r="M34" s="422">
+      <c r="M34" s="429">
         <v>-21.98</v>
       </c>
-      <c r="N34" s="429">
+      <c r="N34" s="423">
         <v>-18.98</v>
       </c>
-      <c r="O34" s="426">
+      <c r="O34" s="417">
         <v>-16.9</v>
       </c>
-      <c r="P34" s="427">
+      <c r="P34" s="418">
         <v>-16.82</v>
       </c>
-      <c r="Q34" s="423">
+      <c r="Q34" s="419">
         <v>-14.32</v>
       </c>
-      <c r="R34" s="417">
+      <c r="R34" s="420">
         <v>-13.66</v>
       </c>
-      <c r="S34" s="418">
+      <c r="S34" s="425">
         <v>-15.99</v>
       </c>
-      <c r="T34" s="421">
+      <c r="T34" s="426">
         <v>-18.07</v>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       <c r="C35" t="str">
         <v>002040</v>
       </c>
-      <c r="D35" s="437" t="str">
+      <c r="D35" s="436" t="str">
         <v>净卖: -895.74万</v>
       </c>
       <c r="E35">
@@ -10535,40 +10535,40 @@
       <c r="H35">
         <v>-7.37</v>
       </c>
-      <c r="I35" s="438">
+      <c r="I35" s="437">
         <v>-2.87</v>
       </c>
-      <c r="J35" s="430">
+      <c r="J35" s="431">
         <v>-8.52</v>
       </c>
-      <c r="K35" s="432">
+      <c r="K35" s="441">
         <v>-8.36</v>
       </c>
-      <c r="L35" s="433">
+      <c r="L35" s="442">
         <v>-10.49</v>
       </c>
-      <c r="M35" s="439">
+      <c r="M35" s="434">
         <v>-8.44</v>
       </c>
-      <c r="N35" s="435">
+      <c r="N35" s="432">
         <v>-9.02</v>
       </c>
-      <c r="O35" s="440">
+      <c r="O35" s="438">
         <v>-9.51</v>
       </c>
-      <c r="P35" s="434">
+      <c r="P35" s="433">
         <v>-12.05</v>
       </c>
-      <c r="Q35" s="441">
+      <c r="Q35" s="439">
         <v>-8.28</v>
       </c>
-      <c r="R35" s="442">
+      <c r="R35" s="430">
         <v>-10.33</v>
       </c>
-      <c r="S35" s="436">
+      <c r="S35" s="440">
         <v>-11.07</v>
       </c>
-      <c r="T35" s="431">
+      <c r="T35" s="435">
         <v>-18.77</v>
       </c>
     </row>
@@ -10597,40 +10597,40 @@
       <c r="H36">
         <v>2.04</v>
       </c>
-      <c r="I36" s="455">
+      <c r="I36" s="452">
         <v>7.84</v>
       </c>
-      <c r="J36" s="445">
+      <c r="J36" s="455">
         <v>7.04</v>
       </c>
-      <c r="K36" s="451">
+      <c r="K36" s="453">
         <v>6.48</v>
       </c>
-      <c r="L36" s="443">
+      <c r="L36" s="449">
         <v>5.04</v>
       </c>
-      <c r="M36" s="444">
+      <c r="M36" s="443">
         <v>7.28</v>
       </c>
-      <c r="N36" s="446">
+      <c r="N36" s="444">
         <v>5.44</v>
       </c>
-      <c r="O36" s="452">
+      <c r="O36" s="451">
         <v>10.72</v>
       </c>
-      <c r="P36" s="453">
+      <c r="P36" s="445">
         <v>10.32</v>
       </c>
-      <c r="Q36" s="448">
+      <c r="Q36" s="446">
         <v>7.92</v>
       </c>
-      <c r="R36" s="449">
+      <c r="R36" s="454">
         <v>1.28</v>
       </c>
-      <c r="S36" s="454">
+      <c r="S36" s="447">
         <v>11.44</v>
       </c>
-      <c r="T36" s="447">
+      <c r="T36" s="448">
         <v>3.36</v>
       </c>
     </row>
@@ -10644,7 +10644,7 @@
       <c r="C37" t="str">
         <v>600495</v>
       </c>
-      <c r="D37" s="456" t="str">
+      <c r="D37" s="461" t="str">
         <v>净买: 998.97万</v>
       </c>
       <c r="E37">
@@ -10659,40 +10659,40 @@
       <c r="H37">
         <v>0</v>
       </c>
-      <c r="I37" s="463">
+      <c r="I37" s="462">
         <v>10.04</v>
       </c>
-      <c r="J37" s="457">
+      <c r="J37" s="468">
         <v>11.16</v>
       </c>
-      <c r="K37" s="465">
+      <c r="K37" s="457">
         <v>12.28</v>
       </c>
-      <c r="L37" s="466">
+      <c r="L37" s="458">
         <v>2.23</v>
       </c>
-      <c r="M37" s="458">
+      <c r="M37" s="463">
         <v>0.67</v>
       </c>
-      <c r="N37" s="459">
+      <c r="N37" s="464">
         <v>4.46</v>
       </c>
-      <c r="O37" s="467">
+      <c r="O37" s="465">
         <v>0.67</v>
       </c>
-      <c r="P37" s="461">
+      <c r="P37" s="456">
         <v>0.45</v>
       </c>
-      <c r="Q37" s="460">
+      <c r="Q37" s="459">
         <v>-1.34</v>
       </c>
-      <c r="R37" s="468">
+      <c r="R37" s="466">
         <v>-1.34</v>
       </c>
-      <c r="S37" s="462">
+      <c r="S37" s="467">
         <v>-2.01</v>
       </c>
-      <c r="T37" s="464">
+      <c r="T37" s="460">
         <v>-2.46</v>
       </c>
     </row>
@@ -10706,7 +10706,7 @@
       <c r="C38" t="str">
         <v>600488</v>
       </c>
-      <c r="D38" s="478" t="str">
+      <c r="D38" s="480" t="str">
         <v>净卖: -1388.23万</v>
       </c>
       <c r="E38">
@@ -10721,40 +10721,40 @@
       <c r="H38">
         <v>9.92</v>
       </c>
-      <c r="I38" s="472">
+      <c r="I38" s="473">
         <v>0</v>
       </c>
-      <c r="J38" s="469">
+      <c r="J38" s="474">
         <v>10.07</v>
       </c>
-      <c r="K38" s="473">
+      <c r="K38" s="471">
         <v>21.01</v>
       </c>
-      <c r="L38" s="474">
+      <c r="L38" s="478">
         <v>33.16</v>
       </c>
-      <c r="M38" s="475">
+      <c r="M38" s="479">
         <v>27.78</v>
       </c>
-      <c r="N38" s="476">
+      <c r="N38" s="475">
         <v>22.92</v>
       </c>
-      <c r="O38" s="479">
+      <c r="O38" s="472">
         <v>11.46</v>
       </c>
-      <c r="P38" s="470">
+      <c r="P38" s="481">
         <v>2.6</v>
       </c>
-      <c r="Q38" s="480">
+      <c r="Q38" s="476">
         <v>7.99</v>
       </c>
       <c r="R38" s="477">
         <v>18.75</v>
       </c>
-      <c r="S38" s="471">
+      <c r="S38" s="469">
         <v>9.2</v>
       </c>
-      <c r="T38" s="481">
+      <c r="T38" s="470">
         <v>5.21</v>
       </c>
     </row>
@@ -10817,37 +10817,37 @@
       <c r="F40" t="str"/>
       <c r="G40" t="str"/>
       <c r="H40" t="str"/>
-      <c r="I40" s="493">
+      <c r="I40" s="492">
         <v>54.05</v>
       </c>
-      <c r="J40" s="489">
+      <c r="J40" s="484">
         <v>62.16</v>
       </c>
-      <c r="K40" s="490">
+      <c r="K40" s="489">
         <v>54.05</v>
       </c>
-      <c r="L40" s="491">
+      <c r="L40" s="485">
         <v>56.76</v>
       </c>
-      <c r="M40" s="483">
+      <c r="M40" s="490">
         <v>51.35</v>
       </c>
-      <c r="N40" s="484">
+      <c r="N40" s="486">
         <v>48.65</v>
       </c>
-      <c r="O40" s="482">
+      <c r="O40" s="493">
         <v>45.95</v>
       </c>
-      <c r="P40" s="485">
+      <c r="P40" s="491">
         <v>40.54</v>
       </c>
-      <c r="Q40" s="487">
+      <c r="Q40" s="482">
         <v>35.14</v>
       </c>
-      <c r="R40" s="492">
+      <c r="R40" s="487">
         <v>37.84</v>
       </c>
-      <c r="S40" s="486">
+      <c r="S40" s="483">
         <v>37.84</v>
       </c>
       <c r="T40" s="488">
@@ -10865,37 +10865,37 @@
       <c r="F41" t="str"/>
       <c r="G41" t="str"/>
       <c r="H41" t="str"/>
-      <c r="I41" s="502">
+      <c r="I41" s="494">
         <v>2.35</v>
       </c>
-      <c r="J41" s="498">
+      <c r="J41" s="496">
         <v>3.37</v>
       </c>
-      <c r="K41" s="499">
+      <c r="K41" s="502">
         <v>3.41</v>
       </c>
-      <c r="L41" s="494">
+      <c r="L41" s="503">
         <v>3.11</v>
       </c>
-      <c r="M41" s="500">
+      <c r="M41" s="504">
         <v>4.56</v>
       </c>
-      <c r="N41" s="503">
+      <c r="N41" s="495">
         <v>3.99</v>
       </c>
-      <c r="O41" s="497">
+      <c r="O41" s="505">
         <v>2.28</v>
       </c>
-      <c r="P41" s="495">
+      <c r="P41" s="498">
         <v>0.79</v>
       </c>
-      <c r="Q41" s="504">
+      <c r="Q41" s="499">
         <v>-0.11</v>
       </c>
-      <c r="R41" s="505">
+      <c r="R41" s="500">
         <v>-0.68</v>
       </c>
-      <c r="S41" s="496">
+      <c r="S41" s="497">
         <v>-0.22</v>
       </c>
       <c r="T41" s="501">

--- a/youzi/湖州劳动路/index.xlsx
+++ b/youzi/湖州劳动路/index.xlsx
@@ -39,6 +39,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD02F3E"/>
         <bgColor/>
       </patternFill>
@@ -69,19 +93,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,18 +117,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -153,6 +153,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -165,25 +183,1249 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8BCF9B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8BCF9B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4553"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4CB564"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8336"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CFD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -195,31 +1437,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -237,43 +1479,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,97 +1629,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -387,19 +1707,775 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F9F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA6DAB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -417,13 +2493,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
+        <fgColor rgb="FFD23040"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -435,55 +2505,205 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF83CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -495,31 +2715,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECEE"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -531,61 +2829,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB1DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFEFA4AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -609,66 +2865,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
@@ -687,67 +2883,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4553"/>
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -759,2257 +3009,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BCF9B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BCF9B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8336"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF78C88A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4CB564"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CFD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2DA949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA6DAB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8136"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF83CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77782"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF95D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AFB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E1BF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3021,7 +3045,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1AFB5"/>
+        <fgColor rgb="FFB62431"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3033,37 +3057,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB5E1BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C41"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -8474,7 +8474,7 @@
       <c r="C2" t="str">
         <v>002105</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="11" t="str">
         <v>净卖: -286.93万</v>
       </c>
       <c r="E2">
@@ -8489,41 +8489,41 @@
       <c r="H2">
         <v>3.63</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="5">
         <v>6.13</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="12">
         <v>16.75</v>
       </c>
-      <c r="K2" s="10">
+      <c r="K2" s="3">
         <v>28.37</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="13">
         <v>41.25</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="7">
         <v>55.38</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="8">
         <v>46.12</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="4">
         <v>46.75</v>
       </c>
-      <c r="P2" s="11">
+      <c r="P2" s="9">
         <v>33.13</v>
       </c>
       <c r="Q2" s="6">
         <v>34.87</v>
       </c>
-      <c r="R2" s="12">
+      <c r="R2" s="1">
         <v>21.38</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="2">
         <v>11.62</v>
       </c>
-      <c r="T2" s="13">
-        <v>-21</v>
+      <c r="T2" s="10">
+        <v>-20.13</v>
       </c>
     </row>
     <row r="3">
@@ -8536,7 +8536,7 @@
       <c r="C3" t="str">
         <v>002760</v>
       </c>
-      <c r="D3" s="21" t="str">
+      <c r="D3" s="24" t="str">
         <v>净买: 1264.22万</v>
       </c>
       <c r="E3">
@@ -8557,35 +8557,35 @@
       <c r="J3" s="19">
         <v>2.8</v>
       </c>
-      <c r="K3" s="26">
+      <c r="K3" s="20">
         <v>-6.84</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="17">
         <v>-13.76</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="25">
         <v>-13.72</v>
       </c>
-      <c r="N3" s="16">
+      <c r="N3" s="23">
         <v>-14.84</v>
       </c>
-      <c r="O3" s="24">
+      <c r="O3" s="26">
         <v>-15.92</v>
       </c>
-      <c r="P3" s="17">
+      <c r="P3" s="14">
         <v>-16.68</v>
       </c>
-      <c r="Q3" s="25">
+      <c r="Q3" s="21">
         <v>-19.6</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="18">
         <v>-22.72</v>
       </c>
-      <c r="S3" s="18">
+      <c r="S3" s="15">
         <v>-23.88</v>
       </c>
-      <c r="T3" s="20">
-        <v>-12.4</v>
+      <c r="T3" s="16">
+        <v>-11.96</v>
       </c>
     </row>
     <row r="4">
@@ -8598,7 +8598,7 @@
       <c r="C4" t="str">
         <v>002760</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="28" t="str">
         <v>净卖: -1488.32万</v>
       </c>
       <c r="E4">
@@ -8613,41 +8613,41 @@
       <c r="H4">
         <v>4.59</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="38">
         <v>-7.59</v>
       </c>
       <c r="J4" s="29">
         <v>-16.25</v>
       </c>
-      <c r="K4" s="33">
+      <c r="K4" s="36">
         <v>-22.47</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="30">
         <v>-22.44</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="34">
         <v>-23.44</v>
       </c>
       <c r="N4" s="39">
         <v>-24.42</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="31">
         <v>-25.1</v>
       </c>
-      <c r="P4" s="37">
+      <c r="P4" s="32">
         <v>-27.72</v>
       </c>
-      <c r="Q4" s="38">
+      <c r="Q4" s="33">
         <v>-30.53</v>
       </c>
-      <c r="R4" s="27">
+      <c r="R4" s="35">
         <v>-31.57</v>
       </c>
-      <c r="S4" s="30">
+      <c r="S4" s="27">
         <v>-31.07</v>
       </c>
-      <c r="T4" s="31">
-        <v>-21.25</v>
+      <c r="T4" s="37">
+        <v>-20.86</v>
       </c>
     </row>
     <row r="5">
@@ -8660,7 +8660,7 @@
       <c r="C5" t="str">
         <v>603958</v>
       </c>
-      <c r="D5" s="41" t="str">
+      <c r="D5" s="52" t="str">
         <v>净买: 2814.34万</v>
       </c>
       <c r="E5">
@@ -8675,41 +8675,41 @@
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="45">
         <v>-3.71</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="40">
         <v>-13.32</v>
       </c>
-      <c r="K5" s="51">
+      <c r="K5" s="41">
         <v>-18.35</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="46">
         <v>-15.42</v>
       </c>
-      <c r="M5" s="46">
+      <c r="M5" s="47">
         <v>-11.81</v>
       </c>
       <c r="N5" s="42">
         <v>-11.27</v>
       </c>
-      <c r="O5" s="52">
+      <c r="O5" s="43">
         <v>-11.13</v>
       </c>
-      <c r="P5" s="43">
+      <c r="P5" s="48">
         <v>-13.08</v>
       </c>
-      <c r="Q5" s="44">
+      <c r="Q5" s="51">
         <v>-16.15</v>
       </c>
-      <c r="R5" s="40">
+      <c r="R5" s="49">
         <v>-17.72</v>
       </c>
-      <c r="S5" s="45">
+      <c r="S5" s="44">
         <v>-18.79</v>
       </c>
-      <c r="T5" s="47">
-        <v>24.11</v>
+      <c r="T5" s="50">
+        <v>22.65</v>
       </c>
     </row>
     <row r="6">
@@ -8722,7 +8722,7 @@
       <c r="C6" t="str">
         <v>603958</v>
       </c>
-      <c r="D6" s="58" t="str">
+      <c r="D6" s="53" t="str">
         <v>净卖: -2283.55万</v>
       </c>
       <c r="E6">
@@ -8737,41 +8737,41 @@
       <c r="H6">
         <v>-6.13</v>
       </c>
-      <c r="I6" s="55">
+      <c r="I6" s="54">
         <v>-4.1</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="63">
         <v>-9.67</v>
       </c>
-      <c r="K6" s="65">
+      <c r="K6" s="60">
         <v>-6.43</v>
       </c>
-      <c r="L6" s="59">
+      <c r="L6" s="55">
         <v>-2.43</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="56">
         <v>-1.84</v>
       </c>
-      <c r="N6" s="56">
+      <c r="N6" s="57">
         <v>-1.67</v>
       </c>
-      <c r="O6" s="60">
+      <c r="O6" s="64">
         <v>-3.83</v>
       </c>
-      <c r="P6" s="61">
+      <c r="P6" s="65">
         <v>-7.24</v>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="58">
         <v>-8.96</v>
       </c>
-      <c r="R6" s="54">
+      <c r="R6" s="61">
         <v>-10.15</v>
       </c>
-      <c r="S6" s="63">
+      <c r="S6" s="59">
         <v>-9.99</v>
       </c>
-      <c r="T6" s="57">
-        <v>37.31</v>
+      <c r="T6" s="62">
+        <v>35.69</v>
       </c>
     </row>
     <row r="7">
@@ -8784,7 +8784,7 @@
       <c r="C7" t="str">
         <v>002645</v>
       </c>
-      <c r="D7" s="76" t="str">
+      <c r="D7" s="67" t="str">
         <v>净买: 1223.21万</v>
       </c>
       <c r="E7">
@@ -8799,41 +8799,41 @@
       <c r="H7">
         <v>1.72</v>
       </c>
-      <c r="I7" s="70">
+      <c r="I7" s="72">
         <v>8.14</v>
       </c>
-      <c r="J7" s="77">
+      <c r="J7" s="73">
         <v>5.31</v>
       </c>
-      <c r="K7" s="73">
+      <c r="K7" s="74">
         <v>9.04</v>
       </c>
-      <c r="L7" s="74">
+      <c r="L7" s="75">
         <v>4.75</v>
       </c>
-      <c r="M7" s="78">
+      <c r="M7" s="68">
         <v>3.5</v>
       </c>
-      <c r="N7" s="66">
+      <c r="N7" s="77">
         <v>-6.89</v>
       </c>
-      <c r="O7" s="71">
+      <c r="O7" s="69">
         <v>-5.42</v>
       </c>
-      <c r="P7" s="75">
+      <c r="P7" s="76">
         <v>-7.12</v>
       </c>
-      <c r="Q7" s="68">
+      <c r="Q7" s="70">
         <v>-7.23</v>
       </c>
-      <c r="R7" s="67">
+      <c r="R7" s="78">
         <v>-10.73</v>
       </c>
-      <c r="S7" s="72">
+      <c r="S7" s="66">
         <v>-9.94</v>
       </c>
-      <c r="T7" s="69">
-        <v>152.09</v>
+      <c r="T7" s="71">
+        <v>158.53</v>
       </c>
     </row>
     <row r="8">
@@ -8846,7 +8846,7 @@
       <c r="C8" t="str">
         <v>600537</v>
       </c>
-      <c r="D8" s="82" t="str">
+      <c r="D8" s="87" t="str">
         <v>净买: 358.47万</v>
       </c>
       <c r="E8">
@@ -8861,41 +8861,41 @@
       <c r="H8">
         <v>5.03</v>
       </c>
-      <c r="I8" s="85">
+      <c r="I8" s="84">
         <v>4.79</v>
       </c>
-      <c r="J8" s="86">
+      <c r="J8" s="85">
         <v>8.98</v>
       </c>
-      <c r="K8" s="83">
+      <c r="K8" s="88">
         <v>-1.8</v>
       </c>
-      <c r="L8" s="87">
+      <c r="L8" s="89">
         <v>8.08</v>
       </c>
-      <c r="M8" s="91">
+      <c r="M8" s="83">
         <v>18.86</v>
       </c>
-      <c r="N8" s="79">
+      <c r="N8" s="90">
         <v>19.76</v>
       </c>
-      <c r="O8" s="80">
+      <c r="O8" s="82">
         <v>19.16</v>
       </c>
-      <c r="P8" s="84">
+      <c r="P8" s="91">
         <v>15.57</v>
       </c>
-      <c r="Q8" s="88">
+      <c r="Q8" s="79">
         <v>8.38</v>
       </c>
-      <c r="R8" s="89">
+      <c r="R8" s="80">
         <v>4.49</v>
       </c>
       <c r="S8" s="81">
         <v>14.97</v>
       </c>
-      <c r="T8" s="90">
-        <v>20.36</v>
+      <c r="T8" s="86">
+        <v>9.88</v>
       </c>
     </row>
     <row r="9">
@@ -8908,7 +8908,7 @@
       <c r="C9" t="str">
         <v>603122</v>
       </c>
-      <c r="D9" s="93" t="str">
+      <c r="D9" s="92" t="str">
         <v>净卖: -557.16万</v>
       </c>
       <c r="E9">
@@ -8923,41 +8923,41 @@
       <c r="H9">
         <v>7.07</v>
       </c>
-      <c r="I9" s="102">
+      <c r="I9" s="95">
         <v>2.8</v>
       </c>
-      <c r="J9" s="96">
+      <c r="J9" s="103">
         <v>13.09</v>
       </c>
-      <c r="K9" s="103">
+      <c r="K9" s="100">
         <v>24.4</v>
       </c>
-      <c r="L9" s="97">
+      <c r="L9" s="93">
         <v>36.85</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="96">
         <v>50.57</v>
       </c>
-      <c r="N9" s="95">
+      <c r="N9" s="104">
         <v>65.69</v>
       </c>
-      <c r="O9" s="98">
+      <c r="O9" s="97">
         <v>82.21</v>
       </c>
-      <c r="P9" s="99">
+      <c r="P9" s="101">
         <v>100.38</v>
       </c>
-      <c r="Q9" s="104">
+      <c r="Q9" s="98">
         <v>110.93</v>
       </c>
-      <c r="R9" s="92">
+      <c r="R9" s="94">
         <v>132.02</v>
       </c>
-      <c r="S9" s="100">
+      <c r="S9" s="102">
         <v>155.27</v>
       </c>
-      <c r="T9" s="101">
-        <v>105.34</v>
+      <c r="T9" s="99">
+        <v>108.13</v>
       </c>
     </row>
     <row r="10">
@@ -8970,7 +8970,7 @@
       <c r="C10" t="str">
         <v>002682</v>
       </c>
-      <c r="D10" s="105" t="str">
+      <c r="D10" s="111" t="str">
         <v>净买: 749.97万</v>
       </c>
       <c r="E10">
@@ -8985,41 +8985,41 @@
       <c r="H10">
         <v>10.02</v>
       </c>
-      <c r="I10" s="106">
+      <c r="I10" s="112">
         <v>0</v>
       </c>
-      <c r="J10" s="107">
+      <c r="J10" s="109">
         <v>10.03</v>
       </c>
-      <c r="K10" s="108">
+      <c r="K10" s="113">
         <v>20.99</v>
       </c>
-      <c r="L10" s="115">
+      <c r="L10" s="105">
         <v>8.95</v>
       </c>
-      <c r="M10" s="116">
+      <c r="M10" s="106">
         <v>-2.01</v>
       </c>
-      <c r="N10" s="109">
+      <c r="N10" s="114">
         <v>-11.73</v>
       </c>
-      <c r="O10" s="111">
+      <c r="O10" s="115">
         <v>-16.05</v>
       </c>
-      <c r="P10" s="112">
+      <c r="P10" s="116">
         <v>-13.73</v>
       </c>
       <c r="Q10" s="117">
         <v>-17.59</v>
       </c>
-      <c r="R10" s="110">
+      <c r="R10" s="107">
         <v>-17.28</v>
       </c>
-      <c r="S10" s="113">
+      <c r="S10" s="108">
         <v>-14.04</v>
       </c>
-      <c r="T10" s="114">
-        <v>-8.33</v>
+      <c r="T10" s="110">
+        <v>-7.1</v>
       </c>
     </row>
     <row r="11">
@@ -9032,7 +9032,7 @@
       <c r="C11" t="str">
         <v>600227</v>
       </c>
-      <c r="D11" s="126" t="str">
+      <c r="D11" s="129" t="str">
         <v>净买: 484.48万</v>
       </c>
       <c r="E11">
@@ -9047,41 +9047,41 @@
       <c r="H11">
         <v>1.56</v>
       </c>
-      <c r="I11" s="120">
+      <c r="I11" s="130">
         <v>8.43</v>
       </c>
-      <c r="J11" s="127">
+      <c r="J11" s="121">
         <v>13.79</v>
       </c>
-      <c r="K11" s="123">
+      <c r="K11" s="122">
         <v>9.2</v>
       </c>
-      <c r="L11" s="118">
+      <c r="L11" s="123">
         <v>7.28</v>
       </c>
-      <c r="M11" s="128">
+      <c r="M11" s="118">
         <v>2.68</v>
       </c>
-      <c r="N11" s="119">
+      <c r="N11" s="124">
         <v>4.6</v>
       </c>
-      <c r="O11" s="121">
+      <c r="O11" s="126">
         <v>0.77</v>
       </c>
-      <c r="P11" s="124">
+      <c r="P11" s="125">
         <v>-4.6</v>
       </c>
-      <c r="Q11" s="125">
+      <c r="Q11" s="119">
         <v>-2.68</v>
       </c>
-      <c r="R11" s="129">
+      <c r="R11" s="127">
         <v>-4.6</v>
       </c>
-      <c r="S11" s="130">
+      <c r="S11" s="120">
         <v>-2.68</v>
       </c>
-      <c r="T11" s="122">
-        <v>32.57</v>
+      <c r="T11" s="128">
+        <v>34.48</v>
       </c>
     </row>
     <row r="12">
@@ -9094,7 +9094,7 @@
       <c r="C12" t="str">
         <v>603386</v>
       </c>
-      <c r="D12" s="142" t="str">
+      <c r="D12" s="131" t="str">
         <v>净卖: -4389.34万</v>
       </c>
       <c r="E12">
@@ -9109,41 +9109,41 @@
       <c r="H12">
         <v>-8.19</v>
       </c>
-      <c r="I12" s="143">
+      <c r="I12" s="132">
         <v>-1.95</v>
       </c>
-      <c r="J12" s="140">
+      <c r="J12" s="138">
         <v>-3.78</v>
       </c>
-      <c r="K12" s="131">
+      <c r="K12" s="133">
         <v>-11.08</v>
       </c>
-      <c r="L12" s="132">
+      <c r="L12" s="134">
         <v>-18.92</v>
       </c>
-      <c r="M12" s="133">
+      <c r="M12" s="139">
         <v>-18.16</v>
       </c>
       <c r="N12" s="141">
         <v>-18.54</v>
       </c>
-      <c r="O12" s="136">
+      <c r="O12" s="142">
         <v>-17.08</v>
       </c>
-      <c r="P12" s="137">
+      <c r="P12" s="140">
         <v>-17.95</v>
       </c>
-      <c r="Q12" s="134">
+      <c r="Q12" s="137">
         <v>-14.43</v>
       </c>
       <c r="R12" s="135">
         <v>-20</v>
       </c>
-      <c r="S12" s="138">
+      <c r="S12" s="143">
         <v>-18.32</v>
       </c>
-      <c r="T12" s="139">
-        <v>-22.43</v>
+      <c r="T12" s="136">
+        <v>-21.68</v>
       </c>
     </row>
     <row r="13">
@@ -9156,7 +9156,7 @@
       <c r="C13" t="str">
         <v>600493</v>
       </c>
-      <c r="D13" s="154" t="str">
+      <c r="D13" s="148" t="str">
         <v>净买: 999.07万</v>
       </c>
       <c r="E13">
@@ -9171,41 +9171,41 @@
       <c r="H13">
         <v>1.85</v>
       </c>
-      <c r="I13" s="144">
+      <c r="I13" s="152">
         <v>8.05</v>
       </c>
-      <c r="J13" s="150">
+      <c r="J13" s="149">
         <v>-0.65</v>
       </c>
-      <c r="K13" s="145">
+      <c r="K13" s="153">
         <v>3.12</v>
       </c>
-      <c r="L13" s="155">
+      <c r="L13" s="144">
         <v>-4.16</v>
       </c>
-      <c r="M13" s="146">
+      <c r="M13" s="145">
         <v>-8.05</v>
       </c>
-      <c r="N13" s="156">
+      <c r="N13" s="154">
         <v>1.17</v>
       </c>
-      <c r="O13" s="147">
+      <c r="O13" s="155">
         <v>-1.3</v>
       </c>
-      <c r="P13" s="148">
+      <c r="P13" s="150">
         <v>-2.47</v>
       </c>
-      <c r="Q13" s="153">
+      <c r="Q13" s="151">
         <v>1.56</v>
       </c>
-      <c r="R13" s="151">
+      <c r="R13" s="146">
         <v>3.77</v>
       </c>
-      <c r="S13" s="149">
+      <c r="S13" s="156">
         <v>4.03</v>
       </c>
-      <c r="T13" s="152">
-        <v>-3.12</v>
+      <c r="T13" s="147">
+        <v>-2.86</v>
       </c>
     </row>
     <row r="14">
@@ -9218,7 +9218,7 @@
       <c r="C14" t="str">
         <v>001330</v>
       </c>
-      <c r="D14" s="168" t="str">
+      <c r="D14" s="162" t="str">
         <v>净卖: -4990.62万</v>
       </c>
       <c r="E14">
@@ -9233,41 +9233,41 @@
       <c r="H14">
         <v>1.65</v>
       </c>
-      <c r="I14" s="169">
+      <c r="I14" s="168">
         <v>8.18</v>
       </c>
-      <c r="J14" s="165">
+      <c r="J14" s="157">
         <v>-2.59</v>
       </c>
-      <c r="K14" s="157">
+      <c r="K14" s="163">
         <v>-12.32</v>
       </c>
-      <c r="L14" s="166">
+      <c r="L14" s="158">
         <v>-20.34</v>
       </c>
-      <c r="M14" s="158">
+      <c r="M14" s="169">
         <v>-12.4</v>
       </c>
-      <c r="N14" s="163">
+      <c r="N14" s="164">
         <v>-18.4</v>
       </c>
       <c r="O14" s="159">
         <v>-26.58</v>
       </c>
-      <c r="P14" s="167">
+      <c r="P14" s="166">
         <v>-33.95</v>
       </c>
-      <c r="Q14" s="160">
+      <c r="Q14" s="165">
         <v>-32.82</v>
       </c>
-      <c r="R14" s="161">
+      <c r="R14" s="160">
         <v>-35.66</v>
       </c>
-      <c r="S14" s="162">
+      <c r="S14" s="161">
         <v>-34.76</v>
       </c>
-      <c r="T14" s="164">
-        <v>-33.31</v>
+      <c r="T14" s="167">
+        <v>-32.01</v>
       </c>
     </row>
     <row r="15">
@@ -9280,7 +9280,7 @@
       <c r="C15" t="str">
         <v>600865</v>
       </c>
-      <c r="D15" s="174" t="str">
+      <c r="D15" s="181" t="str">
         <v>净买: 4692.22万</v>
       </c>
       <c r="E15">
@@ -9295,13 +9295,13 @@
       <c r="H15">
         <v>10.02</v>
       </c>
-      <c r="I15" s="175">
+      <c r="I15" s="182">
         <v>0</v>
       </c>
-      <c r="J15" s="181">
+      <c r="J15" s="176">
         <v>10.01</v>
       </c>
-      <c r="K15" s="182">
+      <c r="K15" s="173">
         <v>21</v>
       </c>
       <c r="L15" s="177">
@@ -9313,22 +9313,22 @@
       <c r="N15" s="178">
         <v>27.75</v>
       </c>
-      <c r="O15" s="172">
+      <c r="O15" s="174">
         <v>37.2</v>
       </c>
-      <c r="P15" s="171">
+      <c r="P15" s="180">
         <v>50.9</v>
       </c>
       <c r="Q15" s="179">
         <v>48.33</v>
       </c>
-      <c r="R15" s="176">
+      <c r="R15" s="171">
         <v>33.52</v>
       </c>
-      <c r="S15" s="180">
+      <c r="S15" s="172">
         <v>20.17</v>
       </c>
-      <c r="T15" s="173">
+      <c r="T15" s="175">
         <v>-20.38</v>
       </c>
     </row>
@@ -9342,7 +9342,7 @@
       <c r="C16" t="str">
         <v>600865</v>
       </c>
-      <c r="D16" s="186" t="str">
+      <c r="D16" s="195" t="str">
         <v>净卖: -5679.38万</v>
       </c>
       <c r="E16">
@@ -9357,37 +9357,37 @@
       <c r="H16">
         <v>10.01</v>
       </c>
-      <c r="I16" s="187">
+      <c r="I16" s="183">
         <v>0</v>
       </c>
-      <c r="J16" s="183">
+      <c r="J16" s="189">
         <v>9.99</v>
       </c>
-      <c r="K16" s="192">
+      <c r="K16" s="184">
         <v>13.84</v>
       </c>
-      <c r="L16" s="188">
+      <c r="L16" s="186">
         <v>20.1</v>
       </c>
-      <c r="M16" s="193">
+      <c r="M16" s="192">
         <v>16.12</v>
       </c>
-      <c r="N16" s="189">
+      <c r="N16" s="193">
         <v>24.72</v>
       </c>
-      <c r="O16" s="184">
+      <c r="O16" s="194">
         <v>37.17</v>
       </c>
-      <c r="P16" s="190">
+      <c r="P16" s="187">
         <v>34.83</v>
       </c>
       <c r="Q16" s="185">
         <v>21.37</v>
       </c>
-      <c r="R16" s="194">
+      <c r="R16" s="190">
         <v>9.23</v>
       </c>
-      <c r="S16" s="195">
+      <c r="S16" s="188">
         <v>3.67</v>
       </c>
       <c r="T16" s="191">
@@ -9404,7 +9404,7 @@
       <c r="C17" t="str">
         <v>600693</v>
       </c>
-      <c r="D17" s="199" t="str">
+      <c r="D17" s="205" t="str">
         <v>净买: 4205.60万</v>
       </c>
       <c r="E17">
@@ -9419,41 +9419,41 @@
       <c r="H17">
         <v>2.51</v>
       </c>
-      <c r="I17" s="200">
+      <c r="I17" s="203">
         <v>0.41</v>
       </c>
-      <c r="J17" s="196">
+      <c r="J17" s="206">
         <v>-0.58</v>
       </c>
-      <c r="K17" s="197">
+      <c r="K17" s="207">
         <v>9.33</v>
       </c>
-      <c r="L17" s="201">
+      <c r="L17" s="204">
         <v>13.77</v>
       </c>
-      <c r="M17" s="205">
+      <c r="M17" s="199">
         <v>25.15</v>
       </c>
-      <c r="N17" s="206">
+      <c r="N17" s="208">
         <v>22</v>
       </c>
-      <c r="O17" s="202">
+      <c r="O17" s="196">
         <v>27.65</v>
       </c>
-      <c r="P17" s="203">
+      <c r="P17" s="197">
         <v>15.52</v>
       </c>
-      <c r="Q17" s="204">
+      <c r="Q17" s="198">
         <v>3.97</v>
       </c>
-      <c r="R17" s="198">
+      <c r="R17" s="201">
         <v>3.97</v>
       </c>
-      <c r="S17" s="207">
+      <c r="S17" s="200">
         <v>7.29</v>
       </c>
-      <c r="T17" s="208">
-        <v>-30.51</v>
+      <c r="T17" s="202">
+        <v>-29.99</v>
       </c>
     </row>
     <row r="18">
@@ -9466,7 +9466,7 @@
       <c r="C18" t="str">
         <v>603023</v>
       </c>
-      <c r="D18" s="211" t="str">
+      <c r="D18" s="215" t="str">
         <v>净买: 2053.34万</v>
       </c>
       <c r="E18">
@@ -9484,38 +9484,38 @@
       <c r="I18" s="218">
         <v>10.48</v>
       </c>
-      <c r="J18" s="210">
+      <c r="J18" s="219">
         <v>13.9</v>
       </c>
-      <c r="K18" s="212">
+      <c r="K18" s="209">
         <v>10.1</v>
       </c>
-      <c r="L18" s="219">
+      <c r="L18" s="210">
         <v>5.14</v>
       </c>
-      <c r="M18" s="213">
+      <c r="M18" s="211">
         <v>4.95</v>
       </c>
-      <c r="N18" s="214">
+      <c r="N18" s="212">
         <v>6.29</v>
       </c>
-      <c r="O18" s="221">
+      <c r="O18" s="216">
         <v>0.57</v>
       </c>
-      <c r="P18" s="215">
+      <c r="P18" s="213">
         <v>1.9</v>
       </c>
-      <c r="Q18" s="216">
+      <c r="Q18" s="217">
         <v>-4.19</v>
       </c>
-      <c r="R18" s="217">
+      <c r="R18" s="214">
         <v>-2.48</v>
       </c>
-      <c r="S18" s="209">
+      <c r="S18" s="220">
         <v>7.24</v>
       </c>
-      <c r="T18" s="220">
-        <v>-14.86</v>
+      <c r="T18" s="221">
+        <v>-14.67</v>
       </c>
     </row>
     <row r="19">
@@ -9528,7 +9528,7 @@
       <c r="C19" t="str">
         <v>601566</v>
       </c>
-      <c r="D19" s="228" t="str">
+      <c r="D19" s="230" t="str">
         <v>净卖: -2383.06万</v>
       </c>
       <c r="E19">
@@ -9543,41 +9543,41 @@
       <c r="H19">
         <v>3.63</v>
       </c>
-      <c r="I19" s="224">
+      <c r="I19" s="231">
         <v>6.13</v>
       </c>
-      <c r="J19" s="225">
+      <c r="J19" s="232">
         <v>2.75</v>
       </c>
       <c r="K19" s="229">
         <v>-4.06</v>
       </c>
-      <c r="L19" s="230">
+      <c r="L19" s="225">
         <v>-3.37</v>
       </c>
-      <c r="M19" s="222">
+      <c r="M19" s="233">
         <v>-6.81</v>
       </c>
       <c r="N19" s="234">
         <v>-7.5</v>
       </c>
-      <c r="O19" s="226">
+      <c r="O19" s="222">
         <v>-12.5</v>
       </c>
-      <c r="P19" s="227">
+      <c r="P19" s="228">
         <v>-13.88</v>
       </c>
-      <c r="Q19" s="231">
+      <c r="Q19" s="223">
         <v>-18.06</v>
       </c>
-      <c r="R19" s="223">
+      <c r="R19" s="226">
         <v>-17.94</v>
       </c>
-      <c r="S19" s="232">
+      <c r="S19" s="227">
         <v>-16.56</v>
       </c>
-      <c r="T19" s="233">
-        <v>-33.25</v>
+      <c r="T19" s="224">
+        <v>-32.38</v>
       </c>
     </row>
     <row r="20">
@@ -9590,7 +9590,7 @@
       <c r="C20" t="str">
         <v>600865</v>
       </c>
-      <c r="D20" s="244" t="str">
+      <c r="D20" s="239" t="str">
         <v>净卖: -5744.79万</v>
       </c>
       <c r="E20">
@@ -9605,40 +9605,40 @@
       <c r="H20">
         <v>-5.17</v>
       </c>
-      <c r="I20" s="247">
+      <c r="I20" s="241">
         <v>9.15</v>
       </c>
-      <c r="J20" s="236">
+      <c r="J20" s="242">
         <v>15.15</v>
       </c>
-      <c r="K20" s="245">
+      <c r="K20" s="237">
         <v>11.33</v>
       </c>
-      <c r="L20" s="241">
+      <c r="L20" s="246">
         <v>19.58</v>
       </c>
-      <c r="M20" s="237">
+      <c r="M20" s="247">
         <v>31.52</v>
       </c>
-      <c r="N20" s="235">
+      <c r="N20" s="238">
         <v>29.27</v>
       </c>
-      <c r="O20" s="238">
+      <c r="O20" s="243">
         <v>16.36</v>
       </c>
-      <c r="P20" s="242">
+      <c r="P20" s="235">
         <v>4.73</v>
       </c>
-      <c r="Q20" s="239">
+      <c r="Q20" s="244">
         <v>-0.61</v>
       </c>
-      <c r="R20" s="240">
+      <c r="R20" s="236">
         <v>0.12</v>
       </c>
-      <c r="S20" s="246">
+      <c r="S20" s="245">
         <v>0.12</v>
       </c>
-      <c r="T20" s="243">
+      <c r="T20" s="240">
         <v>-30.61</v>
       </c>
     </row>
@@ -9652,7 +9652,7 @@
       <c r="C21" t="str">
         <v>001317</v>
       </c>
-      <c r="D21" s="248" t="str">
+      <c r="D21" s="255" t="str">
         <v>净卖: -1614.69万</v>
       </c>
       <c r="E21">
@@ -9667,41 +9667,41 @@
       <c r="H21">
         <v>-0.39</v>
       </c>
-      <c r="I21" s="260">
+      <c r="I21" s="253">
         <v>3.7</v>
       </c>
-      <c r="J21" s="252">
+      <c r="J21" s="260">
         <v>-1.32</v>
       </c>
-      <c r="K21" s="249">
+      <c r="K21" s="256">
         <v>-4.71</v>
       </c>
-      <c r="L21" s="253">
+      <c r="L21" s="257">
         <v>-6.34</v>
       </c>
-      <c r="M21" s="257">
+      <c r="M21" s="258">
         <v>-4.27</v>
       </c>
-      <c r="N21" s="254">
+      <c r="N21" s="249">
         <v>-2.18</v>
       </c>
       <c r="O21" s="250">
         <v>0.05</v>
       </c>
-      <c r="P21" s="258">
+      <c r="P21" s="259">
         <v>-1.59</v>
       </c>
       <c r="Q21" s="251">
         <v>-4.68</v>
       </c>
-      <c r="R21" s="255">
+      <c r="R21" s="252">
         <v>-5.25</v>
       </c>
-      <c r="S21" s="256">
+      <c r="S21" s="254">
         <v>-4.79</v>
       </c>
-      <c r="T21" s="259">
-        <v>-10.84</v>
+      <c r="T21" s="248">
+        <v>-9.36</v>
       </c>
     </row>
     <row r="22">
@@ -9714,7 +9714,7 @@
       <c r="C22" t="str">
         <v>002792</v>
       </c>
-      <c r="D22" s="261" t="str">
+      <c r="D22" s="265" t="str">
         <v>净买: 6812.35万</v>
       </c>
       <c r="E22">
@@ -9729,41 +9729,41 @@
       <c r="H22">
         <v>4.23</v>
       </c>
-      <c r="I22" s="262">
+      <c r="I22" s="266">
         <v>5.52</v>
       </c>
-      <c r="J22" s="263">
+      <c r="J22" s="269">
         <v>-2.54</v>
       </c>
-      <c r="K22" s="268">
+      <c r="K22" s="262">
         <v>3.61</v>
       </c>
-      <c r="L22" s="271">
+      <c r="L22" s="267">
         <v>13.97</v>
       </c>
-      <c r="M22" s="264">
+      <c r="M22" s="270">
         <v>25.37</v>
       </c>
-      <c r="N22" s="269">
+      <c r="N22" s="271">
         <v>26.81</v>
       </c>
-      <c r="O22" s="272">
+      <c r="O22" s="268">
         <v>18.51</v>
       </c>
-      <c r="P22" s="273">
+      <c r="P22" s="263">
         <v>27.46</v>
       </c>
-      <c r="Q22" s="270">
+      <c r="Q22" s="272">
         <v>36.75</v>
       </c>
-      <c r="R22" s="265">
+      <c r="R22" s="273">
         <v>41.37</v>
       </c>
-      <c r="S22" s="266">
+      <c r="S22" s="264">
         <v>55.52</v>
       </c>
-      <c r="T22" s="267">
-        <v>52.3</v>
+      <c r="T22" s="261">
+        <v>57.85</v>
       </c>
     </row>
     <row r="23">
@@ -9776,7 +9776,7 @@
       <c r="C23" t="str">
         <v>603023</v>
       </c>
-      <c r="D23" s="281" t="str">
+      <c r="D23" s="278" t="str">
         <v>净卖: -1105.11万</v>
       </c>
       <c r="E23">
@@ -9791,41 +9791,41 @@
       <c r="H23">
         <v>4.14</v>
       </c>
-      <c r="I23" s="282">
+      <c r="I23" s="274">
         <v>-0.99</v>
       </c>
-      <c r="J23" s="274">
+      <c r="J23" s="283">
         <v>-4.3</v>
       </c>
-      <c r="K23" s="275">
+      <c r="K23" s="284">
         <v>-8.61</v>
       </c>
-      <c r="L23" s="283">
+      <c r="L23" s="286">
         <v>-8.77</v>
       </c>
-      <c r="M23" s="278">
+      <c r="M23" s="275">
         <v>-7.62</v>
       </c>
-      <c r="N23" s="276">
+      <c r="N23" s="279">
         <v>-12.58</v>
       </c>
-      <c r="O23" s="279">
+      <c r="O23" s="280">
         <v>-11.42</v>
       </c>
-      <c r="P23" s="285">
+      <c r="P23" s="276">
         <v>-16.72</v>
       </c>
-      <c r="Q23" s="286">
+      <c r="Q23" s="281">
         <v>-15.23</v>
       </c>
-      <c r="R23" s="277">
+      <c r="R23" s="285">
         <v>-6.79</v>
       </c>
-      <c r="S23" s="284">
+      <c r="S23" s="277">
         <v>-7.62</v>
       </c>
-      <c r="T23" s="280">
-        <v>-25.99</v>
+      <c r="T23" s="282">
+        <v>-25.83</v>
       </c>
     </row>
     <row r="24">
@@ -9853,41 +9853,41 @@
       <c r="H24">
         <v>-1.32</v>
       </c>
-      <c r="I24" s="299">
+      <c r="I24" s="296">
         <v>11.47</v>
       </c>
-      <c r="J24" s="291">
+      <c r="J24" s="287">
         <v>15.39</v>
       </c>
-      <c r="K24" s="292">
+      <c r="K24" s="288">
         <v>21.07</v>
       </c>
-      <c r="L24" s="293">
+      <c r="L24" s="295">
         <v>25.17</v>
       </c>
       <c r="M24" s="297">
         <v>30</v>
       </c>
-      <c r="N24" s="294">
+      <c r="N24" s="298">
         <v>30.59</v>
       </c>
-      <c r="O24" s="287">
+      <c r="O24" s="291">
         <v>21.84</v>
       </c>
-      <c r="P24" s="288">
+      <c r="P24" s="292">
         <v>20.93</v>
       </c>
-      <c r="Q24" s="295">
+      <c r="Q24" s="299">
         <v>20.8</v>
       </c>
-      <c r="R24" s="296">
+      <c r="R24" s="293">
         <v>26.21</v>
       </c>
-      <c r="S24" s="289">
+      <c r="S24" s="294">
         <v>23.73</v>
       </c>
-      <c r="T24" s="298">
-        <v>-4.88</v>
+      <c r="T24" s="289">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="25">
@@ -9900,7 +9900,7 @@
       <c r="C25" t="str">
         <v>600693</v>
       </c>
-      <c r="D25" s="310" t="str">
+      <c r="D25" s="308" t="str">
         <v>净卖: -8573.84万</v>
       </c>
       <c r="E25">
@@ -9915,41 +9915,41 @@
       <c r="H25">
         <v>0</v>
       </c>
-      <c r="I25" s="311">
+      <c r="I25" s="309">
         <v>-2.52</v>
       </c>
-      <c r="J25" s="312">
+      <c r="J25" s="310">
         <v>2</v>
       </c>
-      <c r="K25" s="306">
+      <c r="K25" s="303">
         <v>-7.69</v>
       </c>
-      <c r="L25" s="307">
+      <c r="L25" s="311">
         <v>-16.92</v>
       </c>
-      <c r="M25" s="300">
+      <c r="M25" s="304">
         <v>-16.92</v>
       </c>
-      <c r="N25" s="308">
+      <c r="N25" s="301">
         <v>-14.27</v>
       </c>
-      <c r="O25" s="309">
+      <c r="O25" s="312">
         <v>-16.64</v>
       </c>
-      <c r="P25" s="301">
+      <c r="P25" s="300">
         <v>-16.6</v>
       </c>
-      <c r="Q25" s="302">
+      <c r="Q25" s="305">
         <v>-11.79</v>
       </c>
-      <c r="R25" s="303">
+      <c r="R25" s="306">
         <v>-8.67</v>
       </c>
-      <c r="S25" s="304">
+      <c r="S25" s="307">
         <v>-2.05</v>
       </c>
-      <c r="T25" s="305">
-        <v>-44.48</v>
+      <c r="T25" s="302">
+        <v>-44.06</v>
       </c>
     </row>
     <row r="26">
@@ -9962,7 +9962,7 @@
       <c r="C26" t="str">
         <v>603686</v>
       </c>
-      <c r="D26" s="323" t="str">
+      <c r="D26" s="321" t="str">
         <v>净买: 6401.27万</v>
       </c>
       <c r="E26">
@@ -9977,41 +9977,41 @@
       <c r="H26">
         <v>-1.39</v>
       </c>
-      <c r="I26" s="324">
+      <c r="I26" s="325">
         <v>11.56</v>
       </c>
-      <c r="J26" s="320">
+      <c r="J26" s="322">
         <v>12.1</v>
       </c>
-      <c r="K26" s="325">
+      <c r="K26" s="313">
         <v>23.31</v>
       </c>
-      <c r="L26" s="313">
+      <c r="L26" s="323">
         <v>15.93</v>
       </c>
-      <c r="M26" s="317">
+      <c r="M26" s="316">
         <v>12.77</v>
       </c>
-      <c r="N26" s="318">
+      <c r="N26" s="324">
         <v>13.16</v>
       </c>
-      <c r="O26" s="316">
+      <c r="O26" s="317">
         <v>10.86</v>
       </c>
-      <c r="P26" s="321">
+      <c r="P26" s="314">
         <v>9.14</v>
       </c>
-      <c r="Q26" s="314">
+      <c r="Q26" s="318">
         <v>9.84</v>
       </c>
-      <c r="R26" s="322">
+      <c r="R26" s="315">
         <v>10.82</v>
       </c>
       <c r="S26" s="319">
         <v>-0.23</v>
       </c>
-      <c r="T26" s="315">
-        <v>-26.28</v>
+      <c r="T26" s="320">
+        <v>-25.58</v>
       </c>
     </row>
     <row r="27">
@@ -10024,7 +10024,7 @@
       <c r="C27" t="str">
         <v>603686</v>
       </c>
-      <c r="D27" s="332" t="str">
+      <c r="D27" s="334" t="str">
         <v>净卖: -6520.61万</v>
       </c>
       <c r="E27">
@@ -10039,41 +10039,41 @@
       <c r="H27">
         <v>5.01</v>
       </c>
-      <c r="I27" s="326">
+      <c r="I27" s="335">
         <v>-4.3</v>
       </c>
-      <c r="J27" s="333">
+      <c r="J27" s="336">
         <v>5.27</v>
       </c>
-      <c r="K27" s="328">
+      <c r="K27" s="326">
         <v>-1.03</v>
       </c>
-      <c r="L27" s="334">
+      <c r="L27" s="337">
         <v>-3.73</v>
       </c>
-      <c r="M27" s="335">
+      <c r="M27" s="331">
         <v>-3.4</v>
       </c>
-      <c r="N27" s="329">
+      <c r="N27" s="327">
         <v>-5.37</v>
       </c>
-      <c r="O27" s="336">
+      <c r="O27" s="328">
         <v>-6.83</v>
       </c>
-      <c r="P27" s="327">
+      <c r="P27" s="338">
         <v>-6.23</v>
       </c>
-      <c r="Q27" s="337">
+      <c r="Q27" s="329">
         <v>-5.4</v>
       </c>
-      <c r="R27" s="330">
+      <c r="R27" s="332">
         <v>-14.83</v>
       </c>
-      <c r="S27" s="338">
+      <c r="S27" s="330">
         <v>-14.37</v>
       </c>
-      <c r="T27" s="331">
-        <v>-37.07</v>
+      <c r="T27" s="333">
+        <v>-36.47</v>
       </c>
     </row>
     <row r="28">
@@ -10086,7 +10086,7 @@
       <c r="C28" t="str">
         <v>002361</v>
       </c>
-      <c r="D28" s="351" t="str">
+      <c r="D28" s="349" t="str">
         <v>净卖: -5584.65万</v>
       </c>
       <c r="E28">
@@ -10101,41 +10101,41 @@
       <c r="H28">
         <v>-3.59</v>
       </c>
-      <c r="I28" s="344">
+      <c r="I28" s="343">
         <v>-6.66</v>
       </c>
-      <c r="J28" s="347">
+      <c r="J28" s="350">
         <v>2.65</v>
       </c>
       <c r="K28" s="345">
         <v>-1.93</v>
       </c>
-      <c r="L28" s="346">
+      <c r="L28" s="351">
         <v>3.51</v>
       </c>
       <c r="M28" s="339">
         <v>3.15</v>
       </c>
-      <c r="N28" s="348">
+      <c r="N28" s="340">
         <v>13.46</v>
       </c>
-      <c r="O28" s="349">
+      <c r="O28" s="341">
         <v>11.67</v>
       </c>
-      <c r="P28" s="342">
+      <c r="P28" s="344">
         <v>20.26</v>
       </c>
-      <c r="Q28" s="343">
+      <c r="Q28" s="347">
         <v>17.97</v>
       </c>
-      <c r="R28" s="340">
+      <c r="R28" s="346">
         <v>29.71</v>
       </c>
-      <c r="S28" s="341">
+      <c r="S28" s="342">
         <v>16.75</v>
       </c>
-      <c r="T28" s="350">
-        <v>34.22</v>
+      <c r="T28" s="348">
+        <v>47.67</v>
       </c>
     </row>
     <row r="29">
@@ -10148,7 +10148,7 @@
       <c r="C29" t="str">
         <v>001231</v>
       </c>
-      <c r="D29" s="356" t="str">
+      <c r="D29" s="359" t="str">
         <v>净卖: -943.73万</v>
       </c>
       <c r="E29">
@@ -10163,41 +10163,41 @@
       <c r="H29">
         <v>-10.01</v>
       </c>
-      <c r="I29" s="357">
+      <c r="I29" s="360">
         <v>0</v>
       </c>
-      <c r="J29" s="359">
+      <c r="J29" s="363">
         <v>-1.36</v>
       </c>
-      <c r="K29" s="363">
+      <c r="K29" s="354">
         <v>-7.18</v>
       </c>
-      <c r="L29" s="353">
+      <c r="L29" s="361">
         <v>-8.91</v>
       </c>
-      <c r="M29" s="364">
+      <c r="M29" s="355">
         <v>-9.1</v>
       </c>
-      <c r="N29" s="360">
+      <c r="N29" s="364">
         <v>-9.98</v>
       </c>
       <c r="O29" s="358">
         <v>-8.84</v>
       </c>
-      <c r="P29" s="361">
+      <c r="P29" s="362">
         <v>-10.31</v>
       </c>
-      <c r="Q29" s="354">
+      <c r="Q29" s="352">
         <v>-7.96</v>
       </c>
-      <c r="R29" s="362">
+      <c r="R29" s="353">
         <v>-8.8</v>
       </c>
-      <c r="S29" s="355">
+      <c r="S29" s="356">
         <v>-9.28</v>
       </c>
-      <c r="T29" s="352">
-        <v>-8.18</v>
+      <c r="T29" s="357">
+        <v>-10.83</v>
       </c>
     </row>
     <row r="30">
@@ -10210,7 +10210,7 @@
       <c r="C30" t="str">
         <v>002788</v>
       </c>
-      <c r="D30" s="372" t="str">
+      <c r="D30" s="371" t="str">
         <v>净买: 3825.22万</v>
       </c>
       <c r="E30">
@@ -10225,41 +10225,41 @@
       <c r="H30">
         <v>5.81</v>
       </c>
-      <c r="I30" s="373">
+      <c r="I30" s="375">
         <v>3.95</v>
       </c>
-      <c r="J30" s="374">
+      <c r="J30" s="376">
         <v>14.35</v>
       </c>
-      <c r="K30" s="369">
+      <c r="K30" s="377">
         <v>11.56</v>
       </c>
-      <c r="L30" s="366">
+      <c r="L30" s="365">
         <v>13.48</v>
       </c>
-      <c r="M30" s="367">
+      <c r="M30" s="366">
         <v>9.23</v>
       </c>
-      <c r="N30" s="375">
+      <c r="N30" s="369">
         <v>1.08</v>
       </c>
-      <c r="O30" s="376">
+      <c r="O30" s="372">
         <v>-9.03</v>
       </c>
-      <c r="P30" s="377">
+      <c r="P30" s="367">
         <v>-18.14</v>
       </c>
-      <c r="Q30" s="370">
+      <c r="Q30" s="368">
         <v>-26.33</v>
       </c>
-      <c r="R30" s="365">
+      <c r="R30" s="373">
         <v>-30.78</v>
       </c>
-      <c r="S30" s="371">
+      <c r="S30" s="370">
         <v>-32.45</v>
       </c>
-      <c r="T30" s="368">
-        <v>-37.23</v>
+      <c r="T30" s="374">
+        <v>-37.06</v>
       </c>
     </row>
     <row r="31">
@@ -10272,7 +10272,7 @@
       <c r="C31" t="str">
         <v>002788</v>
       </c>
-      <c r="D31" s="384" t="str">
+      <c r="D31" s="381" t="str">
         <v>净卖: -24.07万</v>
       </c>
       <c r="E31">
@@ -10287,41 +10287,41 @@
       <c r="H31">
         <v>-0.04</v>
       </c>
-      <c r="I31" s="388">
+      <c r="I31" s="389">
         <v>10.05</v>
       </c>
-      <c r="J31" s="385">
+      <c r="J31" s="390">
         <v>7.37</v>
       </c>
-      <c r="K31" s="386">
+      <c r="K31" s="382">
         <v>9.21</v>
       </c>
-      <c r="L31" s="380">
+      <c r="L31" s="387">
         <v>5.12</v>
       </c>
-      <c r="M31" s="381">
+      <c r="M31" s="388">
         <v>-2.72</v>
       </c>
-      <c r="N31" s="390">
+      <c r="N31" s="383">
         <v>-12.45</v>
       </c>
-      <c r="O31" s="389">
+      <c r="O31" s="384">
         <v>-21.22</v>
       </c>
-      <c r="P31" s="382">
+      <c r="P31" s="385">
         <v>-29.1</v>
       </c>
-      <c r="Q31" s="378">
+      <c r="Q31" s="386">
         <v>-33.39</v>
       </c>
-      <c r="R31" s="379">
+      <c r="R31" s="378">
         <v>-34.99</v>
       </c>
-      <c r="S31" s="387">
+      <c r="S31" s="379">
         <v>-32.95</v>
       </c>
-      <c r="T31" s="383">
-        <v>-39.59</v>
+      <c r="T31" s="380">
+        <v>-39.43</v>
       </c>
     </row>
     <row r="32">
@@ -10334,7 +10334,7 @@
       <c r="C32" t="str">
         <v>600151</v>
       </c>
-      <c r="D32" s="398" t="str">
+      <c r="D32" s="399" t="str">
         <v>净买: 7884.07万</v>
       </c>
       <c r="E32">
@@ -10349,41 +10349,41 @@
       <c r="H32">
         <v>3.26</v>
       </c>
-      <c r="I32" s="399">
+      <c r="I32" s="400">
         <v>-11.53</v>
       </c>
-      <c r="J32" s="400">
+      <c r="J32" s="392">
         <v>-20.23</v>
       </c>
-      <c r="K32" s="392">
+      <c r="K32" s="396">
         <v>-21.06</v>
       </c>
-      <c r="L32" s="401">
+      <c r="L32" s="403">
         <v>-24.22</v>
       </c>
-      <c r="M32" s="393">
+      <c r="M32" s="391">
         <v>-21.69</v>
       </c>
-      <c r="N32" s="397">
+      <c r="N32" s="393">
         <v>-16.73</v>
       </c>
-      <c r="O32" s="402">
+      <c r="O32" s="401">
         <v>-25.05</v>
       </c>
-      <c r="P32" s="403">
+      <c r="P32" s="397">
         <v>-25.88</v>
       </c>
       <c r="Q32" s="394">
         <v>-27.43</v>
       </c>
-      <c r="R32" s="391">
+      <c r="R32" s="395">
         <v>-26.65</v>
       </c>
-      <c r="S32" s="395">
+      <c r="S32" s="398">
         <v>-26.61</v>
       </c>
-      <c r="T32" s="396">
-        <v>-28.89</v>
+      <c r="T32" s="402">
+        <v>-27.09</v>
       </c>
     </row>
     <row r="33">
@@ -10396,7 +10396,7 @@
       <c r="C33" t="str">
         <v>600916</v>
       </c>
-      <c r="D33" s="416" t="str">
+      <c r="D33" s="406" t="str">
         <v>净卖: -1428.23万</v>
       </c>
       <c r="E33">
@@ -10411,41 +10411,41 @@
       <c r="H33">
         <v>10.04</v>
       </c>
-      <c r="I33" s="409">
+      <c r="I33" s="414">
         <v>0</v>
       </c>
-      <c r="J33" s="410">
+      <c r="J33" s="407">
         <v>10.02</v>
       </c>
-      <c r="K33" s="411">
+      <c r="K33" s="415">
         <v>19.64</v>
       </c>
-      <c r="L33" s="412">
+      <c r="L33" s="416">
         <v>7.66</v>
       </c>
-      <c r="M33" s="413">
+      <c r="M33" s="410">
         <v>5.87</v>
       </c>
       <c r="N33" s="404">
         <v>-0.81</v>
       </c>
-      <c r="O33" s="405">
+      <c r="O33" s="408">
         <v>-8.96</v>
       </c>
-      <c r="P33" s="414">
+      <c r="P33" s="411">
         <v>-6.93</v>
       </c>
-      <c r="Q33" s="406">
+      <c r="Q33" s="412">
         <v>-5.79</v>
       </c>
-      <c r="R33" s="407">
+      <c r="R33" s="413">
         <v>-8.96</v>
       </c>
-      <c r="S33" s="408">
+      <c r="S33" s="405">
         <v>-9.54</v>
       </c>
-      <c r="T33" s="415">
-        <v>-25.84</v>
+      <c r="T33" s="409">
+        <v>-25.67</v>
       </c>
     </row>
     <row r="34">
@@ -10458,7 +10458,7 @@
       <c r="C34" t="str">
         <v>600969</v>
       </c>
-      <c r="D34" s="427" t="str">
+      <c r="D34" s="423" t="str">
         <v>净卖: -723.23万</v>
       </c>
       <c r="E34">
@@ -10473,41 +10473,41 @@
       <c r="H34">
         <v>0</v>
       </c>
-      <c r="I34" s="421">
+      <c r="I34" s="420">
         <v>-9.99</v>
       </c>
-      <c r="J34" s="428">
+      <c r="J34" s="429">
         <v>-9.99</v>
       </c>
-      <c r="K34" s="422">
+      <c r="K34" s="426">
         <v>-18.98</v>
       </c>
-      <c r="L34" s="424">
+      <c r="L34" s="421">
         <v>-21.07</v>
       </c>
-      <c r="M34" s="429">
+      <c r="M34" s="427">
         <v>-21.98</v>
       </c>
-      <c r="N34" s="423">
+      <c r="N34" s="417">
         <v>-18.98</v>
       </c>
-      <c r="O34" s="417">
+      <c r="O34" s="418">
         <v>-16.9</v>
       </c>
-      <c r="P34" s="418">
+      <c r="P34" s="424">
         <v>-16.82</v>
       </c>
-      <c r="Q34" s="419">
+      <c r="Q34" s="428">
         <v>-14.32</v>
       </c>
-      <c r="R34" s="420">
+      <c r="R34" s="422">
         <v>-13.66</v>
       </c>
-      <c r="S34" s="425">
+      <c r="S34" s="419">
         <v>-15.99</v>
       </c>
-      <c r="T34" s="426">
-        <v>-18.07</v>
+      <c r="T34" s="425">
+        <v>-15.4</v>
       </c>
     </row>
     <row r="35">
@@ -10520,7 +10520,7 @@
       <c r="C35" t="str">
         <v>002040</v>
       </c>
-      <c r="D35" s="436" t="str">
+      <c r="D35" s="438" t="str">
         <v>净卖: -895.74万</v>
       </c>
       <c r="E35">
@@ -10535,41 +10535,41 @@
       <c r="H35">
         <v>-7.37</v>
       </c>
-      <c r="I35" s="437">
+      <c r="I35" s="432">
         <v>-2.87</v>
       </c>
-      <c r="J35" s="431">
+      <c r="J35" s="439">
         <v>-8.52</v>
       </c>
-      <c r="K35" s="441">
+      <c r="K35" s="431">
         <v>-8.36</v>
       </c>
-      <c r="L35" s="442">
+      <c r="L35" s="440">
         <v>-10.49</v>
       </c>
-      <c r="M35" s="434">
+      <c r="M35" s="433">
         <v>-8.44</v>
       </c>
-      <c r="N35" s="432">
+      <c r="N35" s="441">
         <v>-9.02</v>
       </c>
-      <c r="O35" s="438">
+      <c r="O35" s="442">
         <v>-9.51</v>
       </c>
-      <c r="P35" s="433">
+      <c r="P35" s="434">
         <v>-12.05</v>
       </c>
-      <c r="Q35" s="439">
+      <c r="Q35" s="430">
         <v>-8.28</v>
       </c>
-      <c r="R35" s="430">
+      <c r="R35" s="435">
         <v>-10.33</v>
       </c>
-      <c r="S35" s="440">
+      <c r="S35" s="436">
         <v>-11.07</v>
       </c>
-      <c r="T35" s="435">
-        <v>-18.77</v>
+      <c r="T35" s="437">
+        <v>-17.7</v>
       </c>
     </row>
     <row r="36">
@@ -10582,7 +10582,7 @@
       <c r="C36" t="str">
         <v>603017</v>
       </c>
-      <c r="D36" s="450" t="str">
+      <c r="D36" s="446" t="str">
         <v>净买: 694.09万</v>
       </c>
       <c r="E36">
@@ -10597,41 +10597,41 @@
       <c r="H36">
         <v>2.04</v>
       </c>
-      <c r="I36" s="452">
+      <c r="I36" s="447">
         <v>7.84</v>
       </c>
-      <c r="J36" s="455">
+      <c r="J36" s="448">
         <v>7.04</v>
       </c>
-      <c r="K36" s="453">
+      <c r="K36" s="452">
         <v>6.48</v>
       </c>
-      <c r="L36" s="449">
+      <c r="L36" s="455">
         <v>5.04</v>
       </c>
       <c r="M36" s="443">
         <v>7.28</v>
       </c>
-      <c r="N36" s="444">
+      <c r="N36" s="449">
         <v>5.44</v>
       </c>
-      <c r="O36" s="451">
+      <c r="O36" s="450">
         <v>10.72</v>
       </c>
-      <c r="P36" s="445">
+      <c r="P36" s="453">
         <v>10.32</v>
       </c>
-      <c r="Q36" s="446">
+      <c r="Q36" s="445">
         <v>7.92</v>
       </c>
       <c r="R36" s="454">
         <v>1.28</v>
       </c>
-      <c r="S36" s="447">
+      <c r="S36" s="444">
         <v>11.44</v>
       </c>
-      <c r="T36" s="448">
-        <v>3.36</v>
+      <c r="T36" s="451">
+        <v>13.68</v>
       </c>
     </row>
     <row r="37">
@@ -10644,7 +10644,7 @@
       <c r="C37" t="str">
         <v>600495</v>
       </c>
-      <c r="D37" s="461" t="str">
+      <c r="D37" s="465" t="str">
         <v>净买: 998.97万</v>
       </c>
       <c r="E37">
@@ -10659,41 +10659,41 @@
       <c r="H37">
         <v>0</v>
       </c>
-      <c r="I37" s="462">
+      <c r="I37" s="460">
         <v>10.04</v>
       </c>
-      <c r="J37" s="468">
+      <c r="J37" s="461">
         <v>11.16</v>
       </c>
-      <c r="K37" s="457">
+      <c r="K37" s="462">
         <v>12.28</v>
       </c>
-      <c r="L37" s="458">
+      <c r="L37" s="466">
         <v>2.23</v>
       </c>
-      <c r="M37" s="463">
+      <c r="M37" s="467">
         <v>0.67</v>
       </c>
-      <c r="N37" s="464">
+      <c r="N37" s="463">
         <v>4.46</v>
       </c>
-      <c r="O37" s="465">
+      <c r="O37" s="457">
         <v>0.67</v>
       </c>
-      <c r="P37" s="456">
+      <c r="P37" s="458">
         <v>0.45</v>
       </c>
       <c r="Q37" s="459">
         <v>-1.34</v>
       </c>
-      <c r="R37" s="466">
+      <c r="R37" s="468">
         <v>-1.34</v>
       </c>
-      <c r="S37" s="467">
+      <c r="S37" s="456">
         <v>-2.01</v>
       </c>
-      <c r="T37" s="460">
-        <v>-2.46</v>
+      <c r="T37" s="464">
+        <v>0.45</v>
       </c>
     </row>
     <row r="38">
@@ -10706,7 +10706,7 @@
       <c r="C38" t="str">
         <v>600488</v>
       </c>
-      <c r="D38" s="480" t="str">
+      <c r="D38" s="469" t="str">
         <v>净卖: -1388.23万</v>
       </c>
       <c r="E38">
@@ -10721,41 +10721,41 @@
       <c r="H38">
         <v>9.92</v>
       </c>
-      <c r="I38" s="473">
+      <c r="I38" s="472">
         <v>0</v>
       </c>
-      <c r="J38" s="474">
+      <c r="J38" s="473">
         <v>10.07</v>
       </c>
-      <c r="K38" s="471">
+      <c r="K38" s="474">
         <v>21.01</v>
       </c>
-      <c r="L38" s="478">
+      <c r="L38" s="470">
         <v>33.16</v>
       </c>
-      <c r="M38" s="479">
+      <c r="M38" s="478">
         <v>27.78</v>
       </c>
-      <c r="N38" s="475">
+      <c r="N38" s="479">
         <v>22.92</v>
       </c>
-      <c r="O38" s="472">
+      <c r="O38" s="471">
         <v>11.46</v>
       </c>
-      <c r="P38" s="481">
+      <c r="P38" s="480">
         <v>2.6</v>
       </c>
-      <c r="Q38" s="476">
+      <c r="Q38" s="475">
         <v>7.99</v>
       </c>
-      <c r="R38" s="477">
+      <c r="R38" s="476">
         <v>18.75</v>
       </c>
-      <c r="S38" s="469">
+      <c r="S38" s="481">
         <v>9.2</v>
       </c>
-      <c r="T38" s="470">
-        <v>5.21</v>
+      <c r="T38" s="477">
+        <v>11.28</v>
       </c>
     </row>
     <row r="39">
@@ -10817,41 +10817,41 @@
       <c r="F40" t="str"/>
       <c r="G40" t="str"/>
       <c r="H40" t="str"/>
-      <c r="I40" s="492">
+      <c r="I40" s="486">
         <v>54.05</v>
       </c>
-      <c r="J40" s="484">
+      <c r="J40" s="490">
         <v>62.16</v>
       </c>
-      <c r="K40" s="489">
+      <c r="K40" s="482">
         <v>54.05</v>
       </c>
-      <c r="L40" s="485">
+      <c r="L40" s="483">
         <v>56.76</v>
       </c>
-      <c r="M40" s="490">
+      <c r="M40" s="487">
         <v>51.35</v>
       </c>
-      <c r="N40" s="486">
+      <c r="N40" s="484">
         <v>48.65</v>
       </c>
-      <c r="O40" s="493">
+      <c r="O40" s="489">
         <v>45.95</v>
       </c>
       <c r="P40" s="491">
         <v>40.54</v>
       </c>
-      <c r="Q40" s="482">
+      <c r="Q40" s="485">
         <v>35.14</v>
       </c>
-      <c r="R40" s="487">
+      <c r="R40" s="488">
         <v>37.84</v>
       </c>
-      <c r="S40" s="483">
+      <c r="S40" s="492">
         <v>37.84</v>
       </c>
-      <c r="T40" s="488">
-        <v>27.03</v>
+      <c r="T40" s="493">
+        <v>29.73</v>
       </c>
     </row>
     <row r="41">
@@ -10868,38 +10868,38 @@
       <c r="I41" s="494">
         <v>2.35</v>
       </c>
-      <c r="J41" s="496">
+      <c r="J41" s="495">
         <v>3.37</v>
       </c>
       <c r="K41" s="502">
         <v>3.41</v>
       </c>
-      <c r="L41" s="503">
+      <c r="L41" s="496">
         <v>3.11</v>
       </c>
-      <c r="M41" s="504">
+      <c r="M41" s="497">
         <v>4.56</v>
       </c>
-      <c r="N41" s="495">
+      <c r="N41" s="504">
         <v>3.99</v>
       </c>
-      <c r="O41" s="505">
+      <c r="O41" s="499">
         <v>2.28</v>
       </c>
       <c r="P41" s="498">
         <v>0.79</v>
       </c>
-      <c r="Q41" s="499">
+      <c r="Q41" s="503">
         <v>-0.11</v>
       </c>
       <c r="R41" s="500">
         <v>-0.68</v>
       </c>
-      <c r="S41" s="497">
+      <c r="S41" s="501">
         <v>-0.22</v>
       </c>
-      <c r="T41" s="501">
-        <v>-3.8</v>
+      <c r="T41" s="505">
+        <v>-2.34</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/湖州劳动路/index.xlsx
+++ b/youzi/湖州劳动路/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="507">
+  <fills count="509">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -57,7 +57,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,13 +117,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,43 +243,361 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D79"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -153,25 +609,1045 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8BCF9B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4553"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8BCF9B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4CB564"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CFD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8336"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF22913C"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -183,13 +1659,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,139 +1713,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -351,31 +1779,691 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
+        <fgColor rgb="FF92D2A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA6DAB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -387,49 +2475,217 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF83CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -441,115 +2697,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -561,25 +2793,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB1DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFEFA4AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -603,97 +2883,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -705,109 +2937,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BCF9B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BCF9B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4553"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ADB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AFB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -819,2191 +3033,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4CB564"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8336"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CFD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F9F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA6DAB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF83CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3015,13 +3045,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AFB5"/>
+        <fgColor rgb="FFF3FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB5E1BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3033,42 +3075,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB5E1BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE7F5EA"/>
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="506">
+  <borders count="508">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -6615,7 +6641,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="506">
+  <cellXfs count="508">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8130,6 +8156,12 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="505" fillId="506" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="506" fillId="507" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="507" fillId="508" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -8474,7 +8506,7 @@
       <c r="C2" t="str">
         <v>002105</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="4" t="str">
         <v>净卖: -286.93万</v>
       </c>
       <c r="E2">
@@ -8489,16 +8521,16 @@
       <c r="H2">
         <v>3.63</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="11">
         <v>6.13</v>
       </c>
       <c r="J2" s="12">
         <v>16.75</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="5">
         <v>28.37</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="6">
         <v>41.25</v>
       </c>
       <c r="M2" s="7">
@@ -8507,23 +8539,23 @@
       <c r="N2" s="8">
         <v>46.12</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="13">
         <v>46.75</v>
       </c>
       <c r="P2" s="9">
         <v>33.13</v>
       </c>
-      <c r="Q2" s="6">
+      <c r="Q2" s="1">
         <v>34.87</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="2">
         <v>21.38</v>
       </c>
-      <c r="S2" s="2">
+      <c r="S2" s="3">
         <v>11.62</v>
       </c>
       <c r="T2" s="10">
-        <v>-20.13</v>
+        <v>-21</v>
       </c>
     </row>
     <row r="3">
@@ -8536,7 +8568,7 @@
       <c r="C3" t="str">
         <v>002760</v>
       </c>
-      <c r="D3" s="24" t="str">
+      <c r="D3" s="18" t="str">
         <v>净买: 1264.22万</v>
       </c>
       <c r="E3">
@@ -8551,41 +8583,41 @@
       <c r="H3">
         <v>3.43</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="14">
         <v>6.36</v>
       </c>
-      <c r="J3" s="19">
+      <c r="J3" s="15">
         <v>2.8</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="16">
         <v>-6.84</v>
       </c>
-      <c r="L3" s="17">
+      <c r="L3" s="24">
         <v>-13.76</v>
       </c>
       <c r="M3" s="25">
         <v>-13.72</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="26">
         <v>-14.84</v>
       </c>
-      <c r="O3" s="26">
+      <c r="O3" s="21">
         <v>-15.92</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="22">
         <v>-16.68</v>
       </c>
-      <c r="Q3" s="21">
+      <c r="Q3" s="19">
         <v>-19.6</v>
       </c>
-      <c r="R3" s="18">
+      <c r="R3" s="20">
         <v>-22.72</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="17">
         <v>-23.88</v>
       </c>
-      <c r="T3" s="16">
-        <v>-11.96</v>
+      <c r="T3" s="23">
+        <v>-12.4</v>
       </c>
     </row>
     <row r="4">
@@ -8598,7 +8630,7 @@
       <c r="C4" t="str">
         <v>002760</v>
       </c>
-      <c r="D4" s="28" t="str">
+      <c r="D4" s="34" t="str">
         <v>净卖: -1488.32万</v>
       </c>
       <c r="E4">
@@ -8613,41 +8645,41 @@
       <c r="H4">
         <v>4.59</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="37">
         <v>-7.59</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="38">
         <v>-16.25</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="29">
         <v>-22.47</v>
       </c>
       <c r="L4" s="30">
         <v>-22.44</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="35">
         <v>-23.44</v>
       </c>
-      <c r="N4" s="39">
+      <c r="N4" s="36">
         <v>-24.42</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="39">
         <v>-25.1</v>
       </c>
-      <c r="P4" s="32">
+      <c r="P4" s="31">
         <v>-27.72</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="32">
         <v>-30.53</v>
       </c>
-      <c r="R4" s="35">
+      <c r="R4" s="33">
         <v>-31.57</v>
       </c>
       <c r="S4" s="27">
         <v>-31.07</v>
       </c>
-      <c r="T4" s="37">
-        <v>-20.86</v>
+      <c r="T4" s="28">
+        <v>-21.25</v>
       </c>
     </row>
     <row r="5">
@@ -8660,7 +8692,7 @@
       <c r="C5" t="str">
         <v>603958</v>
       </c>
-      <c r="D5" s="52" t="str">
+      <c r="D5" s="40" t="str">
         <v>净买: 2814.34万</v>
       </c>
       <c r="E5">
@@ -8675,41 +8707,41 @@
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5" s="45">
+      <c r="I5" s="43">
         <v>-3.71</v>
       </c>
-      <c r="J5" s="40">
+      <c r="J5" s="41">
         <v>-13.32</v>
       </c>
-      <c r="K5" s="41">
+      <c r="K5" s="48">
         <v>-18.35</v>
       </c>
-      <c r="L5" s="46">
+      <c r="L5" s="42">
         <v>-15.42</v>
       </c>
-      <c r="M5" s="47">
+      <c r="M5" s="52">
         <v>-11.81</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="44">
         <v>-11.27</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="45">
         <v>-11.13</v>
       </c>
-      <c r="P5" s="48">
+      <c r="P5" s="49">
         <v>-13.08</v>
       </c>
-      <c r="Q5" s="51">
+      <c r="Q5" s="46">
         <v>-16.15</v>
       </c>
-      <c r="R5" s="49">
+      <c r="R5" s="50">
         <v>-17.72</v>
       </c>
-      <c r="S5" s="44">
+      <c r="S5" s="47">
         <v>-18.79</v>
       </c>
-      <c r="T5" s="50">
-        <v>22.65</v>
+      <c r="T5" s="51">
+        <v>29.97</v>
       </c>
     </row>
     <row r="6">
@@ -8722,7 +8754,7 @@
       <c r="C6" t="str">
         <v>603958</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="55" t="str">
         <v>净卖: -2283.55万</v>
       </c>
       <c r="E6">
@@ -8737,41 +8769,41 @@
       <c r="H6">
         <v>-6.13</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="56">
         <v>-4.1</v>
       </c>
-      <c r="J6" s="63">
+      <c r="J6" s="57">
         <v>-9.67</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="59">
         <v>-6.43</v>
       </c>
-      <c r="L6" s="55">
+      <c r="L6" s="60">
         <v>-2.43</v>
       </c>
-      <c r="M6" s="56">
+      <c r="M6" s="63">
         <v>-1.84</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="53">
         <v>-1.67</v>
       </c>
-      <c r="O6" s="64">
+      <c r="O6" s="61">
         <v>-3.83</v>
       </c>
-      <c r="P6" s="65">
+      <c r="P6" s="54">
         <v>-7.24</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="64">
         <v>-8.96</v>
       </c>
-      <c r="R6" s="61">
+      <c r="R6" s="65">
         <v>-10.15</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="58">
         <v>-9.99</v>
       </c>
       <c r="T6" s="62">
-        <v>35.69</v>
+        <v>43.79</v>
       </c>
     </row>
     <row r="7">
@@ -8784,7 +8816,7 @@
       <c r="C7" t="str">
         <v>002645</v>
       </c>
-      <c r="D7" s="67" t="str">
+      <c r="D7" s="68" t="str">
         <v>净买: 1223.21万</v>
       </c>
       <c r="E7">
@@ -8799,31 +8831,31 @@
       <c r="H7">
         <v>1.72</v>
       </c>
-      <c r="I7" s="72">
+      <c r="I7" s="71">
         <v>8.14</v>
       </c>
-      <c r="J7" s="73">
+      <c r="J7" s="69">
         <v>5.31</v>
       </c>
-      <c r="K7" s="74">
+      <c r="K7" s="70">
         <v>9.04</v>
       </c>
-      <c r="L7" s="75">
+      <c r="L7" s="73">
         <v>4.75</v>
       </c>
-      <c r="M7" s="68">
+      <c r="M7" s="74">
         <v>3.5</v>
       </c>
-      <c r="N7" s="77">
+      <c r="N7" s="72">
         <v>-6.89</v>
       </c>
-      <c r="O7" s="69">
+      <c r="O7" s="75">
         <v>-5.42</v>
       </c>
       <c r="P7" s="76">
         <v>-7.12</v>
       </c>
-      <c r="Q7" s="70">
+      <c r="Q7" s="77">
         <v>-7.23</v>
       </c>
       <c r="R7" s="78">
@@ -8832,8 +8864,8 @@
       <c r="S7" s="66">
         <v>-9.94</v>
       </c>
-      <c r="T7" s="71">
-        <v>158.53</v>
+      <c r="T7" s="67">
+        <v>159.1</v>
       </c>
     </row>
     <row r="8">
@@ -8846,7 +8878,7 @@
       <c r="C8" t="str">
         <v>600537</v>
       </c>
-      <c r="D8" s="87" t="str">
+      <c r="D8" s="89" t="str">
         <v>净买: 358.47万</v>
       </c>
       <c r="E8">
@@ -8861,41 +8893,41 @@
       <c r="H8">
         <v>5.03</v>
       </c>
-      <c r="I8" s="84">
+      <c r="I8" s="86">
         <v>4.79</v>
       </c>
-      <c r="J8" s="85">
+      <c r="J8" s="90">
         <v>8.98</v>
       </c>
-      <c r="K8" s="88">
+      <c r="K8" s="83">
         <v>-1.8</v>
       </c>
-      <c r="L8" s="89">
+      <c r="L8" s="87">
         <v>8.08</v>
       </c>
-      <c r="M8" s="83">
+      <c r="M8" s="91">
         <v>18.86</v>
       </c>
-      <c r="N8" s="90">
+      <c r="N8" s="79">
         <v>19.76</v>
       </c>
-      <c r="O8" s="82">
+      <c r="O8" s="84">
         <v>19.16</v>
       </c>
-      <c r="P8" s="91">
+      <c r="P8" s="80">
         <v>15.57</v>
       </c>
-      <c r="Q8" s="79">
+      <c r="Q8" s="82">
         <v>8.38</v>
       </c>
-      <c r="R8" s="80">
+      <c r="R8" s="81">
         <v>4.49</v>
       </c>
-      <c r="S8" s="81">
+      <c r="S8" s="85">
         <v>14.97</v>
       </c>
-      <c r="T8" s="86">
-        <v>9.88</v>
+      <c r="T8" s="88">
+        <v>3.59</v>
       </c>
     </row>
     <row r="9">
@@ -8908,7 +8940,7 @@
       <c r="C9" t="str">
         <v>603122</v>
       </c>
-      <c r="D9" s="92" t="str">
+      <c r="D9" s="102" t="str">
         <v>净卖: -557.16万</v>
       </c>
       <c r="E9">
@@ -8926,38 +8958,38 @@
       <c r="I9" s="95">
         <v>2.8</v>
       </c>
-      <c r="J9" s="103">
+      <c r="J9" s="101">
         <v>13.09</v>
       </c>
-      <c r="K9" s="100">
+      <c r="K9" s="103">
         <v>24.4</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="104">
         <v>36.85</v>
       </c>
-      <c r="M9" s="96">
+      <c r="M9" s="98">
         <v>50.57</v>
       </c>
-      <c r="N9" s="104">
+      <c r="N9" s="99">
         <v>65.69</v>
       </c>
-      <c r="O9" s="97">
+      <c r="O9" s="92">
         <v>82.21</v>
       </c>
-      <c r="P9" s="101">
+      <c r="P9" s="96">
         <v>100.38</v>
       </c>
-      <c r="Q9" s="98">
+      <c r="Q9" s="97">
         <v>110.93</v>
       </c>
-      <c r="R9" s="94">
+      <c r="R9" s="93">
         <v>132.02</v>
       </c>
-      <c r="S9" s="102">
+      <c r="S9" s="94">
         <v>155.27</v>
       </c>
-      <c r="T9" s="99">
-        <v>108.13</v>
+      <c r="T9" s="100">
+        <v>101.27</v>
       </c>
     </row>
     <row r="10">
@@ -8970,7 +9002,7 @@
       <c r="C10" t="str">
         <v>002682</v>
       </c>
-      <c r="D10" s="111" t="str">
+      <c r="D10" s="105" t="str">
         <v>净买: 749.97万</v>
       </c>
       <c r="E10">
@@ -8985,41 +9017,41 @@
       <c r="H10">
         <v>10.02</v>
       </c>
-      <c r="I10" s="112">
+      <c r="I10" s="114">
         <v>0</v>
       </c>
-      <c r="J10" s="109">
+      <c r="J10" s="115">
         <v>10.03</v>
       </c>
-      <c r="K10" s="113">
+      <c r="K10" s="112">
         <v>20.99</v>
       </c>
-      <c r="L10" s="105">
+      <c r="L10" s="106">
         <v>8.95</v>
       </c>
-      <c r="M10" s="106">
+      <c r="M10" s="113">
         <v>-2.01</v>
       </c>
-      <c r="N10" s="114">
+      <c r="N10" s="116">
         <v>-11.73</v>
       </c>
-      <c r="O10" s="115">
+      <c r="O10" s="111">
         <v>-16.05</v>
       </c>
-      <c r="P10" s="116">
+      <c r="P10" s="117">
         <v>-13.73</v>
       </c>
-      <c r="Q10" s="117">
+      <c r="Q10" s="107">
         <v>-17.59</v>
       </c>
-      <c r="R10" s="107">
+      <c r="R10" s="108">
         <v>-17.28</v>
       </c>
-      <c r="S10" s="108">
+      <c r="S10" s="109">
         <v>-14.04</v>
       </c>
       <c r="T10" s="110">
-        <v>-7.1</v>
+        <v>-8.33</v>
       </c>
     </row>
     <row r="11">
@@ -9032,7 +9064,7 @@
       <c r="C11" t="str">
         <v>600227</v>
       </c>
-      <c r="D11" s="129" t="str">
+      <c r="D11" s="125" t="str">
         <v>净买: 484.48万</v>
       </c>
       <c r="E11">
@@ -9047,41 +9079,41 @@
       <c r="H11">
         <v>1.56</v>
       </c>
-      <c r="I11" s="130">
+      <c r="I11" s="126">
         <v>8.43</v>
       </c>
-      <c r="J11" s="121">
+      <c r="J11" s="122">
         <v>13.79</v>
       </c>
-      <c r="K11" s="122">
+      <c r="K11" s="123">
         <v>9.2</v>
       </c>
-      <c r="L11" s="123">
+      <c r="L11" s="129">
         <v>7.28</v>
       </c>
-      <c r="M11" s="118">
+      <c r="M11" s="130">
         <v>2.68</v>
       </c>
-      <c r="N11" s="124">
+      <c r="N11" s="127">
         <v>4.6</v>
       </c>
-      <c r="O11" s="126">
+      <c r="O11" s="120">
         <v>0.77</v>
       </c>
-      <c r="P11" s="125">
+      <c r="P11" s="124">
         <v>-4.6</v>
       </c>
-      <c r="Q11" s="119">
+      <c r="Q11" s="128">
         <v>-2.68</v>
       </c>
-      <c r="R11" s="127">
+      <c r="R11" s="118">
         <v>-4.6</v>
       </c>
-      <c r="S11" s="120">
+      <c r="S11" s="121">
         <v>-2.68</v>
       </c>
-      <c r="T11" s="128">
-        <v>34.48</v>
+      <c r="T11" s="119">
+        <v>35.63</v>
       </c>
     </row>
     <row r="12">
@@ -9094,7 +9126,7 @@
       <c r="C12" t="str">
         <v>603386</v>
       </c>
-      <c r="D12" s="131" t="str">
+      <c r="D12" s="136" t="str">
         <v>净卖: -4389.34万</v>
       </c>
       <c r="E12">
@@ -9109,41 +9141,41 @@
       <c r="H12">
         <v>-8.19</v>
       </c>
-      <c r="I12" s="132">
+      <c r="I12" s="143">
         <v>-1.95</v>
       </c>
-      <c r="J12" s="138">
+      <c r="J12" s="137">
         <v>-3.78</v>
       </c>
-      <c r="K12" s="133">
+      <c r="K12" s="142">
         <v>-11.08</v>
       </c>
-      <c r="L12" s="134">
+      <c r="L12" s="138">
         <v>-18.92</v>
       </c>
       <c r="M12" s="139">
         <v>-18.16</v>
       </c>
-      <c r="N12" s="141">
+      <c r="N12" s="140">
         <v>-18.54</v>
       </c>
-      <c r="O12" s="142">
+      <c r="O12" s="133">
         <v>-17.08</v>
       </c>
-      <c r="P12" s="140">
+      <c r="P12" s="141">
         <v>-17.95</v>
       </c>
-      <c r="Q12" s="137">
+      <c r="Q12" s="131">
         <v>-14.43</v>
       </c>
-      <c r="R12" s="135">
+      <c r="R12" s="132">
         <v>-20</v>
       </c>
-      <c r="S12" s="143">
+      <c r="S12" s="134">
         <v>-18.32</v>
       </c>
-      <c r="T12" s="136">
-        <v>-21.68</v>
+      <c r="T12" s="135">
+        <v>-22.16</v>
       </c>
     </row>
     <row r="13">
@@ -9156,7 +9188,7 @@
       <c r="C13" t="str">
         <v>600493</v>
       </c>
-      <c r="D13" s="148" t="str">
+      <c r="D13" s="150" t="str">
         <v>净买: 999.07万</v>
       </c>
       <c r="E13">
@@ -9171,41 +9203,41 @@
       <c r="H13">
         <v>1.85</v>
       </c>
-      <c r="I13" s="152">
+      <c r="I13" s="151">
         <v>8.05</v>
       </c>
-      <c r="J13" s="149">
+      <c r="J13" s="155">
         <v>-0.65</v>
       </c>
-      <c r="K13" s="153">
+      <c r="K13" s="145">
         <v>3.12</v>
       </c>
-      <c r="L13" s="144">
+      <c r="L13" s="146">
         <v>-4.16</v>
       </c>
-      <c r="M13" s="145">
+      <c r="M13" s="156">
         <v>-8.05</v>
       </c>
-      <c r="N13" s="154">
+      <c r="N13" s="152">
         <v>1.17</v>
       </c>
-      <c r="O13" s="155">
+      <c r="O13" s="147">
         <v>-1.3</v>
       </c>
-      <c r="P13" s="150">
+      <c r="P13" s="148">
         <v>-2.47</v>
       </c>
-      <c r="Q13" s="151">
+      <c r="Q13" s="153">
         <v>1.56</v>
       </c>
-      <c r="R13" s="146">
+      <c r="R13" s="149">
         <v>3.77</v>
       </c>
-      <c r="S13" s="156">
+      <c r="S13" s="144">
         <v>4.03</v>
       </c>
-      <c r="T13" s="147">
-        <v>-2.86</v>
+      <c r="T13" s="154">
+        <v>-1.95</v>
       </c>
     </row>
     <row r="14">
@@ -9218,7 +9250,7 @@
       <c r="C14" t="str">
         <v>001330</v>
       </c>
-      <c r="D14" s="162" t="str">
+      <c r="D14" s="161" t="str">
         <v>净卖: -4990.62万</v>
       </c>
       <c r="E14">
@@ -9233,41 +9265,41 @@
       <c r="H14">
         <v>1.65</v>
       </c>
-      <c r="I14" s="168">
+      <c r="I14" s="164">
         <v>8.18</v>
       </c>
-      <c r="J14" s="157">
+      <c r="J14" s="158">
         <v>-2.59</v>
       </c>
-      <c r="K14" s="163">
+      <c r="K14" s="168">
         <v>-12.32</v>
       </c>
-      <c r="L14" s="158">
+      <c r="L14" s="165">
         <v>-20.34</v>
       </c>
-      <c r="M14" s="169">
+      <c r="M14" s="166">
         <v>-12.4</v>
       </c>
-      <c r="N14" s="164">
+      <c r="N14" s="169">
         <v>-18.4</v>
       </c>
-      <c r="O14" s="159">
+      <c r="O14" s="162">
         <v>-26.58</v>
       </c>
-      <c r="P14" s="166">
+      <c r="P14" s="159">
         <v>-33.95</v>
       </c>
-      <c r="Q14" s="165">
+      <c r="Q14" s="167">
         <v>-32.82</v>
       </c>
-      <c r="R14" s="160">
+      <c r="R14" s="157">
         <v>-35.66</v>
       </c>
-      <c r="S14" s="161">
+      <c r="S14" s="163">
         <v>-34.76</v>
       </c>
-      <c r="T14" s="167">
-        <v>-32.01</v>
+      <c r="T14" s="160">
+        <v>-28.44</v>
       </c>
     </row>
     <row r="15">
@@ -9280,7 +9312,7 @@
       <c r="C15" t="str">
         <v>600865</v>
       </c>
-      <c r="D15" s="181" t="str">
+      <c r="D15" s="170" t="str">
         <v>净买: 4692.22万</v>
       </c>
       <c r="E15">
@@ -9295,41 +9327,41 @@
       <c r="H15">
         <v>10.02</v>
       </c>
-      <c r="I15" s="182">
+      <c r="I15" s="171">
         <v>0</v>
       </c>
-      <c r="J15" s="176">
+      <c r="J15" s="174">
         <v>10.01</v>
       </c>
-      <c r="K15" s="173">
+      <c r="K15" s="172">
         <v>21</v>
       </c>
-      <c r="L15" s="177">
+      <c r="L15" s="178">
         <v>25.24</v>
       </c>
-      <c r="M15" s="170">
+      <c r="M15" s="175">
         <v>32.13</v>
       </c>
-      <c r="N15" s="178">
+      <c r="N15" s="176">
         <v>27.75</v>
       </c>
-      <c r="O15" s="174">
+      <c r="O15" s="180">
         <v>37.2</v>
       </c>
-      <c r="P15" s="180">
+      <c r="P15" s="177">
         <v>50.9</v>
       </c>
-      <c r="Q15" s="179">
+      <c r="Q15" s="173">
         <v>48.33</v>
       </c>
-      <c r="R15" s="171">
+      <c r="R15" s="181">
         <v>33.52</v>
       </c>
-      <c r="S15" s="172">
+      <c r="S15" s="179">
         <v>20.17</v>
       </c>
-      <c r="T15" s="175">
-        <v>-20.38</v>
+      <c r="T15" s="182">
+        <v>-20.51</v>
       </c>
     </row>
     <row r="16">
@@ -9342,7 +9374,7 @@
       <c r="C16" t="str">
         <v>600865</v>
       </c>
-      <c r="D16" s="195" t="str">
+      <c r="D16" s="184" t="str">
         <v>净卖: -5679.38万</v>
       </c>
       <c r="E16">
@@ -9357,41 +9389,41 @@
       <c r="H16">
         <v>10.01</v>
       </c>
-      <c r="I16" s="183">
+      <c r="I16" s="193">
         <v>0</v>
       </c>
-      <c r="J16" s="189">
+      <c r="J16" s="195">
         <v>9.99</v>
       </c>
-      <c r="K16" s="184">
+      <c r="K16" s="183">
         <v>13.84</v>
       </c>
-      <c r="L16" s="186">
+      <c r="L16" s="185">
         <v>20.1</v>
       </c>
-      <c r="M16" s="192">
+      <c r="M16" s="186">
         <v>16.12</v>
       </c>
-      <c r="N16" s="193">
+      <c r="N16" s="187">
         <v>24.72</v>
       </c>
-      <c r="O16" s="194">
+      <c r="O16" s="191">
         <v>37.17</v>
       </c>
-      <c r="P16" s="187">
+      <c r="P16" s="188">
         <v>34.83</v>
       </c>
-      <c r="Q16" s="185">
+      <c r="Q16" s="189">
         <v>21.37</v>
       </c>
-      <c r="R16" s="190">
+      <c r="R16" s="192">
         <v>9.23</v>
       </c>
-      <c r="S16" s="188">
+      <c r="S16" s="190">
         <v>3.67</v>
       </c>
-      <c r="T16" s="191">
-        <v>-27.62</v>
+      <c r="T16" s="194">
+        <v>-27.75</v>
       </c>
     </row>
     <row r="17">
@@ -9404,7 +9436,7 @@
       <c r="C17" t="str">
         <v>600693</v>
       </c>
-      <c r="D17" s="205" t="str">
+      <c r="D17" s="197" t="str">
         <v>净买: 4205.60万</v>
       </c>
       <c r="E17">
@@ -9419,41 +9451,41 @@
       <c r="H17">
         <v>2.51</v>
       </c>
-      <c r="I17" s="203">
+      <c r="I17" s="198">
         <v>0.41</v>
       </c>
-      <c r="J17" s="206">
+      <c r="J17" s="204">
         <v>-0.58</v>
       </c>
-      <c r="K17" s="207">
+      <c r="K17" s="199">
         <v>9.33</v>
       </c>
-      <c r="L17" s="204">
+      <c r="L17" s="206">
         <v>13.77</v>
       </c>
-      <c r="M17" s="199">
+      <c r="M17" s="207">
         <v>25.15</v>
       </c>
-      <c r="N17" s="208">
+      <c r="N17" s="200">
         <v>22</v>
       </c>
-      <c r="O17" s="196">
+      <c r="O17" s="205">
         <v>27.65</v>
       </c>
-      <c r="P17" s="197">
+      <c r="P17" s="208">
         <v>15.52</v>
       </c>
-      <c r="Q17" s="198">
+      <c r="Q17" s="202">
         <v>3.97</v>
       </c>
       <c r="R17" s="201">
         <v>3.97</v>
       </c>
-      <c r="S17" s="200">
+      <c r="S17" s="203">
         <v>7.29</v>
       </c>
-      <c r="T17" s="202">
-        <v>-29.99</v>
+      <c r="T17" s="196">
+        <v>-31.74</v>
       </c>
     </row>
     <row r="18">
@@ -9466,7 +9498,7 @@
       <c r="C18" t="str">
         <v>603023</v>
       </c>
-      <c r="D18" s="215" t="str">
+      <c r="D18" s="212" t="str">
         <v>净买: 2053.34万</v>
       </c>
       <c r="E18">
@@ -9481,41 +9513,41 @@
       <c r="H18">
         <v>-0.38</v>
       </c>
-      <c r="I18" s="218">
+      <c r="I18" s="209">
         <v>10.48</v>
       </c>
-      <c r="J18" s="219">
+      <c r="J18" s="218">
         <v>13.9</v>
       </c>
-      <c r="K18" s="209">
+      <c r="K18" s="210">
         <v>10.1</v>
       </c>
-      <c r="L18" s="210">
+      <c r="L18" s="213">
         <v>5.14</v>
       </c>
-      <c r="M18" s="211">
+      <c r="M18" s="214">
         <v>4.95</v>
       </c>
-      <c r="N18" s="212">
+      <c r="N18" s="215">
         <v>6.29</v>
       </c>
-      <c r="O18" s="216">
+      <c r="O18" s="219">
         <v>0.57</v>
       </c>
-      <c r="P18" s="213">
+      <c r="P18" s="217">
         <v>1.9</v>
       </c>
-      <c r="Q18" s="217">
+      <c r="Q18" s="220">
         <v>-4.19</v>
       </c>
-      <c r="R18" s="214">
+      <c r="R18" s="216">
         <v>-2.48</v>
       </c>
-      <c r="S18" s="220">
+      <c r="S18" s="221">
         <v>7.24</v>
       </c>
-      <c r="T18" s="221">
-        <v>-14.67</v>
+      <c r="T18" s="211">
+        <v>-16</v>
       </c>
     </row>
     <row r="19">
@@ -9528,7 +9560,7 @@
       <c r="C19" t="str">
         <v>601566</v>
       </c>
-      <c r="D19" s="230" t="str">
+      <c r="D19" s="228" t="str">
         <v>净卖: -2383.06万</v>
       </c>
       <c r="E19">
@@ -9543,31 +9575,31 @@
       <c r="H19">
         <v>3.63</v>
       </c>
-      <c r="I19" s="231">
+      <c r="I19" s="229">
         <v>6.13</v>
       </c>
-      <c r="J19" s="232">
+      <c r="J19" s="233">
         <v>2.75</v>
       </c>
-      <c r="K19" s="229">
+      <c r="K19" s="230">
         <v>-4.06</v>
       </c>
-      <c r="L19" s="225">
+      <c r="L19" s="222">
         <v>-3.37</v>
       </c>
-      <c r="M19" s="233">
+      <c r="M19" s="234">
         <v>-6.81</v>
       </c>
-      <c r="N19" s="234">
+      <c r="N19" s="231">
         <v>-7.5</v>
       </c>
-      <c r="O19" s="222">
+      <c r="O19" s="223">
         <v>-12.5</v>
       </c>
-      <c r="P19" s="228">
+      <c r="P19" s="232">
         <v>-13.88</v>
       </c>
-      <c r="Q19" s="223">
+      <c r="Q19" s="224">
         <v>-18.06</v>
       </c>
       <c r="R19" s="226">
@@ -9576,8 +9608,8 @@
       <c r="S19" s="227">
         <v>-16.56</v>
       </c>
-      <c r="T19" s="224">
-        <v>-32.38</v>
+      <c r="T19" s="225">
+        <v>-31.81</v>
       </c>
     </row>
     <row r="20">
@@ -9605,41 +9637,41 @@
       <c r="H20">
         <v>-5.17</v>
       </c>
-      <c r="I20" s="241">
+      <c r="I20" s="237">
         <v>9.15</v>
       </c>
-      <c r="J20" s="242">
+      <c r="J20" s="244">
         <v>15.15</v>
       </c>
-      <c r="K20" s="237">
+      <c r="K20" s="245">
         <v>11.33</v>
       </c>
-      <c r="L20" s="246">
+      <c r="L20" s="240">
         <v>19.58</v>
       </c>
-      <c r="M20" s="247">
+      <c r="M20" s="246">
         <v>31.52</v>
       </c>
-      <c r="N20" s="238">
+      <c r="N20" s="242">
         <v>29.27</v>
       </c>
-      <c r="O20" s="243">
+      <c r="O20" s="241">
         <v>16.36</v>
       </c>
-      <c r="P20" s="235">
+      <c r="P20" s="247">
         <v>4.73</v>
       </c>
-      <c r="Q20" s="244">
+      <c r="Q20" s="235">
         <v>-0.61</v>
       </c>
       <c r="R20" s="236">
         <v>0.12</v>
       </c>
-      <c r="S20" s="245">
+      <c r="S20" s="238">
         <v>0.12</v>
       </c>
-      <c r="T20" s="240">
-        <v>-30.61</v>
+      <c r="T20" s="243">
+        <v>-30.73</v>
       </c>
     </row>
     <row r="21">
@@ -9652,7 +9684,7 @@
       <c r="C21" t="str">
         <v>001317</v>
       </c>
-      <c r="D21" s="255" t="str">
+      <c r="D21" s="250" t="str">
         <v>净卖: -1614.69万</v>
       </c>
       <c r="E21">
@@ -9667,41 +9699,41 @@
       <c r="H21">
         <v>-0.39</v>
       </c>
-      <c r="I21" s="253">
+      <c r="I21" s="258">
         <v>3.7</v>
       </c>
-      <c r="J21" s="260">
+      <c r="J21" s="253">
         <v>-1.32</v>
       </c>
-      <c r="K21" s="256">
+      <c r="K21" s="254">
         <v>-4.71</v>
       </c>
-      <c r="L21" s="257">
+      <c r="L21" s="255">
         <v>-6.34</v>
       </c>
-      <c r="M21" s="258">
+      <c r="M21" s="259">
         <v>-4.27</v>
       </c>
-      <c r="N21" s="249">
+      <c r="N21" s="252">
         <v>-2.18</v>
       </c>
-      <c r="O21" s="250">
+      <c r="O21" s="251">
         <v>0.05</v>
       </c>
-      <c r="P21" s="259">
+      <c r="P21" s="260">
         <v>-1.59</v>
       </c>
-      <c r="Q21" s="251">
+      <c r="Q21" s="256">
         <v>-4.68</v>
       </c>
-      <c r="R21" s="252">
+      <c r="R21" s="248">
         <v>-5.25</v>
       </c>
-      <c r="S21" s="254">
+      <c r="S21" s="249">
         <v>-4.79</v>
       </c>
-      <c r="T21" s="248">
-        <v>-9.36</v>
+      <c r="T21" s="257">
+        <v>-10.36</v>
       </c>
     </row>
     <row r="22">
@@ -9714,7 +9746,7 @@
       <c r="C22" t="str">
         <v>002792</v>
       </c>
-      <c r="D22" s="265" t="str">
+      <c r="D22" s="270" t="str">
         <v>净买: 6812.35万</v>
       </c>
       <c r="E22">
@@ -9732,38 +9764,38 @@
       <c r="I22" s="266">
         <v>5.52</v>
       </c>
-      <c r="J22" s="269">
+      <c r="J22" s="267">
         <v>-2.54</v>
       </c>
-      <c r="K22" s="262">
+      <c r="K22" s="268">
         <v>3.61</v>
       </c>
-      <c r="L22" s="267">
+      <c r="L22" s="271">
         <v>13.97</v>
       </c>
-      <c r="M22" s="270">
+      <c r="M22" s="263">
         <v>25.37</v>
       </c>
-      <c r="N22" s="271">
+      <c r="N22" s="264">
         <v>26.81</v>
       </c>
-      <c r="O22" s="268">
+      <c r="O22" s="269">
         <v>18.51</v>
       </c>
-      <c r="P22" s="263">
+      <c r="P22" s="273">
         <v>27.46</v>
       </c>
-      <c r="Q22" s="272">
+      <c r="Q22" s="265">
         <v>36.75</v>
       </c>
-      <c r="R22" s="273">
+      <c r="R22" s="261">
         <v>41.37</v>
       </c>
-      <c r="S22" s="264">
+      <c r="S22" s="272">
         <v>55.52</v>
       </c>
-      <c r="T22" s="261">
-        <v>57.85</v>
+      <c r="T22" s="262">
+        <v>52.78</v>
       </c>
     </row>
     <row r="23">
@@ -9776,7 +9808,7 @@
       <c r="C23" t="str">
         <v>603023</v>
       </c>
-      <c r="D23" s="278" t="str">
+      <c r="D23" s="279" t="str">
         <v>净卖: -1105.11万</v>
       </c>
       <c r="E23">
@@ -9791,41 +9823,41 @@
       <c r="H23">
         <v>4.14</v>
       </c>
-      <c r="I23" s="274">
+      <c r="I23" s="277">
         <v>-0.99</v>
       </c>
-      <c r="J23" s="283">
+      <c r="J23" s="274">
         <v>-4.3</v>
       </c>
-      <c r="K23" s="284">
+      <c r="K23" s="280">
         <v>-8.61</v>
       </c>
-      <c r="L23" s="286">
+      <c r="L23" s="283">
         <v>-8.77</v>
       </c>
-      <c r="M23" s="275">
+      <c r="M23" s="284">
         <v>-7.62</v>
       </c>
-      <c r="N23" s="279">
+      <c r="N23" s="275">
         <v>-12.58</v>
       </c>
-      <c r="O23" s="280">
+      <c r="O23" s="285">
         <v>-11.42</v>
       </c>
-      <c r="P23" s="276">
+      <c r="P23" s="278">
         <v>-16.72</v>
       </c>
-      <c r="Q23" s="281">
+      <c r="Q23" s="276">
         <v>-15.23</v>
       </c>
-      <c r="R23" s="285">
+      <c r="R23" s="281">
         <v>-6.79</v>
       </c>
-      <c r="S23" s="277">
+      <c r="S23" s="282">
         <v>-7.62</v>
       </c>
-      <c r="T23" s="282">
-        <v>-25.83</v>
+      <c r="T23" s="286">
+        <v>-26.99</v>
       </c>
     </row>
     <row r="24">
@@ -9853,41 +9885,41 @@
       <c r="H24">
         <v>-1.32</v>
       </c>
-      <c r="I24" s="296">
+      <c r="I24" s="291">
         <v>11.47</v>
       </c>
-      <c r="J24" s="287">
+      <c r="J24" s="292">
         <v>15.39</v>
       </c>
-      <c r="K24" s="288">
+      <c r="K24" s="289">
         <v>21.07</v>
       </c>
-      <c r="L24" s="295">
+      <c r="L24" s="299">
         <v>25.17</v>
       </c>
-      <c r="M24" s="297">
+      <c r="M24" s="287">
         <v>30</v>
       </c>
-      <c r="N24" s="298">
+      <c r="N24" s="293">
         <v>30.59</v>
       </c>
-      <c r="O24" s="291">
+      <c r="O24" s="294">
         <v>21.84</v>
       </c>
-      <c r="P24" s="292">
+      <c r="P24" s="295">
         <v>20.93</v>
       </c>
-      <c r="Q24" s="299">
+      <c r="Q24" s="288">
         <v>20.8</v>
       </c>
-      <c r="R24" s="293">
+      <c r="R24" s="296">
         <v>26.21</v>
       </c>
-      <c r="S24" s="294">
+      <c r="S24" s="297">
         <v>23.73</v>
       </c>
-      <c r="T24" s="289">
-        <v>-0.29</v>
+      <c r="T24" s="298">
+        <v>-2.35</v>
       </c>
     </row>
     <row r="25">
@@ -9900,7 +9932,7 @@
       <c r="C25" t="str">
         <v>600693</v>
       </c>
-      <c r="D25" s="308" t="str">
+      <c r="D25" s="304" t="str">
         <v>净卖: -8573.84万</v>
       </c>
       <c r="E25">
@@ -9915,41 +9947,41 @@
       <c r="H25">
         <v>0</v>
       </c>
-      <c r="I25" s="309">
+      <c r="I25" s="305">
         <v>-2.52</v>
       </c>
-      <c r="J25" s="310">
+      <c r="J25" s="301">
         <v>2</v>
       </c>
-      <c r="K25" s="303">
+      <c r="K25" s="302">
         <v>-7.69</v>
       </c>
-      <c r="L25" s="311">
+      <c r="L25" s="306">
         <v>-16.92</v>
       </c>
-      <c r="M25" s="304">
+      <c r="M25" s="309">
         <v>-16.92</v>
       </c>
-      <c r="N25" s="301">
+      <c r="N25" s="312">
         <v>-14.27</v>
       </c>
-      <c r="O25" s="312">
+      <c r="O25" s="307">
         <v>-16.64</v>
       </c>
-      <c r="P25" s="300">
+      <c r="P25" s="308">
         <v>-16.6</v>
       </c>
-      <c r="Q25" s="305">
+      <c r="Q25" s="303">
         <v>-11.79</v>
       </c>
-      <c r="R25" s="306">
+      <c r="R25" s="310">
         <v>-8.67</v>
       </c>
-      <c r="S25" s="307">
+      <c r="S25" s="311">
         <v>-2.05</v>
       </c>
-      <c r="T25" s="302">
-        <v>-44.06</v>
+      <c r="T25" s="300">
+        <v>-45.45</v>
       </c>
     </row>
     <row r="26">
@@ -9977,41 +10009,41 @@
       <c r="H26">
         <v>-1.39</v>
       </c>
-      <c r="I26" s="325">
+      <c r="I26" s="314">
         <v>11.56</v>
       </c>
-      <c r="J26" s="322">
+      <c r="J26" s="315">
         <v>12.1</v>
       </c>
-      <c r="K26" s="313">
+      <c r="K26" s="324">
         <v>23.31</v>
       </c>
-      <c r="L26" s="323">
+      <c r="L26" s="316">
         <v>15.93</v>
       </c>
-      <c r="M26" s="316">
+      <c r="M26" s="317">
         <v>12.77</v>
       </c>
-      <c r="N26" s="324">
+      <c r="N26" s="322">
         <v>13.16</v>
       </c>
-      <c r="O26" s="317">
+      <c r="O26" s="318">
         <v>10.86</v>
       </c>
-      <c r="P26" s="314">
+      <c r="P26" s="323">
         <v>9.14</v>
       </c>
-      <c r="Q26" s="318">
+      <c r="Q26" s="325">
         <v>9.84</v>
       </c>
-      <c r="R26" s="315">
+      <c r="R26" s="320">
         <v>10.82</v>
       </c>
       <c r="S26" s="319">
         <v>-0.23</v>
       </c>
-      <c r="T26" s="320">
-        <v>-25.58</v>
+      <c r="T26" s="313">
+        <v>-26.2</v>
       </c>
     </row>
     <row r="27">
@@ -10039,41 +10071,41 @@
       <c r="H27">
         <v>5.01</v>
       </c>
-      <c r="I27" s="335">
+      <c r="I27" s="332">
         <v>-4.3</v>
       </c>
-      <c r="J27" s="336">
+      <c r="J27" s="330">
         <v>5.27</v>
       </c>
-      <c r="K27" s="326">
+      <c r="K27" s="338">
         <v>-1.03</v>
       </c>
-      <c r="L27" s="337">
+      <c r="L27" s="335">
         <v>-3.73</v>
       </c>
       <c r="M27" s="331">
         <v>-3.4</v>
       </c>
-      <c r="N27" s="327">
+      <c r="N27" s="326">
         <v>-5.37</v>
       </c>
-      <c r="O27" s="328">
+      <c r="O27" s="327">
         <v>-6.83</v>
       </c>
-      <c r="P27" s="338">
+      <c r="P27" s="336">
         <v>-6.23</v>
       </c>
-      <c r="Q27" s="329">
+      <c r="Q27" s="333">
         <v>-5.4</v>
       </c>
-      <c r="R27" s="332">
+      <c r="R27" s="328">
         <v>-14.83</v>
       </c>
-      <c r="S27" s="330">
+      <c r="S27" s="329">
         <v>-14.37</v>
       </c>
-      <c r="T27" s="333">
-        <v>-36.47</v>
+      <c r="T27" s="337">
+        <v>-37</v>
       </c>
     </row>
     <row r="28">
@@ -10086,7 +10118,7 @@
       <c r="C28" t="str">
         <v>002361</v>
       </c>
-      <c r="D28" s="349" t="str">
+      <c r="D28" s="341" t="str">
         <v>净卖: -5584.65万</v>
       </c>
       <c r="E28">
@@ -10101,41 +10133,41 @@
       <c r="H28">
         <v>-3.59</v>
       </c>
-      <c r="I28" s="343">
+      <c r="I28" s="347">
         <v>-6.66</v>
       </c>
-      <c r="J28" s="350">
+      <c r="J28" s="348">
         <v>2.65</v>
       </c>
-      <c r="K28" s="345">
+      <c r="K28" s="349">
         <v>-1.93</v>
       </c>
-      <c r="L28" s="351">
+      <c r="L28" s="344">
         <v>3.51</v>
       </c>
-      <c r="M28" s="339">
+      <c r="M28" s="350">
         <v>3.15</v>
       </c>
       <c r="N28" s="340">
         <v>13.46</v>
       </c>
-      <c r="O28" s="341">
+      <c r="O28" s="351">
         <v>11.67</v>
       </c>
-      <c r="P28" s="344">
+      <c r="P28" s="342">
         <v>20.26</v>
       </c>
-      <c r="Q28" s="347">
+      <c r="Q28" s="339">
         <v>17.97</v>
       </c>
-      <c r="R28" s="346">
+      <c r="R28" s="345">
         <v>29.71</v>
       </c>
-      <c r="S28" s="342">
+      <c r="S28" s="343">
         <v>16.75</v>
       </c>
-      <c r="T28" s="348">
-        <v>47.67</v>
+      <c r="T28" s="346">
+        <v>62.42</v>
       </c>
     </row>
     <row r="29">
@@ -10166,38 +10198,38 @@
       <c r="I29" s="360">
         <v>0</v>
       </c>
-      <c r="J29" s="363">
+      <c r="J29" s="353">
         <v>-1.36</v>
       </c>
-      <c r="K29" s="354">
+      <c r="K29" s="362">
         <v>-7.18</v>
       </c>
-      <c r="L29" s="361">
+      <c r="L29" s="357">
         <v>-8.91</v>
       </c>
-      <c r="M29" s="355">
+      <c r="M29" s="354">
         <v>-9.1</v>
       </c>
-      <c r="N29" s="364">
+      <c r="N29" s="358">
         <v>-9.98</v>
       </c>
-      <c r="O29" s="358">
+      <c r="O29" s="363">
         <v>-8.84</v>
       </c>
-      <c r="P29" s="362">
+      <c r="P29" s="355">
         <v>-10.31</v>
       </c>
-      <c r="Q29" s="352">
+      <c r="Q29" s="364">
         <v>-7.96</v>
       </c>
-      <c r="R29" s="353">
+      <c r="R29" s="361">
         <v>-8.8</v>
       </c>
-      <c r="S29" s="356">
+      <c r="S29" s="352">
         <v>-9.28</v>
       </c>
-      <c r="T29" s="357">
-        <v>-10.83</v>
+      <c r="T29" s="356">
+        <v>-12.49</v>
       </c>
     </row>
     <row r="30">
@@ -10210,7 +10242,7 @@
       <c r="C30" t="str">
         <v>002788</v>
       </c>
-      <c r="D30" s="371" t="str">
+      <c r="D30" s="374" t="str">
         <v>净买: 3825.22万</v>
       </c>
       <c r="E30">
@@ -10225,41 +10257,41 @@
       <c r="H30">
         <v>5.81</v>
       </c>
-      <c r="I30" s="375">
+      <c r="I30" s="365">
         <v>3.95</v>
       </c>
-      <c r="J30" s="376">
+      <c r="J30" s="366">
         <v>14.35</v>
       </c>
-      <c r="K30" s="377">
+      <c r="K30" s="375">
         <v>11.56</v>
       </c>
-      <c r="L30" s="365">
+      <c r="L30" s="376">
         <v>13.48</v>
       </c>
-      <c r="M30" s="366">
+      <c r="M30" s="367">
         <v>9.23</v>
       </c>
-      <c r="N30" s="369">
+      <c r="N30" s="368">
         <v>1.08</v>
       </c>
-      <c r="O30" s="372">
+      <c r="O30" s="373">
         <v>-9.03</v>
       </c>
-      <c r="P30" s="367">
+      <c r="P30" s="371">
         <v>-18.14</v>
       </c>
-      <c r="Q30" s="368">
+      <c r="Q30" s="377">
         <v>-26.33</v>
       </c>
-      <c r="R30" s="373">
+      <c r="R30" s="369">
         <v>-30.78</v>
       </c>
-      <c r="S30" s="370">
+      <c r="S30" s="372">
         <v>-32.45</v>
       </c>
-      <c r="T30" s="374">
-        <v>-37.06</v>
+      <c r="T30" s="370">
+        <v>-38.77</v>
       </c>
     </row>
     <row r="31">
@@ -10272,7 +10304,7 @@
       <c r="C31" t="str">
         <v>002788</v>
       </c>
-      <c r="D31" s="381" t="str">
+      <c r="D31" s="389" t="str">
         <v>净卖: -24.07万</v>
       </c>
       <c r="E31">
@@ -10287,41 +10319,41 @@
       <c r="H31">
         <v>-0.04</v>
       </c>
-      <c r="I31" s="389">
+      <c r="I31" s="379">
         <v>10.05</v>
       </c>
-      <c r="J31" s="390">
+      <c r="J31" s="380">
         <v>7.37</v>
       </c>
-      <c r="K31" s="382">
+      <c r="K31" s="383">
         <v>9.21</v>
       </c>
-      <c r="L31" s="387">
+      <c r="L31" s="384">
         <v>5.12</v>
       </c>
-      <c r="M31" s="388">
+      <c r="M31" s="385">
         <v>-2.72</v>
       </c>
-      <c r="N31" s="383">
+      <c r="N31" s="390">
         <v>-12.45</v>
       </c>
-      <c r="O31" s="384">
+      <c r="O31" s="386">
         <v>-21.22</v>
       </c>
-      <c r="P31" s="385">
+      <c r="P31" s="388">
         <v>-29.1</v>
       </c>
-      <c r="Q31" s="386">
+      <c r="Q31" s="381">
         <v>-33.39</v>
       </c>
-      <c r="R31" s="378">
+      <c r="R31" s="387">
         <v>-34.99</v>
       </c>
-      <c r="S31" s="379">
+      <c r="S31" s="378">
         <v>-32.95</v>
       </c>
-      <c r="T31" s="380">
-        <v>-39.43</v>
+      <c r="T31" s="382">
+        <v>-41.07</v>
       </c>
     </row>
     <row r="32">
@@ -10334,7 +10366,7 @@
       <c r="C32" t="str">
         <v>600151</v>
       </c>
-      <c r="D32" s="399" t="str">
+      <c r="D32" s="391" t="str">
         <v>净买: 7884.07万</v>
       </c>
       <c r="E32">
@@ -10349,41 +10381,41 @@
       <c r="H32">
         <v>3.26</v>
       </c>
-      <c r="I32" s="400">
+      <c r="I32" s="395">
         <v>-11.53</v>
       </c>
-      <c r="J32" s="392">
+      <c r="J32" s="401">
         <v>-20.23</v>
       </c>
       <c r="K32" s="396">
         <v>-21.06</v>
       </c>
-      <c r="L32" s="403">
+      <c r="L32" s="397">
         <v>-24.22</v>
       </c>
-      <c r="M32" s="391">
+      <c r="M32" s="398">
         <v>-21.69</v>
       </c>
-      <c r="N32" s="393">
+      <c r="N32" s="402">
         <v>-16.73</v>
       </c>
-      <c r="O32" s="401">
+      <c r="O32" s="392">
         <v>-25.05</v>
       </c>
-      <c r="P32" s="397">
+      <c r="P32" s="403">
         <v>-25.88</v>
       </c>
-      <c r="Q32" s="394">
+      <c r="Q32" s="393">
         <v>-27.43</v>
       </c>
-      <c r="R32" s="395">
+      <c r="R32" s="394">
         <v>-26.65</v>
       </c>
-      <c r="S32" s="398">
+      <c r="S32" s="399">
         <v>-26.61</v>
       </c>
-      <c r="T32" s="402">
-        <v>-27.09</v>
+      <c r="T32" s="400">
+        <v>-26.46</v>
       </c>
     </row>
     <row r="33">
@@ -10396,7 +10428,7 @@
       <c r="C33" t="str">
         <v>600916</v>
       </c>
-      <c r="D33" s="406" t="str">
+      <c r="D33" s="415" t="str">
         <v>净卖: -1428.23万</v>
       </c>
       <c r="E33">
@@ -10411,41 +10443,41 @@
       <c r="H33">
         <v>10.04</v>
       </c>
-      <c r="I33" s="414">
+      <c r="I33" s="407">
         <v>0</v>
       </c>
-      <c r="J33" s="407">
+      <c r="J33" s="409">
         <v>10.02</v>
       </c>
-      <c r="K33" s="415">
+      <c r="K33" s="416">
         <v>19.64</v>
       </c>
-      <c r="L33" s="416">
+      <c r="L33" s="404">
         <v>7.66</v>
       </c>
       <c r="M33" s="410">
         <v>5.87</v>
       </c>
-      <c r="N33" s="404">
+      <c r="N33" s="411">
         <v>-0.81</v>
       </c>
-      <c r="O33" s="408">
+      <c r="O33" s="412">
         <v>-8.96</v>
       </c>
-      <c r="P33" s="411">
+      <c r="P33" s="405">
         <v>-6.93</v>
       </c>
-      <c r="Q33" s="412">
+      <c r="Q33" s="413">
         <v>-5.79</v>
       </c>
-      <c r="R33" s="413">
+      <c r="R33" s="406">
         <v>-8.96</v>
       </c>
-      <c r="S33" s="405">
+      <c r="S33" s="408">
         <v>-9.54</v>
       </c>
-      <c r="T33" s="409">
-        <v>-25.67</v>
+      <c r="T33" s="414">
+        <v>-26</v>
       </c>
     </row>
     <row r="34">
@@ -10458,7 +10490,7 @@
       <c r="C34" t="str">
         <v>600969</v>
       </c>
-      <c r="D34" s="423" t="str">
+      <c r="D34" s="422" t="str">
         <v>净卖: -723.23万</v>
       </c>
       <c r="E34">
@@ -10473,41 +10505,41 @@
       <c r="H34">
         <v>0</v>
       </c>
-      <c r="I34" s="420">
+      <c r="I34" s="426">
         <v>-9.99</v>
       </c>
-      <c r="J34" s="429">
+      <c r="J34" s="417">
         <v>-9.99</v>
       </c>
-      <c r="K34" s="426">
+      <c r="K34" s="423">
         <v>-18.98</v>
       </c>
-      <c r="L34" s="421">
+      <c r="L34" s="424">
         <v>-21.07</v>
       </c>
-      <c r="M34" s="427">
+      <c r="M34" s="418">
         <v>-21.98</v>
       </c>
-      <c r="N34" s="417">
+      <c r="N34" s="419">
         <v>-18.98</v>
       </c>
-      <c r="O34" s="418">
+      <c r="O34" s="420">
         <v>-16.9</v>
       </c>
-      <c r="P34" s="424">
+      <c r="P34" s="427">
         <v>-16.82</v>
       </c>
       <c r="Q34" s="428">
         <v>-14.32</v>
       </c>
-      <c r="R34" s="422">
+      <c r="R34" s="425">
         <v>-13.66</v>
       </c>
-      <c r="S34" s="419">
+      <c r="S34" s="421">
         <v>-15.99</v>
       </c>
-      <c r="T34" s="425">
-        <v>-15.4</v>
+      <c r="T34" s="429">
+        <v>-14.74</v>
       </c>
     </row>
     <row r="35">
@@ -10520,7 +10552,7 @@
       <c r="C35" t="str">
         <v>002040</v>
       </c>
-      <c r="D35" s="438" t="str">
+      <c r="D35" s="440" t="str">
         <v>净卖: -895.74万</v>
       </c>
       <c r="E35">
@@ -10535,41 +10567,41 @@
       <c r="H35">
         <v>-7.37</v>
       </c>
-      <c r="I35" s="432">
+      <c r="I35" s="435">
         <v>-2.87</v>
       </c>
-      <c r="J35" s="439">
+      <c r="J35" s="441">
         <v>-8.52</v>
       </c>
-      <c r="K35" s="431">
+      <c r="K35" s="442">
         <v>-8.36</v>
       </c>
-      <c r="L35" s="440">
+      <c r="L35" s="438">
         <v>-10.49</v>
       </c>
-      <c r="M35" s="433">
+      <c r="M35" s="432">
         <v>-8.44</v>
       </c>
-      <c r="N35" s="441">
+      <c r="N35" s="439">
         <v>-9.02</v>
       </c>
-      <c r="O35" s="442">
+      <c r="O35" s="436">
         <v>-9.51</v>
       </c>
-      <c r="P35" s="434">
+      <c r="P35" s="430">
         <v>-12.05</v>
       </c>
-      <c r="Q35" s="430">
+      <c r="Q35" s="431">
         <v>-8.28</v>
       </c>
-      <c r="R35" s="435">
+      <c r="R35" s="433">
         <v>-10.33</v>
       </c>
-      <c r="S35" s="436">
+      <c r="S35" s="434">
         <v>-11.07</v>
       </c>
       <c r="T35" s="437">
-        <v>-17.7</v>
+        <v>-17.54</v>
       </c>
     </row>
     <row r="36">
@@ -10582,7 +10614,7 @@
       <c r="C36" t="str">
         <v>603017</v>
       </c>
-      <c r="D36" s="446" t="str">
+      <c r="D36" s="443" t="str">
         <v>净买: 694.09万</v>
       </c>
       <c r="E36">
@@ -10597,41 +10629,41 @@
       <c r="H36">
         <v>2.04</v>
       </c>
-      <c r="I36" s="447">
+      <c r="I36" s="448">
         <v>7.84</v>
       </c>
-      <c r="J36" s="448">
+      <c r="J36" s="451">
         <v>7.04</v>
       </c>
-      <c r="K36" s="452">
+      <c r="K36" s="444">
         <v>6.48</v>
       </c>
-      <c r="L36" s="455">
+      <c r="L36" s="445">
         <v>5.04</v>
       </c>
-      <c r="M36" s="443">
+      <c r="M36" s="446">
         <v>7.28</v>
       </c>
       <c r="N36" s="449">
         <v>5.44</v>
       </c>
-      <c r="O36" s="450">
+      <c r="O36" s="452">
         <v>10.72</v>
       </c>
       <c r="P36" s="453">
         <v>10.32</v>
       </c>
-      <c r="Q36" s="445">
+      <c r="Q36" s="454">
         <v>7.92</v>
       </c>
-      <c r="R36" s="454">
+      <c r="R36" s="447">
         <v>1.28</v>
       </c>
-      <c r="S36" s="444">
+      <c r="S36" s="450">
         <v>11.44</v>
       </c>
-      <c r="T36" s="451">
-        <v>13.68</v>
+      <c r="T36" s="455">
+        <v>25.04</v>
       </c>
     </row>
     <row r="37">
@@ -10644,7 +10676,7 @@
       <c r="C37" t="str">
         <v>600495</v>
       </c>
-      <c r="D37" s="465" t="str">
+      <c r="D37" s="459" t="str">
         <v>净买: 998.97万</v>
       </c>
       <c r="E37">
@@ -10659,41 +10691,41 @@
       <c r="H37">
         <v>0</v>
       </c>
-      <c r="I37" s="460">
+      <c r="I37" s="467">
         <v>10.04</v>
       </c>
-      <c r="J37" s="461">
+      <c r="J37" s="463">
         <v>11.16</v>
       </c>
-      <c r="K37" s="462">
+      <c r="K37" s="464">
         <v>12.28</v>
       </c>
-      <c r="L37" s="466">
+      <c r="L37" s="460">
         <v>2.23</v>
       </c>
-      <c r="M37" s="467">
+      <c r="M37" s="465">
         <v>0.67</v>
       </c>
-      <c r="N37" s="463">
+      <c r="N37" s="461">
         <v>4.46</v>
       </c>
-      <c r="O37" s="457">
+      <c r="O37" s="458">
         <v>0.67</v>
       </c>
-      <c r="P37" s="458">
+      <c r="P37" s="468">
         <v>0.45</v>
       </c>
-      <c r="Q37" s="459">
+      <c r="Q37" s="462">
         <v>-1.34</v>
       </c>
-      <c r="R37" s="468">
+      <c r="R37" s="456">
         <v>-1.34</v>
       </c>
-      <c r="S37" s="456">
+      <c r="S37" s="457">
         <v>-2.01</v>
       </c>
-      <c r="T37" s="464">
-        <v>0.45</v>
+      <c r="T37" s="466">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="38">
@@ -10706,7 +10738,7 @@
       <c r="C38" t="str">
         <v>600488</v>
       </c>
-      <c r="D38" s="469" t="str">
+      <c r="D38" s="472" t="str">
         <v>净卖: -1388.23万</v>
       </c>
       <c r="E38">
@@ -10721,94 +10753,86 @@
       <c r="H38">
         <v>9.92</v>
       </c>
-      <c r="I38" s="472">
+      <c r="I38" s="470">
         <v>0</v>
       </c>
       <c r="J38" s="473">
         <v>10.07</v>
       </c>
-      <c r="K38" s="474">
+      <c r="K38" s="478">
         <v>21.01</v>
       </c>
-      <c r="L38" s="470">
+      <c r="L38" s="474">
         <v>33.16</v>
       </c>
-      <c r="M38" s="478">
+      <c r="M38" s="475">
         <v>27.78</v>
       </c>
       <c r="N38" s="479">
         <v>22.92</v>
       </c>
-      <c r="O38" s="471">
+      <c r="O38" s="480">
         <v>11.46</v>
       </c>
-      <c r="P38" s="480">
+      <c r="P38" s="476">
         <v>2.6</v>
       </c>
-      <c r="Q38" s="475">
+      <c r="Q38" s="477">
         <v>7.99</v>
       </c>
-      <c r="R38" s="476">
+      <c r="R38" s="469">
         <v>18.75</v>
       </c>
       <c r="S38" s="481">
         <v>9.2</v>
       </c>
-      <c r="T38" s="477">
-        <v>11.28</v>
+      <c r="T38" s="471">
+        <v>9.55</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>纪录总数</v>
-      </c>
-      <c r="B39" t="str"/>
-      <c r="C39" t="str"/>
-      <c r="D39" t="str"/>
-      <c r="E39" t="str"/>
-      <c r="F39" t="str"/>
-      <c r="G39" t="str"/>
-      <c r="H39" t="str"/>
-      <c r="I39">
-        <v>37</v>
-      </c>
-      <c r="J39">
-        <v>37</v>
-      </c>
-      <c r="K39">
-        <v>37</v>
-      </c>
-      <c r="L39">
-        <v>37</v>
-      </c>
-      <c r="M39">
-        <v>37</v>
-      </c>
-      <c r="N39">
-        <v>37</v>
-      </c>
-      <c r="O39">
-        <v>37</v>
-      </c>
-      <c r="P39">
-        <v>37</v>
-      </c>
-      <c r="Q39">
-        <v>37</v>
-      </c>
-      <c r="R39">
-        <v>37</v>
-      </c>
-      <c r="S39">
-        <v>37</v>
-      </c>
-      <c r="T39">
-        <v>37</v>
-      </c>
+        <v>2026-04-21</v>
+      </c>
+      <c r="B39" t="str">
+        <v>海泰科</v>
+      </c>
+      <c r="C39" t="str">
+        <v>301022</v>
+      </c>
+      <c r="D39" s="483" t="str">
+        <v>净买: 646.40万</v>
+      </c>
+      <c r="E39">
+        <v>33.4</v>
+      </c>
+      <c r="F39">
+        <v>33.4</v>
+      </c>
+      <c r="G39">
+        <v>33.4</v>
+      </c>
+      <c r="H39">
+        <v>20.01</v>
+      </c>
+      <c r="I39" s="482">
+        <v>0</v>
+      </c>
+      <c r="J39" t="str"/>
+      <c r="K39" t="str"/>
+      <c r="L39" t="str"/>
+      <c r="M39" t="str"/>
+      <c r="N39" t="str"/>
+      <c r="O39" t="str"/>
+      <c r="P39" t="str"/>
+      <c r="Q39" t="str"/>
+      <c r="R39" t="str"/>
+      <c r="S39" t="str"/>
+      <c r="T39" t="str"/>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>上涨比例</v>
+        <v>纪录总数</v>
       </c>
       <c r="B40" t="str"/>
       <c r="C40" t="str"/>
@@ -10817,46 +10841,46 @@
       <c r="F40" t="str"/>
       <c r="G40" t="str"/>
       <c r="H40" t="str"/>
-      <c r="I40" s="486">
-        <v>54.05</v>
-      </c>
-      <c r="J40" s="490">
-        <v>62.16</v>
-      </c>
-      <c r="K40" s="482">
-        <v>54.05</v>
-      </c>
-      <c r="L40" s="483">
-        <v>56.76</v>
-      </c>
-      <c r="M40" s="487">
-        <v>51.35</v>
-      </c>
-      <c r="N40" s="484">
-        <v>48.65</v>
-      </c>
-      <c r="O40" s="489">
-        <v>45.95</v>
-      </c>
-      <c r="P40" s="491">
-        <v>40.54</v>
-      </c>
-      <c r="Q40" s="485">
-        <v>35.14</v>
-      </c>
-      <c r="R40" s="488">
-        <v>37.84</v>
-      </c>
-      <c r="S40" s="492">
-        <v>37.84</v>
-      </c>
-      <c r="T40" s="493">
-        <v>29.73</v>
+      <c r="I40">
+        <v>38</v>
+      </c>
+      <c r="J40">
+        <v>37</v>
+      </c>
+      <c r="K40">
+        <v>37</v>
+      </c>
+      <c r="L40">
+        <v>37</v>
+      </c>
+      <c r="M40">
+        <v>37</v>
+      </c>
+      <c r="N40">
+        <v>37</v>
+      </c>
+      <c r="O40">
+        <v>37</v>
+      </c>
+      <c r="P40">
+        <v>37</v>
+      </c>
+      <c r="Q40">
+        <v>37</v>
+      </c>
+      <c r="R40">
+        <v>37</v>
+      </c>
+      <c r="S40">
+        <v>37</v>
+      </c>
+      <c r="T40">
+        <v>37</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>平均涨幅</v>
+        <v>上涨比例</v>
       </c>
       <c r="B41" t="str"/>
       <c r="C41" t="str"/>
@@ -10865,41 +10889,89 @@
       <c r="F41" t="str"/>
       <c r="G41" t="str"/>
       <c r="H41" t="str"/>
-      <c r="I41" s="494">
-        <v>2.35</v>
-      </c>
-      <c r="J41" s="495">
+      <c r="I41" s="489">
+        <v>52.63</v>
+      </c>
+      <c r="J41" s="490">
+        <v>62.16</v>
+      </c>
+      <c r="K41" s="486">
+        <v>54.05</v>
+      </c>
+      <c r="L41" s="491">
+        <v>56.76</v>
+      </c>
+      <c r="M41" s="495">
+        <v>51.35</v>
+      </c>
+      <c r="N41" s="492">
+        <v>48.65</v>
+      </c>
+      <c r="O41" s="493">
+        <v>45.95</v>
+      </c>
+      <c r="P41" s="484">
+        <v>40.54</v>
+      </c>
+      <c r="Q41" s="487">
+        <v>35.14</v>
+      </c>
+      <c r="R41" s="488">
+        <v>37.84</v>
+      </c>
+      <c r="S41" s="494">
+        <v>37.84</v>
+      </c>
+      <c r="T41" s="485">
+        <v>27.03</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>平均涨幅</v>
+      </c>
+      <c r="B42" t="str"/>
+      <c r="C42" t="str"/>
+      <c r="D42" t="str"/>
+      <c r="E42" t="str"/>
+      <c r="F42" t="str"/>
+      <c r="G42" t="str"/>
+      <c r="H42" t="str"/>
+      <c r="I42" s="496">
+        <v>2.29</v>
+      </c>
+      <c r="J42" s="499">
         <v>3.37</v>
       </c>
-      <c r="K41" s="502">
+      <c r="K42" s="504">
         <v>3.41</v>
       </c>
-      <c r="L41" s="496">
+      <c r="L42" s="501">
         <v>3.11</v>
       </c>
-      <c r="M41" s="497">
+      <c r="M42" s="505">
         <v>4.56</v>
       </c>
-      <c r="N41" s="504">
+      <c r="N42" s="500">
         <v>3.99</v>
       </c>
-      <c r="O41" s="499">
+      <c r="O42" s="506">
         <v>2.28</v>
       </c>
-      <c r="P41" s="498">
+      <c r="P42" s="497">
         <v>0.79</v>
       </c>
-      <c r="Q41" s="503">
+      <c r="Q42" s="502">
         <v>-0.11</v>
       </c>
-      <c r="R41" s="500">
+      <c r="R42" s="503">
         <v>-0.68</v>
       </c>
-      <c r="S41" s="501">
+      <c r="S42" s="507">
         <v>-0.22</v>
       </c>
-      <c r="T41" s="505">
-        <v>-2.34</v>
+      <c r="T42" s="498">
+        <v>-2.08</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/湖州劳动路/index.xlsx
+++ b/youzi/湖州劳动路/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="509">
+  <fills count="513">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,6 +39,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -63,42 +105,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD02F3E"/>
         <bgColor/>
       </patternFill>
@@ -111,12 +117,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFCD2E3D"/>
         <bgColor/>
       </patternFill>
@@ -129,6 +129,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF22913C"/>
         <bgColor/>
       </patternFill>
@@ -141,6 +153,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -153,79 +351,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -243,31 +417,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,79 +447,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -363,55 +489,1969 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4553"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8BCF9B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8BCF9B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4CB564"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8336"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CFD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8336"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA6DAB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -423,13 +2463,295 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF83CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -447,121 +2769,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D79"/>
+        <fgColor rgb="FFFBECEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF82CB93"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -573,73 +2847,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -651,6 +2871,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -669,1555 +2931,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BCF9B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4553"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BCF9B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4CB564"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CFD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8336"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA6DAB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -2229,781 +3021,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF83CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ADB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF249A40"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF249A40"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3021,31 +3075,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3057,30 +3093,46 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD43141"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
+        <fgColor rgb="FFB42331"/>
         <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="508">
+  <borders count="512">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -6641,7 +6693,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="508">
+  <cellXfs count="512">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8162,6 +8214,18 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="507" fillId="508" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="508" fillId="509" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="509" fillId="510" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="510" fillId="511" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="511" fillId="512" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -8506,7 +8570,7 @@
       <c r="C2" t="str">
         <v>002105</v>
       </c>
-      <c r="D2" s="4" t="str">
+      <c r="D2" s="11" t="str">
         <v>净卖: -286.93万</v>
       </c>
       <c r="E2">
@@ -8521,41 +8585,41 @@
       <c r="H2">
         <v>3.63</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>6.13</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="2">
         <v>16.75</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="7">
         <v>28.37</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="13">
         <v>41.25</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="3">
         <v>55.38</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="4">
         <v>46.12</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="8">
         <v>46.75</v>
       </c>
       <c r="P2" s="9">
         <v>33.13</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="10">
         <v>34.87</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="5">
         <v>21.38</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="6">
         <v>11.62</v>
       </c>
-      <c r="T2" s="10">
-        <v>-21</v>
+      <c r="T2" s="1">
+        <v>-22.12</v>
       </c>
     </row>
     <row r="3">
@@ -8568,7 +8632,7 @@
       <c r="C3" t="str">
         <v>002760</v>
       </c>
-      <c r="D3" s="18" t="str">
+      <c r="D3" s="17" t="str">
         <v>净买: 1264.22万</v>
       </c>
       <c r="E3">
@@ -8589,35 +8653,35 @@
       <c r="J3" s="15">
         <v>2.8</v>
       </c>
-      <c r="K3" s="16">
+      <c r="K3" s="18">
         <v>-6.84</v>
       </c>
       <c r="L3" s="24">
         <v>-13.76</v>
       </c>
-      <c r="M3" s="25">
+      <c r="M3" s="21">
         <v>-13.72</v>
       </c>
-      <c r="N3" s="26">
+      <c r="N3" s="25">
         <v>-14.84</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="16">
         <v>-15.92</v>
       </c>
       <c r="P3" s="22">
         <v>-16.68</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="26">
         <v>-19.6</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3" s="19">
         <v>-22.72</v>
       </c>
-      <c r="S3" s="17">
+      <c r="S3" s="23">
         <v>-23.88</v>
       </c>
-      <c r="T3" s="23">
-        <v>-12.4</v>
+      <c r="T3" s="20">
+        <v>-11.76</v>
       </c>
     </row>
     <row r="4">
@@ -8630,7 +8694,7 @@
       <c r="C4" t="str">
         <v>002760</v>
       </c>
-      <c r="D4" s="34" t="str">
+      <c r="D4" s="27" t="str">
         <v>净卖: -1488.32万</v>
       </c>
       <c r="E4">
@@ -8645,41 +8709,41 @@
       <c r="H4">
         <v>4.59</v>
       </c>
-      <c r="I4" s="37">
+      <c r="I4" s="30">
         <v>-7.59</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="33">
         <v>-16.25</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="31">
         <v>-22.47</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="28">
         <v>-22.44</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="34">
         <v>-23.44</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="35">
         <v>-24.42</v>
       </c>
-      <c r="O4" s="39">
+      <c r="O4" s="36">
         <v>-25.1</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="37">
         <v>-27.72</v>
       </c>
       <c r="Q4" s="32">
         <v>-30.53</v>
       </c>
-      <c r="R4" s="33">
+      <c r="R4" s="38">
         <v>-31.57</v>
       </c>
-      <c r="S4" s="27">
+      <c r="S4" s="29">
         <v>-31.07</v>
       </c>
-      <c r="T4" s="28">
-        <v>-21.25</v>
+      <c r="T4" s="39">
+        <v>-20.68</v>
       </c>
     </row>
     <row r="5">
@@ -8692,7 +8756,7 @@
       <c r="C5" t="str">
         <v>603958</v>
       </c>
-      <c r="D5" s="40" t="str">
+      <c r="D5" s="51" t="str">
         <v>净买: 2814.34万</v>
       </c>
       <c r="E5">
@@ -8707,41 +8771,41 @@
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="44">
         <v>-3.71</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="52">
         <v>-13.32</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="40">
         <v>-18.35</v>
       </c>
-      <c r="L5" s="42">
+      <c r="L5" s="45">
         <v>-15.42</v>
       </c>
-      <c r="M5" s="52">
+      <c r="M5" s="49">
         <v>-11.81</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="42">
         <v>-11.27</v>
       </c>
-      <c r="O5" s="45">
+      <c r="O5" s="43">
         <v>-11.13</v>
       </c>
-      <c r="P5" s="49">
+      <c r="P5" s="46">
         <v>-13.08</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="41">
         <v>-16.15</v>
       </c>
-      <c r="R5" s="50">
+      <c r="R5" s="47">
         <v>-17.72</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="48">
         <v>-18.79</v>
       </c>
-      <c r="T5" s="51">
-        <v>29.97</v>
+      <c r="T5" s="50">
+        <v>21.18</v>
       </c>
     </row>
     <row r="6">
@@ -8754,7 +8818,7 @@
       <c r="C6" t="str">
         <v>603958</v>
       </c>
-      <c r="D6" s="55" t="str">
+      <c r="D6" s="63" t="str">
         <v>净卖: -2283.55万</v>
       </c>
       <c r="E6">
@@ -8772,38 +8836,38 @@
       <c r="I6" s="56">
         <v>-4.1</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="64">
         <v>-9.67</v>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="60">
         <v>-6.43</v>
       </c>
-      <c r="L6" s="60">
+      <c r="L6" s="65">
         <v>-2.43</v>
       </c>
-      <c r="M6" s="63">
+      <c r="M6" s="53">
         <v>-1.84</v>
       </c>
-      <c r="N6" s="53">
+      <c r="N6" s="54">
         <v>-1.67</v>
       </c>
-      <c r="O6" s="61">
+      <c r="O6" s="57">
         <v>-3.83</v>
       </c>
-      <c r="P6" s="54">
+      <c r="P6" s="61">
         <v>-7.24</v>
       </c>
-      <c r="Q6" s="64">
+      <c r="Q6" s="58">
         <v>-8.96</v>
       </c>
-      <c r="R6" s="65">
+      <c r="R6" s="62">
         <v>-10.15</v>
       </c>
-      <c r="S6" s="58">
+      <c r="S6" s="59">
         <v>-9.99</v>
       </c>
-      <c r="T6" s="62">
-        <v>43.79</v>
+      <c r="T6" s="55">
+        <v>34.07</v>
       </c>
     </row>
     <row r="7">
@@ -8831,41 +8895,41 @@
       <c r="H7">
         <v>1.72</v>
       </c>
-      <c r="I7" s="71">
+      <c r="I7" s="76">
         <v>8.14</v>
       </c>
       <c r="J7" s="69">
         <v>5.31</v>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="73">
         <v>9.04</v>
       </c>
-      <c r="L7" s="73">
+      <c r="L7" s="77">
         <v>4.75</v>
       </c>
       <c r="M7" s="74">
         <v>3.5</v>
       </c>
-      <c r="N7" s="72">
+      <c r="N7" s="70">
         <v>-6.89</v>
       </c>
-      <c r="O7" s="75">
+      <c r="O7" s="78">
         <v>-5.42</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="67">
         <v>-7.12</v>
       </c>
-      <c r="Q7" s="77">
+      <c r="Q7" s="75">
         <v>-7.23</v>
       </c>
-      <c r="R7" s="78">
+      <c r="R7" s="71">
         <v>-10.73</v>
       </c>
-      <c r="S7" s="66">
+      <c r="S7" s="72">
         <v>-9.94</v>
       </c>
-      <c r="T7" s="67">
-        <v>159.1</v>
+      <c r="T7" s="66">
+        <v>153.22</v>
       </c>
     </row>
     <row r="8">
@@ -8878,7 +8942,7 @@
       <c r="C8" t="str">
         <v>600537</v>
       </c>
-      <c r="D8" s="89" t="str">
+      <c r="D8" s="79" t="str">
         <v>净买: 358.47万</v>
       </c>
       <c r="E8">
@@ -8893,41 +8957,41 @@
       <c r="H8">
         <v>5.03</v>
       </c>
-      <c r="I8" s="86">
+      <c r="I8" s="84">
         <v>4.79</v>
       </c>
-      <c r="J8" s="90">
+      <c r="J8" s="89">
         <v>8.98</v>
       </c>
-      <c r="K8" s="83">
+      <c r="K8" s="85">
         <v>-1.8</v>
       </c>
-      <c r="L8" s="87">
+      <c r="L8" s="80">
         <v>8.08</v>
       </c>
-      <c r="M8" s="91">
+      <c r="M8" s="81">
         <v>18.86</v>
       </c>
-      <c r="N8" s="79">
+      <c r="N8" s="87">
         <v>19.76</v>
       </c>
-      <c r="O8" s="84">
+      <c r="O8" s="90">
         <v>19.16</v>
       </c>
-      <c r="P8" s="80">
+      <c r="P8" s="86">
         <v>15.57</v>
       </c>
-      <c r="Q8" s="82">
+      <c r="Q8" s="88">
         <v>8.38</v>
       </c>
-      <c r="R8" s="81">
+      <c r="R8" s="82">
         <v>4.49</v>
       </c>
-      <c r="S8" s="85">
+      <c r="S8" s="91">
         <v>14.97</v>
       </c>
-      <c r="T8" s="88">
-        <v>3.59</v>
+      <c r="T8" s="83">
+        <v>11.38</v>
       </c>
     </row>
     <row r="9">
@@ -8940,7 +9004,7 @@
       <c r="C9" t="str">
         <v>603122</v>
       </c>
-      <c r="D9" s="102" t="str">
+      <c r="D9" s="93" t="str">
         <v>净卖: -557.16万</v>
       </c>
       <c r="E9">
@@ -8955,41 +9019,41 @@
       <c r="H9">
         <v>7.07</v>
       </c>
-      <c r="I9" s="95">
+      <c r="I9" s="101">
         <v>2.8</v>
       </c>
-      <c r="J9" s="101">
+      <c r="J9" s="102">
         <v>13.09</v>
       </c>
-      <c r="K9" s="103">
+      <c r="K9" s="94">
         <v>24.4</v>
       </c>
-      <c r="L9" s="104">
+      <c r="L9" s="95">
         <v>36.85</v>
       </c>
-      <c r="M9" s="98">
+      <c r="M9" s="96">
         <v>50.57</v>
       </c>
-      <c r="N9" s="99">
+      <c r="N9" s="97">
         <v>65.69</v>
       </c>
-      <c r="O9" s="92">
+      <c r="O9" s="98">
         <v>82.21</v>
       </c>
-      <c r="P9" s="96">
+      <c r="P9" s="103">
         <v>100.38</v>
       </c>
-      <c r="Q9" s="97">
+      <c r="Q9" s="99">
         <v>110.93</v>
       </c>
-      <c r="R9" s="93">
+      <c r="R9" s="100">
         <v>132.02</v>
       </c>
-      <c r="S9" s="94">
+      <c r="S9" s="104">
         <v>155.27</v>
       </c>
-      <c r="T9" s="100">
-        <v>101.27</v>
+      <c r="T9" s="92">
+        <v>93.52</v>
       </c>
     </row>
     <row r="10">
@@ -9017,41 +9081,41 @@
       <c r="H10">
         <v>10.02</v>
       </c>
-      <c r="I10" s="114">
+      <c r="I10" s="108">
         <v>0</v>
       </c>
-      <c r="J10" s="115">
+      <c r="J10" s="114">
         <v>10.03</v>
       </c>
-      <c r="K10" s="112">
+      <c r="K10" s="106">
         <v>20.99</v>
       </c>
-      <c r="L10" s="106">
+      <c r="L10" s="109">
         <v>8.95</v>
       </c>
-      <c r="M10" s="113">
+      <c r="M10" s="115">
         <v>-2.01</v>
       </c>
-      <c r="N10" s="116">
+      <c r="N10" s="110">
         <v>-11.73</v>
       </c>
       <c r="O10" s="111">
         <v>-16.05</v>
       </c>
-      <c r="P10" s="117">
+      <c r="P10" s="116">
         <v>-13.73</v>
       </c>
-      <c r="Q10" s="107">
+      <c r="Q10" s="112">
         <v>-17.59</v>
       </c>
-      <c r="R10" s="108">
+      <c r="R10" s="113">
         <v>-17.28</v>
       </c>
-      <c r="S10" s="109">
+      <c r="S10" s="107">
         <v>-14.04</v>
       </c>
-      <c r="T10" s="110">
-        <v>-8.33</v>
+      <c r="T10" s="117">
+        <v>-11.88</v>
       </c>
     </row>
     <row r="11">
@@ -9064,7 +9128,7 @@
       <c r="C11" t="str">
         <v>600227</v>
       </c>
-      <c r="D11" s="125" t="str">
+      <c r="D11" s="128" t="str">
         <v>净买: 484.48万</v>
       </c>
       <c r="E11">
@@ -9079,41 +9143,41 @@
       <c r="H11">
         <v>1.56</v>
       </c>
-      <c r="I11" s="126">
+      <c r="I11" s="127">
         <v>8.43</v>
       </c>
       <c r="J11" s="122">
         <v>13.79</v>
       </c>
-      <c r="K11" s="123">
+      <c r="K11" s="129">
         <v>9.2</v>
       </c>
-      <c r="L11" s="129">
+      <c r="L11" s="123">
         <v>7.28</v>
       </c>
       <c r="M11" s="130">
         <v>2.68</v>
       </c>
-      <c r="N11" s="127">
+      <c r="N11" s="118">
         <v>4.6</v>
       </c>
-      <c r="O11" s="120">
+      <c r="O11" s="119">
         <v>0.77</v>
       </c>
-      <c r="P11" s="124">
+      <c r="P11" s="120">
         <v>-4.6</v>
       </c>
-      <c r="Q11" s="128">
+      <c r="Q11" s="121">
         <v>-2.68</v>
       </c>
-      <c r="R11" s="118">
+      <c r="R11" s="125">
         <v>-4.6</v>
       </c>
-      <c r="S11" s="121">
+      <c r="S11" s="124">
         <v>-2.68</v>
       </c>
-      <c r="T11" s="119">
-        <v>35.63</v>
+      <c r="T11" s="126">
+        <v>51.72</v>
       </c>
     </row>
     <row r="12">
@@ -9126,7 +9190,7 @@
       <c r="C12" t="str">
         <v>603386</v>
       </c>
-      <c r="D12" s="136" t="str">
+      <c r="D12" s="131" t="str">
         <v>净卖: -4389.34万</v>
       </c>
       <c r="E12">
@@ -9141,41 +9205,41 @@
       <c r="H12">
         <v>-8.19</v>
       </c>
-      <c r="I12" s="143">
+      <c r="I12" s="141">
         <v>-1.95</v>
       </c>
-      <c r="J12" s="137">
+      <c r="J12" s="136">
         <v>-3.78</v>
       </c>
-      <c r="K12" s="142">
+      <c r="K12" s="132">
         <v>-11.08</v>
       </c>
-      <c r="L12" s="138">
+      <c r="L12" s="133">
         <v>-18.92</v>
       </c>
-      <c r="M12" s="139">
+      <c r="M12" s="137">
         <v>-18.16</v>
       </c>
-      <c r="N12" s="140">
+      <c r="N12" s="134">
         <v>-18.54</v>
       </c>
-      <c r="O12" s="133">
+      <c r="O12" s="142">
         <v>-17.08</v>
       </c>
-      <c r="P12" s="141">
+      <c r="P12" s="138">
         <v>-17.95</v>
       </c>
-      <c r="Q12" s="131">
+      <c r="Q12" s="139">
         <v>-14.43</v>
       </c>
-      <c r="R12" s="132">
+      <c r="R12" s="135">
         <v>-20</v>
       </c>
-      <c r="S12" s="134">
+      <c r="S12" s="143">
         <v>-18.32</v>
       </c>
-      <c r="T12" s="135">
-        <v>-22.16</v>
+      <c r="T12" s="140">
+        <v>-24.16</v>
       </c>
     </row>
     <row r="13">
@@ -9188,7 +9252,7 @@
       <c r="C13" t="str">
         <v>600493</v>
       </c>
-      <c r="D13" s="150" t="str">
+      <c r="D13" s="151" t="str">
         <v>净买: 999.07万</v>
       </c>
       <c r="E13">
@@ -9203,41 +9267,41 @@
       <c r="H13">
         <v>1.85</v>
       </c>
-      <c r="I13" s="151">
+      <c r="I13" s="155">
         <v>8.05</v>
       </c>
-      <c r="J13" s="155">
+      <c r="J13" s="156">
         <v>-0.65</v>
       </c>
-      <c r="K13" s="145">
+      <c r="K13" s="153">
         <v>3.12</v>
       </c>
-      <c r="L13" s="146">
+      <c r="L13" s="144">
         <v>-4.16</v>
       </c>
-      <c r="M13" s="156">
+      <c r="M13" s="145">
         <v>-8.05</v>
       </c>
-      <c r="N13" s="152">
+      <c r="N13" s="149">
         <v>1.17</v>
       </c>
-      <c r="O13" s="147">
+      <c r="O13" s="146">
         <v>-1.3</v>
       </c>
-      <c r="P13" s="148">
+      <c r="P13" s="150">
         <v>-2.47</v>
       </c>
-      <c r="Q13" s="153">
+      <c r="Q13" s="147">
         <v>1.56</v>
       </c>
-      <c r="R13" s="149">
+      <c r="R13" s="148">
         <v>3.77</v>
       </c>
-      <c r="S13" s="144">
+      <c r="S13" s="152">
         <v>4.03</v>
       </c>
       <c r="T13" s="154">
-        <v>-1.95</v>
+        <v>-8.05</v>
       </c>
     </row>
     <row r="14">
@@ -9250,7 +9314,7 @@
       <c r="C14" t="str">
         <v>001330</v>
       </c>
-      <c r="D14" s="161" t="str">
+      <c r="D14" s="169" t="str">
         <v>净卖: -4990.62万</v>
       </c>
       <c r="E14">
@@ -9265,41 +9329,41 @@
       <c r="H14">
         <v>1.65</v>
       </c>
-      <c r="I14" s="164">
+      <c r="I14" s="161">
         <v>8.18</v>
       </c>
-      <c r="J14" s="158">
+      <c r="J14" s="165">
         <v>-2.59</v>
       </c>
-      <c r="K14" s="168">
+      <c r="K14" s="166">
         <v>-12.32</v>
       </c>
-      <c r="L14" s="165">
+      <c r="L14" s="162">
         <v>-20.34</v>
       </c>
-      <c r="M14" s="166">
+      <c r="M14" s="167">
         <v>-12.4</v>
       </c>
-      <c r="N14" s="169">
+      <c r="N14" s="168">
         <v>-18.4</v>
       </c>
-      <c r="O14" s="162">
+      <c r="O14" s="164">
         <v>-26.58</v>
       </c>
-      <c r="P14" s="159">
+      <c r="P14" s="157">
         <v>-33.95</v>
       </c>
-      <c r="Q14" s="167">
+      <c r="Q14" s="158">
         <v>-32.82</v>
       </c>
-      <c r="R14" s="157">
+      <c r="R14" s="159">
         <v>-35.66</v>
       </c>
       <c r="S14" s="163">
         <v>-34.76</v>
       </c>
       <c r="T14" s="160">
-        <v>-28.44</v>
+        <v>-36.71</v>
       </c>
     </row>
     <row r="15">
@@ -9312,7 +9376,7 @@
       <c r="C15" t="str">
         <v>600865</v>
       </c>
-      <c r="D15" s="170" t="str">
+      <c r="D15" s="175" t="str">
         <v>净买: 4692.22万</v>
       </c>
       <c r="E15">
@@ -9327,41 +9391,41 @@
       <c r="H15">
         <v>10.02</v>
       </c>
-      <c r="I15" s="171">
+      <c r="I15" s="173">
         <v>0</v>
       </c>
-      <c r="J15" s="174">
+      <c r="J15" s="176">
         <v>10.01</v>
       </c>
-      <c r="K15" s="172">
+      <c r="K15" s="181">
         <v>21</v>
       </c>
-      <c r="L15" s="178">
+      <c r="L15" s="177">
         <v>25.24</v>
       </c>
-      <c r="M15" s="175">
+      <c r="M15" s="182">
         <v>32.13</v>
       </c>
-      <c r="N15" s="176">
+      <c r="N15" s="178">
         <v>27.75</v>
       </c>
-      <c r="O15" s="180">
+      <c r="O15" s="170">
         <v>37.2</v>
       </c>
-      <c r="P15" s="177">
+      <c r="P15" s="171">
         <v>50.9</v>
       </c>
-      <c r="Q15" s="173">
+      <c r="Q15" s="179">
         <v>48.33</v>
       </c>
-      <c r="R15" s="181">
+      <c r="R15" s="172">
         <v>33.52</v>
       </c>
-      <c r="S15" s="179">
+      <c r="S15" s="174">
         <v>20.17</v>
       </c>
-      <c r="T15" s="182">
-        <v>-20.51</v>
+      <c r="T15" s="180">
+        <v>-23.57</v>
       </c>
     </row>
     <row r="16">
@@ -9374,7 +9438,7 @@
       <c r="C16" t="str">
         <v>600865</v>
       </c>
-      <c r="D16" s="184" t="str">
+      <c r="D16" s="194" t="str">
         <v>净卖: -5679.38万</v>
       </c>
       <c r="E16">
@@ -9389,41 +9453,41 @@
       <c r="H16">
         <v>10.01</v>
       </c>
-      <c r="I16" s="193">
+      <c r="I16" s="191">
         <v>0</v>
       </c>
-      <c r="J16" s="195">
+      <c r="J16" s="192">
         <v>9.99</v>
       </c>
-      <c r="K16" s="183">
+      <c r="K16" s="186">
         <v>13.84</v>
       </c>
-      <c r="L16" s="185">
+      <c r="L16" s="193">
         <v>20.1</v>
       </c>
-      <c r="M16" s="186">
+      <c r="M16" s="187">
         <v>16.12</v>
       </c>
-      <c r="N16" s="187">
+      <c r="N16" s="188">
         <v>24.72</v>
       </c>
-      <c r="O16" s="191">
+      <c r="O16" s="195">
         <v>37.17</v>
       </c>
-      <c r="P16" s="188">
+      <c r="P16" s="189">
         <v>34.83</v>
       </c>
-      <c r="Q16" s="189">
+      <c r="Q16" s="190">
         <v>21.37</v>
       </c>
-      <c r="R16" s="192">
+      <c r="R16" s="183">
         <v>9.23</v>
       </c>
-      <c r="S16" s="190">
+      <c r="S16" s="185">
         <v>3.67</v>
       </c>
-      <c r="T16" s="194">
-        <v>-27.75</v>
+      <c r="T16" s="184">
+        <v>-30.53</v>
       </c>
     </row>
     <row r="17">
@@ -9451,41 +9515,41 @@
       <c r="H17">
         <v>2.51</v>
       </c>
-      <c r="I17" s="198">
+      <c r="I17" s="202">
         <v>0.41</v>
       </c>
-      <c r="J17" s="204">
+      <c r="J17" s="207">
         <v>-0.58</v>
       </c>
-      <c r="K17" s="199">
+      <c r="K17" s="208">
         <v>9.33</v>
       </c>
-      <c r="L17" s="206">
+      <c r="L17" s="198">
         <v>13.77</v>
       </c>
-      <c r="M17" s="207">
+      <c r="M17" s="203">
         <v>25.15</v>
       </c>
-      <c r="N17" s="200">
+      <c r="N17" s="199">
         <v>22</v>
       </c>
-      <c r="O17" s="205">
+      <c r="O17" s="204">
         <v>27.65</v>
       </c>
-      <c r="P17" s="208">
+      <c r="P17" s="205">
         <v>15.52</v>
       </c>
-      <c r="Q17" s="202">
+      <c r="Q17" s="196">
         <v>3.97</v>
       </c>
-      <c r="R17" s="201">
+      <c r="R17" s="206">
         <v>3.97</v>
       </c>
-      <c r="S17" s="203">
+      <c r="S17" s="200">
         <v>7.29</v>
       </c>
-      <c r="T17" s="196">
-        <v>-31.74</v>
+      <c r="T17" s="201">
+        <v>-38.86</v>
       </c>
     </row>
     <row r="18">
@@ -9498,7 +9562,7 @@
       <c r="C18" t="str">
         <v>603023</v>
       </c>
-      <c r="D18" s="212" t="str">
+      <c r="D18" s="217" t="str">
         <v>净买: 2053.34万</v>
       </c>
       <c r="E18">
@@ -9513,41 +9577,41 @@
       <c r="H18">
         <v>-0.38</v>
       </c>
-      <c r="I18" s="209">
+      <c r="I18" s="212">
         <v>10.48</v>
       </c>
-      <c r="J18" s="218">
+      <c r="J18" s="209">
         <v>13.9</v>
       </c>
-      <c r="K18" s="210">
+      <c r="K18" s="218">
         <v>10.1</v>
       </c>
       <c r="L18" s="213">
         <v>5.14</v>
       </c>
-      <c r="M18" s="214">
+      <c r="M18" s="220">
         <v>4.95</v>
       </c>
-      <c r="N18" s="215">
+      <c r="N18" s="214">
         <v>6.29</v>
       </c>
-      <c r="O18" s="219">
+      <c r="O18" s="215">
         <v>0.57</v>
       </c>
-      <c r="P18" s="217">
+      <c r="P18" s="210">
         <v>1.9</v>
       </c>
-      <c r="Q18" s="220">
+      <c r="Q18" s="221">
         <v>-4.19</v>
       </c>
-      <c r="R18" s="216">
+      <c r="R18" s="219">
         <v>-2.48</v>
       </c>
-      <c r="S18" s="221">
+      <c r="S18" s="211">
         <v>7.24</v>
       </c>
-      <c r="T18" s="211">
-        <v>-16</v>
+      <c r="T18" s="216">
+        <v>-16.38</v>
       </c>
     </row>
     <row r="19">
@@ -9560,7 +9624,7 @@
       <c r="C19" t="str">
         <v>601566</v>
       </c>
-      <c r="D19" s="228" t="str">
+      <c r="D19" s="230" t="str">
         <v>净卖: -2383.06万</v>
       </c>
       <c r="E19">
@@ -9575,41 +9639,41 @@
       <c r="H19">
         <v>3.63</v>
       </c>
-      <c r="I19" s="229">
+      <c r="I19" s="227">
         <v>6.13</v>
       </c>
-      <c r="J19" s="233">
+      <c r="J19" s="228">
         <v>2.75</v>
       </c>
-      <c r="K19" s="230">
+      <c r="K19" s="234">
         <v>-4.06</v>
       </c>
-      <c r="L19" s="222">
+      <c r="L19" s="231">
         <v>-3.37</v>
       </c>
-      <c r="M19" s="234">
+      <c r="M19" s="232">
         <v>-6.81</v>
       </c>
-      <c r="N19" s="231">
+      <c r="N19" s="223">
         <v>-7.5</v>
       </c>
-      <c r="O19" s="223">
+      <c r="O19" s="222">
         <v>-12.5</v>
       </c>
-      <c r="P19" s="232">
+      <c r="P19" s="224">
         <v>-13.88</v>
       </c>
-      <c r="Q19" s="224">
+      <c r="Q19" s="233">
         <v>-18.06</v>
       </c>
-      <c r="R19" s="226">
+      <c r="R19" s="229">
         <v>-17.94</v>
       </c>
-      <c r="S19" s="227">
+      <c r="S19" s="225">
         <v>-16.56</v>
       </c>
-      <c r="T19" s="225">
-        <v>-31.81</v>
+      <c r="T19" s="226">
+        <v>-33</v>
       </c>
     </row>
     <row r="20">
@@ -9622,7 +9686,7 @@
       <c r="C20" t="str">
         <v>600865</v>
       </c>
-      <c r="D20" s="239" t="str">
+      <c r="D20" s="242" t="str">
         <v>净卖: -5744.79万</v>
       </c>
       <c r="E20">
@@ -9637,41 +9701,41 @@
       <c r="H20">
         <v>-5.17</v>
       </c>
-      <c r="I20" s="237">
+      <c r="I20" s="245">
         <v>9.15</v>
       </c>
-      <c r="J20" s="244">
+      <c r="J20" s="238">
         <v>15.15</v>
       </c>
-      <c r="K20" s="245">
+      <c r="K20" s="243">
         <v>11.33</v>
       </c>
-      <c r="L20" s="240">
+      <c r="L20" s="246">
         <v>19.58</v>
       </c>
-      <c r="M20" s="246">
+      <c r="M20" s="235">
         <v>31.52</v>
       </c>
-      <c r="N20" s="242">
+      <c r="N20" s="236">
         <v>29.27</v>
       </c>
-      <c r="O20" s="241">
+      <c r="O20" s="239">
         <v>16.36</v>
       </c>
-      <c r="P20" s="247">
+      <c r="P20" s="244">
         <v>4.73</v>
       </c>
-      <c r="Q20" s="235">
+      <c r="Q20" s="247">
         <v>-0.61</v>
       </c>
-      <c r="R20" s="236">
+      <c r="R20" s="237">
         <v>0.12</v>
       </c>
-      <c r="S20" s="238">
+      <c r="S20" s="240">
         <v>0.12</v>
       </c>
-      <c r="T20" s="243">
-        <v>-30.73</v>
+      <c r="T20" s="241">
+        <v>-33.39</v>
       </c>
     </row>
     <row r="21">
@@ -9684,7 +9748,7 @@
       <c r="C21" t="str">
         <v>001317</v>
       </c>
-      <c r="D21" s="250" t="str">
+      <c r="D21" s="255" t="str">
         <v>净卖: -1614.69万</v>
       </c>
       <c r="E21">
@@ -9699,41 +9763,41 @@
       <c r="H21">
         <v>-0.39</v>
       </c>
-      <c r="I21" s="258">
+      <c r="I21" s="259">
         <v>3.7</v>
       </c>
-      <c r="J21" s="253">
+      <c r="J21" s="260">
         <v>-1.32</v>
       </c>
-      <c r="K21" s="254">
+      <c r="K21" s="248">
         <v>-4.71</v>
       </c>
-      <c r="L21" s="255">
+      <c r="L21" s="249">
         <v>-6.34</v>
       </c>
-      <c r="M21" s="259">
+      <c r="M21" s="256">
         <v>-4.27</v>
       </c>
-      <c r="N21" s="252">
+      <c r="N21" s="250">
         <v>-2.18</v>
       </c>
-      <c r="O21" s="251">
+      <c r="O21" s="257">
         <v>0.05</v>
       </c>
-      <c r="P21" s="260">
+      <c r="P21" s="251">
         <v>-1.59</v>
       </c>
-      <c r="Q21" s="256">
+      <c r="Q21" s="252">
         <v>-4.68</v>
       </c>
-      <c r="R21" s="248">
+      <c r="R21" s="253">
         <v>-5.25</v>
       </c>
-      <c r="S21" s="249">
+      <c r="S21" s="254">
         <v>-4.79</v>
       </c>
-      <c r="T21" s="257">
-        <v>-10.36</v>
+      <c r="T21" s="258">
+        <v>-9.09</v>
       </c>
     </row>
     <row r="22">
@@ -9746,7 +9810,7 @@
       <c r="C22" t="str">
         <v>002792</v>
       </c>
-      <c r="D22" s="270" t="str">
+      <c r="D22" s="267" t="str">
         <v>净买: 6812.35万</v>
       </c>
       <c r="E22">
@@ -9761,41 +9825,41 @@
       <c r="H22">
         <v>4.23</v>
       </c>
-      <c r="I22" s="266">
+      <c r="I22" s="262">
         <v>5.52</v>
       </c>
-      <c r="J22" s="267">
+      <c r="J22" s="272">
         <v>-2.54</v>
       </c>
       <c r="K22" s="268">
         <v>3.61</v>
       </c>
-      <c r="L22" s="271">
+      <c r="L22" s="263">
         <v>13.97</v>
       </c>
-      <c r="M22" s="263">
+      <c r="M22" s="269">
         <v>25.37</v>
       </c>
-      <c r="N22" s="264">
+      <c r="N22" s="265">
         <v>26.81</v>
       </c>
-      <c r="O22" s="269">
+      <c r="O22" s="270">
         <v>18.51</v>
       </c>
       <c r="P22" s="273">
         <v>27.46</v>
       </c>
-      <c r="Q22" s="265">
+      <c r="Q22" s="261">
         <v>36.75</v>
       </c>
-      <c r="R22" s="261">
+      <c r="R22" s="264">
         <v>41.37</v>
       </c>
-      <c r="S22" s="272">
+      <c r="S22" s="266">
         <v>55.52</v>
       </c>
-      <c r="T22" s="262">
-        <v>52.78</v>
+      <c r="T22" s="271">
+        <v>36.18</v>
       </c>
     </row>
     <row r="23">
@@ -9808,7 +9872,7 @@
       <c r="C23" t="str">
         <v>603023</v>
       </c>
-      <c r="D23" s="279" t="str">
+      <c r="D23" s="276" t="str">
         <v>净卖: -1105.11万</v>
       </c>
       <c r="E23">
@@ -9823,41 +9887,41 @@
       <c r="H23">
         <v>4.14</v>
       </c>
-      <c r="I23" s="277">
+      <c r="I23" s="282">
         <v>-0.99</v>
       </c>
-      <c r="J23" s="274">
+      <c r="J23" s="277">
         <v>-4.3</v>
       </c>
-      <c r="K23" s="280">
+      <c r="K23" s="284">
         <v>-8.61</v>
       </c>
       <c r="L23" s="283">
         <v>-8.77</v>
       </c>
-      <c r="M23" s="284">
+      <c r="M23" s="285">
         <v>-7.62</v>
       </c>
-      <c r="N23" s="275">
+      <c r="N23" s="278">
         <v>-12.58</v>
       </c>
-      <c r="O23" s="285">
+      <c r="O23" s="286">
         <v>-11.42</v>
       </c>
-      <c r="P23" s="278">
+      <c r="P23" s="274">
         <v>-16.72</v>
       </c>
-      <c r="Q23" s="276">
+      <c r="Q23" s="279">
         <v>-15.23</v>
       </c>
-      <c r="R23" s="281">
+      <c r="R23" s="280">
         <v>-6.79</v>
       </c>
-      <c r="S23" s="282">
+      <c r="S23" s="281">
         <v>-7.62</v>
       </c>
-      <c r="T23" s="286">
-        <v>-26.99</v>
+      <c r="T23" s="275">
+        <v>-27.32</v>
       </c>
     </row>
     <row r="24">
@@ -9870,7 +9934,7 @@
       <c r="C24" t="str">
         <v>600343</v>
       </c>
-      <c r="D24" s="290" t="str">
+      <c r="D24" s="298" t="str">
         <v>净买: 1.33亿</v>
       </c>
       <c r="E24">
@@ -9885,41 +9949,41 @@
       <c r="H24">
         <v>-1.32</v>
       </c>
-      <c r="I24" s="291">
+      <c r="I24" s="292">
         <v>11.47</v>
       </c>
-      <c r="J24" s="292">
+      <c r="J24" s="299">
         <v>15.39</v>
       </c>
-      <c r="K24" s="289">
+      <c r="K24" s="296">
         <v>21.07</v>
       </c>
-      <c r="L24" s="299">
+      <c r="L24" s="288">
         <v>25.17</v>
       </c>
-      <c r="M24" s="287">
+      <c r="M24" s="289">
         <v>30</v>
       </c>
-      <c r="N24" s="293">
+      <c r="N24" s="290">
         <v>30.59</v>
       </c>
-      <c r="O24" s="294">
+      <c r="O24" s="293">
         <v>21.84</v>
       </c>
-      <c r="P24" s="295">
+      <c r="P24" s="297">
         <v>20.93</v>
       </c>
-      <c r="Q24" s="288">
+      <c r="Q24" s="291">
         <v>20.8</v>
       </c>
-      <c r="R24" s="296">
+      <c r="R24" s="294">
         <v>26.21</v>
       </c>
-      <c r="S24" s="297">
+      <c r="S24" s="287">
         <v>23.73</v>
       </c>
-      <c r="T24" s="298">
-        <v>-2.35</v>
+      <c r="T24" s="295">
+        <v>-6.64</v>
       </c>
     </row>
     <row r="25">
@@ -9932,7 +9996,7 @@
       <c r="C25" t="str">
         <v>600693</v>
       </c>
-      <c r="D25" s="304" t="str">
+      <c r="D25" s="300" t="str">
         <v>净卖: -8573.84万</v>
       </c>
       <c r="E25">
@@ -9947,41 +10011,41 @@
       <c r="H25">
         <v>0</v>
       </c>
-      <c r="I25" s="305">
+      <c r="I25" s="309">
         <v>-2.52</v>
       </c>
-      <c r="J25" s="301">
+      <c r="J25" s="311">
         <v>2</v>
       </c>
-      <c r="K25" s="302">
+      <c r="K25" s="312">
         <v>-7.69</v>
       </c>
       <c r="L25" s="306">
         <v>-16.92</v>
       </c>
-      <c r="M25" s="309">
+      <c r="M25" s="310">
         <v>-16.92</v>
       </c>
-      <c r="N25" s="312">
+      <c r="N25" s="301">
         <v>-14.27</v>
       </c>
-      <c r="O25" s="307">
+      <c r="O25" s="302">
         <v>-16.64</v>
       </c>
-      <c r="P25" s="308">
+      <c r="P25" s="303">
         <v>-16.6</v>
       </c>
-      <c r="Q25" s="303">
+      <c r="Q25" s="307">
         <v>-11.79</v>
       </c>
-      <c r="R25" s="310">
+      <c r="R25" s="304">
         <v>-8.67</v>
       </c>
-      <c r="S25" s="311">
+      <c r="S25" s="308">
         <v>-2.05</v>
       </c>
-      <c r="T25" s="300">
-        <v>-45.45</v>
+      <c r="T25" s="305">
+        <v>-51.14</v>
       </c>
     </row>
     <row r="26">
@@ -9994,7 +10058,7 @@
       <c r="C26" t="str">
         <v>603686</v>
       </c>
-      <c r="D26" s="321" t="str">
+      <c r="D26" s="316" t="str">
         <v>净买: 6401.27万</v>
       </c>
       <c r="E26">
@@ -10009,41 +10073,41 @@
       <c r="H26">
         <v>-1.39</v>
       </c>
-      <c r="I26" s="314">
+      <c r="I26" s="317">
         <v>11.56</v>
       </c>
-      <c r="J26" s="315">
+      <c r="J26" s="318">
         <v>12.1</v>
       </c>
-      <c r="K26" s="324">
+      <c r="K26" s="313">
         <v>23.31</v>
       </c>
-      <c r="L26" s="316">
+      <c r="L26" s="322">
         <v>15.93</v>
       </c>
-      <c r="M26" s="317">
+      <c r="M26" s="323">
         <v>12.77</v>
       </c>
-      <c r="N26" s="322">
+      <c r="N26" s="314">
         <v>13.16</v>
       </c>
-      <c r="O26" s="318">
+      <c r="O26" s="320">
         <v>10.86</v>
       </c>
-      <c r="P26" s="323">
+      <c r="P26" s="319">
         <v>9.14</v>
       </c>
-      <c r="Q26" s="325">
+      <c r="Q26" s="321">
         <v>9.84</v>
       </c>
-      <c r="R26" s="320">
+      <c r="R26" s="324">
         <v>10.82</v>
       </c>
-      <c r="S26" s="319">
+      <c r="S26" s="325">
         <v>-0.23</v>
       </c>
-      <c r="T26" s="313">
-        <v>-26.2</v>
+      <c r="T26" s="315">
+        <v>-27.14</v>
       </c>
     </row>
     <row r="27">
@@ -10056,7 +10120,7 @@
       <c r="C27" t="str">
         <v>603686</v>
       </c>
-      <c r="D27" s="334" t="str">
+      <c r="D27" s="328" t="str">
         <v>净卖: -6520.61万</v>
       </c>
       <c r="E27">
@@ -10071,41 +10135,41 @@
       <c r="H27">
         <v>5.01</v>
       </c>
-      <c r="I27" s="332">
+      <c r="I27" s="334">
         <v>-4.3</v>
       </c>
-      <c r="J27" s="330">
+      <c r="J27" s="335">
         <v>5.27</v>
       </c>
-      <c r="K27" s="338">
+      <c r="K27" s="337">
         <v>-1.03</v>
       </c>
-      <c r="L27" s="335">
+      <c r="L27" s="332">
         <v>-3.73</v>
       </c>
-      <c r="M27" s="331">
+      <c r="M27" s="338">
         <v>-3.4</v>
       </c>
-      <c r="N27" s="326">
+      <c r="N27" s="329">
         <v>-5.37</v>
       </c>
-      <c r="O27" s="327">
+      <c r="O27" s="336">
         <v>-6.83</v>
       </c>
-      <c r="P27" s="336">
+      <c r="P27" s="330">
         <v>-6.23</v>
       </c>
       <c r="Q27" s="333">
         <v>-5.4</v>
       </c>
-      <c r="R27" s="328">
+      <c r="R27" s="326">
         <v>-14.83</v>
       </c>
-      <c r="S27" s="329">
+      <c r="S27" s="331">
         <v>-14.37</v>
       </c>
-      <c r="T27" s="337">
-        <v>-37</v>
+      <c r="T27" s="327">
+        <v>-37.8</v>
       </c>
     </row>
     <row r="28">
@@ -10133,25 +10197,25 @@
       <c r="H28">
         <v>-3.59</v>
       </c>
-      <c r="I28" s="347">
+      <c r="I28" s="343">
         <v>-6.66</v>
       </c>
-      <c r="J28" s="348">
+      <c r="J28" s="345">
         <v>2.65</v>
       </c>
-      <c r="K28" s="349">
+      <c r="K28" s="346">
         <v>-1.93</v>
       </c>
-      <c r="L28" s="344">
+      <c r="L28" s="350">
         <v>3.51</v>
       </c>
-      <c r="M28" s="350">
+      <c r="M28" s="347">
         <v>3.15</v>
       </c>
-      <c r="N28" s="340">
+      <c r="N28" s="351">
         <v>13.46</v>
       </c>
-      <c r="O28" s="351">
+      <c r="O28" s="348">
         <v>11.67</v>
       </c>
       <c r="P28" s="342">
@@ -10160,14 +10224,14 @@
       <c r="Q28" s="339">
         <v>17.97</v>
       </c>
-      <c r="R28" s="345">
+      <c r="R28" s="349">
         <v>29.71</v>
       </c>
-      <c r="S28" s="343">
+      <c r="S28" s="344">
         <v>16.75</v>
       </c>
-      <c r="T28" s="346">
-        <v>62.42</v>
+      <c r="T28" s="340">
+        <v>53.61</v>
       </c>
     </row>
     <row r="29">
@@ -10180,7 +10244,7 @@
       <c r="C29" t="str">
         <v>001231</v>
       </c>
-      <c r="D29" s="359" t="str">
+      <c r="D29" s="355" t="str">
         <v>净卖: -943.73万</v>
       </c>
       <c r="E29">
@@ -10198,38 +10262,38 @@
       <c r="I29" s="360">
         <v>0</v>
       </c>
-      <c r="J29" s="353">
+      <c r="J29" s="361">
         <v>-1.36</v>
       </c>
-      <c r="K29" s="362">
+      <c r="K29" s="353">
         <v>-7.18</v>
       </c>
-      <c r="L29" s="357">
+      <c r="L29" s="358">
         <v>-8.91</v>
       </c>
-      <c r="M29" s="354">
+      <c r="M29" s="362">
         <v>-9.1</v>
       </c>
-      <c r="N29" s="358">
+      <c r="N29" s="363">
         <v>-9.98</v>
       </c>
-      <c r="O29" s="363">
+      <c r="O29" s="364">
         <v>-8.84</v>
       </c>
-      <c r="P29" s="355">
+      <c r="P29" s="352">
         <v>-10.31</v>
       </c>
-      <c r="Q29" s="364">
+      <c r="Q29" s="359">
         <v>-7.96</v>
       </c>
-      <c r="R29" s="361">
+      <c r="R29" s="356">
         <v>-8.8</v>
       </c>
-      <c r="S29" s="352">
+      <c r="S29" s="357">
         <v>-9.28</v>
       </c>
-      <c r="T29" s="356">
-        <v>-12.49</v>
+      <c r="T29" s="354">
+        <v>-12.27</v>
       </c>
     </row>
     <row r="30">
@@ -10242,7 +10306,7 @@
       <c r="C30" t="str">
         <v>002788</v>
       </c>
-      <c r="D30" s="374" t="str">
+      <c r="D30" s="376" t="str">
         <v>净买: 3825.22万</v>
       </c>
       <c r="E30">
@@ -10257,41 +10321,41 @@
       <c r="H30">
         <v>5.81</v>
       </c>
-      <c r="I30" s="365">
+      <c r="I30" s="369">
         <v>3.95</v>
       </c>
-      <c r="J30" s="366">
+      <c r="J30" s="367">
         <v>14.35</v>
       </c>
-      <c r="K30" s="375">
+      <c r="K30" s="377">
         <v>11.56</v>
       </c>
-      <c r="L30" s="376">
+      <c r="L30" s="370">
         <v>13.48</v>
       </c>
-      <c r="M30" s="367">
+      <c r="M30" s="365">
         <v>9.23</v>
       </c>
       <c r="N30" s="368">
         <v>1.08</v>
       </c>
-      <c r="O30" s="373">
+      <c r="O30" s="374">
         <v>-9.03</v>
       </c>
-      <c r="P30" s="371">
+      <c r="P30" s="375">
         <v>-18.14</v>
       </c>
-      <c r="Q30" s="377">
+      <c r="Q30" s="366">
         <v>-26.33</v>
       </c>
-      <c r="R30" s="369">
+      <c r="R30" s="371">
         <v>-30.78</v>
       </c>
       <c r="S30" s="372">
         <v>-32.45</v>
       </c>
-      <c r="T30" s="370">
-        <v>-38.77</v>
+      <c r="T30" s="373">
+        <v>-42.64</v>
       </c>
     </row>
     <row r="31">
@@ -10304,7 +10368,7 @@
       <c r="C31" t="str">
         <v>002788</v>
       </c>
-      <c r="D31" s="389" t="str">
+      <c r="D31" s="378" t="str">
         <v>净卖: -24.07万</v>
       </c>
       <c r="E31">
@@ -10319,41 +10383,41 @@
       <c r="H31">
         <v>-0.04</v>
       </c>
-      <c r="I31" s="379">
+      <c r="I31" s="382">
         <v>10.05</v>
       </c>
-      <c r="J31" s="380">
+      <c r="J31" s="383">
         <v>7.37</v>
       </c>
-      <c r="K31" s="383">
+      <c r="K31" s="388">
         <v>9.21</v>
       </c>
-      <c r="L31" s="384">
+      <c r="L31" s="379">
         <v>5.12</v>
       </c>
-      <c r="M31" s="385">
+      <c r="M31" s="380">
         <v>-2.72</v>
       </c>
-      <c r="N31" s="390">
+      <c r="N31" s="389">
         <v>-12.45</v>
       </c>
-      <c r="O31" s="386">
+      <c r="O31" s="390">
         <v>-21.22</v>
       </c>
-      <c r="P31" s="388">
+      <c r="P31" s="384">
         <v>-29.1</v>
       </c>
       <c r="Q31" s="381">
         <v>-33.39</v>
       </c>
-      <c r="R31" s="387">
+      <c r="R31" s="385">
         <v>-34.99</v>
       </c>
-      <c r="S31" s="378">
+      <c r="S31" s="386">
         <v>-32.95</v>
       </c>
-      <c r="T31" s="382">
-        <v>-41.07</v>
+      <c r="T31" s="387">
+        <v>-44.8</v>
       </c>
     </row>
     <row r="32">
@@ -10366,7 +10430,7 @@
       <c r="C32" t="str">
         <v>600151</v>
       </c>
-      <c r="D32" s="391" t="str">
+      <c r="D32" s="393" t="str">
         <v>净买: 7884.07万</v>
       </c>
       <c r="E32">
@@ -10381,41 +10445,41 @@
       <c r="H32">
         <v>3.26</v>
       </c>
-      <c r="I32" s="395">
+      <c r="I32" s="397">
         <v>-11.53</v>
       </c>
-      <c r="J32" s="401">
+      <c r="J32" s="403">
         <v>-20.23</v>
       </c>
-      <c r="K32" s="396">
+      <c r="K32" s="394">
         <v>-21.06</v>
       </c>
-      <c r="L32" s="397">
+      <c r="L32" s="395">
         <v>-24.22</v>
       </c>
       <c r="M32" s="398">
         <v>-21.69</v>
       </c>
-      <c r="N32" s="402">
+      <c r="N32" s="399">
         <v>-16.73</v>
       </c>
-      <c r="O32" s="392">
+      <c r="O32" s="400">
         <v>-25.05</v>
       </c>
-      <c r="P32" s="403">
+      <c r="P32" s="391">
         <v>-25.88</v>
       </c>
-      <c r="Q32" s="393">
+      <c r="Q32" s="396">
         <v>-27.43</v>
       </c>
-      <c r="R32" s="394">
+      <c r="R32" s="401">
         <v>-26.65</v>
       </c>
-      <c r="S32" s="399">
+      <c r="S32" s="392">
         <v>-26.61</v>
       </c>
-      <c r="T32" s="400">
-        <v>-26.46</v>
+      <c r="T32" s="402">
+        <v>-28.26</v>
       </c>
     </row>
     <row r="33">
@@ -10428,7 +10492,7 @@
       <c r="C33" t="str">
         <v>600916</v>
       </c>
-      <c r="D33" s="415" t="str">
+      <c r="D33" s="405" t="str">
         <v>净卖: -1428.23万</v>
       </c>
       <c r="E33">
@@ -10443,41 +10507,41 @@
       <c r="H33">
         <v>10.04</v>
       </c>
-      <c r="I33" s="407">
+      <c r="I33" s="406">
         <v>0</v>
       </c>
-      <c r="J33" s="409">
+      <c r="J33" s="411">
         <v>10.02</v>
       </c>
-      <c r="K33" s="416">
+      <c r="K33" s="407">
         <v>19.64</v>
       </c>
-      <c r="L33" s="404">
+      <c r="L33" s="412">
         <v>7.66</v>
       </c>
-      <c r="M33" s="410">
+      <c r="M33" s="415">
         <v>5.87</v>
       </c>
-      <c r="N33" s="411">
+      <c r="N33" s="416">
         <v>-0.81</v>
       </c>
-      <c r="O33" s="412">
+      <c r="O33" s="408">
         <v>-8.96</v>
       </c>
-      <c r="P33" s="405">
+      <c r="P33" s="409">
         <v>-6.93</v>
       </c>
-      <c r="Q33" s="413">
+      <c r="Q33" s="410">
         <v>-5.79</v>
       </c>
-      <c r="R33" s="406">
+      <c r="R33" s="404">
         <v>-8.96</v>
       </c>
-      <c r="S33" s="408">
+      <c r="S33" s="413">
         <v>-9.54</v>
       </c>
       <c r="T33" s="414">
-        <v>-26</v>
+        <v>-27.95</v>
       </c>
     </row>
     <row r="34">
@@ -10490,7 +10554,7 @@
       <c r="C34" t="str">
         <v>600969</v>
       </c>
-      <c r="D34" s="422" t="str">
+      <c r="D34" s="417" t="str">
         <v>净卖: -723.23万</v>
       </c>
       <c r="E34">
@@ -10505,41 +10569,41 @@
       <c r="H34">
         <v>0</v>
       </c>
-      <c r="I34" s="426">
+      <c r="I34" s="424">
         <v>-9.99</v>
       </c>
-      <c r="J34" s="417">
+      <c r="J34" s="418">
         <v>-9.99</v>
       </c>
-      <c r="K34" s="423">
+      <c r="K34" s="419">
         <v>-18.98</v>
       </c>
-      <c r="L34" s="424">
+      <c r="L34" s="425">
         <v>-21.07</v>
       </c>
-      <c r="M34" s="418">
+      <c r="M34" s="427">
         <v>-21.98</v>
       </c>
-      <c r="N34" s="419">
+      <c r="N34" s="420">
         <v>-18.98</v>
       </c>
-      <c r="O34" s="420">
+      <c r="O34" s="428">
         <v>-16.9</v>
       </c>
-      <c r="P34" s="427">
+      <c r="P34" s="429">
         <v>-16.82</v>
       </c>
-      <c r="Q34" s="428">
+      <c r="Q34" s="421">
         <v>-14.32</v>
       </c>
-      <c r="R34" s="425">
+      <c r="R34" s="426">
         <v>-13.66</v>
       </c>
-      <c r="S34" s="421">
+      <c r="S34" s="422">
         <v>-15.99</v>
       </c>
-      <c r="T34" s="429">
-        <v>-14.74</v>
+      <c r="T34" s="423">
+        <v>-15.9</v>
       </c>
     </row>
     <row r="35">
@@ -10552,7 +10616,7 @@
       <c r="C35" t="str">
         <v>002040</v>
       </c>
-      <c r="D35" s="440" t="str">
+      <c r="D35" s="439" t="str">
         <v>净卖: -895.74万</v>
       </c>
       <c r="E35">
@@ -10567,41 +10631,41 @@
       <c r="H35">
         <v>-7.37</v>
       </c>
-      <c r="I35" s="435">
+      <c r="I35" s="430">
         <v>-2.87</v>
       </c>
-      <c r="J35" s="441">
+      <c r="J35" s="440">
         <v>-8.52</v>
       </c>
-      <c r="K35" s="442">
+      <c r="K35" s="431">
         <v>-8.36</v>
       </c>
-      <c r="L35" s="438">
+      <c r="L35" s="432">
         <v>-10.49</v>
       </c>
-      <c r="M35" s="432">
+      <c r="M35" s="435">
         <v>-8.44</v>
       </c>
-      <c r="N35" s="439">
+      <c r="N35" s="433">
         <v>-9.02</v>
       </c>
       <c r="O35" s="436">
         <v>-9.51</v>
       </c>
-      <c r="P35" s="430">
+      <c r="P35" s="441">
         <v>-12.05</v>
       </c>
-      <c r="Q35" s="431">
+      <c r="Q35" s="442">
         <v>-8.28</v>
       </c>
-      <c r="R35" s="433">
+      <c r="R35" s="437">
         <v>-10.33</v>
       </c>
-      <c r="S35" s="434">
+      <c r="S35" s="438">
         <v>-11.07</v>
       </c>
-      <c r="T35" s="437">
-        <v>-17.54</v>
+      <c r="T35" s="434">
+        <v>-19.26</v>
       </c>
     </row>
     <row r="36">
@@ -10614,7 +10678,7 @@
       <c r="C36" t="str">
         <v>603017</v>
       </c>
-      <c r="D36" s="443" t="str">
+      <c r="D36" s="455" t="str">
         <v>净买: 694.09万</v>
       </c>
       <c r="E36">
@@ -10629,41 +10693,41 @@
       <c r="H36">
         <v>2.04</v>
       </c>
-      <c r="I36" s="448">
+      <c r="I36" s="449">
         <v>7.84</v>
       </c>
-      <c r="J36" s="451">
+      <c r="J36" s="453">
         <v>7.04</v>
       </c>
-      <c r="K36" s="444">
+      <c r="K36" s="446">
         <v>6.48</v>
       </c>
-      <c r="L36" s="445">
+      <c r="L36" s="450">
         <v>5.04</v>
       </c>
-      <c r="M36" s="446">
+      <c r="M36" s="447">
         <v>7.28</v>
       </c>
-      <c r="N36" s="449">
+      <c r="N36" s="443">
         <v>5.44</v>
       </c>
-      <c r="O36" s="452">
+      <c r="O36" s="444">
         <v>10.72</v>
       </c>
-      <c r="P36" s="453">
+      <c r="P36" s="454">
         <v>10.32</v>
       </c>
-      <c r="Q36" s="454">
+      <c r="Q36" s="445">
         <v>7.92</v>
       </c>
-      <c r="R36" s="447">
+      <c r="R36" s="448">
         <v>1.28</v>
       </c>
-      <c r="S36" s="450">
+      <c r="S36" s="451">
         <v>11.44</v>
       </c>
-      <c r="T36" s="455">
-        <v>25.04</v>
+      <c r="T36" s="452">
+        <v>22.08</v>
       </c>
     </row>
     <row r="37">
@@ -10676,7 +10740,7 @@
       <c r="C37" t="str">
         <v>600495</v>
       </c>
-      <c r="D37" s="459" t="str">
+      <c r="D37" s="468" t="str">
         <v>净买: 998.97万</v>
       </c>
       <c r="E37">
@@ -10691,41 +10755,41 @@
       <c r="H37">
         <v>0</v>
       </c>
-      <c r="I37" s="467">
+      <c r="I37" s="463">
         <v>10.04</v>
       </c>
-      <c r="J37" s="463">
+      <c r="J37" s="459">
         <v>11.16</v>
       </c>
       <c r="K37" s="464">
         <v>12.28</v>
       </c>
-      <c r="L37" s="460">
+      <c r="L37" s="465">
         <v>2.23</v>
       </c>
-      <c r="M37" s="465">
+      <c r="M37" s="460">
         <v>0.67</v>
       </c>
       <c r="N37" s="461">
         <v>4.46</v>
       </c>
-      <c r="O37" s="458">
+      <c r="O37" s="457">
         <v>0.67</v>
       </c>
-      <c r="P37" s="468">
+      <c r="P37" s="456">
         <v>0.45</v>
       </c>
       <c r="Q37" s="462">
         <v>-1.34</v>
       </c>
-      <c r="R37" s="456">
+      <c r="R37" s="466">
         <v>-1.34</v>
       </c>
-      <c r="S37" s="457">
+      <c r="S37" s="467">
         <v>-2.01</v>
       </c>
-      <c r="T37" s="466">
-        <v>-0.67</v>
+      <c r="T37" s="458">
+        <v>-2.9</v>
       </c>
     </row>
     <row r="38">
@@ -10753,41 +10817,41 @@
       <c r="H38">
         <v>9.92</v>
       </c>
-      <c r="I38" s="470">
+      <c r="I38" s="473">
         <v>0</v>
       </c>
-      <c r="J38" s="473">
+      <c r="J38" s="474">
         <v>10.07</v>
       </c>
-      <c r="K38" s="478">
+      <c r="K38" s="480">
         <v>21.01</v>
       </c>
-      <c r="L38" s="474">
+      <c r="L38" s="481">
         <v>33.16</v>
       </c>
       <c r="M38" s="475">
         <v>27.78</v>
       </c>
-      <c r="N38" s="479">
+      <c r="N38" s="476">
         <v>22.92</v>
       </c>
-      <c r="O38" s="480">
+      <c r="O38" s="477">
         <v>11.46</v>
       </c>
-      <c r="P38" s="476">
+      <c r="P38" s="478">
         <v>2.6</v>
       </c>
-      <c r="Q38" s="477">
+      <c r="Q38" s="479">
         <v>7.99</v>
       </c>
       <c r="R38" s="469">
         <v>18.75</v>
       </c>
-      <c r="S38" s="481">
+      <c r="S38" s="470">
         <v>9.2</v>
       </c>
       <c r="T38" s="471">
-        <v>9.55</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="39">
@@ -10800,7 +10864,7 @@
       <c r="C39" t="str">
         <v>301022</v>
       </c>
-      <c r="D39" s="483" t="str">
+      <c r="D39" s="482" t="str">
         <v>净买: 646.40万</v>
       </c>
       <c r="E39">
@@ -10815,12 +10879,18 @@
       <c r="H39">
         <v>20.01</v>
       </c>
-      <c r="I39" s="482">
+      <c r="I39" s="483">
         <v>0</v>
       </c>
-      <c r="J39" t="str"/>
-      <c r="K39" t="str"/>
-      <c r="L39" t="str"/>
+      <c r="J39" s="484">
+        <v>7.49</v>
+      </c>
+      <c r="K39" s="485">
+        <v>4.1</v>
+      </c>
+      <c r="L39" s="486">
+        <v>3.89</v>
+      </c>
       <c r="M39" t="str"/>
       <c r="N39" t="str"/>
       <c r="O39" t="str"/>
@@ -10828,7 +10898,9 @@
       <c r="Q39" t="str"/>
       <c r="R39" t="str"/>
       <c r="S39" t="str"/>
-      <c r="T39" t="str"/>
+      <c r="T39" s="487">
+        <v>3.89</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -10845,13 +10917,13 @@
         <v>38</v>
       </c>
       <c r="J40">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K40">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L40">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M40">
         <v>37</v>
@@ -10875,7 +10947,7 @@
         <v>37</v>
       </c>
       <c r="T40">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41">
@@ -10889,41 +10961,41 @@
       <c r="F41" t="str"/>
       <c r="G41" t="str"/>
       <c r="H41" t="str"/>
-      <c r="I41" s="489">
+      <c r="I41" s="495">
         <v>52.63</v>
       </c>
-      <c r="J41" s="490">
-        <v>62.16</v>
-      </c>
-      <c r="K41" s="486">
-        <v>54.05</v>
-      </c>
-      <c r="L41" s="491">
-        <v>56.76</v>
-      </c>
-      <c r="M41" s="495">
+      <c r="J41" s="496">
+        <v>63.16</v>
+      </c>
+      <c r="K41" s="489">
+        <v>55.26</v>
+      </c>
+      <c r="L41" s="497">
+        <v>57.89</v>
+      </c>
+      <c r="M41" s="493">
         <v>51.35</v>
       </c>
-      <c r="N41" s="492">
+      <c r="N41" s="491">
         <v>48.65</v>
       </c>
-      <c r="O41" s="493">
+      <c r="O41" s="494">
         <v>45.95</v>
       </c>
-      <c r="P41" s="484">
+      <c r="P41" s="492">
         <v>40.54</v>
       </c>
-      <c r="Q41" s="487">
+      <c r="Q41" s="490">
         <v>35.14</v>
       </c>
-      <c r="R41" s="488">
+      <c r="R41" s="498">
         <v>37.84</v>
       </c>
-      <c r="S41" s="494">
+      <c r="S41" s="499">
         <v>37.84</v>
       </c>
-      <c r="T41" s="485">
-        <v>27.03</v>
+      <c r="T41" s="488">
+        <v>28.95</v>
       </c>
     </row>
     <row r="42">
@@ -10937,41 +11009,41 @@
       <c r="F42" t="str"/>
       <c r="G42" t="str"/>
       <c r="H42" t="str"/>
-      <c r="I42" s="496">
+      <c r="I42" s="510">
         <v>2.29</v>
       </c>
-      <c r="J42" s="499">
-        <v>3.37</v>
-      </c>
-      <c r="K42" s="504">
-        <v>3.41</v>
-      </c>
-      <c r="L42" s="501">
-        <v>3.11</v>
-      </c>
-      <c r="M42" s="505">
+      <c r="J42" s="511">
+        <v>3.48</v>
+      </c>
+      <c r="K42" s="500">
+        <v>3.42</v>
+      </c>
+      <c r="L42" s="504">
+        <v>3.13</v>
+      </c>
+      <c r="M42" s="502">
         <v>4.56</v>
       </c>
-      <c r="N42" s="500">
+      <c r="N42" s="508">
         <v>3.99</v>
       </c>
-      <c r="O42" s="506">
+      <c r="O42" s="505">
         <v>2.28</v>
       </c>
-      <c r="P42" s="497">
+      <c r="P42" s="506">
         <v>0.79</v>
       </c>
-      <c r="Q42" s="502">
+      <c r="Q42" s="501">
         <v>-0.11</v>
       </c>
-      <c r="R42" s="503">
+      <c r="R42" s="509">
         <v>-0.68</v>
       </c>
       <c r="S42" s="507">
         <v>-0.22</v>
       </c>
-      <c r="T42" s="498">
-        <v>-2.08</v>
+      <c r="T42" s="503">
+        <v>-4.66</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/湖州劳动路/index.xlsx
+++ b/youzi/湖州劳动路/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="513">
+  <fills count="514">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -39,61 +39,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,7 +117,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,13 +141,523 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEB8D96"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,6 +669,738 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4553"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8BCF9B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8BCF9B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4CB564"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8336"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CFD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF22913C"/>
         <bgColor/>
       </patternFill>
@@ -153,37 +1413,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFD02F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -201,133 +1485,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -345,37 +1617,859 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA6DAB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCF0E0"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -387,25 +2481,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -417,7 +2529,367 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF83CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD7AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -435,7 +2907,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -447,625 +2931,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4553"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BCF9B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BCF9B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4CB564"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8336"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CFD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8336"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1077,1957 +3033,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA6DAB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF83CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF82CB93"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE1F3E5"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AFB5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3039,6 +3069,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF3FAF4"/>
         <bgColor/>
       </patternFill>
@@ -3051,25 +3093,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFD43141"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1AFB5"/>
+        <fgColor rgb="FFB5E1BF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3079,32 +3109,15 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E1BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="512">
+  <borders count="513">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -6693,7 +6706,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="512">
+  <cellXfs count="513">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8226,6 +8239,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="511" fillId="512" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="512" fillId="513" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -8570,7 +8586,7 @@
       <c r="C2" t="str">
         <v>002105</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="12" t="str">
         <v>净卖: -286.93万</v>
       </c>
       <c r="E2">
@@ -8585,41 +8601,41 @@
       <c r="H2">
         <v>3.63</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="13">
         <v>6.13</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="1">
         <v>16.75</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="8">
         <v>28.37</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="4">
         <v>41.25</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="5">
         <v>55.38</v>
       </c>
-      <c r="N2" s="4">
+      <c r="N2" s="9">
         <v>46.12</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="6">
         <v>46.75</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="2">
         <v>33.13</v>
       </c>
       <c r="Q2" s="10">
         <v>34.87</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="7">
         <v>21.38</v>
       </c>
-      <c r="S2" s="6">
+      <c r="S2" s="3">
         <v>11.62</v>
       </c>
-      <c r="T2" s="1">
-        <v>-22.12</v>
+      <c r="T2" s="11">
+        <v>-19</v>
       </c>
     </row>
     <row r="3">
@@ -8632,7 +8648,7 @@
       <c r="C3" t="str">
         <v>002760</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="23" t="str">
         <v>净买: 1264.22万</v>
       </c>
       <c r="E3">
@@ -8647,41 +8663,41 @@
       <c r="H3">
         <v>3.43</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="17">
         <v>6.36</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="14">
         <v>2.8</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="21">
         <v>-6.84</v>
       </c>
       <c r="L3" s="24">
         <v>-13.76</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="18">
         <v>-13.72</v>
       </c>
-      <c r="N3" s="25">
+      <c r="N3" s="19">
         <v>-14.84</v>
       </c>
-      <c r="O3" s="16">
+      <c r="O3" s="25">
         <v>-15.92</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="15">
         <v>-16.68</v>
       </c>
       <c r="Q3" s="26">
         <v>-19.6</v>
       </c>
-      <c r="R3" s="19">
+      <c r="R3" s="20">
         <v>-22.72</v>
       </c>
-      <c r="S3" s="23">
+      <c r="S3" s="22">
         <v>-23.88</v>
       </c>
-      <c r="T3" s="20">
-        <v>-11.76</v>
+      <c r="T3" s="16">
+        <v>-11.24</v>
       </c>
     </row>
     <row r="4">
@@ -8694,7 +8710,7 @@
       <c r="C4" t="str">
         <v>002760</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="30" t="str">
         <v>净卖: -1488.32万</v>
       </c>
       <c r="E4">
@@ -8709,41 +8725,41 @@
       <c r="H4">
         <v>4.59</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="31">
         <v>-7.59</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="38">
         <v>-16.25</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="32">
         <v>-22.47</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="39">
         <v>-22.44</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="27">
         <v>-23.44</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="33">
         <v>-24.42</v>
       </c>
-      <c r="O4" s="36">
+      <c r="O4" s="35">
         <v>-25.1</v>
       </c>
-      <c r="P4" s="37">
+      <c r="P4" s="34">
         <v>-27.72</v>
       </c>
-      <c r="Q4" s="32">
+      <c r="Q4" s="28">
         <v>-30.53</v>
       </c>
-      <c r="R4" s="38">
+      <c r="R4" s="29">
         <v>-31.57</v>
       </c>
-      <c r="S4" s="29">
+      <c r="S4" s="36">
         <v>-31.07</v>
       </c>
-      <c r="T4" s="39">
-        <v>-20.68</v>
+      <c r="T4" s="37">
+        <v>-20.21</v>
       </c>
     </row>
     <row r="5">
@@ -8756,7 +8772,7 @@
       <c r="C5" t="str">
         <v>603958</v>
       </c>
-      <c r="D5" s="51" t="str">
+      <c r="D5" s="41" t="str">
         <v>净买: 2814.34万</v>
       </c>
       <c r="E5">
@@ -8771,41 +8787,41 @@
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="51">
         <v>-3.71</v>
       </c>
-      <c r="J5" s="52">
+      <c r="J5" s="48">
         <v>-13.32</v>
       </c>
-      <c r="K5" s="40">
+      <c r="K5" s="42">
         <v>-18.35</v>
       </c>
       <c r="L5" s="45">
         <v>-15.42</v>
       </c>
-      <c r="M5" s="49">
+      <c r="M5" s="43">
         <v>-11.81</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="49">
         <v>-11.27</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="52">
         <v>-11.13</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="44">
         <v>-13.08</v>
       </c>
-      <c r="Q5" s="41">
+      <c r="Q5" s="50">
         <v>-16.15</v>
       </c>
-      <c r="R5" s="47">
+      <c r="R5" s="46">
         <v>-17.72</v>
       </c>
-      <c r="S5" s="48">
+      <c r="S5" s="40">
         <v>-18.79</v>
       </c>
-      <c r="T5" s="50">
-        <v>21.18</v>
+      <c r="T5" s="47">
+        <v>15.18</v>
       </c>
     </row>
     <row r="6">
@@ -8833,41 +8849,41 @@
       <c r="H6">
         <v>-6.13</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="57">
         <v>-4.1</v>
       </c>
       <c r="J6" s="64">
         <v>-9.67</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="55">
         <v>-6.43</v>
       </c>
-      <c r="L6" s="65">
+      <c r="L6" s="58">
         <v>-2.43</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="59">
         <v>-1.84</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="65">
         <v>-1.67</v>
       </c>
-      <c r="O6" s="57">
+      <c r="O6" s="61">
         <v>-3.83</v>
       </c>
-      <c r="P6" s="61">
+      <c r="P6" s="62">
         <v>-7.24</v>
       </c>
-      <c r="Q6" s="58">
+      <c r="Q6" s="60">
         <v>-8.96</v>
       </c>
-      <c r="R6" s="62">
+      <c r="R6" s="53">
         <v>-10.15</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="56">
         <v>-9.99</v>
       </c>
-      <c r="T6" s="55">
-        <v>34.07</v>
+      <c r="T6" s="54">
+        <v>27.43</v>
       </c>
     </row>
     <row r="7">
@@ -8880,7 +8896,7 @@
       <c r="C7" t="str">
         <v>002645</v>
       </c>
-      <c r="D7" s="68" t="str">
+      <c r="D7" s="78" t="str">
         <v>净买: 1223.21万</v>
       </c>
       <c r="E7">
@@ -8895,13 +8911,13 @@
       <c r="H7">
         <v>1.72</v>
       </c>
-      <c r="I7" s="76">
+      <c r="I7" s="72">
         <v>8.14</v>
       </c>
-      <c r="J7" s="69">
+      <c r="J7" s="73">
         <v>5.31</v>
       </c>
-      <c r="K7" s="73">
+      <c r="K7" s="68">
         <v>9.04</v>
       </c>
       <c r="L7" s="77">
@@ -8910,26 +8926,26 @@
       <c r="M7" s="74">
         <v>3.5</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="69">
         <v>-6.89</v>
       </c>
-      <c r="O7" s="78">
+      <c r="O7" s="70">
         <v>-5.42</v>
       </c>
-      <c r="P7" s="67">
+      <c r="P7" s="66">
         <v>-7.12</v>
       </c>
-      <c r="Q7" s="75">
+      <c r="Q7" s="71">
         <v>-7.23</v>
       </c>
-      <c r="R7" s="71">
+      <c r="R7" s="67">
         <v>-10.73</v>
       </c>
-      <c r="S7" s="72">
+      <c r="S7" s="75">
         <v>-9.94</v>
       </c>
-      <c r="T7" s="66">
-        <v>153.22</v>
+      <c r="T7" s="76">
+        <v>149.38</v>
       </c>
     </row>
     <row r="8">
@@ -8942,7 +8958,7 @@
       <c r="C8" t="str">
         <v>600537</v>
       </c>
-      <c r="D8" s="79" t="str">
+      <c r="D8" s="89" t="str">
         <v>净买: 358.47万</v>
       </c>
       <c r="E8">
@@ -8957,25 +8973,25 @@
       <c r="H8">
         <v>5.03</v>
       </c>
-      <c r="I8" s="84">
+      <c r="I8" s="90">
         <v>4.79</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="85">
         <v>8.98</v>
       </c>
-      <c r="K8" s="85">
+      <c r="K8" s="91">
         <v>-1.8</v>
       </c>
-      <c r="L8" s="80">
+      <c r="L8" s="81">
         <v>8.08</v>
       </c>
-      <c r="M8" s="81">
+      <c r="M8" s="82">
         <v>18.86</v>
       </c>
-      <c r="N8" s="87">
+      <c r="N8" s="79">
         <v>19.76</v>
       </c>
-      <c r="O8" s="90">
+      <c r="O8" s="87">
         <v>19.16</v>
       </c>
       <c r="P8" s="86">
@@ -8984,14 +9000,14 @@
       <c r="Q8" s="88">
         <v>8.38</v>
       </c>
-      <c r="R8" s="82">
+      <c r="R8" s="80">
         <v>4.49</v>
       </c>
-      <c r="S8" s="91">
+      <c r="S8" s="83">
         <v>14.97</v>
       </c>
-      <c r="T8" s="83">
-        <v>11.38</v>
+      <c r="T8" s="84">
+        <v>6.29</v>
       </c>
     </row>
     <row r="9">
@@ -9004,7 +9020,7 @@
       <c r="C9" t="str">
         <v>603122</v>
       </c>
-      <c r="D9" s="93" t="str">
+      <c r="D9" s="96" t="str">
         <v>净卖: -557.16万</v>
       </c>
       <c r="E9">
@@ -9022,38 +9038,38 @@
       <c r="I9" s="101">
         <v>2.8</v>
       </c>
-      <c r="J9" s="102">
+      <c r="J9" s="97">
         <v>13.09</v>
       </c>
-      <c r="K9" s="94">
+      <c r="K9" s="92">
         <v>24.4</v>
       </c>
-      <c r="L9" s="95">
+      <c r="L9" s="98">
         <v>36.85</v>
       </c>
-      <c r="M9" s="96">
+      <c r="M9" s="99">
         <v>50.57</v>
       </c>
-      <c r="N9" s="97">
+      <c r="N9" s="93">
         <v>65.69</v>
       </c>
-      <c r="O9" s="98">
+      <c r="O9" s="94">
         <v>82.21</v>
       </c>
-      <c r="P9" s="103">
+      <c r="P9" s="100">
         <v>100.38</v>
       </c>
-      <c r="Q9" s="99">
+      <c r="Q9" s="102">
         <v>110.93</v>
       </c>
-      <c r="R9" s="100">
+      <c r="R9" s="103">
         <v>132.02</v>
       </c>
       <c r="S9" s="104">
         <v>155.27</v>
       </c>
-      <c r="T9" s="92">
-        <v>93.52</v>
+      <c r="T9" s="95">
+        <v>96.06</v>
       </c>
     </row>
     <row r="10">
@@ -9081,41 +9097,41 @@
       <c r="H10">
         <v>10.02</v>
       </c>
-      <c r="I10" s="108">
+      <c r="I10" s="106">
         <v>0</v>
       </c>
-      <c r="J10" s="114">
+      <c r="J10" s="112">
         <v>10.03</v>
       </c>
-      <c r="K10" s="106">
+      <c r="K10" s="107">
         <v>20.99</v>
       </c>
-      <c r="L10" s="109">
+      <c r="L10" s="116">
         <v>8.95</v>
       </c>
-      <c r="M10" s="115">
+      <c r="M10" s="110">
         <v>-2.01</v>
       </c>
-      <c r="N10" s="110">
+      <c r="N10" s="111">
         <v>-11.73</v>
       </c>
-      <c r="O10" s="111">
+      <c r="O10" s="113">
         <v>-16.05</v>
       </c>
-      <c r="P10" s="116">
+      <c r="P10" s="108">
         <v>-13.73</v>
       </c>
-      <c r="Q10" s="112">
+      <c r="Q10" s="117">
         <v>-17.59</v>
       </c>
-      <c r="R10" s="113">
+      <c r="R10" s="114">
         <v>-17.28</v>
       </c>
-      <c r="S10" s="107">
+      <c r="S10" s="109">
         <v>-14.04</v>
       </c>
-      <c r="T10" s="117">
-        <v>-11.88</v>
+      <c r="T10" s="115">
+        <v>-10.96</v>
       </c>
     </row>
     <row r="11">
@@ -9143,41 +9159,41 @@
       <c r="H11">
         <v>1.56</v>
       </c>
-      <c r="I11" s="127">
+      <c r="I11" s="125">
         <v>8.43</v>
       </c>
-      <c r="J11" s="122">
+      <c r="J11" s="121">
         <v>13.79</v>
       </c>
-      <c r="K11" s="129">
+      <c r="K11" s="118">
         <v>9.2</v>
       </c>
-      <c r="L11" s="123">
+      <c r="L11" s="119">
         <v>7.28</v>
       </c>
-      <c r="M11" s="130">
+      <c r="M11" s="122">
         <v>2.68</v>
       </c>
-      <c r="N11" s="118">
+      <c r="N11" s="120">
         <v>4.6</v>
       </c>
-      <c r="O11" s="119">
+      <c r="O11" s="126">
         <v>0.77</v>
       </c>
-      <c r="P11" s="120">
+      <c r="P11" s="127">
         <v>-4.6</v>
       </c>
-      <c r="Q11" s="121">
+      <c r="Q11" s="123">
         <v>-2.68</v>
       </c>
-      <c r="R11" s="125">
+      <c r="R11" s="129">
         <v>-4.6</v>
       </c>
-      <c r="S11" s="124">
+      <c r="S11" s="130">
         <v>-2.68</v>
       </c>
-      <c r="T11" s="126">
-        <v>51.72</v>
+      <c r="T11" s="124">
+        <v>41</v>
       </c>
     </row>
     <row r="12">
@@ -9190,7 +9206,7 @@
       <c r="C12" t="str">
         <v>603386</v>
       </c>
-      <c r="D12" s="131" t="str">
+      <c r="D12" s="134" t="str">
         <v>净卖: -4389.34万</v>
       </c>
       <c r="E12">
@@ -9205,41 +9221,41 @@
       <c r="H12">
         <v>-8.19</v>
       </c>
-      <c r="I12" s="141">
+      <c r="I12" s="140">
         <v>-1.95</v>
       </c>
-      <c r="J12" s="136">
+      <c r="J12" s="137">
         <v>-3.78</v>
       </c>
-      <c r="K12" s="132">
+      <c r="K12" s="138">
         <v>-11.08</v>
       </c>
-      <c r="L12" s="133">
+      <c r="L12" s="135">
         <v>-18.92</v>
       </c>
-      <c r="M12" s="137">
+      <c r="M12" s="141">
         <v>-18.16</v>
       </c>
-      <c r="N12" s="134">
+      <c r="N12" s="139">
         <v>-18.54</v>
       </c>
-      <c r="O12" s="142">
+      <c r="O12" s="131">
         <v>-17.08</v>
       </c>
-      <c r="P12" s="138">
+      <c r="P12" s="136">
         <v>-17.95</v>
       </c>
-      <c r="Q12" s="139">
+      <c r="Q12" s="132">
         <v>-14.43</v>
       </c>
-      <c r="R12" s="135">
+      <c r="R12" s="142">
         <v>-20</v>
       </c>
       <c r="S12" s="143">
         <v>-18.32</v>
       </c>
-      <c r="T12" s="140">
-        <v>-24.16</v>
+      <c r="T12" s="133">
+        <v>-22.22</v>
       </c>
     </row>
     <row r="13">
@@ -9252,7 +9268,7 @@
       <c r="C13" t="str">
         <v>600493</v>
       </c>
-      <c r="D13" s="151" t="str">
+      <c r="D13" s="156" t="str">
         <v>净买: 999.07万</v>
       </c>
       <c r="E13">
@@ -9267,41 +9283,41 @@
       <c r="H13">
         <v>1.85</v>
       </c>
-      <c r="I13" s="155">
+      <c r="I13" s="144">
         <v>8.05</v>
       </c>
-      <c r="J13" s="156">
+      <c r="J13" s="152">
         <v>-0.65</v>
       </c>
-      <c r="K13" s="153">
+      <c r="K13" s="145">
         <v>3.12</v>
       </c>
-      <c r="L13" s="144">
+      <c r="L13" s="148">
         <v>-4.16</v>
       </c>
-      <c r="M13" s="145">
+      <c r="M13" s="149">
         <v>-8.05</v>
       </c>
-      <c r="N13" s="149">
+      <c r="N13" s="155">
         <v>1.17</v>
       </c>
-      <c r="O13" s="146">
+      <c r="O13" s="153">
         <v>-1.3</v>
       </c>
       <c r="P13" s="150">
         <v>-2.47</v>
       </c>
-      <c r="Q13" s="147">
+      <c r="Q13" s="151">
         <v>1.56</v>
       </c>
-      <c r="R13" s="148">
+      <c r="R13" s="146">
         <v>3.77</v>
       </c>
-      <c r="S13" s="152">
+      <c r="S13" s="147">
         <v>4.03</v>
       </c>
       <c r="T13" s="154">
-        <v>-8.05</v>
+        <v>-5.45</v>
       </c>
     </row>
     <row r="14">
@@ -9314,7 +9330,7 @@
       <c r="C14" t="str">
         <v>001330</v>
       </c>
-      <c r="D14" s="169" t="str">
+      <c r="D14" s="165" t="str">
         <v>净卖: -4990.62万</v>
       </c>
       <c r="E14">
@@ -9329,28 +9345,28 @@
       <c r="H14">
         <v>1.65</v>
       </c>
-      <c r="I14" s="161">
+      <c r="I14" s="162">
         <v>8.18</v>
       </c>
-      <c r="J14" s="165">
+      <c r="J14" s="163">
         <v>-2.59</v>
       </c>
       <c r="K14" s="166">
         <v>-12.32</v>
       </c>
-      <c r="L14" s="162">
+      <c r="L14" s="167">
         <v>-20.34</v>
       </c>
-      <c r="M14" s="167">
+      <c r="M14" s="168">
         <v>-12.4</v>
       </c>
-      <c r="N14" s="168">
+      <c r="N14" s="169">
         <v>-18.4</v>
       </c>
-      <c r="O14" s="164">
+      <c r="O14" s="157">
         <v>-26.58</v>
       </c>
-      <c r="P14" s="157">
+      <c r="P14" s="164">
         <v>-33.95</v>
       </c>
       <c r="Q14" s="158">
@@ -9359,11 +9375,11 @@
       <c r="R14" s="159">
         <v>-35.66</v>
       </c>
-      <c r="S14" s="163">
+      <c r="S14" s="160">
         <v>-34.76</v>
       </c>
-      <c r="T14" s="160">
-        <v>-36.71</v>
+      <c r="T14" s="161">
+        <v>-33.79</v>
       </c>
     </row>
     <row r="15">
@@ -9376,7 +9392,7 @@
       <c r="C15" t="str">
         <v>600865</v>
       </c>
-      <c r="D15" s="175" t="str">
+      <c r="D15" s="170" t="str">
         <v>净买: 4692.22万</v>
       </c>
       <c r="E15">
@@ -9391,41 +9407,41 @@
       <c r="H15">
         <v>10.02</v>
       </c>
-      <c r="I15" s="173">
+      <c r="I15" s="171">
         <v>0</v>
       </c>
-      <c r="J15" s="176">
+      <c r="J15" s="181">
         <v>10.01</v>
       </c>
-      <c r="K15" s="181">
+      <c r="K15" s="176">
         <v>21</v>
       </c>
       <c r="L15" s="177">
         <v>25.24</v>
       </c>
-      <c r="M15" s="182">
+      <c r="M15" s="172">
         <v>32.13</v>
       </c>
-      <c r="N15" s="178">
+      <c r="N15" s="173">
         <v>27.75</v>
       </c>
-      <c r="O15" s="170">
+      <c r="O15" s="179">
         <v>37.2</v>
       </c>
-      <c r="P15" s="171">
+      <c r="P15" s="182">
         <v>50.9</v>
       </c>
-      <c r="Q15" s="179">
+      <c r="Q15" s="180">
         <v>48.33</v>
       </c>
-      <c r="R15" s="172">
+      <c r="R15" s="174">
         <v>33.52</v>
       </c>
-      <c r="S15" s="174">
+      <c r="S15" s="178">
         <v>20.17</v>
       </c>
-      <c r="T15" s="180">
-        <v>-23.57</v>
+      <c r="T15" s="175">
+        <v>-19.05</v>
       </c>
     </row>
     <row r="16">
@@ -9438,7 +9454,7 @@
       <c r="C16" t="str">
         <v>600865</v>
       </c>
-      <c r="D16" s="194" t="str">
+      <c r="D16" s="189" t="str">
         <v>净卖: -5679.38万</v>
       </c>
       <c r="E16">
@@ -9453,41 +9469,41 @@
       <c r="H16">
         <v>10.01</v>
       </c>
-      <c r="I16" s="191">
+      <c r="I16" s="185">
         <v>0</v>
       </c>
-      <c r="J16" s="192">
+      <c r="J16" s="186">
         <v>9.99</v>
       </c>
-      <c r="K16" s="186">
+      <c r="K16" s="193">
         <v>13.84</v>
       </c>
-      <c r="L16" s="193">
+      <c r="L16" s="190">
         <v>20.1</v>
       </c>
-      <c r="M16" s="187">
+      <c r="M16" s="183">
         <v>16.12</v>
       </c>
-      <c r="N16" s="188">
+      <c r="N16" s="194">
         <v>24.72</v>
       </c>
-      <c r="O16" s="195">
+      <c r="O16" s="191">
         <v>37.17</v>
       </c>
-      <c r="P16" s="189">
+      <c r="P16" s="192">
         <v>34.83</v>
       </c>
-      <c r="Q16" s="190">
+      <c r="Q16" s="187">
         <v>21.37</v>
       </c>
-      <c r="R16" s="183">
+      <c r="R16" s="184">
         <v>9.23</v>
       </c>
-      <c r="S16" s="185">
+      <c r="S16" s="188">
         <v>3.67</v>
       </c>
-      <c r="T16" s="184">
-        <v>-30.53</v>
+      <c r="T16" s="195">
+        <v>-26.42</v>
       </c>
     </row>
     <row r="17">
@@ -9500,7 +9516,7 @@
       <c r="C17" t="str">
         <v>600693</v>
       </c>
-      <c r="D17" s="197" t="str">
+      <c r="D17" s="201" t="str">
         <v>净买: 4205.60万</v>
       </c>
       <c r="E17">
@@ -9515,41 +9531,41 @@
       <c r="H17">
         <v>2.51</v>
       </c>
-      <c r="I17" s="202">
+      <c r="I17" s="207">
         <v>0.41</v>
       </c>
-      <c r="J17" s="207">
+      <c r="J17" s="199">
         <v>-0.58</v>
       </c>
-      <c r="K17" s="208">
+      <c r="K17" s="205">
         <v>9.33</v>
       </c>
-      <c r="L17" s="198">
+      <c r="L17" s="208">
         <v>13.77</v>
       </c>
-      <c r="M17" s="203">
+      <c r="M17" s="202">
         <v>25.15</v>
       </c>
-      <c r="N17" s="199">
+      <c r="N17" s="203">
         <v>22</v>
       </c>
-      <c r="O17" s="204">
+      <c r="O17" s="196">
         <v>27.65</v>
       </c>
-      <c r="P17" s="205">
+      <c r="P17" s="204">
         <v>15.52</v>
       </c>
-      <c r="Q17" s="196">
+      <c r="Q17" s="197">
         <v>3.97</v>
       </c>
-      <c r="R17" s="206">
+      <c r="R17" s="198">
         <v>3.97</v>
       </c>
       <c r="S17" s="200">
         <v>7.29</v>
       </c>
-      <c r="T17" s="201">
-        <v>-38.86</v>
+      <c r="T17" s="206">
+        <v>-32.73</v>
       </c>
     </row>
     <row r="18">
@@ -9562,7 +9578,7 @@
       <c r="C18" t="str">
         <v>603023</v>
       </c>
-      <c r="D18" s="217" t="str">
+      <c r="D18" s="213" t="str">
         <v>净买: 2053.34万</v>
       </c>
       <c r="E18">
@@ -9577,41 +9593,41 @@
       <c r="H18">
         <v>-0.38</v>
       </c>
-      <c r="I18" s="212">
+      <c r="I18" s="209">
         <v>10.48</v>
       </c>
-      <c r="J18" s="209">
+      <c r="J18" s="214">
         <v>13.9</v>
       </c>
-      <c r="K18" s="218">
+      <c r="K18" s="210">
         <v>10.1</v>
       </c>
-      <c r="L18" s="213">
+      <c r="L18" s="211">
         <v>5.14</v>
       </c>
-      <c r="M18" s="220">
+      <c r="M18" s="219">
         <v>4.95</v>
       </c>
-      <c r="N18" s="214">
+      <c r="N18" s="217">
         <v>6.29</v>
       </c>
-      <c r="O18" s="215">
+      <c r="O18" s="218">
         <v>0.57</v>
       </c>
-      <c r="P18" s="210">
+      <c r="P18" s="212">
         <v>1.9</v>
       </c>
-      <c r="Q18" s="221">
+      <c r="Q18" s="220">
         <v>-4.19</v>
       </c>
-      <c r="R18" s="219">
+      <c r="R18" s="221">
         <v>-2.48</v>
       </c>
-      <c r="S18" s="211">
+      <c r="S18" s="215">
         <v>7.24</v>
       </c>
       <c r="T18" s="216">
-        <v>-16.38</v>
+        <v>-14.86</v>
       </c>
     </row>
     <row r="19">
@@ -9624,7 +9640,7 @@
       <c r="C19" t="str">
         <v>601566</v>
       </c>
-      <c r="D19" s="230" t="str">
+      <c r="D19" s="224" t="str">
         <v>净卖: -2383.06万</v>
       </c>
       <c r="E19">
@@ -9639,41 +9655,41 @@
       <c r="H19">
         <v>3.63</v>
       </c>
-      <c r="I19" s="227">
+      <c r="I19" s="230">
         <v>6.13</v>
       </c>
-      <c r="J19" s="228">
+      <c r="J19" s="225">
         <v>2.75</v>
       </c>
-      <c r="K19" s="234">
+      <c r="K19" s="233">
         <v>-4.06</v>
       </c>
-      <c r="L19" s="231">
+      <c r="L19" s="226">
         <v>-3.37</v>
       </c>
-      <c r="M19" s="232">
+      <c r="M19" s="228">
         <v>-6.81</v>
       </c>
-      <c r="N19" s="223">
+      <c r="N19" s="227">
         <v>-7.5</v>
       </c>
-      <c r="O19" s="222">
+      <c r="O19" s="234">
         <v>-12.5</v>
       </c>
-      <c r="P19" s="224">
+      <c r="P19" s="231">
         <v>-13.88</v>
       </c>
-      <c r="Q19" s="233">
+      <c r="Q19" s="232">
         <v>-18.06</v>
       </c>
-      <c r="R19" s="229">
+      <c r="R19" s="222">
         <v>-17.94</v>
       </c>
-      <c r="S19" s="225">
+      <c r="S19" s="223">
         <v>-16.56</v>
       </c>
-      <c r="T19" s="226">
-        <v>-33</v>
+      <c r="T19" s="229">
+        <v>-31.69</v>
       </c>
     </row>
     <row r="20">
@@ -9686,7 +9702,7 @@
       <c r="C20" t="str">
         <v>600865</v>
       </c>
-      <c r="D20" s="242" t="str">
+      <c r="D20" s="241" t="str">
         <v>净卖: -5744.79万</v>
       </c>
       <c r="E20">
@@ -9701,41 +9717,41 @@
       <c r="H20">
         <v>-5.17</v>
       </c>
-      <c r="I20" s="245">
+      <c r="I20" s="246">
         <v>9.15</v>
       </c>
-      <c r="J20" s="238">
+      <c r="J20" s="236">
         <v>15.15</v>
       </c>
-      <c r="K20" s="243">
+      <c r="K20" s="237">
         <v>11.33</v>
       </c>
-      <c r="L20" s="246">
+      <c r="L20" s="247">
         <v>19.58</v>
       </c>
-      <c r="M20" s="235">
+      <c r="M20" s="238">
         <v>31.52</v>
       </c>
-      <c r="N20" s="236">
+      <c r="N20" s="242">
         <v>29.27</v>
       </c>
-      <c r="O20" s="239">
+      <c r="O20" s="243">
         <v>16.36</v>
       </c>
-      <c r="P20" s="244">
+      <c r="P20" s="245">
         <v>4.73</v>
       </c>
-      <c r="Q20" s="247">
+      <c r="Q20" s="235">
         <v>-0.61</v>
       </c>
-      <c r="R20" s="237">
+      <c r="R20" s="239">
         <v>0.12</v>
       </c>
-      <c r="S20" s="240">
+      <c r="S20" s="244">
         <v>0.12</v>
       </c>
-      <c r="T20" s="241">
-        <v>-33.39</v>
+      <c r="T20" s="240">
+        <v>-29.45</v>
       </c>
     </row>
     <row r="21">
@@ -9763,41 +9779,41 @@
       <c r="H21">
         <v>-0.39</v>
       </c>
-      <c r="I21" s="259">
+      <c r="I21" s="256">
         <v>3.7</v>
       </c>
       <c r="J21" s="260">
         <v>-1.32</v>
       </c>
-      <c r="K21" s="248">
+      <c r="K21" s="251">
         <v>-4.71</v>
       </c>
-      <c r="L21" s="249">
+      <c r="L21" s="257">
         <v>-6.34</v>
       </c>
-      <c r="M21" s="256">
+      <c r="M21" s="252">
         <v>-4.27</v>
       </c>
-      <c r="N21" s="250">
+      <c r="N21" s="248">
         <v>-2.18</v>
       </c>
-      <c r="O21" s="257">
+      <c r="O21" s="253">
         <v>0.05</v>
       </c>
-      <c r="P21" s="251">
+      <c r="P21" s="258">
         <v>-1.59</v>
       </c>
-      <c r="Q21" s="252">
+      <c r="Q21" s="249">
         <v>-4.68</v>
       </c>
-      <c r="R21" s="253">
+      <c r="R21" s="250">
         <v>-5.25</v>
       </c>
-      <c r="S21" s="254">
+      <c r="S21" s="259">
         <v>-4.79</v>
       </c>
-      <c r="T21" s="258">
-        <v>-9.09</v>
+      <c r="T21" s="254">
+        <v>-6.11</v>
       </c>
     </row>
     <row r="22">
@@ -9810,7 +9826,7 @@
       <c r="C22" t="str">
         <v>002792</v>
       </c>
-      <c r="D22" s="267" t="str">
+      <c r="D22" s="263" t="str">
         <v>净买: 6812.35万</v>
       </c>
       <c r="E22">
@@ -9825,22 +9841,22 @@
       <c r="H22">
         <v>4.23</v>
       </c>
-      <c r="I22" s="262">
+      <c r="I22" s="271">
         <v>5.52</v>
       </c>
-      <c r="J22" s="272">
+      <c r="J22" s="268">
         <v>-2.54</v>
       </c>
-      <c r="K22" s="268">
+      <c r="K22" s="272">
         <v>3.61</v>
       </c>
-      <c r="L22" s="263">
+      <c r="L22" s="264">
         <v>13.97</v>
       </c>
-      <c r="M22" s="269">
+      <c r="M22" s="265">
         <v>25.37</v>
       </c>
-      <c r="N22" s="265">
+      <c r="N22" s="269">
         <v>26.81</v>
       </c>
       <c r="O22" s="270">
@@ -9852,14 +9868,14 @@
       <c r="Q22" s="261">
         <v>36.75</v>
       </c>
-      <c r="R22" s="264">
+      <c r="R22" s="266">
         <v>41.37</v>
       </c>
-      <c r="S22" s="266">
+      <c r="S22" s="262">
         <v>55.52</v>
       </c>
-      <c r="T22" s="271">
-        <v>36.18</v>
+      <c r="T22" s="267">
+        <v>34.48</v>
       </c>
     </row>
     <row r="23">
@@ -9872,7 +9888,7 @@
       <c r="C23" t="str">
         <v>603023</v>
       </c>
-      <c r="D23" s="276" t="str">
+      <c r="D23" s="279" t="str">
         <v>净卖: -1105.11万</v>
       </c>
       <c r="E23">
@@ -9887,41 +9903,41 @@
       <c r="H23">
         <v>4.14</v>
       </c>
-      <c r="I23" s="282">
+      <c r="I23" s="275">
         <v>-0.99</v>
       </c>
-      <c r="J23" s="277">
+      <c r="J23" s="276">
         <v>-4.3</v>
       </c>
-      <c r="K23" s="284">
+      <c r="K23" s="285">
         <v>-8.61</v>
       </c>
       <c r="L23" s="283">
         <v>-8.77</v>
       </c>
-      <c r="M23" s="285">
+      <c r="M23" s="280">
         <v>-7.62</v>
       </c>
-      <c r="N23" s="278">
+      <c r="N23" s="286">
         <v>-12.58</v>
       </c>
-      <c r="O23" s="286">
+      <c r="O23" s="277">
         <v>-11.42</v>
       </c>
       <c r="P23" s="274">
         <v>-16.72</v>
       </c>
-      <c r="Q23" s="279">
+      <c r="Q23" s="284">
         <v>-15.23</v>
       </c>
-      <c r="R23" s="280">
+      <c r="R23" s="281">
         <v>-6.79</v>
       </c>
-      <c r="S23" s="281">
+      <c r="S23" s="278">
         <v>-7.62</v>
       </c>
-      <c r="T23" s="275">
-        <v>-27.32</v>
+      <c r="T23" s="282">
+        <v>-25.99</v>
       </c>
     </row>
     <row r="24">
@@ -9934,7 +9950,7 @@
       <c r="C24" t="str">
         <v>600343</v>
       </c>
-      <c r="D24" s="298" t="str">
+      <c r="D24" s="295" t="str">
         <v>净买: 1.33亿</v>
       </c>
       <c r="E24">
@@ -9949,41 +9965,41 @@
       <c r="H24">
         <v>-1.32</v>
       </c>
-      <c r="I24" s="292">
+      <c r="I24" s="288">
         <v>11.47</v>
       </c>
-      <c r="J24" s="299">
+      <c r="J24" s="297">
         <v>15.39</v>
       </c>
-      <c r="K24" s="296">
+      <c r="K24" s="293">
         <v>21.07</v>
       </c>
-      <c r="L24" s="288">
+      <c r="L24" s="289">
         <v>25.17</v>
       </c>
-      <c r="M24" s="289">
+      <c r="M24" s="298">
         <v>30</v>
       </c>
-      <c r="N24" s="290">
+      <c r="N24" s="299">
         <v>30.59</v>
       </c>
-      <c r="O24" s="293">
+      <c r="O24" s="296">
         <v>21.84</v>
       </c>
-      <c r="P24" s="297">
+      <c r="P24" s="290">
         <v>20.93</v>
       </c>
       <c r="Q24" s="291">
         <v>20.8</v>
       </c>
-      <c r="R24" s="294">
+      <c r="R24" s="292">
         <v>26.21</v>
       </c>
       <c r="S24" s="287">
         <v>23.73</v>
       </c>
-      <c r="T24" s="295">
-        <v>-6.64</v>
+      <c r="T24" s="294">
+        <v>-8.75</v>
       </c>
     </row>
     <row r="25">
@@ -9996,7 +10012,7 @@
       <c r="C25" t="str">
         <v>600693</v>
       </c>
-      <c r="D25" s="300" t="str">
+      <c r="D25" s="305" t="str">
         <v>净卖: -8573.84万</v>
       </c>
       <c r="E25">
@@ -10011,41 +10027,41 @@
       <c r="H25">
         <v>0</v>
       </c>
-      <c r="I25" s="309">
+      <c r="I25" s="308">
         <v>-2.52</v>
       </c>
-      <c r="J25" s="311">
+      <c r="J25" s="309">
         <v>2</v>
       </c>
-      <c r="K25" s="312">
+      <c r="K25" s="310">
         <v>-7.69</v>
       </c>
-      <c r="L25" s="306">
+      <c r="L25" s="311">
         <v>-16.92</v>
       </c>
-      <c r="M25" s="310">
+      <c r="M25" s="306">
         <v>-16.92</v>
       </c>
-      <c r="N25" s="301">
+      <c r="N25" s="307">
         <v>-14.27</v>
       </c>
-      <c r="O25" s="302">
+      <c r="O25" s="312">
         <v>-16.64</v>
       </c>
       <c r="P25" s="303">
         <v>-16.6</v>
       </c>
-      <c r="Q25" s="307">
+      <c r="Q25" s="300">
         <v>-11.79</v>
       </c>
       <c r="R25" s="304">
         <v>-8.67</v>
       </c>
-      <c r="S25" s="308">
+      <c r="S25" s="301">
         <v>-2.05</v>
       </c>
-      <c r="T25" s="305">
-        <v>-51.14</v>
+      <c r="T25" s="302">
+        <v>-46.25</v>
       </c>
     </row>
     <row r="26">
@@ -10058,7 +10074,7 @@
       <c r="C26" t="str">
         <v>603686</v>
       </c>
-      <c r="D26" s="316" t="str">
+      <c r="D26" s="318" t="str">
         <v>净买: 6401.27万</v>
       </c>
       <c r="E26">
@@ -10073,41 +10089,41 @@
       <c r="H26">
         <v>-1.39</v>
       </c>
-      <c r="I26" s="317">
+      <c r="I26" s="322">
         <v>11.56</v>
       </c>
-      <c r="J26" s="318">
+      <c r="J26" s="314">
         <v>12.1</v>
       </c>
-      <c r="K26" s="313">
+      <c r="K26" s="323">
         <v>23.31</v>
       </c>
-      <c r="L26" s="322">
+      <c r="L26" s="319">
         <v>15.93</v>
       </c>
-      <c r="M26" s="323">
+      <c r="M26" s="315">
         <v>12.77</v>
       </c>
-      <c r="N26" s="314">
+      <c r="N26" s="324">
         <v>13.16</v>
       </c>
-      <c r="O26" s="320">
+      <c r="O26" s="316">
         <v>10.86</v>
       </c>
-      <c r="P26" s="319">
+      <c r="P26" s="325">
         <v>9.14</v>
       </c>
       <c r="Q26" s="321">
         <v>9.84</v>
       </c>
-      <c r="R26" s="324">
+      <c r="R26" s="320">
         <v>10.82</v>
       </c>
-      <c r="S26" s="325">
+      <c r="S26" s="313">
         <v>-0.23</v>
       </c>
-      <c r="T26" s="315">
-        <v>-27.14</v>
+      <c r="T26" s="317">
+        <v>-26.55</v>
       </c>
     </row>
     <row r="27">
@@ -10120,7 +10136,7 @@
       <c r="C27" t="str">
         <v>603686</v>
       </c>
-      <c r="D27" s="328" t="str">
+      <c r="D27" s="336" t="str">
         <v>净卖: -6520.61万</v>
       </c>
       <c r="E27">
@@ -10135,41 +10151,41 @@
       <c r="H27">
         <v>5.01</v>
       </c>
-      <c r="I27" s="334">
+      <c r="I27" s="332">
         <v>-4.3</v>
       </c>
-      <c r="J27" s="335">
+      <c r="J27" s="330">
         <v>5.27</v>
       </c>
       <c r="K27" s="337">
         <v>-1.03</v>
       </c>
-      <c r="L27" s="332">
+      <c r="L27" s="333">
         <v>-3.73</v>
       </c>
-      <c r="M27" s="338">
+      <c r="M27" s="327">
         <v>-3.4</v>
       </c>
-      <c r="N27" s="329">
+      <c r="N27" s="334">
         <v>-5.37</v>
       </c>
-      <c r="O27" s="336">
+      <c r="O27" s="335">
         <v>-6.83</v>
       </c>
-      <c r="P27" s="330">
+      <c r="P27" s="331">
         <v>-6.23</v>
       </c>
-      <c r="Q27" s="333">
+      <c r="Q27" s="338">
         <v>-5.4</v>
       </c>
       <c r="R27" s="326">
         <v>-14.83</v>
       </c>
-      <c r="S27" s="331">
+      <c r="S27" s="328">
         <v>-14.37</v>
       </c>
-      <c r="T27" s="327">
-        <v>-37.8</v>
+      <c r="T27" s="329">
+        <v>-37.3</v>
       </c>
     </row>
     <row r="28">
@@ -10197,41 +10213,41 @@
       <c r="H28">
         <v>-3.59</v>
       </c>
-      <c r="I28" s="343">
+      <c r="I28" s="345">
         <v>-6.66</v>
       </c>
-      <c r="J28" s="345">
+      <c r="J28" s="346">
         <v>2.65</v>
       </c>
-      <c r="K28" s="346">
+      <c r="K28" s="347">
         <v>-1.93</v>
       </c>
-      <c r="L28" s="350">
+      <c r="L28" s="342">
         <v>3.51</v>
       </c>
-      <c r="M28" s="347">
+      <c r="M28" s="348">
         <v>3.15</v>
       </c>
       <c r="N28" s="351">
         <v>13.46</v>
       </c>
-      <c r="O28" s="348">
+      <c r="O28" s="344">
         <v>11.67</v>
       </c>
-      <c r="P28" s="342">
+      <c r="P28" s="343">
         <v>20.26</v>
       </c>
-      <c r="Q28" s="339">
+      <c r="Q28" s="349">
         <v>17.97</v>
       </c>
-      <c r="R28" s="349">
+      <c r="R28" s="350">
         <v>29.71</v>
       </c>
-      <c r="S28" s="344">
+      <c r="S28" s="339">
         <v>16.75</v>
       </c>
       <c r="T28" s="340">
-        <v>53.61</v>
+        <v>55.05</v>
       </c>
     </row>
     <row r="29">
@@ -10244,7 +10260,7 @@
       <c r="C29" t="str">
         <v>001231</v>
       </c>
-      <c r="D29" s="355" t="str">
+      <c r="D29" s="357" t="str">
         <v>净卖: -943.73万</v>
       </c>
       <c r="E29">
@@ -10259,41 +10275,41 @@
       <c r="H29">
         <v>-10.01</v>
       </c>
-      <c r="I29" s="360">
+      <c r="I29" s="363">
         <v>0</v>
       </c>
-      <c r="J29" s="361">
+      <c r="J29" s="358">
         <v>-1.36</v>
       </c>
-      <c r="K29" s="353">
+      <c r="K29" s="359">
         <v>-7.18</v>
       </c>
-      <c r="L29" s="358">
+      <c r="L29" s="353">
         <v>-8.91</v>
       </c>
-      <c r="M29" s="362">
+      <c r="M29" s="360">
         <v>-9.1</v>
       </c>
-      <c r="N29" s="363">
+      <c r="N29" s="354">
         <v>-9.98</v>
       </c>
-      <c r="O29" s="364">
+      <c r="O29" s="361">
         <v>-8.84</v>
       </c>
-      <c r="P29" s="352">
+      <c r="P29" s="362">
         <v>-10.31</v>
       </c>
-      <c r="Q29" s="359">
+      <c r="Q29" s="364">
         <v>-7.96</v>
       </c>
-      <c r="R29" s="356">
+      <c r="R29" s="355">
         <v>-8.8</v>
       </c>
-      <c r="S29" s="357">
+      <c r="S29" s="356">
         <v>-9.28</v>
       </c>
-      <c r="T29" s="354">
-        <v>-12.27</v>
+      <c r="T29" s="352">
+        <v>-7.29</v>
       </c>
     </row>
     <row r="30">
@@ -10321,41 +10337,41 @@
       <c r="H30">
         <v>5.81</v>
       </c>
-      <c r="I30" s="369">
+      <c r="I30" s="366">
         <v>3.95</v>
       </c>
-      <c r="J30" s="367">
+      <c r="J30" s="370">
         <v>14.35</v>
       </c>
       <c r="K30" s="377">
         <v>11.56</v>
       </c>
-      <c r="L30" s="370">
+      <c r="L30" s="371">
         <v>13.48</v>
       </c>
-      <c r="M30" s="365">
+      <c r="M30" s="367">
         <v>9.23</v>
       </c>
-      <c r="N30" s="368">
+      <c r="N30" s="372">
         <v>1.08</v>
       </c>
-      <c r="O30" s="374">
+      <c r="O30" s="373">
         <v>-9.03</v>
       </c>
-      <c r="P30" s="375">
+      <c r="P30" s="365">
         <v>-18.14</v>
       </c>
-      <c r="Q30" s="366">
+      <c r="Q30" s="368">
         <v>-26.33</v>
       </c>
-      <c r="R30" s="371">
+      <c r="R30" s="369">
         <v>-30.78</v>
       </c>
-      <c r="S30" s="372">
+      <c r="S30" s="374">
         <v>-32.45</v>
       </c>
-      <c r="T30" s="373">
-        <v>-42.64</v>
+      <c r="T30" s="375">
+        <v>-42.39</v>
       </c>
     </row>
     <row r="31">
@@ -10368,7 +10384,7 @@
       <c r="C31" t="str">
         <v>002788</v>
       </c>
-      <c r="D31" s="378" t="str">
+      <c r="D31" s="380" t="str">
         <v>净卖: -24.07万</v>
       </c>
       <c r="E31">
@@ -10383,41 +10399,41 @@
       <c r="H31">
         <v>-0.04</v>
       </c>
-      <c r="I31" s="382">
+      <c r="I31" s="385">
         <v>10.05</v>
       </c>
       <c r="J31" s="383">
         <v>7.37</v>
       </c>
-      <c r="K31" s="388">
+      <c r="K31" s="386">
         <v>9.21</v>
       </c>
-      <c r="L31" s="379">
+      <c r="L31" s="381">
         <v>5.12</v>
       </c>
-      <c r="M31" s="380">
+      <c r="M31" s="382">
         <v>-2.72</v>
       </c>
-      <c r="N31" s="389">
+      <c r="N31" s="390">
         <v>-12.45</v>
       </c>
-      <c r="O31" s="390">
+      <c r="O31" s="378">
         <v>-21.22</v>
       </c>
-      <c r="P31" s="384">
+      <c r="P31" s="387">
         <v>-29.1</v>
       </c>
-      <c r="Q31" s="381">
+      <c r="Q31" s="388">
         <v>-33.39</v>
       </c>
-      <c r="R31" s="385">
+      <c r="R31" s="389">
         <v>-34.99</v>
       </c>
-      <c r="S31" s="386">
+      <c r="S31" s="384">
         <v>-32.95</v>
       </c>
-      <c r="T31" s="387">
-        <v>-44.8</v>
+      <c r="T31" s="379">
+        <v>-44.56</v>
       </c>
     </row>
     <row r="32">
@@ -10430,7 +10446,7 @@
       <c r="C32" t="str">
         <v>600151</v>
       </c>
-      <c r="D32" s="393" t="str">
+      <c r="D32" s="401" t="str">
         <v>净买: 7884.07万</v>
       </c>
       <c r="E32">
@@ -10448,38 +10464,38 @@
       <c r="I32" s="397">
         <v>-11.53</v>
       </c>
-      <c r="J32" s="403">
+      <c r="J32" s="402">
         <v>-20.23</v>
       </c>
-      <c r="K32" s="394">
+      <c r="K32" s="398">
         <v>-21.06</v>
       </c>
-      <c r="L32" s="395">
+      <c r="L32" s="403">
         <v>-24.22</v>
       </c>
-      <c r="M32" s="398">
+      <c r="M32" s="391">
         <v>-21.69</v>
       </c>
-      <c r="N32" s="399">
+      <c r="N32" s="400">
         <v>-16.73</v>
       </c>
-      <c r="O32" s="400">
+      <c r="O32" s="399">
         <v>-25.05</v>
       </c>
-      <c r="P32" s="391">
+      <c r="P32" s="392">
         <v>-25.88</v>
       </c>
-      <c r="Q32" s="396">
+      <c r="Q32" s="393">
         <v>-27.43</v>
       </c>
-      <c r="R32" s="401">
+      <c r="R32" s="394">
         <v>-26.65</v>
       </c>
-      <c r="S32" s="392">
+      <c r="S32" s="395">
         <v>-26.61</v>
       </c>
-      <c r="T32" s="402">
-        <v>-28.26</v>
+      <c r="T32" s="396">
+        <v>-31.13</v>
       </c>
     </row>
     <row r="33">
@@ -10492,7 +10508,7 @@
       <c r="C33" t="str">
         <v>600916</v>
       </c>
-      <c r="D33" s="405" t="str">
+      <c r="D33" s="415" t="str">
         <v>净卖: -1428.23万</v>
       </c>
       <c r="E33">
@@ -10507,41 +10523,41 @@
       <c r="H33">
         <v>10.04</v>
       </c>
-      <c r="I33" s="406">
+      <c r="I33" s="408">
         <v>0</v>
       </c>
-      <c r="J33" s="411">
+      <c r="J33" s="405">
         <v>10.02</v>
       </c>
-      <c r="K33" s="407">
+      <c r="K33" s="416">
         <v>19.64</v>
       </c>
-      <c r="L33" s="412">
+      <c r="L33" s="409">
         <v>7.66</v>
       </c>
-      <c r="M33" s="415">
+      <c r="M33" s="410">
         <v>5.87</v>
       </c>
-      <c r="N33" s="416">
+      <c r="N33" s="406">
         <v>-0.81</v>
       </c>
-      <c r="O33" s="408">
+      <c r="O33" s="414">
         <v>-8.96</v>
       </c>
-      <c r="P33" s="409">
+      <c r="P33" s="411">
         <v>-6.93</v>
       </c>
-      <c r="Q33" s="410">
+      <c r="Q33" s="412">
         <v>-5.79</v>
       </c>
-      <c r="R33" s="404">
+      <c r="R33" s="407">
         <v>-8.96</v>
       </c>
-      <c r="S33" s="413">
+      <c r="S33" s="404">
         <v>-9.54</v>
       </c>
-      <c r="T33" s="414">
-        <v>-27.95</v>
+      <c r="T33" s="413">
+        <v>-28.36</v>
       </c>
     </row>
     <row r="34">
@@ -10554,7 +10570,7 @@
       <c r="C34" t="str">
         <v>600969</v>
       </c>
-      <c r="D34" s="417" t="str">
+      <c r="D34" s="421" t="str">
         <v>净卖: -723.23万</v>
       </c>
       <c r="E34">
@@ -10569,41 +10585,41 @@
       <c r="H34">
         <v>0</v>
       </c>
-      <c r="I34" s="424">
+      <c r="I34" s="429">
         <v>-9.99</v>
       </c>
-      <c r="J34" s="418">
+      <c r="J34" s="422">
         <v>-9.99</v>
       </c>
-      <c r="K34" s="419">
+      <c r="K34" s="425">
         <v>-18.98</v>
       </c>
-      <c r="L34" s="425">
+      <c r="L34" s="417">
         <v>-21.07</v>
       </c>
-      <c r="M34" s="427">
+      <c r="M34" s="418">
         <v>-21.98</v>
       </c>
-      <c r="N34" s="420">
+      <c r="N34" s="423">
         <v>-18.98</v>
       </c>
-      <c r="O34" s="428">
+      <c r="O34" s="426">
         <v>-16.9</v>
       </c>
-      <c r="P34" s="429">
+      <c r="P34" s="419">
         <v>-16.82</v>
       </c>
-      <c r="Q34" s="421">
+      <c r="Q34" s="427">
         <v>-14.32</v>
       </c>
-      <c r="R34" s="426">
+      <c r="R34" s="428">
         <v>-13.66</v>
       </c>
-      <c r="S34" s="422">
+      <c r="S34" s="424">
         <v>-15.99</v>
       </c>
-      <c r="T34" s="423">
-        <v>-15.9</v>
+      <c r="T34" s="420">
+        <v>-15.24</v>
       </c>
     </row>
     <row r="35">
@@ -10616,7 +10632,7 @@
       <c r="C35" t="str">
         <v>002040</v>
       </c>
-      <c r="D35" s="439" t="str">
+      <c r="D35" s="436" t="str">
         <v>净卖: -895.74万</v>
       </c>
       <c r="E35">
@@ -10631,41 +10647,41 @@
       <c r="H35">
         <v>-7.37</v>
       </c>
-      <c r="I35" s="430">
+      <c r="I35" s="442">
         <v>-2.87</v>
       </c>
-      <c r="J35" s="440">
+      <c r="J35" s="438">
         <v>-8.52</v>
       </c>
-      <c r="K35" s="431">
+      <c r="K35" s="430">
         <v>-8.36</v>
       </c>
-      <c r="L35" s="432">
+      <c r="L35" s="439">
         <v>-10.49</v>
       </c>
-      <c r="M35" s="435">
+      <c r="M35" s="440">
         <v>-8.44</v>
       </c>
-      <c r="N35" s="433">
+      <c r="N35" s="431">
         <v>-9.02</v>
       </c>
-      <c r="O35" s="436">
+      <c r="O35" s="432">
         <v>-9.51</v>
       </c>
-      <c r="P35" s="441">
+      <c r="P35" s="433">
         <v>-12.05</v>
       </c>
-      <c r="Q35" s="442">
+      <c r="Q35" s="434">
         <v>-8.28</v>
       </c>
-      <c r="R35" s="437">
+      <c r="R35" s="441">
         <v>-10.33</v>
       </c>
-      <c r="S35" s="438">
+      <c r="S35" s="437">
         <v>-11.07</v>
       </c>
-      <c r="T35" s="434">
-        <v>-19.26</v>
+      <c r="T35" s="435">
+        <v>-18.93</v>
       </c>
     </row>
     <row r="36">
@@ -10678,7 +10694,7 @@
       <c r="C36" t="str">
         <v>603017</v>
       </c>
-      <c r="D36" s="455" t="str">
+      <c r="D36" s="453" t="str">
         <v>净买: 694.09万</v>
       </c>
       <c r="E36">
@@ -10693,41 +10709,41 @@
       <c r="H36">
         <v>2.04</v>
       </c>
-      <c r="I36" s="449">
+      <c r="I36" s="447">
         <v>7.84</v>
       </c>
-      <c r="J36" s="453">
+      <c r="J36" s="454">
         <v>7.04</v>
       </c>
-      <c r="K36" s="446">
+      <c r="K36" s="455">
         <v>6.48</v>
       </c>
-      <c r="L36" s="450">
+      <c r="L36" s="448">
         <v>5.04</v>
       </c>
-      <c r="M36" s="447">
+      <c r="M36" s="449">
         <v>7.28</v>
       </c>
-      <c r="N36" s="443">
+      <c r="N36" s="451">
         <v>5.44</v>
       </c>
-      <c r="O36" s="444">
+      <c r="O36" s="452">
         <v>10.72</v>
       </c>
-      <c r="P36" s="454">
+      <c r="P36" s="443">
         <v>10.32</v>
       </c>
-      <c r="Q36" s="445">
+      <c r="Q36" s="444">
         <v>7.92</v>
       </c>
-      <c r="R36" s="448">
+      <c r="R36" s="445">
         <v>1.28</v>
       </c>
-      <c r="S36" s="451">
+      <c r="S36" s="450">
         <v>11.44</v>
       </c>
-      <c r="T36" s="452">
-        <v>22.08</v>
+      <c r="T36" s="446">
+        <v>19.6</v>
       </c>
     </row>
     <row r="37">
@@ -10740,7 +10756,7 @@
       <c r="C37" t="str">
         <v>600495</v>
       </c>
-      <c r="D37" s="468" t="str">
+      <c r="D37" s="466" t="str">
         <v>净买: 998.97万</v>
       </c>
       <c r="E37">
@@ -10755,41 +10771,41 @@
       <c r="H37">
         <v>0</v>
       </c>
-      <c r="I37" s="463">
+      <c r="I37" s="459">
         <v>10.04</v>
       </c>
-      <c r="J37" s="459">
+      <c r="J37" s="464">
         <v>11.16</v>
       </c>
-      <c r="K37" s="464">
+      <c r="K37" s="467">
         <v>12.28</v>
       </c>
-      <c r="L37" s="465">
+      <c r="L37" s="460">
         <v>2.23</v>
       </c>
-      <c r="M37" s="460">
+      <c r="M37" s="468">
         <v>0.67</v>
       </c>
-      <c r="N37" s="461">
+      <c r="N37" s="456">
         <v>4.46</v>
       </c>
       <c r="O37" s="457">
         <v>0.67</v>
       </c>
-      <c r="P37" s="456">
+      <c r="P37" s="462">
         <v>0.45</v>
       </c>
-      <c r="Q37" s="462">
+      <c r="Q37" s="461">
         <v>-1.34</v>
       </c>
-      <c r="R37" s="466">
+      <c r="R37" s="465">
         <v>-1.34</v>
       </c>
-      <c r="S37" s="467">
+      <c r="S37" s="458">
         <v>-2.01</v>
       </c>
-      <c r="T37" s="458">
-        <v>-2.9</v>
+      <c r="T37" s="463">
+        <v>-2.23</v>
       </c>
     </row>
     <row r="38">
@@ -10817,41 +10833,41 @@
       <c r="H38">
         <v>9.92</v>
       </c>
-      <c r="I38" s="473">
+      <c r="I38" s="475">
         <v>0</v>
       </c>
-      <c r="J38" s="474">
+      <c r="J38" s="476">
         <v>10.07</v>
       </c>
-      <c r="K38" s="480">
+      <c r="K38" s="481">
         <v>21.01</v>
       </c>
-      <c r="L38" s="481">
+      <c r="L38" s="469">
         <v>33.16</v>
       </c>
-      <c r="M38" s="475">
+      <c r="M38" s="478">
         <v>27.78</v>
       </c>
-      <c r="N38" s="476">
+      <c r="N38" s="473">
         <v>22.92</v>
       </c>
-      <c r="O38" s="477">
+      <c r="O38" s="474">
         <v>11.46</v>
       </c>
-      <c r="P38" s="478">
+      <c r="P38" s="479">
         <v>2.6</v>
       </c>
-      <c r="Q38" s="479">
+      <c r="Q38" s="480">
         <v>7.99</v>
       </c>
-      <c r="R38" s="469">
+      <c r="R38" s="470">
         <v>18.75</v>
       </c>
-      <c r="S38" s="470">
+      <c r="S38" s="471">
         <v>9.2</v>
       </c>
-      <c r="T38" s="471">
-        <v>6.25</v>
+      <c r="T38" s="477">
+        <v>-2.43</v>
       </c>
     </row>
     <row r="39">
@@ -10891,15 +10907,17 @@
       <c r="L39" s="486">
         <v>3.89</v>
       </c>
-      <c r="M39" t="str"/>
+      <c r="M39" s="487">
+        <v>-7.51</v>
+      </c>
       <c r="N39" t="str"/>
       <c r="O39" t="str"/>
       <c r="P39" t="str"/>
       <c r="Q39" t="str"/>
       <c r="R39" t="str"/>
       <c r="S39" t="str"/>
-      <c r="T39" s="487">
-        <v>3.89</v>
+      <c r="T39" s="488">
+        <v>-7.51</v>
       </c>
     </row>
     <row r="40">
@@ -10926,7 +10944,7 @@
         <v>38</v>
       </c>
       <c r="M40">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N40">
         <v>37</v>
@@ -10961,41 +10979,41 @@
       <c r="F41" t="str"/>
       <c r="G41" t="str"/>
       <c r="H41" t="str"/>
-      <c r="I41" s="495">
+      <c r="I41" s="493">
         <v>52.63</v>
       </c>
-      <c r="J41" s="496">
+      <c r="J41" s="497">
         <v>63.16</v>
       </c>
-      <c r="K41" s="489">
+      <c r="K41" s="494">
         <v>55.26</v>
       </c>
-      <c r="L41" s="497">
+      <c r="L41" s="498">
         <v>57.89</v>
       </c>
-      <c r="M41" s="493">
-        <v>51.35</v>
-      </c>
-      <c r="N41" s="491">
+      <c r="M41" s="499">
+        <v>50</v>
+      </c>
+      <c r="N41" s="500">
         <v>48.65</v>
       </c>
-      <c r="O41" s="494">
+      <c r="O41" s="491">
         <v>45.95</v>
       </c>
-      <c r="P41" s="492">
+      <c r="P41" s="495">
         <v>40.54</v>
       </c>
-      <c r="Q41" s="490">
+      <c r="Q41" s="496">
         <v>35.14</v>
       </c>
-      <c r="R41" s="498">
+      <c r="R41" s="490">
         <v>37.84</v>
       </c>
-      <c r="S41" s="499">
+      <c r="S41" s="492">
         <v>37.84</v>
       </c>
-      <c r="T41" s="488">
-        <v>28.95</v>
+      <c r="T41" s="489">
+        <v>23.68</v>
       </c>
     </row>
     <row r="42">
@@ -11009,41 +11027,41 @@
       <c r="F42" t="str"/>
       <c r="G42" t="str"/>
       <c r="H42" t="str"/>
-      <c r="I42" s="510">
+      <c r="I42" s="506">
         <v>2.29</v>
       </c>
-      <c r="J42" s="511">
+      <c r="J42" s="504">
         <v>3.48</v>
       </c>
-      <c r="K42" s="500">
+      <c r="K42" s="505">
         <v>3.42</v>
       </c>
-      <c r="L42" s="504">
+      <c r="L42" s="502">
         <v>3.13</v>
       </c>
-      <c r="M42" s="502">
-        <v>4.56</v>
-      </c>
-      <c r="N42" s="508">
+      <c r="M42" s="507">
+        <v>4.24</v>
+      </c>
+      <c r="N42" s="509">
         <v>3.99</v>
       </c>
-      <c r="O42" s="505">
+      <c r="O42" s="510">
         <v>2.28</v>
       </c>
-      <c r="P42" s="506">
+      <c r="P42" s="503">
         <v>0.79</v>
       </c>
-      <c r="Q42" s="501">
+      <c r="Q42" s="508">
         <v>-0.11</v>
       </c>
-      <c r="R42" s="509">
+      <c r="R42" s="511">
         <v>-0.68</v>
       </c>
-      <c r="S42" s="507">
+      <c r="S42" s="512">
         <v>-0.22</v>
       </c>
-      <c r="T42" s="503">
-        <v>-4.66</v>
+      <c r="T42" s="501">
+        <v>-4.83</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/湖州劳动路/index.xlsx
+++ b/youzi/湖州劳动路/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="514">
+  <fills count="515">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -51,72 +51,144 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD02F3E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFEB8D96"/>
         <bgColor/>
       </patternFill>
@@ -135,25 +207,1231 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5FBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196F2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF96D4A4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5ABB70"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2534"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8BCF9B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8BCF9B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4553"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DFE2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE53"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3F3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46672"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9808A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC7E8CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8336"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CFD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4CB564"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8FD19E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56A76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6F4E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35E6B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE7E9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4AB563"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3746"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF94D3A2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8F98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,7 +1443,229 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3F4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFAFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF47B360"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF35AC50"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAE3C3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AA4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA1D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFCFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A443"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF91D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56D78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -177,31 +1677,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208838"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -219,55 +1719,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF208839"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,109 +1797,721 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5FBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23963E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA6DAB2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AEB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF46B35F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD93343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC380"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22913C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2ECD8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5EBD74"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A243"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC939C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87F89"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6717C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7833"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8437"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4E7CC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218D3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7632"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D3D6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8ACF99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -399,13 +2523,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5ABB70"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
+        <fgColor rgb="FFDCF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7832"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -417,85 +2601,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196F2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2534"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF83CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7F35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7E35"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -507,61 +2715,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4957"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
+        <fgColor rgb="FFBD2735"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBD2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC2D3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CBCF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5CBC72"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBECEE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC5E7CD"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -573,37 +2811,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA4AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE3E6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32A38"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -627,37 +2871,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFEC959E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAF202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -675,55 +2937,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFC12937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25966"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC949D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF33AB4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA7DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5C9CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6E7CE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2735"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -735,2317 +3075,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4553"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BCF9B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9DFE2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE53"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BCF9B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5CBC72"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9808A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46672"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4CB564"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8336"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3F3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC7E8CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A142"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CFD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8FD19E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56A76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35E6B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F4E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE7E9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3746"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4AB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF94D3A2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8F98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6EC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFAFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3F4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA1D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF35AC50"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A443"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF47B360"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFCFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBAE3C3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AA4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF91D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56D78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208838"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA6DAB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7B34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AEB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC380"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD93343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF46B35F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5EBD74"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22913C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2ECD8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF26A243"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6717C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC939C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87F89"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7833"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC4E7CC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218D3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7632"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8437"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D3D6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8ACF99"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDCF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7832"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7F35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7E35"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF83CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CBCF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBD2735"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC2D3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA4AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBECEE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD7AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC5E7CD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE3E6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAF202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF96D4A4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC959E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC12937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25966"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA7DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5C9CE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC949D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF33AB4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2735"/>
+        <fgColor rgb="FFB5E1BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3FAF4"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3055,62 +3115,15 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3FAF4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB5E1BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="513">
+  <borders count="514">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -6706,7 +6719,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="513">
+  <cellXfs count="514">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -8242,6 +8255,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="512" fillId="513" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="513" fillId="514" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -8586,7 +8602,7 @@
       <c r="C2" t="str">
         <v>002105</v>
       </c>
-      <c r="D2" s="12" t="str">
+      <c r="D2" s="3" t="str">
         <v>净卖: -286.93万</v>
       </c>
       <c r="E2">
@@ -8601,41 +8617,41 @@
       <c r="H2">
         <v>3.63</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="7">
         <v>6.13</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="9">
         <v>16.75</v>
       </c>
-      <c r="K2" s="8">
+      <c r="K2" s="4">
         <v>28.37</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="11">
         <v>41.25</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="12">
         <v>55.38</v>
       </c>
-      <c r="N2" s="9">
+      <c r="N2" s="13">
         <v>46.12</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="10">
         <v>46.75</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="8">
         <v>33.13</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="1">
         <v>34.87</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="5">
         <v>21.38</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="2">
         <v>11.62</v>
       </c>
-      <c r="T2" s="11">
-        <v>-19</v>
+      <c r="T2" s="6">
+        <v>-19.5</v>
       </c>
     </row>
     <row r="3">
@@ -8648,7 +8664,7 @@
       <c r="C3" t="str">
         <v>002760</v>
       </c>
-      <c r="D3" s="23" t="str">
+      <c r="D3" s="25" t="str">
         <v>净买: 1264.22万</v>
       </c>
       <c r="E3">
@@ -8663,41 +8679,41 @@
       <c r="H3">
         <v>3.43</v>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="19">
         <v>6.36</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="26">
         <v>2.8</v>
       </c>
-      <c r="K3" s="21">
+      <c r="K3" s="14">
         <v>-6.84</v>
       </c>
-      <c r="L3" s="24">
+      <c r="L3" s="21">
         <v>-13.76</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M3" s="15">
         <v>-13.72</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="20">
         <v>-14.84</v>
       </c>
-      <c r="O3" s="25">
+      <c r="O3" s="16">
         <v>-15.92</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="17">
         <v>-16.68</v>
       </c>
-      <c r="Q3" s="26">
+      <c r="Q3" s="22">
         <v>-19.6</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3" s="18">
         <v>-22.72</v>
       </c>
-      <c r="S3" s="22">
+      <c r="S3" s="23">
         <v>-23.88</v>
       </c>
-      <c r="T3" s="16">
-        <v>-11.24</v>
+      <c r="T3" s="24">
+        <v>-11.08</v>
       </c>
     </row>
     <row r="4">
@@ -8710,7 +8726,7 @@
       <c r="C4" t="str">
         <v>002760</v>
       </c>
-      <c r="D4" s="30" t="str">
+      <c r="D4" s="38" t="str">
         <v>净卖: -1488.32万</v>
       </c>
       <c r="E4">
@@ -8725,41 +8741,41 @@
       <c r="H4">
         <v>4.59</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="39">
         <v>-7.59</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="27">
         <v>-16.25</v>
       </c>
-      <c r="K4" s="32">
+      <c r="K4" s="35">
         <v>-22.47</v>
       </c>
-      <c r="L4" s="39">
+      <c r="L4" s="30">
         <v>-22.44</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="31">
         <v>-23.44</v>
       </c>
-      <c r="N4" s="33">
+      <c r="N4" s="28">
         <v>-24.42</v>
       </c>
-      <c r="O4" s="35">
+      <c r="O4" s="36">
         <v>-25.1</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="32">
         <v>-27.72</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="37">
         <v>-30.53</v>
       </c>
       <c r="R4" s="29">
         <v>-31.57</v>
       </c>
-      <c r="S4" s="36">
+      <c r="S4" s="33">
         <v>-31.07</v>
       </c>
-      <c r="T4" s="37">
-        <v>-20.21</v>
+      <c r="T4" s="34">
+        <v>-20.06</v>
       </c>
     </row>
     <row r="5">
@@ -8772,7 +8788,7 @@
       <c r="C5" t="str">
         <v>603958</v>
       </c>
-      <c r="D5" s="41" t="str">
+      <c r="D5" s="46" t="str">
         <v>净买: 2814.34万</v>
       </c>
       <c r="E5">
@@ -8787,41 +8803,41 @@
       <c r="H5">
         <v>0</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="43">
         <v>-3.71</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="49">
         <v>-13.32</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="47">
         <v>-18.35</v>
       </c>
-      <c r="L5" s="45">
+      <c r="L5" s="44">
         <v>-15.42</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="50">
         <v>-11.81</v>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="45">
         <v>-11.27</v>
       </c>
-      <c r="O5" s="52">
+      <c r="O5" s="51">
         <v>-11.13</v>
       </c>
-      <c r="P5" s="44">
+      <c r="P5" s="48">
         <v>-13.08</v>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="52">
         <v>-16.15</v>
       </c>
-      <c r="R5" s="46">
+      <c r="R5" s="40">
         <v>-17.72</v>
       </c>
-      <c r="S5" s="40">
+      <c r="S5" s="41">
         <v>-18.79</v>
       </c>
-      <c r="T5" s="47">
-        <v>15.18</v>
+      <c r="T5" s="42">
+        <v>13.67</v>
       </c>
     </row>
     <row r="6">
@@ -8834,7 +8850,7 @@
       <c r="C6" t="str">
         <v>603958</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="60" t="str">
         <v>净卖: -2283.55万</v>
       </c>
       <c r="E6">
@@ -8849,41 +8865,41 @@
       <c r="H6">
         <v>-6.13</v>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="53">
         <v>-4.1</v>
       </c>
-      <c r="J6" s="64">
+      <c r="J6" s="54">
         <v>-9.67</v>
       </c>
-      <c r="K6" s="55">
+      <c r="K6" s="61">
         <v>-6.43</v>
       </c>
-      <c r="L6" s="58">
+      <c r="L6" s="55">
         <v>-2.43</v>
       </c>
-      <c r="M6" s="59">
+      <c r="M6" s="64">
         <v>-1.84</v>
       </c>
-      <c r="N6" s="65">
+      <c r="N6" s="56">
         <v>-1.67</v>
       </c>
-      <c r="O6" s="61">
+      <c r="O6" s="62">
         <v>-3.83</v>
       </c>
-      <c r="P6" s="62">
+      <c r="P6" s="63">
         <v>-7.24</v>
       </c>
-      <c r="Q6" s="60">
+      <c r="Q6" s="57">
         <v>-8.96</v>
       </c>
-      <c r="R6" s="53">
+      <c r="R6" s="58">
         <v>-10.15</v>
       </c>
-      <c r="S6" s="56">
+      <c r="S6" s="65">
         <v>-9.99</v>
       </c>
-      <c r="T6" s="54">
-        <v>27.43</v>
+      <c r="T6" s="59">
+        <v>25.76</v>
       </c>
     </row>
     <row r="7">
@@ -8896,7 +8912,7 @@
       <c r="C7" t="str">
         <v>002645</v>
       </c>
-      <c r="D7" s="78" t="str">
+      <c r="D7" s="73" t="str">
         <v>净买: 1223.21万</v>
       </c>
       <c r="E7">
@@ -8911,41 +8927,41 @@
       <c r="H7">
         <v>1.72</v>
       </c>
-      <c r="I7" s="72">
+      <c r="I7" s="74">
         <v>8.14</v>
       </c>
-      <c r="J7" s="73">
+      <c r="J7" s="69">
         <v>5.31</v>
       </c>
-      <c r="K7" s="68">
+      <c r="K7" s="70">
         <v>9.04</v>
       </c>
-      <c r="L7" s="77">
+      <c r="L7" s="75">
         <v>4.75</v>
       </c>
-      <c r="M7" s="74">
+      <c r="M7" s="66">
         <v>3.5</v>
       </c>
-      <c r="N7" s="69">
+      <c r="N7" s="76">
         <v>-6.89</v>
       </c>
-      <c r="O7" s="70">
+      <c r="O7" s="71">
         <v>-5.42</v>
       </c>
-      <c r="P7" s="66">
+      <c r="P7" s="77">
         <v>-7.12</v>
       </c>
-      <c r="Q7" s="71">
+      <c r="Q7" s="67">
         <v>-7.23</v>
       </c>
-      <c r="R7" s="67">
+      <c r="R7" s="72">
         <v>-10.73</v>
       </c>
-      <c r="S7" s="75">
+      <c r="S7" s="78">
         <v>-9.94</v>
       </c>
-      <c r="T7" s="76">
-        <v>149.38</v>
+      <c r="T7" s="68">
+        <v>140.68</v>
       </c>
     </row>
     <row r="8">
@@ -8958,7 +8974,7 @@
       <c r="C8" t="str">
         <v>600537</v>
       </c>
-      <c r="D8" s="89" t="str">
+      <c r="D8" s="83" t="str">
         <v>净买: 358.47万</v>
       </c>
       <c r="E8">
@@ -8973,40 +8989,40 @@
       <c r="H8">
         <v>5.03</v>
       </c>
-      <c r="I8" s="90">
+      <c r="I8" s="81">
         <v>4.79</v>
       </c>
-      <c r="J8" s="85">
+      <c r="J8" s="84">
         <v>8.98</v>
       </c>
       <c r="K8" s="91">
         <v>-1.8</v>
       </c>
-      <c r="L8" s="81">
+      <c r="L8" s="85">
         <v>8.08</v>
       </c>
-      <c r="M8" s="82">
+      <c r="M8" s="86">
         <v>18.86</v>
       </c>
       <c r="N8" s="79">
         <v>19.76</v>
       </c>
-      <c r="O8" s="87">
+      <c r="O8" s="80">
         <v>19.16</v>
       </c>
-      <c r="P8" s="86">
+      <c r="P8" s="82">
         <v>15.57</v>
       </c>
-      <c r="Q8" s="88">
+      <c r="Q8" s="87">
         <v>8.38</v>
       </c>
-      <c r="R8" s="80">
+      <c r="R8" s="88">
         <v>4.49</v>
       </c>
-      <c r="S8" s="83">
+      <c r="S8" s="89">
         <v>14.97</v>
       </c>
-      <c r="T8" s="84">
+      <c r="T8" s="90">
         <v>6.29</v>
       </c>
     </row>
@@ -9020,7 +9036,7 @@
       <c r="C9" t="str">
         <v>603122</v>
       </c>
-      <c r="D9" s="96" t="str">
+      <c r="D9" s="104" t="str">
         <v>净卖: -557.16万</v>
       </c>
       <c r="E9">
@@ -9035,41 +9051,41 @@
       <c r="H9">
         <v>7.07</v>
       </c>
-      <c r="I9" s="101">
+      <c r="I9" s="100">
         <v>2.8</v>
       </c>
-      <c r="J9" s="97">
+      <c r="J9" s="96">
         <v>13.09</v>
       </c>
       <c r="K9" s="92">
         <v>24.4</v>
       </c>
-      <c r="L9" s="98">
+      <c r="L9" s="101">
         <v>36.85</v>
       </c>
-      <c r="M9" s="99">
+      <c r="M9" s="93">
         <v>50.57</v>
       </c>
-      <c r="N9" s="93">
+      <c r="N9" s="94">
         <v>65.69</v>
       </c>
-      <c r="O9" s="94">
+      <c r="O9" s="102">
         <v>82.21</v>
       </c>
-      <c r="P9" s="100">
+      <c r="P9" s="97">
         <v>100.38</v>
       </c>
-      <c r="Q9" s="102">
+      <c r="Q9" s="98">
         <v>110.93</v>
       </c>
-      <c r="R9" s="103">
+      <c r="R9" s="95">
         <v>132.02</v>
       </c>
-      <c r="S9" s="104">
+      <c r="S9" s="99">
         <v>155.27</v>
       </c>
-      <c r="T9" s="95">
-        <v>96.06</v>
+      <c r="T9" s="103">
+        <v>97.59</v>
       </c>
     </row>
     <row r="10">
@@ -9082,7 +9098,7 @@
       <c r="C10" t="str">
         <v>002682</v>
       </c>
-      <c r="D10" s="105" t="str">
+      <c r="D10" s="117" t="str">
         <v>净买: 749.97万</v>
       </c>
       <c r="E10">
@@ -9097,41 +9113,41 @@
       <c r="H10">
         <v>10.02</v>
       </c>
-      <c r="I10" s="106">
+      <c r="I10" s="109">
         <v>0</v>
       </c>
-      <c r="J10" s="112">
+      <c r="J10" s="105">
         <v>10.03</v>
       </c>
-      <c r="K10" s="107">
+      <c r="K10" s="113">
         <v>20.99</v>
       </c>
-      <c r="L10" s="116">
+      <c r="L10" s="106">
         <v>8.95</v>
       </c>
-      <c r="M10" s="110">
+      <c r="M10" s="114">
         <v>-2.01</v>
       </c>
-      <c r="N10" s="111">
+      <c r="N10" s="110">
         <v>-11.73</v>
       </c>
-      <c r="O10" s="113">
+      <c r="O10" s="115">
         <v>-16.05</v>
       </c>
-      <c r="P10" s="108">
+      <c r="P10" s="116">
         <v>-13.73</v>
       </c>
-      <c r="Q10" s="117">
+      <c r="Q10" s="107">
         <v>-17.59</v>
       </c>
-      <c r="R10" s="114">
+      <c r="R10" s="111">
         <v>-17.28</v>
       </c>
-      <c r="S10" s="109">
+      <c r="S10" s="108">
         <v>-14.04</v>
       </c>
-      <c r="T10" s="115">
-        <v>-10.96</v>
+      <c r="T10" s="112">
+        <v>-10.8</v>
       </c>
     </row>
     <row r="11">
@@ -9144,7 +9160,7 @@
       <c r="C11" t="str">
         <v>600227</v>
       </c>
-      <c r="D11" s="128" t="str">
+      <c r="D11" s="123" t="str">
         <v>净买: 484.48万</v>
       </c>
       <c r="E11">
@@ -9159,41 +9175,41 @@
       <c r="H11">
         <v>1.56</v>
       </c>
-      <c r="I11" s="125">
+      <c r="I11" s="119">
         <v>8.43</v>
       </c>
-      <c r="J11" s="121">
+      <c r="J11" s="124">
         <v>13.79</v>
       </c>
-      <c r="K11" s="118">
+      <c r="K11" s="125">
         <v>9.2</v>
       </c>
-      <c r="L11" s="119">
+      <c r="L11" s="120">
         <v>7.28</v>
       </c>
-      <c r="M11" s="122">
+      <c r="M11" s="126">
         <v>2.68</v>
       </c>
-      <c r="N11" s="120">
+      <c r="N11" s="127">
         <v>4.6</v>
       </c>
-      <c r="O11" s="126">
+      <c r="O11" s="128">
         <v>0.77</v>
       </c>
-      <c r="P11" s="127">
+      <c r="P11" s="130">
         <v>-4.6</v>
       </c>
-      <c r="Q11" s="123">
+      <c r="Q11" s="118">
         <v>-2.68</v>
       </c>
       <c r="R11" s="129">
         <v>-4.6</v>
       </c>
-      <c r="S11" s="130">
+      <c r="S11" s="121">
         <v>-2.68</v>
       </c>
-      <c r="T11" s="124">
-        <v>41</v>
+      <c r="T11" s="122">
+        <v>55.17</v>
       </c>
     </row>
     <row r="12">
@@ -9206,7 +9222,7 @@
       <c r="C12" t="str">
         <v>603386</v>
       </c>
-      <c r="D12" s="134" t="str">
+      <c r="D12" s="138" t="str">
         <v>净卖: -4389.34万</v>
       </c>
       <c r="E12">
@@ -9221,41 +9237,41 @@
       <c r="H12">
         <v>-8.19</v>
       </c>
-      <c r="I12" s="140">
+      <c r="I12" s="136">
         <v>-1.95</v>
       </c>
-      <c r="J12" s="137">
+      <c r="J12" s="132">
         <v>-3.78</v>
       </c>
-      <c r="K12" s="138">
+      <c r="K12" s="139">
         <v>-11.08</v>
       </c>
-      <c r="L12" s="135">
+      <c r="L12" s="143">
         <v>-18.92</v>
       </c>
-      <c r="M12" s="141">
+      <c r="M12" s="133">
         <v>-18.16</v>
       </c>
-      <c r="N12" s="139">
+      <c r="N12" s="140">
         <v>-18.54</v>
       </c>
       <c r="O12" s="131">
         <v>-17.08</v>
       </c>
-      <c r="P12" s="136">
+      <c r="P12" s="137">
         <v>-17.95</v>
       </c>
-      <c r="Q12" s="132">
+      <c r="Q12" s="134">
         <v>-14.43</v>
       </c>
-      <c r="R12" s="142">
+      <c r="R12" s="141">
         <v>-20</v>
       </c>
-      <c r="S12" s="143">
+      <c r="S12" s="142">
         <v>-18.32</v>
       </c>
-      <c r="T12" s="133">
-        <v>-22.22</v>
+      <c r="T12" s="135">
+        <v>-29.89</v>
       </c>
     </row>
     <row r="13">
@@ -9268,7 +9284,7 @@
       <c r="C13" t="str">
         <v>600493</v>
       </c>
-      <c r="D13" s="156" t="str">
+      <c r="D13" s="152" t="str">
         <v>净买: 999.07万</v>
       </c>
       <c r="E13">
@@ -9283,41 +9299,41 @@
       <c r="H13">
         <v>1.85</v>
       </c>
-      <c r="I13" s="144">
+      <c r="I13" s="145">
         <v>8.05</v>
       </c>
-      <c r="J13" s="152">
+      <c r="J13" s="146">
         <v>-0.65</v>
       </c>
-      <c r="K13" s="145">
+      <c r="K13" s="150">
         <v>3.12</v>
       </c>
-      <c r="L13" s="148">
+      <c r="L13" s="156">
         <v>-4.16</v>
       </c>
-      <c r="M13" s="149">
+      <c r="M13" s="153">
         <v>-8.05</v>
       </c>
-      <c r="N13" s="155">
+      <c r="N13" s="154">
         <v>1.17</v>
       </c>
-      <c r="O13" s="153">
+      <c r="O13" s="151">
         <v>-1.3</v>
       </c>
-      <c r="P13" s="150">
+      <c r="P13" s="144">
         <v>-2.47</v>
       </c>
-      <c r="Q13" s="151">
+      <c r="Q13" s="155">
         <v>1.56</v>
       </c>
-      <c r="R13" s="146">
+      <c r="R13" s="147">
         <v>3.77</v>
       </c>
-      <c r="S13" s="147">
+      <c r="S13" s="148">
         <v>4.03</v>
       </c>
-      <c r="T13" s="154">
-        <v>-5.45</v>
+      <c r="T13" s="149">
+        <v>-5.19</v>
       </c>
     </row>
     <row r="14">
@@ -9330,7 +9346,7 @@
       <c r="C14" t="str">
         <v>001330</v>
       </c>
-      <c r="D14" s="165" t="str">
+      <c r="D14" s="157" t="str">
         <v>净卖: -4990.62万</v>
       </c>
       <c r="E14">
@@ -9345,41 +9361,41 @@
       <c r="H14">
         <v>1.65</v>
       </c>
-      <c r="I14" s="162">
+      <c r="I14" s="163">
         <v>8.18</v>
       </c>
-      <c r="J14" s="163">
+      <c r="J14" s="158">
         <v>-2.59</v>
       </c>
-      <c r="K14" s="166">
+      <c r="K14" s="160">
         <v>-12.32</v>
       </c>
-      <c r="L14" s="167">
+      <c r="L14" s="159">
         <v>-20.34</v>
       </c>
-      <c r="M14" s="168">
+      <c r="M14" s="164">
         <v>-12.4</v>
       </c>
-      <c r="N14" s="169">
+      <c r="N14" s="161">
         <v>-18.4</v>
       </c>
-      <c r="O14" s="157">
+      <c r="O14" s="165">
         <v>-26.58</v>
       </c>
-      <c r="P14" s="164">
+      <c r="P14" s="167">
         <v>-33.95</v>
       </c>
-      <c r="Q14" s="158">
+      <c r="Q14" s="168">
         <v>-32.82</v>
       </c>
-      <c r="R14" s="159">
+      <c r="R14" s="166">
         <v>-35.66</v>
       </c>
-      <c r="S14" s="160">
+      <c r="S14" s="162">
         <v>-34.76</v>
       </c>
-      <c r="T14" s="161">
-        <v>-33.79</v>
+      <c r="T14" s="169">
+        <v>-35.66</v>
       </c>
     </row>
     <row r="15">
@@ -9392,7 +9408,7 @@
       <c r="C15" t="str">
         <v>600865</v>
       </c>
-      <c r="D15" s="170" t="str">
+      <c r="D15" s="178" t="str">
         <v>净买: 4692.22万</v>
       </c>
       <c r="E15">
@@ -9407,41 +9423,41 @@
       <c r="H15">
         <v>10.02</v>
       </c>
-      <c r="I15" s="171">
+      <c r="I15" s="173">
         <v>0</v>
       </c>
-      <c r="J15" s="181">
+      <c r="J15" s="182">
         <v>10.01</v>
       </c>
-      <c r="K15" s="176">
+      <c r="K15" s="174">
         <v>21</v>
       </c>
-      <c r="L15" s="177">
+      <c r="L15" s="170">
         <v>25.24</v>
       </c>
-      <c r="M15" s="172">
+      <c r="M15" s="180">
         <v>32.13</v>
       </c>
-      <c r="N15" s="173">
+      <c r="N15" s="175">
         <v>27.75</v>
       </c>
-      <c r="O15" s="179">
+      <c r="O15" s="171">
         <v>37.2</v>
       </c>
-      <c r="P15" s="182">
+      <c r="P15" s="176">
         <v>50.9</v>
       </c>
-      <c r="Q15" s="180">
+      <c r="Q15" s="177">
         <v>48.33</v>
       </c>
-      <c r="R15" s="174">
+      <c r="R15" s="179">
         <v>33.52</v>
       </c>
-      <c r="S15" s="178">
+      <c r="S15" s="172">
         <v>20.17</v>
       </c>
-      <c r="T15" s="175">
-        <v>-19.05</v>
+      <c r="T15" s="181">
+        <v>-22.04</v>
       </c>
     </row>
     <row r="16">
@@ -9454,7 +9470,7 @@
       <c r="C16" t="str">
         <v>600865</v>
       </c>
-      <c r="D16" s="189" t="str">
+      <c r="D16" s="192" t="str">
         <v>净卖: -5679.38万</v>
       </c>
       <c r="E16">
@@ -9469,41 +9485,41 @@
       <c r="H16">
         <v>10.01</v>
       </c>
-      <c r="I16" s="185">
+      <c r="I16" s="189">
         <v>0</v>
       </c>
-      <c r="J16" s="186">
+      <c r="J16" s="195">
         <v>9.99</v>
       </c>
-      <c r="K16" s="193">
+      <c r="K16" s="190">
         <v>13.84</v>
       </c>
-      <c r="L16" s="190">
+      <c r="L16" s="185">
         <v>20.1</v>
       </c>
-      <c r="M16" s="183">
+      <c r="M16" s="186">
         <v>16.12</v>
       </c>
-      <c r="N16" s="194">
+      <c r="N16" s="193">
         <v>24.72</v>
       </c>
       <c r="O16" s="191">
         <v>37.17</v>
       </c>
-      <c r="P16" s="192">
+      <c r="P16" s="187">
         <v>34.83</v>
       </c>
-      <c r="Q16" s="187">
+      <c r="Q16" s="194">
         <v>21.37</v>
       </c>
-      <c r="R16" s="184">
+      <c r="R16" s="183">
         <v>9.23</v>
       </c>
       <c r="S16" s="188">
         <v>3.67</v>
       </c>
-      <c r="T16" s="195">
-        <v>-26.42</v>
+      <c r="T16" s="184">
+        <v>-29.14</v>
       </c>
     </row>
     <row r="17">
@@ -9516,7 +9532,7 @@
       <c r="C17" t="str">
         <v>600693</v>
       </c>
-      <c r="D17" s="201" t="str">
+      <c r="D17" s="202" t="str">
         <v>净买: 4205.60万</v>
       </c>
       <c r="E17">
@@ -9531,41 +9547,41 @@
       <c r="H17">
         <v>2.51</v>
       </c>
-      <c r="I17" s="207">
+      <c r="I17" s="203">
         <v>0.41</v>
       </c>
       <c r="J17" s="199">
         <v>-0.58</v>
       </c>
-      <c r="K17" s="205">
+      <c r="K17" s="200">
         <v>9.33</v>
       </c>
-      <c r="L17" s="208">
+      <c r="L17" s="204">
         <v>13.77</v>
       </c>
-      <c r="M17" s="202">
+      <c r="M17" s="201">
         <v>25.15</v>
       </c>
-      <c r="N17" s="203">
+      <c r="N17" s="196">
         <v>22</v>
       </c>
-      <c r="O17" s="196">
+      <c r="O17" s="197">
         <v>27.65</v>
       </c>
-      <c r="P17" s="204">
+      <c r="P17" s="205">
         <v>15.52</v>
       </c>
-      <c r="Q17" s="197">
+      <c r="Q17" s="198">
         <v>3.97</v>
       </c>
-      <c r="R17" s="198">
+      <c r="R17" s="206">
         <v>3.97</v>
       </c>
-      <c r="S17" s="200">
+      <c r="S17" s="207">
         <v>7.29</v>
       </c>
-      <c r="T17" s="206">
-        <v>-32.73</v>
+      <c r="T17" s="208">
+        <v>-33.49</v>
       </c>
     </row>
     <row r="18">
@@ -9578,7 +9594,7 @@
       <c r="C18" t="str">
         <v>603023</v>
       </c>
-      <c r="D18" s="213" t="str">
+      <c r="D18" s="221" t="str">
         <v>净买: 2053.34万</v>
       </c>
       <c r="E18">
@@ -9593,41 +9609,41 @@
       <c r="H18">
         <v>-0.38</v>
       </c>
-      <c r="I18" s="209">
+      <c r="I18" s="214">
         <v>10.48</v>
       </c>
-      <c r="J18" s="214">
+      <c r="J18" s="213">
         <v>13.9</v>
       </c>
-      <c r="K18" s="210">
+      <c r="K18" s="217">
         <v>10.1</v>
       </c>
-      <c r="L18" s="211">
+      <c r="L18" s="209">
         <v>5.14</v>
       </c>
-      <c r="M18" s="219">
+      <c r="M18" s="218">
         <v>4.95</v>
       </c>
-      <c r="N18" s="217">
+      <c r="N18" s="210">
         <v>6.29</v>
       </c>
-      <c r="O18" s="218">
+      <c r="O18" s="211">
         <v>0.57</v>
       </c>
       <c r="P18" s="212">
         <v>1.9</v>
       </c>
-      <c r="Q18" s="220">
+      <c r="Q18" s="215">
         <v>-4.19</v>
       </c>
-      <c r="R18" s="221">
+      <c r="R18" s="219">
         <v>-2.48</v>
       </c>
-      <c r="S18" s="215">
+      <c r="S18" s="216">
         <v>7.24</v>
       </c>
-      <c r="T18" s="216">
-        <v>-14.86</v>
+      <c r="T18" s="220">
+        <v>-16.38</v>
       </c>
     </row>
     <row r="19">
@@ -9640,7 +9656,7 @@
       <c r="C19" t="str">
         <v>601566</v>
       </c>
-      <c r="D19" s="224" t="str">
+      <c r="D19" s="226" t="str">
         <v>净卖: -2383.06万</v>
       </c>
       <c r="E19">
@@ -9655,41 +9671,41 @@
       <c r="H19">
         <v>3.63</v>
       </c>
-      <c r="I19" s="230">
+      <c r="I19" s="227">
         <v>6.13</v>
       </c>
       <c r="J19" s="225">
         <v>2.75</v>
       </c>
-      <c r="K19" s="233">
+      <c r="K19" s="232">
         <v>-4.06</v>
       </c>
-      <c r="L19" s="226">
+      <c r="L19" s="233">
         <v>-3.37</v>
       </c>
-      <c r="M19" s="228">
+      <c r="M19" s="234">
         <v>-6.81</v>
       </c>
-      <c r="N19" s="227">
+      <c r="N19" s="229">
         <v>-7.5</v>
       </c>
-      <c r="O19" s="234">
+      <c r="O19" s="228">
         <v>-12.5</v>
       </c>
-      <c r="P19" s="231">
+      <c r="P19" s="222">
         <v>-13.88</v>
       </c>
-      <c r="Q19" s="232">
+      <c r="Q19" s="223">
         <v>-18.06</v>
       </c>
-      <c r="R19" s="222">
+      <c r="R19" s="224">
         <v>-17.94</v>
       </c>
-      <c r="S19" s="223">
+      <c r="S19" s="230">
         <v>-16.56</v>
       </c>
-      <c r="T19" s="229">
-        <v>-31.69</v>
+      <c r="T19" s="231">
+        <v>-32.69</v>
       </c>
     </row>
     <row r="20">
@@ -9702,7 +9718,7 @@
       <c r="C20" t="str">
         <v>600865</v>
       </c>
-      <c r="D20" s="241" t="str">
+      <c r="D20" s="236" t="str">
         <v>净卖: -5744.79万</v>
       </c>
       <c r="E20">
@@ -9717,41 +9733,41 @@
       <c r="H20">
         <v>-5.17</v>
       </c>
-      <c r="I20" s="246">
+      <c r="I20" s="242">
         <v>9.15</v>
       </c>
-      <c r="J20" s="236">
+      <c r="J20" s="246">
         <v>15.15</v>
       </c>
       <c r="K20" s="237">
         <v>11.33</v>
       </c>
-      <c r="L20" s="247">
+      <c r="L20" s="238">
         <v>19.58</v>
       </c>
-      <c r="M20" s="238">
+      <c r="M20" s="247">
         <v>31.52</v>
       </c>
-      <c r="N20" s="242">
+      <c r="N20" s="239">
         <v>29.27</v>
       </c>
-      <c r="O20" s="243">
+      <c r="O20" s="235">
         <v>16.36</v>
       </c>
-      <c r="P20" s="245">
+      <c r="P20" s="240">
         <v>4.73</v>
       </c>
-      <c r="Q20" s="235">
+      <c r="Q20" s="243">
         <v>-0.61</v>
       </c>
-      <c r="R20" s="239">
+      <c r="R20" s="244">
         <v>0.12</v>
       </c>
-      <c r="S20" s="244">
+      <c r="S20" s="245">
         <v>0.12</v>
       </c>
-      <c r="T20" s="240">
-        <v>-29.45</v>
+      <c r="T20" s="241">
+        <v>-32.06</v>
       </c>
     </row>
     <row r="21">
@@ -9779,41 +9795,41 @@
       <c r="H21">
         <v>-0.39</v>
       </c>
-      <c r="I21" s="256">
+      <c r="I21" s="253">
         <v>3.7</v>
       </c>
-      <c r="J21" s="260">
+      <c r="J21" s="256">
         <v>-1.32</v>
       </c>
       <c r="K21" s="251">
         <v>-4.71</v>
       </c>
-      <c r="L21" s="257">
+      <c r="L21" s="260">
         <v>-6.34</v>
       </c>
-      <c r="M21" s="252">
+      <c r="M21" s="248">
         <v>-4.27</v>
       </c>
-      <c r="N21" s="248">
+      <c r="N21" s="257">
         <v>-2.18</v>
       </c>
-      <c r="O21" s="253">
+      <c r="O21" s="258">
         <v>0.05</v>
       </c>
-      <c r="P21" s="258">
+      <c r="P21" s="252">
         <v>-1.59</v>
       </c>
       <c r="Q21" s="249">
         <v>-4.68</v>
       </c>
-      <c r="R21" s="250">
+      <c r="R21" s="259">
         <v>-5.25</v>
       </c>
-      <c r="S21" s="259">
+      <c r="S21" s="254">
         <v>-4.79</v>
       </c>
-      <c r="T21" s="254">
-        <v>-6.11</v>
+      <c r="T21" s="250">
+        <v>-7.77</v>
       </c>
     </row>
     <row r="22">
@@ -9826,7 +9842,7 @@
       <c r="C22" t="str">
         <v>002792</v>
       </c>
-      <c r="D22" s="263" t="str">
+      <c r="D22" s="273" t="str">
         <v>净买: 6812.35万</v>
       </c>
       <c r="E22">
@@ -9841,41 +9857,41 @@
       <c r="H22">
         <v>4.23</v>
       </c>
-      <c r="I22" s="271">
+      <c r="I22" s="269">
         <v>5.52</v>
       </c>
-      <c r="J22" s="268">
+      <c r="J22" s="266">
         <v>-2.54</v>
       </c>
-      <c r="K22" s="272">
+      <c r="K22" s="270">
         <v>3.61</v>
       </c>
-      <c r="L22" s="264">
+      <c r="L22" s="261">
         <v>13.97</v>
       </c>
-      <c r="M22" s="265">
+      <c r="M22" s="271">
         <v>25.37</v>
       </c>
-      <c r="N22" s="269">
+      <c r="N22" s="267">
         <v>26.81</v>
       </c>
-      <c r="O22" s="270">
+      <c r="O22" s="262">
         <v>18.51</v>
       </c>
-      <c r="P22" s="273">
+      <c r="P22" s="272">
         <v>27.46</v>
       </c>
-      <c r="Q22" s="261">
+      <c r="Q22" s="263">
         <v>36.75</v>
       </c>
-      <c r="R22" s="266">
+      <c r="R22" s="264">
         <v>41.37</v>
       </c>
-      <c r="S22" s="262">
+      <c r="S22" s="268">
         <v>55.52</v>
       </c>
-      <c r="T22" s="267">
-        <v>34.48</v>
+      <c r="T22" s="265">
+        <v>26.18</v>
       </c>
     </row>
     <row r="23">
@@ -9888,7 +9904,7 @@
       <c r="C23" t="str">
         <v>603023</v>
       </c>
-      <c r="D23" s="279" t="str">
+      <c r="D23" s="280" t="str">
         <v>净卖: -1105.11万</v>
       </c>
       <c r="E23">
@@ -9903,41 +9919,41 @@
       <c r="H23">
         <v>4.14</v>
       </c>
-      <c r="I23" s="275">
+      <c r="I23" s="277">
         <v>-0.99</v>
       </c>
-      <c r="J23" s="276">
+      <c r="J23" s="285">
         <v>-4.3</v>
       </c>
-      <c r="K23" s="285">
+      <c r="K23" s="286">
         <v>-8.61</v>
       </c>
-      <c r="L23" s="283">
+      <c r="L23" s="278">
         <v>-8.77</v>
       </c>
-      <c r="M23" s="280">
+      <c r="M23" s="274">
         <v>-7.62</v>
       </c>
-      <c r="N23" s="286">
+      <c r="N23" s="279">
         <v>-12.58</v>
       </c>
-      <c r="O23" s="277">
+      <c r="O23" s="281">
         <v>-11.42</v>
       </c>
-      <c r="P23" s="274">
+      <c r="P23" s="282">
         <v>-16.72</v>
       </c>
-      <c r="Q23" s="284">
+      <c r="Q23" s="283">
         <v>-15.23</v>
       </c>
-      <c r="R23" s="281">
+      <c r="R23" s="275">
         <v>-6.79</v>
       </c>
-      <c r="S23" s="278">
+      <c r="S23" s="276">
         <v>-7.62</v>
       </c>
-      <c r="T23" s="282">
-        <v>-25.99</v>
+      <c r="T23" s="284">
+        <v>-27.32</v>
       </c>
     </row>
     <row r="24">
@@ -9950,7 +9966,7 @@
       <c r="C24" t="str">
         <v>600343</v>
       </c>
-      <c r="D24" s="295" t="str">
+      <c r="D24" s="293" t="str">
         <v>净买: 1.33亿</v>
       </c>
       <c r="E24">
@@ -9965,41 +9981,41 @@
       <c r="H24">
         <v>-1.32</v>
       </c>
-      <c r="I24" s="288">
+      <c r="I24" s="294">
         <v>11.47</v>
       </c>
-      <c r="J24" s="297">
+      <c r="J24" s="295">
         <v>15.39</v>
       </c>
-      <c r="K24" s="293">
+      <c r="K24" s="290">
         <v>21.07</v>
       </c>
-      <c r="L24" s="289">
+      <c r="L24" s="298">
         <v>25.17</v>
       </c>
-      <c r="M24" s="298">
+      <c r="M24" s="299">
         <v>30</v>
       </c>
-      <c r="N24" s="299">
+      <c r="N24" s="296">
         <v>30.59</v>
       </c>
-      <c r="O24" s="296">
+      <c r="O24" s="287">
         <v>21.84</v>
       </c>
-      <c r="P24" s="290">
+      <c r="P24" s="288">
         <v>20.93</v>
       </c>
       <c r="Q24" s="291">
         <v>20.8</v>
       </c>
-      <c r="R24" s="292">
+      <c r="R24" s="289">
         <v>26.21</v>
       </c>
-      <c r="S24" s="287">
+      <c r="S24" s="297">
         <v>23.73</v>
       </c>
-      <c r="T24" s="294">
-        <v>-8.75</v>
+      <c r="T24" s="292">
+        <v>-12.43</v>
       </c>
     </row>
     <row r="25">
@@ -10012,7 +10028,7 @@
       <c r="C25" t="str">
         <v>600693</v>
       </c>
-      <c r="D25" s="305" t="str">
+      <c r="D25" s="304" t="str">
         <v>净卖: -8573.84万</v>
       </c>
       <c r="E25">
@@ -10030,38 +10046,38 @@
       <c r="I25" s="308">
         <v>-2.52</v>
       </c>
-      <c r="J25" s="309">
+      <c r="J25" s="310">
         <v>2</v>
       </c>
-      <c r="K25" s="310">
+      <c r="K25" s="309">
         <v>-7.69</v>
       </c>
       <c r="L25" s="311">
         <v>-16.92</v>
       </c>
-      <c r="M25" s="306">
+      <c r="M25" s="312">
         <v>-16.92</v>
       </c>
-      <c r="N25" s="307">
+      <c r="N25" s="302">
         <v>-14.27</v>
       </c>
-      <c r="O25" s="312">
+      <c r="O25" s="303">
         <v>-16.64</v>
       </c>
-      <c r="P25" s="303">
+      <c r="P25" s="300">
         <v>-16.6</v>
       </c>
-      <c r="Q25" s="300">
+      <c r="Q25" s="305">
         <v>-11.79</v>
       </c>
-      <c r="R25" s="304">
+      <c r="R25" s="301">
         <v>-8.67</v>
       </c>
-      <c r="S25" s="301">
+      <c r="S25" s="306">
         <v>-2.05</v>
       </c>
-      <c r="T25" s="302">
-        <v>-46.25</v>
+      <c r="T25" s="307">
+        <v>-46.85</v>
       </c>
     </row>
     <row r="26">
@@ -10089,41 +10105,41 @@
       <c r="H26">
         <v>-1.39</v>
       </c>
-      <c r="I26" s="322">
+      <c r="I26" s="315">
         <v>11.56</v>
       </c>
-      <c r="J26" s="314">
+      <c r="J26" s="319">
         <v>12.1</v>
       </c>
-      <c r="K26" s="323">
+      <c r="K26" s="320">
         <v>23.31</v>
       </c>
-      <c r="L26" s="319">
+      <c r="L26" s="321">
         <v>15.93</v>
       </c>
-      <c r="M26" s="315">
+      <c r="M26" s="324">
         <v>12.77</v>
       </c>
-      <c r="N26" s="324">
+      <c r="N26" s="323">
         <v>13.16</v>
       </c>
-      <c r="O26" s="316">
+      <c r="O26" s="325">
         <v>10.86</v>
       </c>
-      <c r="P26" s="325">
+      <c r="P26" s="316">
         <v>9.14</v>
       </c>
-      <c r="Q26" s="321">
+      <c r="Q26" s="317">
         <v>9.84</v>
       </c>
-      <c r="R26" s="320">
+      <c r="R26" s="313">
         <v>10.82</v>
       </c>
-      <c r="S26" s="313">
+      <c r="S26" s="314">
         <v>-0.23</v>
       </c>
-      <c r="T26" s="317">
-        <v>-26.55</v>
+      <c r="T26" s="322">
+        <v>-27.37</v>
       </c>
     </row>
     <row r="27">
@@ -10136,7 +10152,7 @@
       <c r="C27" t="str">
         <v>603686</v>
       </c>
-      <c r="D27" s="336" t="str">
+      <c r="D27" s="338" t="str">
         <v>净卖: -6520.61万</v>
       </c>
       <c r="E27">
@@ -10151,41 +10167,41 @@
       <c r="H27">
         <v>5.01</v>
       </c>
-      <c r="I27" s="332">
+      <c r="I27" s="326">
         <v>-4.3</v>
       </c>
-      <c r="J27" s="330">
+      <c r="J27" s="327">
         <v>5.27</v>
       </c>
-      <c r="K27" s="337">
+      <c r="K27" s="334">
         <v>-1.03</v>
       </c>
-      <c r="L27" s="333">
+      <c r="L27" s="335">
         <v>-3.73</v>
       </c>
-      <c r="M27" s="327">
+      <c r="M27" s="328">
         <v>-3.4</v>
       </c>
-      <c r="N27" s="334">
+      <c r="N27" s="329">
         <v>-5.37</v>
       </c>
-      <c r="O27" s="335">
+      <c r="O27" s="330">
         <v>-6.83</v>
       </c>
-      <c r="P27" s="331">
+      <c r="P27" s="336">
         <v>-6.23</v>
       </c>
-      <c r="Q27" s="338">
+      <c r="Q27" s="337">
         <v>-5.4</v>
       </c>
-      <c r="R27" s="326">
+      <c r="R27" s="331">
         <v>-14.83</v>
       </c>
-      <c r="S27" s="328">
+      <c r="S27" s="333">
         <v>-14.37</v>
       </c>
-      <c r="T27" s="329">
-        <v>-37.3</v>
+      <c r="T27" s="332">
+        <v>-38</v>
       </c>
     </row>
     <row r="28">
@@ -10198,7 +10214,7 @@
       <c r="C28" t="str">
         <v>002361</v>
       </c>
-      <c r="D28" s="341" t="str">
+      <c r="D28" s="346" t="str">
         <v>净卖: -5584.65万</v>
       </c>
       <c r="E28">
@@ -10213,41 +10229,41 @@
       <c r="H28">
         <v>-3.59</v>
       </c>
-      <c r="I28" s="345">
+      <c r="I28" s="343">
         <v>-6.66</v>
       </c>
-      <c r="J28" s="346">
+      <c r="J28" s="344">
         <v>2.65</v>
       </c>
-      <c r="K28" s="347">
+      <c r="K28" s="339">
         <v>-1.93</v>
       </c>
-      <c r="L28" s="342">
+      <c r="L28" s="350">
         <v>3.51</v>
       </c>
-      <c r="M28" s="348">
+      <c r="M28" s="345">
         <v>3.15</v>
       </c>
-      <c r="N28" s="351">
+      <c r="N28" s="340">
         <v>13.46</v>
       </c>
-      <c r="O28" s="344">
+      <c r="O28" s="341">
         <v>11.67</v>
       </c>
-      <c r="P28" s="343">
+      <c r="P28" s="342">
         <v>20.26</v>
       </c>
-      <c r="Q28" s="349">
+      <c r="Q28" s="347">
         <v>17.97</v>
       </c>
-      <c r="R28" s="350">
+      <c r="R28" s="351">
         <v>29.71</v>
       </c>
-      <c r="S28" s="339">
+      <c r="S28" s="348">
         <v>16.75</v>
       </c>
-      <c r="T28" s="340">
-        <v>55.05</v>
+      <c r="T28" s="349">
+        <v>43.31</v>
       </c>
     </row>
     <row r="29">
@@ -10260,7 +10276,7 @@
       <c r="C29" t="str">
         <v>001231</v>
       </c>
-      <c r="D29" s="357" t="str">
+      <c r="D29" s="359" t="str">
         <v>净卖: -943.73万</v>
       </c>
       <c r="E29">
@@ -10275,41 +10291,41 @@
       <c r="H29">
         <v>-10.01</v>
       </c>
-      <c r="I29" s="363">
+      <c r="I29" s="364">
         <v>0</v>
       </c>
-      <c r="J29" s="358">
+      <c r="J29" s="360">
         <v>-1.36</v>
       </c>
-      <c r="K29" s="359">
+      <c r="K29" s="361">
         <v>-7.18</v>
       </c>
-      <c r="L29" s="353">
+      <c r="L29" s="352">
         <v>-8.91</v>
       </c>
-      <c r="M29" s="360">
+      <c r="M29" s="362">
         <v>-9.1</v>
       </c>
-      <c r="N29" s="354">
+      <c r="N29" s="363">
         <v>-9.98</v>
       </c>
-      <c r="O29" s="361">
+      <c r="O29" s="355">
         <v>-8.84</v>
       </c>
-      <c r="P29" s="362">
+      <c r="P29" s="356">
         <v>-10.31</v>
       </c>
-      <c r="Q29" s="364">
+      <c r="Q29" s="357">
         <v>-7.96</v>
       </c>
-      <c r="R29" s="355">
+      <c r="R29" s="358">
         <v>-8.8</v>
       </c>
-      <c r="S29" s="356">
+      <c r="S29" s="353">
         <v>-9.28</v>
       </c>
-      <c r="T29" s="352">
-        <v>-7.29</v>
+      <c r="T29" s="354">
+        <v>-7.22</v>
       </c>
     </row>
     <row r="30">
@@ -10322,7 +10338,7 @@
       <c r="C30" t="str">
         <v>002788</v>
       </c>
-      <c r="D30" s="376" t="str">
+      <c r="D30" s="373" t="str">
         <v>净买: 3825.22万</v>
       </c>
       <c r="E30">
@@ -10337,41 +10353,41 @@
       <c r="H30">
         <v>5.81</v>
       </c>
-      <c r="I30" s="366">
+      <c r="I30" s="370">
         <v>3.95</v>
       </c>
-      <c r="J30" s="370">
+      <c r="J30" s="374">
         <v>14.35</v>
       </c>
-      <c r="K30" s="377">
+      <c r="K30" s="367">
         <v>11.56</v>
       </c>
-      <c r="L30" s="371">
+      <c r="L30" s="375">
         <v>13.48</v>
       </c>
-      <c r="M30" s="367">
+      <c r="M30" s="368">
         <v>9.23</v>
       </c>
-      <c r="N30" s="372">
+      <c r="N30" s="371">
         <v>1.08</v>
       </c>
-      <c r="O30" s="373">
+      <c r="O30" s="376">
         <v>-9.03</v>
       </c>
-      <c r="P30" s="365">
+      <c r="P30" s="377">
         <v>-18.14</v>
       </c>
-      <c r="Q30" s="368">
+      <c r="Q30" s="369">
         <v>-26.33</v>
       </c>
-      <c r="R30" s="369">
+      <c r="R30" s="365">
         <v>-30.78</v>
       </c>
-      <c r="S30" s="374">
+      <c r="S30" s="366">
         <v>-32.45</v>
       </c>
-      <c r="T30" s="375">
-        <v>-42.39</v>
+      <c r="T30" s="372">
+        <v>-41.1</v>
       </c>
     </row>
     <row r="31">
@@ -10384,7 +10400,7 @@
       <c r="C31" t="str">
         <v>002788</v>
       </c>
-      <c r="D31" s="380" t="str">
+      <c r="D31" s="387" t="str">
         <v>净卖: -24.07万</v>
       </c>
       <c r="E31">
@@ -10399,41 +10415,41 @@
       <c r="H31">
         <v>-0.04</v>
       </c>
-      <c r="I31" s="385">
+      <c r="I31" s="384">
         <v>10.05</v>
       </c>
-      <c r="J31" s="383">
+      <c r="J31" s="385">
         <v>7.37</v>
       </c>
-      <c r="K31" s="386">
+      <c r="K31" s="388">
         <v>9.21</v>
       </c>
-      <c r="L31" s="381">
+      <c r="L31" s="379">
         <v>5.12</v>
       </c>
-      <c r="M31" s="382">
+      <c r="M31" s="386">
         <v>-2.72</v>
       </c>
-      <c r="N31" s="390">
+      <c r="N31" s="380">
         <v>-12.45</v>
       </c>
-      <c r="O31" s="378">
+      <c r="O31" s="389">
         <v>-21.22</v>
       </c>
-      <c r="P31" s="387">
+      <c r="P31" s="390">
         <v>-29.1</v>
       </c>
-      <c r="Q31" s="388">
+      <c r="Q31" s="381">
         <v>-33.39</v>
       </c>
-      <c r="R31" s="389">
+      <c r="R31" s="382">
         <v>-34.99</v>
       </c>
-      <c r="S31" s="384">
+      <c r="S31" s="378">
         <v>-32.95</v>
       </c>
-      <c r="T31" s="379">
-        <v>-44.56</v>
+      <c r="T31" s="383">
+        <v>-43.31</v>
       </c>
     </row>
     <row r="32">
@@ -10446,7 +10462,7 @@
       <c r="C32" t="str">
         <v>600151</v>
       </c>
-      <c r="D32" s="401" t="str">
+      <c r="D32" s="403" t="str">
         <v>净买: 7884.07万</v>
       </c>
       <c r="E32">
@@ -10461,41 +10477,41 @@
       <c r="H32">
         <v>3.26</v>
       </c>
-      <c r="I32" s="397">
+      <c r="I32" s="391">
         <v>-11.53</v>
       </c>
-      <c r="J32" s="402">
+      <c r="J32" s="392">
         <v>-20.23</v>
       </c>
-      <c r="K32" s="398">
+      <c r="K32" s="397">
         <v>-21.06</v>
       </c>
-      <c r="L32" s="403">
+      <c r="L32" s="393">
         <v>-24.22</v>
       </c>
-      <c r="M32" s="391">
+      <c r="M32" s="394">
         <v>-21.69</v>
       </c>
-      <c r="N32" s="400">
+      <c r="N32" s="398">
         <v>-16.73</v>
       </c>
-      <c r="O32" s="399">
+      <c r="O32" s="402">
         <v>-25.05</v>
       </c>
-      <c r="P32" s="392">
+      <c r="P32" s="401">
         <v>-25.88</v>
       </c>
-      <c r="Q32" s="393">
+      <c r="Q32" s="395">
         <v>-27.43</v>
       </c>
-      <c r="R32" s="394">
+      <c r="R32" s="396">
         <v>-26.65</v>
       </c>
-      <c r="S32" s="395">
+      <c r="S32" s="399">
         <v>-26.61</v>
       </c>
-      <c r="T32" s="396">
-        <v>-31.13</v>
+      <c r="T32" s="400">
+        <v>-33.37</v>
       </c>
     </row>
     <row r="33">
@@ -10508,7 +10524,7 @@
       <c r="C33" t="str">
         <v>600916</v>
       </c>
-      <c r="D33" s="415" t="str">
+      <c r="D33" s="408" t="str">
         <v>净卖: -1428.23万</v>
       </c>
       <c r="E33">
@@ -10523,41 +10539,41 @@
       <c r="H33">
         <v>10.04</v>
       </c>
-      <c r="I33" s="408">
+      <c r="I33" s="405">
         <v>0</v>
       </c>
-      <c r="J33" s="405">
+      <c r="J33" s="409">
         <v>10.02</v>
       </c>
-      <c r="K33" s="416">
+      <c r="K33" s="410">
         <v>19.64</v>
       </c>
-      <c r="L33" s="409">
+      <c r="L33" s="406">
         <v>7.66</v>
       </c>
-      <c r="M33" s="410">
+      <c r="M33" s="411">
         <v>5.87</v>
       </c>
-      <c r="N33" s="406">
+      <c r="N33" s="415">
         <v>-0.81</v>
       </c>
-      <c r="O33" s="414">
+      <c r="O33" s="416">
         <v>-8.96</v>
       </c>
-      <c r="P33" s="411">
+      <c r="P33" s="413">
         <v>-6.93</v>
       </c>
-      <c r="Q33" s="412">
+      <c r="Q33" s="407">
         <v>-5.79</v>
       </c>
-      <c r="R33" s="407">
+      <c r="R33" s="414">
         <v>-8.96</v>
       </c>
-      <c r="S33" s="404">
+      <c r="S33" s="412">
         <v>-9.54</v>
       </c>
-      <c r="T33" s="413">
-        <v>-28.36</v>
+      <c r="T33" s="404">
+        <v>-29.26</v>
       </c>
     </row>
     <row r="34">
@@ -10570,7 +10586,7 @@
       <c r="C34" t="str">
         <v>600969</v>
       </c>
-      <c r="D34" s="421" t="str">
+      <c r="D34" s="427" t="str">
         <v>净卖: -723.23万</v>
       </c>
       <c r="E34">
@@ -10588,38 +10604,38 @@
       <c r="I34" s="429">
         <v>-9.99</v>
       </c>
-      <c r="J34" s="422">
+      <c r="J34" s="428">
         <v>-9.99</v>
       </c>
-      <c r="K34" s="425">
+      <c r="K34" s="421">
         <v>-18.98</v>
       </c>
       <c r="L34" s="417">
         <v>-21.07</v>
       </c>
-      <c r="M34" s="418">
+      <c r="M34" s="422">
         <v>-21.98</v>
       </c>
       <c r="N34" s="423">
         <v>-18.98</v>
       </c>
-      <c r="O34" s="426">
+      <c r="O34" s="418">
         <v>-16.9</v>
       </c>
       <c r="P34" s="419">
         <v>-16.82</v>
       </c>
-      <c r="Q34" s="427">
+      <c r="Q34" s="424">
         <v>-14.32</v>
       </c>
-      <c r="R34" s="428">
+      <c r="R34" s="425">
         <v>-13.66</v>
       </c>
-      <c r="S34" s="424">
+      <c r="S34" s="426">
         <v>-15.99</v>
       </c>
       <c r="T34" s="420">
-        <v>-15.24</v>
+        <v>-18.23</v>
       </c>
     </row>
     <row r="35">
@@ -10632,7 +10648,7 @@
       <c r="C35" t="str">
         <v>002040</v>
       </c>
-      <c r="D35" s="436" t="str">
+      <c r="D35" s="441" t="str">
         <v>净卖: -895.74万</v>
       </c>
       <c r="E35">
@@ -10647,41 +10663,41 @@
       <c r="H35">
         <v>-7.37</v>
       </c>
-      <c r="I35" s="442">
+      <c r="I35" s="437">
         <v>-2.87</v>
       </c>
-      <c r="J35" s="438">
+      <c r="J35" s="435">
         <v>-8.52</v>
       </c>
-      <c r="K35" s="430">
+      <c r="K35" s="438">
         <v>-8.36</v>
       </c>
-      <c r="L35" s="439">
+      <c r="L35" s="442">
         <v>-10.49</v>
       </c>
-      <c r="M35" s="440">
+      <c r="M35" s="439">
         <v>-8.44</v>
       </c>
-      <c r="N35" s="431">
+      <c r="N35" s="430">
         <v>-9.02</v>
       </c>
-      <c r="O35" s="432">
+      <c r="O35" s="431">
         <v>-9.51</v>
       </c>
-      <c r="P35" s="433">
+      <c r="P35" s="440">
         <v>-12.05</v>
       </c>
-      <c r="Q35" s="434">
+      <c r="Q35" s="432">
         <v>-8.28</v>
       </c>
-      <c r="R35" s="441">
+      <c r="R35" s="436">
         <v>-10.33</v>
       </c>
-      <c r="S35" s="437">
+      <c r="S35" s="433">
         <v>-11.07</v>
       </c>
-      <c r="T35" s="435">
-        <v>-18.93</v>
+      <c r="T35" s="434">
+        <v>-19.26</v>
       </c>
     </row>
     <row r="36">
@@ -10694,7 +10710,7 @@
       <c r="C36" t="str">
         <v>603017</v>
       </c>
-      <c r="D36" s="453" t="str">
+      <c r="D36" s="446" t="str">
         <v>净买: 694.09万</v>
       </c>
       <c r="E36">
@@ -10712,38 +10728,38 @@
       <c r="I36" s="447">
         <v>7.84</v>
       </c>
-      <c r="J36" s="454">
+      <c r="J36" s="452">
         <v>7.04</v>
       </c>
-      <c r="K36" s="455">
+      <c r="K36" s="453">
         <v>6.48</v>
       </c>
-      <c r="L36" s="448">
+      <c r="L36" s="445">
         <v>5.04</v>
       </c>
-      <c r="M36" s="449">
+      <c r="M36" s="454">
         <v>7.28</v>
       </c>
-      <c r="N36" s="451">
+      <c r="N36" s="448">
         <v>5.44</v>
       </c>
-      <c r="O36" s="452">
+      <c r="O36" s="443">
         <v>10.72</v>
       </c>
-      <c r="P36" s="443">
+      <c r="P36" s="444">
         <v>10.32</v>
       </c>
-      <c r="Q36" s="444">
+      <c r="Q36" s="449">
         <v>7.92</v>
       </c>
-      <c r="R36" s="445">
+      <c r="R36" s="455">
         <v>1.28</v>
       </c>
       <c r="S36" s="450">
         <v>11.44</v>
       </c>
-      <c r="T36" s="446">
-        <v>19.6</v>
+      <c r="T36" s="451">
+        <v>11.2</v>
       </c>
     </row>
     <row r="37">
@@ -10756,7 +10772,7 @@
       <c r="C37" t="str">
         <v>600495</v>
       </c>
-      <c r="D37" s="466" t="str">
+      <c r="D37" s="462" t="str">
         <v>净买: 998.97万</v>
       </c>
       <c r="E37">
@@ -10771,41 +10787,41 @@
       <c r="H37">
         <v>0</v>
       </c>
-      <c r="I37" s="459">
+      <c r="I37" s="468">
         <v>10.04</v>
       </c>
-      <c r="J37" s="464">
+      <c r="J37" s="463">
         <v>11.16</v>
       </c>
-      <c r="K37" s="467">
+      <c r="K37" s="456">
         <v>12.28</v>
       </c>
-      <c r="L37" s="460">
+      <c r="L37" s="464">
         <v>2.23</v>
       </c>
-      <c r="M37" s="468">
+      <c r="M37" s="466">
         <v>0.67</v>
       </c>
-      <c r="N37" s="456">
+      <c r="N37" s="465">
         <v>4.46</v>
       </c>
       <c r="O37" s="457">
         <v>0.67</v>
       </c>
-      <c r="P37" s="462">
+      <c r="P37" s="460">
         <v>0.45</v>
       </c>
       <c r="Q37" s="461">
         <v>-1.34</v>
       </c>
-      <c r="R37" s="465">
+      <c r="R37" s="458">
         <v>-1.34</v>
       </c>
-      <c r="S37" s="458">
+      <c r="S37" s="467">
         <v>-2.01</v>
       </c>
-      <c r="T37" s="463">
-        <v>-2.23</v>
+      <c r="T37" s="459">
+        <v>-3.79</v>
       </c>
     </row>
     <row r="38">
@@ -10818,7 +10834,7 @@
       <c r="C38" t="str">
         <v>600488</v>
       </c>
-      <c r="D38" s="472" t="str">
+      <c r="D38" s="470" t="str">
         <v>净卖: -1388.23万</v>
       </c>
       <c r="E38">
@@ -10836,38 +10852,38 @@
       <c r="I38" s="475">
         <v>0</v>
       </c>
-      <c r="J38" s="476">
+      <c r="J38" s="471">
         <v>10.07</v>
       </c>
-      <c r="K38" s="481">
+      <c r="K38" s="472">
         <v>21.01</v>
       </c>
-      <c r="L38" s="469">
+      <c r="L38" s="476">
         <v>33.16</v>
       </c>
-      <c r="M38" s="478">
+      <c r="M38" s="474">
         <v>27.78</v>
       </c>
-      <c r="N38" s="473">
+      <c r="N38" s="477">
         <v>22.92</v>
       </c>
-      <c r="O38" s="474">
+      <c r="O38" s="480">
         <v>11.46</v>
       </c>
-      <c r="P38" s="479">
+      <c r="P38" s="473">
         <v>2.6</v>
       </c>
-      <c r="Q38" s="480">
+      <c r="Q38" s="481">
         <v>7.99</v>
       </c>
-      <c r="R38" s="470">
+      <c r="R38" s="478">
         <v>18.75</v>
       </c>
-      <c r="S38" s="471">
+      <c r="S38" s="479">
         <v>9.2</v>
       </c>
-      <c r="T38" s="477">
-        <v>-2.43</v>
+      <c r="T38" s="469">
+        <v>7.29</v>
       </c>
     </row>
     <row r="39">
@@ -10910,14 +10926,16 @@
       <c r="M39" s="487">
         <v>-7.51</v>
       </c>
-      <c r="N39" t="str"/>
+      <c r="N39" s="488">
+        <v>-11.86</v>
+      </c>
       <c r="O39" t="str"/>
       <c r="P39" t="str"/>
       <c r="Q39" t="str"/>
       <c r="R39" t="str"/>
       <c r="S39" t="str"/>
-      <c r="T39" s="488">
-        <v>-7.51</v>
+      <c r="T39" s="489">
+        <v>-11.86</v>
       </c>
     </row>
     <row r="40">
@@ -10947,7 +10965,7 @@
         <v>38</v>
       </c>
       <c r="N40">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O40">
         <v>37</v>
@@ -10979,41 +10997,41 @@
       <c r="F41" t="str"/>
       <c r="G41" t="str"/>
       <c r="H41" t="str"/>
-      <c r="I41" s="493">
+      <c r="I41" s="495">
         <v>52.63</v>
       </c>
-      <c r="J41" s="497">
+      <c r="J41" s="496">
         <v>63.16</v>
       </c>
-      <c r="K41" s="494">
+      <c r="K41" s="491">
         <v>55.26</v>
       </c>
-      <c r="L41" s="498">
+      <c r="L41" s="501">
         <v>57.89</v>
       </c>
-      <c r="M41" s="499">
+      <c r="M41" s="490">
         <v>50</v>
       </c>
-      <c r="N41" s="500">
-        <v>48.65</v>
-      </c>
-      <c r="O41" s="491">
+      <c r="N41" s="497">
+        <v>47.37</v>
+      </c>
+      <c r="O41" s="493">
         <v>45.95</v>
       </c>
-      <c r="P41" s="495">
+      <c r="P41" s="492">
         <v>40.54</v>
       </c>
-      <c r="Q41" s="496">
+      <c r="Q41" s="498">
         <v>35.14</v>
       </c>
-      <c r="R41" s="490">
+      <c r="R41" s="499">
         <v>37.84</v>
       </c>
-      <c r="S41" s="492">
+      <c r="S41" s="494">
         <v>37.84</v>
       </c>
-      <c r="T41" s="489">
-        <v>23.68</v>
+      <c r="T41" s="500">
+        <v>26.32</v>
       </c>
     </row>
     <row r="42">
@@ -11027,41 +11045,41 @@
       <c r="F42" t="str"/>
       <c r="G42" t="str"/>
       <c r="H42" t="str"/>
-      <c r="I42" s="506">
+      <c r="I42" s="503">
         <v>2.29</v>
       </c>
       <c r="J42" s="504">
         <v>3.48</v>
       </c>
-      <c r="K42" s="505">
+      <c r="K42" s="510">
         <v>3.42</v>
       </c>
-      <c r="L42" s="502">
+      <c r="L42" s="505">
         <v>3.13</v>
       </c>
-      <c r="M42" s="507">
+      <c r="M42" s="511">
         <v>4.24</v>
       </c>
-      <c r="N42" s="509">
-        <v>3.99</v>
-      </c>
-      <c r="O42" s="510">
+      <c r="N42" s="506">
+        <v>3.57</v>
+      </c>
+      <c r="O42" s="508">
         <v>2.28</v>
       </c>
-      <c r="P42" s="503">
+      <c r="P42" s="513">
         <v>0.79</v>
       </c>
-      <c r="Q42" s="508">
+      <c r="Q42" s="512">
         <v>-0.11</v>
       </c>
-      <c r="R42" s="511">
+      <c r="R42" s="507">
         <v>-0.68</v>
       </c>
-      <c r="S42" s="512">
+      <c r="S42" s="502">
         <v>-0.22</v>
       </c>
-      <c r="T42" s="501">
-        <v>-4.83</v>
+      <c r="T42" s="509">
+        <v>-6.26</v>
       </c>
     </row>
   </sheetData>
